--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -527,13 +527,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Validator</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B12" t="str">
-        <v>ICC 配置文件验证器</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C12" t="str">
-        <v>ICC 設定檔驗證器</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="13">
@@ -714,13 +714,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Validator · powered by IccProfLib</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B29" t="str">
-        <v>ICC 配置文件验证器 · 由 IccProfLib 提供支持</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C29" t="str">
-        <v>ICC 設定檔驗證器 · 由 IccProfLib 提供支援</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="30">

--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C69"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -734,9 +734,438 @@
         <v>錯誤：</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B31" t="str">
+        <v>转换为 XML</v>
+      </c>
+      <c r="C31" t="str">
+        <v>轉換為 XML</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B32" t="str">
+        <v>转换为 JSON</v>
+      </c>
+      <c r="C32" t="str">
+        <v>轉換為 JSON</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B33" t="str">
+        <v>转换为 ICC</v>
+      </c>
+      <c r="C33" t="str">
+        <v>轉換為 ICC</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B34" t="str">
+        <v>正在转换为 XML…</v>
+      </c>
+      <c r="C34" t="str">
+        <v>正在轉換為 XML…</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B35" t="str">
+        <v>正在转换为 JSON…</v>
+      </c>
+      <c r="C35" t="str">
+        <v>正在轉換為 JSON…</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B36" t="str">
+        <v>正在转换为 ICC…</v>
+      </c>
+      <c r="C36" t="str">
+        <v>正在轉換為 ICC…</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B37" t="str">
+        <v>加载 ICC 配置文件</v>
+      </c>
+      <c r="C37" t="str">
+        <v>載入 ICC 設定檔</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B38" t="str">
+        <v>ICC 配置文件拖放区</v>
+      </c>
+      <c r="C38" t="str">
+        <v>ICC 設定檔拖放區</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B39" t="str">
+        <v>配置文件 ID</v>
+      </c>
+      <c r="C39" t="str">
+        <v>設定檔 ID</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B40" t="str">
+        <v>未找到标签。</v>
+      </c>
+      <c r="C40" t="str">
+        <v>找不到標籤。</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B41" t="str">
+        <v>标签名称</v>
+      </c>
+      <c r="C41" t="str">
+        <v>標籤名稱</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C42" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B43" t="str">
+        <v>偏移</v>
+      </c>
+      <c r="C43" t="str">
+        <v>偏移</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B44" t="str">
+        <v>大小</v>
+      </c>
+      <c r="C44" t="str">
+        <v>大小</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B45" t="str">
+        <v>填充</v>
+      </c>
+      <c r="C45" t="str">
+        <v>填充</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B46" t="str">
+        <v>加载后字节已更改</v>
+      </c>
+      <c r="C46" t="str">
+        <v>載入後位元組已變更</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B47" t="str">
+        <v>类型</v>
+      </c>
+      <c r="C47" t="str">
+        <v>類型</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B48" t="str">
+        <v>{type} 数组</v>
+      </c>
+      <c r="C48" t="str">
+        <v>{type} 陣列</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>（无内容）</v>
+      </c>
+      <c r="C49" t="str">
+        <v>（無內容）</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B50" t="str">
+        <v>字节</v>
+      </c>
+      <c r="C50" t="str">
+        <v>位元組</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B51" t="str">
+        <v>正在加载完整描述…</v>
+      </c>
+      <c r="C51" t="str">
+        <v>正在載入完整描述…</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B52" t="str">
+        <v>无法加载完整描述：</v>
+      </c>
+      <c r="C52" t="str">
+        <v>無法載入完整描述：</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B53" t="str">
+        <v>无验证输出</v>
+      </c>
+      <c r="C53" t="str">
+        <v>無驗證輸出</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B54" t="str">
+        <v>未发现警告或错误。</v>
+      </c>
+      <c r="C54" t="str">
+        <v>未發現警告或錯誤。</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B55" t="str">
+        <v>有效</v>
+      </c>
+      <c r="C55" t="str">
+        <v>有效</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B56" t="str">
+        <v>警告</v>
+      </c>
+      <c r="C56" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B57" t="str">
+        <v>错误</v>
+      </c>
+      <c r="C57" t="str">
+        <v>錯誤</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B58" t="str">
+        <v>未知</v>
+      </c>
+      <c r="C58" t="str">
+        <v>未知</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B59" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C59" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B60" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C60" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B61" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C61" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B62" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C62" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B63" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C63" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B64" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C64" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B65" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C65" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B66" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C66" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B67" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C67" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B68" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C68" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Profile written from edits, but re-validation failed:</v>
+      </c>
+      <c r="B69" t="str">
+        <v>已从编辑写入配置文件，但重新验证失败：</v>
+      </c>
+      <c r="C69" t="str">
+        <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C79"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1044,128 +1044,238 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B59" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C59" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B60" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>验证详情</v>
       </c>
       <c r="C60" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B61" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>触发字段</v>
       </c>
       <c r="C61" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B62" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>字段</v>
       </c>
       <c r="C62" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B63" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>当前值</v>
       </c>
       <c r="C63" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B64" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>要求：0</v>
       </c>
       <c r="C64" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B65" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C65" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B66" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>无效</v>
       </c>
       <c r="C66" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B67" t="str">
-        <v>缩进</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C67" t="str">
-        <v>縮排</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B68" t="str">
-        <v>排序键</v>
+        <v>关闭</v>
       </c>
       <c r="C68" t="str">
-        <v>排序鍵</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B69" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C69" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B70" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C70" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B71" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C71" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B72" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C72" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B73" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C73" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B74" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C74" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B75" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C75" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B76" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C76" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B77" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C77" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B78" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C78" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B79" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C69" t="str">
+      <c r="C79" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C81"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -978,304 +978,326 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B53" t="str">
-        <v>无验证输出</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C53" t="str">
-        <v>無驗證輸出</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B54" t="str">
-        <v>未发现警告或错误。</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C54" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B55" t="str">
-        <v>有效</v>
+        <v>无验证输出</v>
       </c>
       <c r="C55" t="str">
-        <v>有效</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B56" t="str">
-        <v>警告</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C56" t="str">
-        <v>警告</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B57" t="str">
-        <v>错误</v>
+        <v>有效</v>
       </c>
       <c r="C57" t="str">
-        <v>錯誤</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B58" t="str">
-        <v>未知</v>
+        <v>警告</v>
       </c>
       <c r="C58" t="str">
-        <v>未知</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B59" t="str">
-        <v>在上下文中查看</v>
+        <v>错误</v>
       </c>
       <c r="C59" t="str">
-        <v>在上下文中檢視</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B60" t="str">
-        <v>验证详情</v>
+        <v>未知</v>
       </c>
       <c r="C60" t="str">
-        <v>驗證詳情</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B61" t="str">
-        <v>触发字段</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C61" t="str">
-        <v>觸發欄位</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B62" t="str">
-        <v>字段</v>
+        <v>验证详情</v>
       </c>
       <c r="C62" t="str">
-        <v>欄位</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B63" t="str">
-        <v>当前值</v>
+        <v>触发字段</v>
       </c>
       <c r="C63" t="str">
-        <v>目前值</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B64" t="str">
-        <v>要求：0</v>
+        <v>字段</v>
       </c>
       <c r="C64" t="str">
-        <v>要求：0</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B65" t="str">
-        <v>预期：{value}</v>
+        <v>当前值</v>
       </c>
       <c r="C65" t="str">
-        <v>預期：{value}</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B66" t="str">
-        <v>无效</v>
+        <v>要求：0</v>
       </c>
       <c r="C66" t="str">
-        <v>無效</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B67" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C67" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B68" t="str">
-        <v>关闭</v>
+        <v>无效</v>
       </c>
       <c r="C68" t="str">
-        <v>關閉</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B69" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C69" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B70" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>关闭</v>
       </c>
       <c r="C70" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B71" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C71" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B72" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C72" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B73" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C73" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B74" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C74" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B75" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C75" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B76" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C76" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B77" t="str">
-        <v>缩进</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C77" t="str">
-        <v>縮排</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B78" t="str">
-        <v>排序键</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C78" t="str">
-        <v>排序鍵</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B79" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C79" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B80" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C80" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B81" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C79" t="str">
+      <c r="C81" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C87"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1011,293 +1011,359 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B56" t="str">
-        <v>未发现警告或错误。</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C56" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B57" t="str">
-        <v>有效</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C57" t="str">
-        <v>有效</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Warning</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B58" t="str">
-        <v>警告</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C58" t="str">
-        <v>警告</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Error</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B59" t="str">
-        <v>错误</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C59" t="str">
-        <v>錯誤</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B60" t="str">
-        <v>未知</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C60" t="str">
-        <v>未知</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B61" t="str">
-        <v>在上下文中查看</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C61" t="str">
-        <v>在上下文中檢視</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B62" t="str">
-        <v>验证详情</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C62" t="str">
-        <v>驗證詳情</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B63" t="str">
-        <v>触发字段</v>
+        <v>有效</v>
       </c>
       <c r="C63" t="str">
-        <v>觸發欄位</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B64" t="str">
-        <v>字段</v>
+        <v>警告</v>
       </c>
       <c r="C64" t="str">
-        <v>欄位</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B65" t="str">
-        <v>当前值</v>
+        <v>错误</v>
       </c>
       <c r="C65" t="str">
-        <v>目前值</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B66" t="str">
-        <v>要求：0</v>
+        <v>未知</v>
       </c>
       <c r="C66" t="str">
-        <v>要求：0</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Expected: {value}</v>
+        <v>View in context</v>
       </c>
       <c r="B67" t="str">
-        <v>预期：{value}</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C67" t="str">
-        <v>預期：{value}</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Invalid</v>
+        <v>Validation detail</v>
       </c>
       <c r="B68" t="str">
-        <v>无效</v>
+        <v>验证详情</v>
       </c>
       <c r="C68" t="str">
-        <v>無效</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Triggered by</v>
       </c>
       <c r="B69" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>触发字段</v>
       </c>
       <c r="C69" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Close</v>
+        <v>Field</v>
       </c>
       <c r="B70" t="str">
-        <v>关闭</v>
+        <v>字段</v>
       </c>
       <c r="C70" t="str">
-        <v>關閉</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Loading XML editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B71" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>当前值</v>
       </c>
       <c r="C71" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B72" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>要求：0</v>
       </c>
       <c r="C72" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B73" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C73" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B74" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>无效</v>
       </c>
       <c r="C74" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>● unsaved XML edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B75" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C75" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Close</v>
       </c>
       <c r="B76" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>关闭</v>
       </c>
       <c r="C76" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B77" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C77" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B78" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C78" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>indent</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B79" t="str">
-        <v>缩进</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C79" t="str">
-        <v>縮排</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B80" t="str">
-        <v>排序键</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C80" t="str">
-        <v>排序鍵</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B81" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C81" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B82" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C82" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B83" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C83" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B84" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C84" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B85" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C85" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B86" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C86" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B87" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C81" t="str">
+      <c r="C87" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C98"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -681,689 +681,810 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Raw Output</v>
+        <v>Profile Assessment WG</v>
       </c>
       <c r="B26" t="str">
-        <v>原始输出</v>
+        <v/>
       </c>
       <c r="C26" t="str">
-        <v>原始輸出</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B27" t="str">
-        <v>XML</v>
+        <v>原始输出</v>
       </c>
       <c r="C27" t="str">
-        <v>XML</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="C28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>JSON</v>
       </c>
       <c r="B29" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>JSON</v>
       </c>
       <c r="C29" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Error:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B30" t="str">
-        <v>错误：</v>
+        <v/>
       </c>
       <c r="C30" t="str">
-        <v>錯誤：</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Convert to XML</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B31" t="str">
-        <v>转换为 XML</v>
+        <v/>
       </c>
       <c r="C31" t="str">
-        <v>轉換為 XML</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Convert to JSON</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B32" t="str">
-        <v>转换为 JSON</v>
+        <v/>
       </c>
       <c r="C32" t="str">
-        <v>轉換為 JSON</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Convert to ICC</v>
+        <v>Security</v>
       </c>
       <c r="B33" t="str">
-        <v>转换为 ICC</v>
+        <v/>
       </c>
       <c r="C33" t="str">
-        <v>轉換為 ICC</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Converting to XML…</v>
+        <v>Conformance</v>
       </c>
       <c r="B34" t="str">
-        <v>正在转换为 XML…</v>
+        <v/>
       </c>
       <c r="C34" t="str">
-        <v>正在轉換為 XML…</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Converting to JSON…</v>
+        <v>Quality</v>
       </c>
       <c r="B35" t="str">
-        <v>正在转换为 JSON…</v>
+        <v/>
       </c>
       <c r="C35" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Converting to ICC…</v>
+        <v>REPORT</v>
       </c>
       <c r="B36" t="str">
-        <v>正在转换为 ICC…</v>
+        <v/>
       </c>
       <c r="C36" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Load ICC profile</v>
+        <v>FAIL</v>
       </c>
       <c r="B37" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v/>
       </c>
       <c r="C37" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>checks</v>
       </c>
       <c r="B38" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v/>
       </c>
       <c r="C38" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Profile ID</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B39" t="str">
-        <v>配置文件 ID</v>
+        <v/>
       </c>
       <c r="C39" t="str">
-        <v>設定檔 ID</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B40" t="str">
-        <v>未找到标签。</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C40" t="str">
-        <v>找不到標籤。</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B41" t="str">
-        <v>标签名称</v>
+        <v>错误：</v>
       </c>
       <c r="C41" t="str">
-        <v>標籤名稱</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B42" t="str">
-        <v>ID</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C42" t="str">
-        <v>ID</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B43" t="str">
-        <v>偏移</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C43" t="str">
-        <v>偏移</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B44" t="str">
-        <v>大小</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C44" t="str">
-        <v>大小</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B45" t="str">
-        <v>填充</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C45" t="str">
-        <v>填充</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B46" t="str">
-        <v>加载后字节已更改</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C46" t="str">
-        <v>載入後位元組已變更</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B47" t="str">
-        <v>类型</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C47" t="str">
-        <v>類型</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B48" t="str">
-        <v>{type} 数组</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C48" t="str">
-        <v>{type} 陣列</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B49" t="str">
-        <v>（无内容）</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C49" t="str">
-        <v>（無內容）</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B50" t="str">
-        <v>字节</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C50" t="str">
-        <v>位元組</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B51" t="str">
-        <v>正在加载完整描述…</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C51" t="str">
-        <v>正在載入完整描述…</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B52" t="str">
-        <v>无法加载完整描述：</v>
+        <v>标签名称</v>
       </c>
       <c r="C52" t="str">
-        <v>無法載入完整描述：</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B53" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>ID</v>
       </c>
       <c r="C53" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B54" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>偏移</v>
       </c>
       <c r="C54" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B55" t="str">
-        <v>无验证输出</v>
+        <v>大小</v>
       </c>
       <c r="C55" t="str">
-        <v>無驗證輸出</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B56" t="str">
-        <v>配置文件有效</v>
+        <v>填充</v>
       </c>
       <c r="C56" t="str">
-        <v>設定檔有效</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B57" t="str">
-        <v>配置文件有警告</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C57" t="str">
-        <v>設定檔有警告</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B58" t="str">
-        <v>配置文件不合规</v>
+        <v>类型</v>
       </c>
       <c r="C58" t="str">
-        <v>設定檔不符合規範</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B59" t="str">
-        <v>严重验证错误</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C59" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B60" t="str">
-        <v>未知验证状态</v>
+        <v>（无内容）</v>
       </c>
       <c r="C60" t="str">
-        <v>未知驗證狀態</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B61" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>字节</v>
       </c>
       <c r="C61" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B62" t="str">
-        <v>未发现警告或错误。</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C62" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B63" t="str">
-        <v>有效</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C63" t="str">
-        <v>有效</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B64" t="str">
-        <v>警告</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C64" t="str">
-        <v>警告</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B65" t="str">
-        <v>错误</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C65" t="str">
-        <v>錯誤</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B66" t="str">
-        <v>未知</v>
+        <v>无验证输出</v>
       </c>
       <c r="C66" t="str">
-        <v>未知</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B67" t="str">
-        <v>在上下文中查看</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C67" t="str">
-        <v>在上下文中檢視</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B68" t="str">
-        <v>验证详情</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C68" t="str">
-        <v>驗證詳情</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B69" t="str">
-        <v>触发字段</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C69" t="str">
-        <v>觸發欄位</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B70" t="str">
-        <v>字段</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C70" t="str">
-        <v>欄位</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B71" t="str">
-        <v>当前值</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C71" t="str">
-        <v>目前值</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B72" t="str">
-        <v>要求：0</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C72" t="str">
-        <v>要求：0</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B73" t="str">
-        <v>预期：{value}</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C73" t="str">
-        <v>預期：{value}</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B74" t="str">
-        <v>无效</v>
+        <v>有效</v>
       </c>
       <c r="C74" t="str">
-        <v>無效</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B75" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>警告</v>
       </c>
       <c r="C75" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B76" t="str">
-        <v>关闭</v>
+        <v>错误</v>
       </c>
       <c r="C76" t="str">
-        <v>關閉</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B77" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>未知</v>
       </c>
       <c r="C77" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B78" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C78" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B79" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>验证详情</v>
       </c>
       <c r="C79" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B80" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>触发字段</v>
       </c>
       <c r="C80" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B81" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>字段</v>
       </c>
       <c r="C81" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B82" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>当前值</v>
       </c>
       <c r="C82" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B83" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>要求：0</v>
       </c>
       <c r="C83" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B84" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C84" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B85" t="str">
-        <v>缩进</v>
+        <v>无效</v>
       </c>
       <c r="C85" t="str">
-        <v>縮排</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B86" t="str">
-        <v>排序键</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C86" t="str">
-        <v>排序鍵</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B87" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C87" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B88" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C88" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B89" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C89" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B90" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C90" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B91" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C91" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B92" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C92" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B93" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C93" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B94" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C94" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B95" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C95" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B96" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C96" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B97" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C97" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B98" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C87" t="str">
+      <c r="C98" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C100"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -725,29 +725,29 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -758,7 +758,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Security</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -769,7 +769,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Conformance</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -780,7 +780,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Quality</v>
+        <v>Security</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -791,7 +791,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>REPORT</v>
+        <v>Conformance</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -802,7 +802,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FAIL</v>
+        <v>Quality</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -813,7 +813,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -824,7 +824,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -835,656 +835,678 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B40" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v/>
       </c>
       <c r="C40" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Error:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B41" t="str">
-        <v>错误：</v>
+        <v/>
       </c>
       <c r="C41" t="str">
-        <v>錯誤：</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Convert to XML</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B42" t="str">
-        <v>转换为 XML</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C42" t="str">
-        <v>轉換為 XML</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B43" t="str">
-        <v>转换为 JSON</v>
+        <v>错误：</v>
       </c>
       <c r="C43" t="str">
-        <v>轉換為 JSON</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B44" t="str">
-        <v>转换为 ICC</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C44" t="str">
-        <v>轉換為 ICC</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B45" t="str">
-        <v>正在转换为 XML…</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C45" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B46" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C46" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B47" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C47" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B48" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C48" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B49" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C49" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B50" t="str">
-        <v>配置文件 ID</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C50" t="str">
-        <v>設定檔 ID</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B51" t="str">
-        <v>未找到标签。</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C51" t="str">
-        <v>找不到標籤。</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B52" t="str">
-        <v>标签名称</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C52" t="str">
-        <v>標籤名稱</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B53" t="str">
-        <v>ID</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C53" t="str">
-        <v>ID</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B54" t="str">
-        <v>偏移</v>
+        <v>标签名称</v>
       </c>
       <c r="C54" t="str">
-        <v>偏移</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B55" t="str">
-        <v>大小</v>
+        <v>ID</v>
       </c>
       <c r="C55" t="str">
-        <v>大小</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B56" t="str">
-        <v>填充</v>
+        <v>偏移</v>
       </c>
       <c r="C56" t="str">
-        <v>填充</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B57" t="str">
-        <v>加载后字节已更改</v>
+        <v>大小</v>
       </c>
       <c r="C57" t="str">
-        <v>載入後位元組已變更</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B58" t="str">
-        <v>类型</v>
+        <v>填充</v>
       </c>
       <c r="C58" t="str">
-        <v>類型</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B59" t="str">
-        <v>{type} 数组</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C59" t="str">
-        <v>{type} 陣列</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B60" t="str">
-        <v>（无内容）</v>
+        <v>类型</v>
       </c>
       <c r="C60" t="str">
-        <v>（無內容）</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B61" t="str">
-        <v>字节</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C61" t="str">
-        <v>位元組</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B62" t="str">
-        <v>正在加载完整描述…</v>
+        <v>（无内容）</v>
       </c>
       <c r="C62" t="str">
-        <v>正在載入完整描述…</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B63" t="str">
-        <v>无法加载完整描述：</v>
+        <v>字节</v>
       </c>
       <c r="C63" t="str">
-        <v>無法載入完整描述：</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B64" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C64" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B65" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C65" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B66" t="str">
-        <v>无验证输出</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C66" t="str">
-        <v>無驗證輸出</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B67" t="str">
-        <v>配置文件有效</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C67" t="str">
-        <v>設定檔有效</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B68" t="str">
-        <v>配置文件有警告</v>
+        <v>无验证输出</v>
       </c>
       <c r="C68" t="str">
-        <v>設定檔有警告</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B69" t="str">
-        <v>配置文件不合规</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C69" t="str">
-        <v>設定檔不符合規範</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B70" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C70" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B71" t="str">
-        <v>未知验证状态</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C71" t="str">
-        <v>未知驗證狀態</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B72" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C72" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B73" t="str">
-        <v>未发现警告或错误。</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C73" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B74" t="str">
-        <v>有效</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C74" t="str">
-        <v>有效</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B75" t="str">
-        <v>警告</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C75" t="str">
-        <v>警告</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B76" t="str">
-        <v>错误</v>
+        <v>有效</v>
       </c>
       <c r="C76" t="str">
-        <v>錯誤</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B77" t="str">
-        <v>未知</v>
+        <v>警告</v>
       </c>
       <c r="C77" t="str">
-        <v>未知</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B78" t="str">
-        <v>在上下文中查看</v>
+        <v>错误</v>
       </c>
       <c r="C78" t="str">
-        <v>在上下文中檢視</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B79" t="str">
-        <v>验证详情</v>
+        <v>未知</v>
       </c>
       <c r="C79" t="str">
-        <v>驗證詳情</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B80" t="str">
-        <v>触发字段</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C80" t="str">
-        <v>觸發欄位</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B81" t="str">
-        <v>字段</v>
+        <v>验证详情</v>
       </c>
       <c r="C81" t="str">
-        <v>欄位</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B82" t="str">
-        <v>当前值</v>
+        <v>触发字段</v>
       </c>
       <c r="C82" t="str">
-        <v>目前值</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B83" t="str">
-        <v>要求：0</v>
+        <v>字段</v>
       </c>
       <c r="C83" t="str">
-        <v>要求：0</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B84" t="str">
-        <v>预期：{value}</v>
+        <v>当前值</v>
       </c>
       <c r="C84" t="str">
-        <v>預期：{value}</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B85" t="str">
-        <v>无效</v>
+        <v>要求：0</v>
       </c>
       <c r="C85" t="str">
-        <v>無效</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B86" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C86" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B87" t="str">
-        <v>关闭</v>
+        <v>无效</v>
       </c>
       <c r="C87" t="str">
-        <v>關閉</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B88" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C88" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B89" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>关闭</v>
       </c>
       <c r="C89" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B90" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C90" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B91" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C91" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B92" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C92" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B93" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C93" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B94" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C94" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B95" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C95" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B96" t="str">
-        <v>缩进</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C96" t="str">
-        <v>縮排</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B97" t="str">
-        <v>排序键</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C97" t="str">
-        <v>排序鍵</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B98" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C98" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B99" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C99" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B100" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C98" t="str">
+      <c r="C100" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C129"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -560,953 +560,1272 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>reference implementation.</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B15" t="str">
-        <v>参考实现进行验证。</v>
+        <v>演示实现进行验证。</v>
       </c>
       <c r="C15" t="str">
-        <v>參考實作進行驗證。</v>
+        <v>示範實作進行驗證。</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Validating…</v>
+        <v>Based on</v>
       </c>
       <c r="B16" t="str">
-        <v>正在验证…</v>
+        <v>基于</v>
       </c>
       <c r="C16" t="str">
-        <v>驗證中…</v>
+        <v>基於</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Save ICC profile</v>
+        <v>demo implementation</v>
       </c>
       <c r="B17" t="str">
-        <v>保存 ICC 配置文件</v>
+        <v>演示实现</v>
       </c>
       <c r="C17" t="str">
-        <v>儲存 ICC 設定檔</v>
+        <v>示範實作</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Validating…</v>
       </c>
       <c r="B18" t="str">
-        <v>● 已修改 — 尚未保存</v>
+        <v>正在验证…</v>
       </c>
       <c r="C18" t="str">
-        <v>● 已修改 — 尚未儲存</v>
+        <v>驗證中…</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B19" t="str">
-        <v>将 ICC 配置文件拖到此处</v>
+        <v>保存 ICC 配置文件</v>
       </c>
       <c r="C19" t="str">
-        <v>將 ICC 設定檔拖到此處</v>
+        <v>儲存 ICC 設定檔</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>or</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B20" t="str">
-        <v>或</v>
+        <v>● 已修改 — 尚未保存</v>
       </c>
       <c r="C20" t="str">
-        <v>或</v>
+        <v>● 已修改 — 尚未儲存</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Choose file</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B21" t="str">
-        <v>选择文件</v>
+        <v>将 ICC 配置文件拖到此处</v>
       </c>
       <c r="C21" t="str">
-        <v>選擇檔案</v>
+        <v>將 ICC 設定檔拖到此處</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>.icc and .icm files</v>
+        <v>or</v>
       </c>
       <c r="B22" t="str">
-        <v>.icc 和 .icm 文件</v>
+        <v>或</v>
       </c>
       <c r="C22" t="str">
-        <v>.icc 與 .icm 檔案</v>
+        <v>或</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Header</v>
+        <v>Choose file</v>
       </c>
       <c r="B23" t="str">
-        <v>标头</v>
+        <v>选择文件</v>
       </c>
       <c r="C23" t="str">
-        <v>標頭</v>
+        <v>選擇檔案</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tags</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B24" t="str">
-        <v>标签</v>
+        <v>.icc 和 .icm 文件</v>
       </c>
       <c r="C24" t="str">
-        <v>標籤</v>
+        <v>.icc 與 .icm 檔案</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Validation</v>
+        <v>Header</v>
       </c>
       <c r="B25" t="str">
-        <v>验证</v>
+        <v>标头</v>
       </c>
       <c r="C25" t="str">
-        <v>驗證</v>
+        <v>標頭</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Tags</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>标签</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>標籤</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Raw Output</v>
+        <v>Validation</v>
       </c>
       <c r="B27" t="str">
-        <v>原始输出</v>
+        <v>验证</v>
       </c>
       <c r="C27" t="str">
-        <v>原始輸出</v>
+        <v>驗證</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>XML</v>
+        <v>Plot</v>
       </c>
       <c r="B28" t="str">
-        <v>XML</v>
+        <v>绘图</v>
       </c>
       <c r="C28" t="str">
-        <v>XML</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>JSON</v>
+        <v>Raw Output</v>
       </c>
       <c r="B29" t="str">
-        <v>JSON</v>
+        <v>原始输出</v>
       </c>
       <c r="C29" t="str">
-        <v>JSON</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Invalid profile URL:</v>
+        <v>XML</v>
       </c>
       <c r="B30" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>XML</v>
       </c>
       <c r="C30" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>JSON</v>
       </c>
       <c r="B31" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>JSON</v>
       </c>
       <c r="C31" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Curves</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>曲线</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>曲線</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Input curves</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>输入曲线</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Output curves</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>输出曲线</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Security</v>
+        <v>CLUT image</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>CLUT 图像</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Conformance</v>
+        <v>Gamut image</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>色域图像</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Quality</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>色度</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>色度</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>REPORT</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>散点图</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FAIL</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>色调响应曲线</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>checks</v>
+        <v>Curve table</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>曲线表</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Tables</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>表格</v>
       </c>
       <c r="C41" t="str">
-        <v/>
+        <v>表格</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Data</v>
       </c>
       <c r="B42" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>数据</v>
       </c>
       <c r="C42" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Error:</v>
+        <v>Evaluate</v>
       </c>
       <c r="B43" t="str">
-        <v>错误：</v>
+        <v>求值</v>
       </c>
       <c r="C43" t="str">
-        <v>錯誤：</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to XML</v>
+        <v>Loading…</v>
       </c>
       <c r="B44" t="str">
-        <v>转换为 XML</v>
+        <v>加载中…</v>
       </c>
       <c r="C44" t="str">
-        <v>轉換為 XML</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Convert to JSON</v>
+        <v>Input</v>
       </c>
       <c r="B45" t="str">
-        <v>转换为 JSON</v>
+        <v>输入</v>
       </c>
       <c r="C45" t="str">
-        <v>轉換為 JSON</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Convert to ICC</v>
+        <v>Output</v>
       </c>
       <c r="B46" t="str">
-        <v>转换为 ICC</v>
+        <v>输出</v>
       </c>
       <c r="C46" t="str">
-        <v>轉換為 ICC</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to XML…</v>
+        <v>Floating point</v>
       </c>
       <c r="B47" t="str">
-        <v>正在转换为 XML…</v>
+        <v>浮点值</v>
       </c>
       <c r="C47" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Converting to JSON…</v>
+        <v>Grid point</v>
       </c>
       <c r="B48" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>网格点</v>
       </c>
       <c r="C48" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Converting to ICC…</v>
+        <v>Normalized</v>
       </c>
       <c r="B49" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>归一化</v>
       </c>
       <c r="C49" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Load ICC profile</v>
+        <v>Human</v>
       </c>
       <c r="B50" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>可读值</v>
       </c>
       <c r="C50" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B51" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C51" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Profile ID</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B52" t="str">
-        <v>配置文件 ID</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C52" t="str">
-        <v>設定檔 ID</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No tags found.</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B53" t="str">
-        <v>未找到标签。</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C53" t="str">
-        <v>找不到標籤。</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag Name</v>
+        <v>Loading…</v>
       </c>
       <c r="B54" t="str">
-        <v>标签名称</v>
+        <v>加载中…</v>
       </c>
       <c r="C54" t="str">
-        <v>標籤名稱</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ID</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B55" t="str">
-        <v>ID</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C55" t="str">
-        <v>ID</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Offset</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B56" t="str">
-        <v>偏移</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C56" t="str">
-        <v>偏移</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Size</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B57" t="str">
-        <v>大小</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C57" t="str">
-        <v>大小</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Pad</v>
+        <v>Loading plot module…</v>
       </c>
       <c r="B58" t="str">
-        <v>填充</v>
+        <v/>
       </c>
       <c r="C58" t="str">
-        <v>填充</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bytes changed since load</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B59" t="str">
-        <v>加载后字节已更改</v>
+        <v/>
       </c>
       <c r="C59" t="str">
-        <v>載入後位元組已變更</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Type</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B60" t="str">
-        <v>类型</v>
+        <v/>
       </c>
       <c r="C60" t="str">
-        <v>類型</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Array of {type}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B61" t="str">
-        <v>{type} 数组</v>
+        <v/>
       </c>
       <c r="C61" t="str">
-        <v>{type} 陣列</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>(No content)</v>
+        <v>Security</v>
       </c>
       <c r="B62" t="str">
-        <v>（无内容）</v>
+        <v/>
       </c>
       <c r="C62" t="str">
-        <v>（無內容）</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>bytes</v>
+        <v>Conformance</v>
       </c>
       <c r="B63" t="str">
-        <v>字节</v>
+        <v/>
       </c>
       <c r="C63" t="str">
-        <v>位元組</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Loading full description…</v>
+        <v>Quality</v>
       </c>
       <c r="B64" t="str">
-        <v>正在加载完整描述…</v>
+        <v/>
       </c>
       <c r="C64" t="str">
-        <v>正在載入完整描述…</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Could not load full description:</v>
+        <v>REPORT</v>
       </c>
       <c r="B65" t="str">
-        <v>无法加载完整描述：</v>
+        <v/>
       </c>
       <c r="C65" t="str">
-        <v>無法載入完整描述：</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>FAIL</v>
       </c>
       <c r="B66" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v/>
       </c>
       <c r="C66" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>checks</v>
       </c>
       <c r="B67" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v/>
       </c>
       <c r="C67" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No validation output</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B68" t="str">
-        <v>无验证输出</v>
+        <v/>
       </c>
       <c r="C68" t="str">
-        <v>無驗證輸出</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is valid</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B69" t="str">
-        <v>配置文件有效</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C69" t="str">
-        <v>設定檔有效</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Error:</v>
       </c>
       <c r="B70" t="str">
-        <v>配置文件有警告</v>
+        <v>错误：</v>
       </c>
       <c r="C70" t="str">
-        <v>設定檔有警告</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B71" t="str">
-        <v>配置文件不合规</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C71" t="str">
-        <v>設定檔不符合規範</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical validation error</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B72" t="str">
-        <v>严重验证错误</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C72" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Unknown validation status</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B73" t="str">
-        <v>未知验证状态</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C73" t="str">
-        <v>未知驗證狀態</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B74" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C74" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B75" t="str">
-        <v>未发现警告或错误。</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C75" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B76" t="str">
-        <v>有效</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C76" t="str">
-        <v>有效</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Warning</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B77" t="str">
-        <v>警告</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C77" t="str">
-        <v>警告</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Error</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B78" t="str">
-        <v>错误</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C78" t="str">
-        <v>錯誤</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Unknown</v>
+        <v>Profile ID</v>
       </c>
       <c r="B79" t="str">
-        <v>未知</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C79" t="str">
-        <v>未知</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>View in context</v>
+        <v>No tags found.</v>
       </c>
       <c r="B80" t="str">
-        <v>在上下文中查看</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C80" t="str">
-        <v>在上下文中檢視</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Validation detail</v>
+        <v>Tag Name</v>
       </c>
       <c r="B81" t="str">
-        <v>验证详情</v>
+        <v>标签名称</v>
       </c>
       <c r="C81" t="str">
-        <v>驗證詳情</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Triggered by</v>
+        <v>ID</v>
       </c>
       <c r="B82" t="str">
-        <v>触发字段</v>
+        <v>ID</v>
       </c>
       <c r="C82" t="str">
-        <v>觸發欄位</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Field</v>
+        <v>Offset</v>
       </c>
       <c r="B83" t="str">
-        <v>字段</v>
+        <v>偏移</v>
       </c>
       <c r="C83" t="str">
-        <v>欄位</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Current value</v>
+        <v>Size</v>
       </c>
       <c r="B84" t="str">
-        <v>当前值</v>
+        <v>大小</v>
       </c>
       <c r="C84" t="str">
-        <v>目前值</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Required: 0</v>
+        <v>Pad</v>
       </c>
       <c r="B85" t="str">
-        <v>要求：0</v>
+        <v>填充</v>
       </c>
       <c r="C85" t="str">
-        <v>要求：0</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Expected: {value}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B86" t="str">
-        <v>预期：{value}</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C86" t="str">
-        <v>預期：{value}</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Invalid</v>
+        <v>Type</v>
       </c>
       <c r="B87" t="str">
-        <v>无效</v>
+        <v>类型</v>
       </c>
       <c r="C87" t="str">
-        <v>無效</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B88" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C88" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Close</v>
+        <v>(No content)</v>
       </c>
       <c r="B89" t="str">
-        <v>关闭</v>
+        <v>（无内容）</v>
       </c>
       <c r="C89" t="str">
-        <v>關閉</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading XML editor…</v>
+        <v>bytes</v>
       </c>
       <c r="B90" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>字节</v>
       </c>
       <c r="C90" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B91" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C91" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B92" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C92" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B93" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C93" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B94" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C94" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>No validation output</v>
       </c>
       <c r="B95" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>无验证输出</v>
       </c>
       <c r="C95" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B96" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C96" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B97" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C97" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>indent</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B98" t="str">
-        <v>缩进</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C98" t="str">
-        <v>縮排</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>sort keys</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B99" t="str">
-        <v>排序键</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C99" t="str">
-        <v>排序鍵</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B100" t="str">
+        <v>未知验证状态</v>
+      </c>
+      <c r="C100" t="str">
+        <v>未知驗證狀態</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B101" t="str">
+        <v>严重 — 仅供检查显示</v>
+      </c>
+      <c r="C101" t="str">
+        <v>嚴重 — 僅供檢視顯示</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B102" t="str">
+        <v>未发现警告或错误。</v>
+      </c>
+      <c r="C102" t="str">
+        <v>未發現警告或錯誤。</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B103" t="str">
+        <v>有效</v>
+      </c>
+      <c r="C103" t="str">
+        <v>有效</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B104" t="str">
+        <v>警告</v>
+      </c>
+      <c r="C104" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B105" t="str">
+        <v>错误</v>
+      </c>
+      <c r="C105" t="str">
+        <v>錯誤</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B106" t="str">
+        <v>未知</v>
+      </c>
+      <c r="C106" t="str">
+        <v>未知</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B107" t="str">
+        <v>通过</v>
+      </c>
+      <c r="C107" t="str">
+        <v>通過</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B108" t="str">
+        <v>失败</v>
+      </c>
+      <c r="C108" t="str">
+        <v>失敗</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B109" t="str">
+        <v>在上下文中查看</v>
+      </c>
+      <c r="C109" t="str">
+        <v>在上下文中檢視</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B110" t="str">
+        <v>验证详情</v>
+      </c>
+      <c r="C110" t="str">
+        <v>驗證詳情</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B111" t="str">
+        <v>触发字段</v>
+      </c>
+      <c r="C111" t="str">
+        <v>觸發欄位</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B112" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C112" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B113" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C113" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B114" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C114" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B115" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C115" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B116" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C116" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B117" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C117" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B118" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C118" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B119" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C119" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B120" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C120" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B121" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C121" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B122" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C122" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B123" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C123" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B124" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C124" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B125" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C125" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B126" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C126" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B127" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C127" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B128" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C128" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B129" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C100" t="str">
+      <c r="C129" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C128"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1033,799 +1033,788 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading plot module…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Security</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>安全性</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>安全性</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Security</v>
+        <v>Conformance</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>符合性</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>符合性</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Conformance</v>
+        <v>Quality</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>质量</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>品質</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quality</v>
+        <v>REPORT</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>报告</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>報告</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>REPORT</v>
+        <v>FAIL</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>失败</v>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>失敗</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FAIL</v>
+        <v>checks</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>项检查</v>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>checks</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C68" t="str">
-        <v/>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Error:</v>
       </c>
       <c r="B69" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>错误：</v>
       </c>
       <c r="C69" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Error:</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B70" t="str">
-        <v>错误：</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C70" t="str">
-        <v>錯誤：</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to XML</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B71" t="str">
-        <v>转换为 XML</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C71" t="str">
-        <v>轉換為 XML</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B72" t="str">
-        <v>转换为 JSON</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C72" t="str">
-        <v>轉換為 JSON</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B73" t="str">
-        <v>转换为 ICC</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C73" t="str">
-        <v>轉換為 ICC</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to XML…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B74" t="str">
-        <v>正在转换为 XML…</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C74" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B75" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C75" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to ICC…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B76" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C76" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Load ICC profile</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B77" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C77" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Profile ID</v>
       </c>
       <c r="B78" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C78" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Profile ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B79" t="str">
-        <v>配置文件 ID</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C79" t="str">
-        <v>設定檔 ID</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>No tags found.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B80" t="str">
-        <v>未找到标签。</v>
+        <v>标签名称</v>
       </c>
       <c r="C80" t="str">
-        <v>找不到標籤。</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tag Name</v>
+        <v>ID</v>
       </c>
       <c r="B81" t="str">
-        <v>标签名称</v>
+        <v>ID</v>
       </c>
       <c r="C81" t="str">
-        <v>標籤名稱</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
       <c r="B82" t="str">
-        <v>ID</v>
+        <v>偏移</v>
       </c>
       <c r="C82" t="str">
-        <v>ID</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Offset</v>
+        <v>Size</v>
       </c>
       <c r="B83" t="str">
-        <v>偏移</v>
+        <v>大小</v>
       </c>
       <c r="C83" t="str">
-        <v>偏移</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Size</v>
+        <v>Pad</v>
       </c>
       <c r="B84" t="str">
-        <v>大小</v>
+        <v>填充</v>
       </c>
       <c r="C84" t="str">
-        <v>大小</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Pad</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B85" t="str">
-        <v>填充</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C85" t="str">
-        <v>填充</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bytes changed since load</v>
+        <v>Type</v>
       </c>
       <c r="B86" t="str">
-        <v>加载后字节已更改</v>
+        <v>类型</v>
       </c>
       <c r="C86" t="str">
-        <v>載入後位元組已變更</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Type</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B87" t="str">
-        <v>类型</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C87" t="str">
-        <v>類型</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Array of {type}</v>
+        <v>(No content)</v>
       </c>
       <c r="B88" t="str">
-        <v>{type} 数组</v>
+        <v>（无内容）</v>
       </c>
       <c r="C88" t="str">
-        <v>{type} 陣列</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>(No content)</v>
+        <v>bytes</v>
       </c>
       <c r="B89" t="str">
-        <v>（无内容）</v>
+        <v>字节</v>
       </c>
       <c r="C89" t="str">
-        <v>（無內容）</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>bytes</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B90" t="str">
-        <v>字节</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C90" t="str">
-        <v>位元組</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading full description…</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B91" t="str">
-        <v>正在加载完整描述…</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C91" t="str">
-        <v>正在載入完整描述…</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not load full description:</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B92" t="str">
-        <v>无法加载完整描述：</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C92" t="str">
-        <v>無法載入完整描述：</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B93" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C93" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>No validation output</v>
       </c>
       <c r="B94" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无验证输出</v>
       </c>
       <c r="C94" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>No validation output</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B95" t="str">
-        <v>无验证输出</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C95" t="str">
-        <v>無驗證輸出</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile is valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B96" t="str">
-        <v>配置文件有效</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C96" t="str">
-        <v>設定檔有效</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B97" t="str">
-        <v>配置文件有警告</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C97" t="str">
-        <v>設定檔有警告</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B98" t="str">
-        <v>配置文件不合规</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C98" t="str">
-        <v>設定檔不符合規範</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Critical validation error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B99" t="str">
-        <v>严重验证错误</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C99" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B100" t="str">
-        <v>未知验证状态</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C100" t="str">
-        <v>未知驗證狀態</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B101" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C101" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Valid</v>
       </c>
       <c r="B102" t="str">
-        <v>未发现警告或错误。</v>
+        <v>有效</v>
       </c>
       <c r="C102" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Valid</v>
+        <v>Warning</v>
       </c>
       <c r="B103" t="str">
-        <v>有效</v>
+        <v>警告</v>
       </c>
       <c r="C103" t="str">
-        <v>有效</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Warning</v>
+        <v>Error</v>
       </c>
       <c r="B104" t="str">
-        <v>警告</v>
+        <v>错误</v>
       </c>
       <c r="C104" t="str">
-        <v>警告</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Error</v>
+        <v>Unknown</v>
       </c>
       <c r="B105" t="str">
-        <v>错误</v>
+        <v>未知</v>
       </c>
       <c r="C105" t="str">
-        <v>錯誤</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Unknown</v>
+        <v>Pass</v>
       </c>
       <c r="B106" t="str">
-        <v>未知</v>
+        <v>通过</v>
       </c>
       <c r="C106" t="str">
-        <v>未知</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="B107" t="str">
-        <v>通过</v>
+        <v>失败</v>
       </c>
       <c r="C107" t="str">
-        <v>通過</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Fail</v>
+        <v>View in context</v>
       </c>
       <c r="B108" t="str">
-        <v>失败</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C108" t="str">
-        <v>失敗</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>View in context</v>
+        <v>Validation detail</v>
       </c>
       <c r="B109" t="str">
-        <v>在上下文中查看</v>
+        <v>验证详情</v>
       </c>
       <c r="C109" t="str">
-        <v>在上下文中檢視</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Validation detail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B110" t="str">
-        <v>验证详情</v>
+        <v>触发字段</v>
       </c>
       <c r="C110" t="str">
-        <v>驗證詳情</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Triggered by</v>
+        <v>Field</v>
       </c>
       <c r="B111" t="str">
-        <v>触发字段</v>
+        <v>字段</v>
       </c>
       <c r="C111" t="str">
-        <v>觸發欄位</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Field</v>
+        <v>Current value</v>
       </c>
       <c r="B112" t="str">
-        <v>字段</v>
+        <v>当前值</v>
       </c>
       <c r="C112" t="str">
-        <v>欄位</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Current value</v>
+        <v>Required: 0</v>
       </c>
       <c r="B113" t="str">
-        <v>当前值</v>
+        <v>要求：0</v>
       </c>
       <c r="C113" t="str">
-        <v>目前值</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Required: 0</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B114" t="str">
-        <v>要求：0</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C114" t="str">
-        <v>要求：0</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid</v>
       </c>
       <c r="B115" t="str">
-        <v>预期：{value}</v>
+        <v>无效</v>
       </c>
       <c r="C115" t="str">
-        <v>預期：{value}</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Invalid</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B116" t="str">
-        <v>无效</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C116" t="str">
-        <v>無效</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Close</v>
       </c>
       <c r="B117" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>关闭</v>
       </c>
       <c r="C117" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Close</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B118" t="str">
-        <v>关闭</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C118" t="str">
-        <v>關閉</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading XML editor…</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B119" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C119" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Loading JSON editor…</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B120" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C120" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B121" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C121" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B122" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C122" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved XML edits</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B123" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C123" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B124" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C124" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B125" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C125" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>indent</v>
       </c>
       <c r="B126" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>缩进</v>
       </c>
       <c r="C126" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>縮排</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>indent</v>
+        <v>sort keys</v>
       </c>
       <c r="B127" t="str">
-        <v>缩进</v>
+        <v>排序键</v>
       </c>
       <c r="C127" t="str">
-        <v>縮排</v>
+        <v>排序鍵</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sort keys</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B128" t="str">
-        <v>排序键</v>
+        <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
       <c r="C128" t="str">
-        <v>排序鍵</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B129" t="str">
-        <v>已从编辑写入配置文件，但重新验证失败：</v>
-      </c>
-      <c r="C129" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C128"/>
+  <dimension ref="A1:C131"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -505,1316 +505,1349 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Help</v>
+        <v>Number format</v>
       </c>
       <c r="B10" t="str">
-        <v>帮助</v>
+        <v>数字格式</v>
       </c>
       <c r="C10" t="str">
-        <v>說明</v>
+        <v>數字格式</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Contact</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B11" t="str">
-        <v>联系</v>
+        <v>十六进制</v>
       </c>
       <c r="C11" t="str">
-        <v>聯絡</v>
+        <v>十六進位</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Decimal</v>
       </c>
       <c r="B12" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>十进制</v>
       </c>
       <c r="C12" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>十進位</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Help</v>
       </c>
       <c r="B13" t="str">
-        <v>上传一个 ICC 配置文件，依据</v>
+        <v>帮助</v>
       </c>
       <c r="C13" t="str">
-        <v>上傳一個 ICC 設定檔，依據</v>
+        <v>說明</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>specification using the</v>
+        <v>Contact</v>
       </c>
       <c r="B14" t="str">
-        <v>规范使用</v>
+        <v>联系</v>
       </c>
       <c r="C14" t="str">
-        <v>規範使用</v>
+        <v>聯絡</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>demo implementation.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B15" t="str">
-        <v>演示实现进行验证。</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C15" t="str">
-        <v>示範實作進行驗證。</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Based on</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B16" t="str">
-        <v>基于</v>
+        <v>上传一个 ICC 配置文件，依据</v>
       </c>
       <c r="C16" t="str">
-        <v>基於</v>
+        <v>上傳一個 ICC 設定檔，依據</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>demo implementation</v>
+        <v>specification using the</v>
       </c>
       <c r="B17" t="str">
-        <v>演示实现</v>
+        <v>规范使用</v>
       </c>
       <c r="C17" t="str">
-        <v>示範實作</v>
+        <v>規範使用</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Validating…</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B18" t="str">
-        <v>正在验证…</v>
+        <v>演示实现进行验证。</v>
       </c>
       <c r="C18" t="str">
-        <v>驗證中…</v>
+        <v>示範實作進行驗證。</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Save ICC profile</v>
+        <v>Based on</v>
       </c>
       <c r="B19" t="str">
-        <v>保存 ICC 配置文件</v>
+        <v>基于</v>
       </c>
       <c r="C19" t="str">
-        <v>儲存 ICC 設定檔</v>
+        <v>基於</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>demo implementation</v>
       </c>
       <c r="B20" t="str">
-        <v>● 已修改 — 尚未保存</v>
+        <v>演示实现</v>
       </c>
       <c r="C20" t="str">
-        <v>● 已修改 — 尚未儲存</v>
+        <v>示範實作</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Validating…</v>
       </c>
       <c r="B21" t="str">
-        <v>将 ICC 配置文件拖到此处</v>
+        <v>正在验证…</v>
       </c>
       <c r="C21" t="str">
-        <v>將 ICC 設定檔拖到此處</v>
+        <v>驗證中…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>or</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B22" t="str">
-        <v>或</v>
+        <v>保存 ICC 配置文件</v>
       </c>
       <c r="C22" t="str">
-        <v>或</v>
+        <v>儲存 ICC 設定檔</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Choose file</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B23" t="str">
-        <v>选择文件</v>
+        <v>● 已修改 — 尚未保存</v>
       </c>
       <c r="C23" t="str">
-        <v>選擇檔案</v>
+        <v>● 已修改 — 尚未儲存</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>.icc and .icm files</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B24" t="str">
-        <v>.icc 和 .icm 文件</v>
+        <v>将 ICC 配置文件拖到此处</v>
       </c>
       <c r="C24" t="str">
-        <v>.icc 與 .icm 檔案</v>
+        <v>將 ICC 設定檔拖到此處</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Header</v>
+        <v>or</v>
       </c>
       <c r="B25" t="str">
-        <v>标头</v>
+        <v>或</v>
       </c>
       <c r="C25" t="str">
-        <v>標頭</v>
+        <v>或</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tags</v>
+        <v>Choose file</v>
       </c>
       <c r="B26" t="str">
-        <v>标签</v>
+        <v>选择文件</v>
       </c>
       <c r="C26" t="str">
-        <v>標籤</v>
+        <v>選擇檔案</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Validation</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B27" t="str">
-        <v>验证</v>
+        <v>.icc 和 .icm 文件</v>
       </c>
       <c r="C27" t="str">
-        <v>驗證</v>
+        <v>.icc 與 .icm 檔案</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Plot</v>
+        <v>Header</v>
       </c>
       <c r="B28" t="str">
-        <v>绘图</v>
+        <v>标头</v>
       </c>
       <c r="C28" t="str">
-        <v>繪圖</v>
+        <v>標頭</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Raw Output</v>
+        <v>Tags</v>
       </c>
       <c r="B29" t="str">
-        <v>原始输出</v>
+        <v>标签</v>
       </c>
       <c r="C29" t="str">
-        <v>原始輸出</v>
+        <v>標籤</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>XML</v>
+        <v>Validation</v>
       </c>
       <c r="B30" t="str">
-        <v>XML</v>
+        <v>验证</v>
       </c>
       <c r="C30" t="str">
-        <v>XML</v>
+        <v>驗證</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>JSON</v>
+        <v>Plot</v>
       </c>
       <c r="B31" t="str">
-        <v>JSON</v>
+        <v>绘图</v>
       </c>
       <c r="C31" t="str">
-        <v>JSON</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B32" t="str">
-        <v>曲线</v>
+        <v>原始输出</v>
       </c>
       <c r="C32" t="str">
-        <v>曲線</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Input curves</v>
+        <v>XML</v>
       </c>
       <c r="B33" t="str">
-        <v>输入曲线</v>
+        <v>XML</v>
       </c>
       <c r="C33" t="str">
-        <v>輸入曲線</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Output curves</v>
+        <v>JSON</v>
       </c>
       <c r="B34" t="str">
-        <v>输出曲线</v>
+        <v>JSON</v>
       </c>
       <c r="C34" t="str">
-        <v>輸出曲線</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CLUT image</v>
+        <v>Curves</v>
       </c>
       <c r="B35" t="str">
-        <v>CLUT 图像</v>
+        <v>曲线</v>
       </c>
       <c r="C35" t="str">
-        <v>CLUT 影像</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gamut image</v>
+        <v>Input curves</v>
       </c>
       <c r="B36" t="str">
-        <v>色域图像</v>
+        <v>输入曲线</v>
       </c>
       <c r="C36" t="str">
-        <v>色域影像</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Chromaticity</v>
+        <v>Output curves</v>
       </c>
       <c r="B37" t="str">
-        <v>色度</v>
+        <v>输出曲线</v>
       </c>
       <c r="C37" t="str">
-        <v>色度</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Scatter plot</v>
+        <v>CLUT image</v>
       </c>
       <c r="B38" t="str">
-        <v>散点图</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C38" t="str">
-        <v>散佈圖</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tone response curve</v>
+        <v>Gamut image</v>
       </c>
       <c r="B39" t="str">
-        <v>色调响应曲线</v>
+        <v>色域图像</v>
       </c>
       <c r="C39" t="str">
-        <v>色調響應曲線</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Curve table</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B40" t="str">
-        <v>曲线表</v>
+        <v>色度</v>
       </c>
       <c r="C40" t="str">
-        <v>曲線表</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tables</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B41" t="str">
-        <v>表格</v>
+        <v>散点图</v>
       </c>
       <c r="C41" t="str">
-        <v>表格</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Data</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B42" t="str">
-        <v>数据</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C42" t="str">
-        <v>資料</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Evaluate</v>
+        <v>Curve table</v>
       </c>
       <c r="B43" t="str">
-        <v>求值</v>
+        <v>曲线表</v>
       </c>
       <c r="C43" t="str">
-        <v>求值</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Loading…</v>
+        <v>Tables</v>
       </c>
       <c r="B44" t="str">
-        <v>加载中…</v>
+        <v>表格</v>
       </c>
       <c r="C44" t="str">
-        <v>載入中…</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Input</v>
+        <v>Data</v>
       </c>
       <c r="B45" t="str">
-        <v>输入</v>
+        <v>数据</v>
       </c>
       <c r="C45" t="str">
-        <v>輸入</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Output</v>
+        <v>Evaluate</v>
       </c>
       <c r="B46" t="str">
-        <v>输出</v>
+        <v>求值</v>
       </c>
       <c r="C46" t="str">
-        <v>輸出</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Floating point</v>
+        <v>Loading…</v>
       </c>
       <c r="B47" t="str">
-        <v>浮点值</v>
+        <v>加载中…</v>
       </c>
       <c r="C47" t="str">
-        <v>浮點值</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grid point</v>
+        <v>Input</v>
       </c>
       <c r="B48" t="str">
-        <v>网格点</v>
+        <v>输入</v>
       </c>
       <c r="C48" t="str">
-        <v>網格點</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Normalized</v>
+        <v>Output</v>
       </c>
       <c r="B49" t="str">
-        <v>归一化</v>
+        <v>输出</v>
       </c>
       <c r="C49" t="str">
-        <v>正規化</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Human</v>
+        <v>Floating point</v>
       </c>
       <c r="B50" t="str">
-        <v>可读值</v>
+        <v>浮点值</v>
       </c>
       <c r="C50" t="str">
-        <v>可讀值</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Device → PCS</v>
+        <v>Grid point</v>
       </c>
       <c r="B51" t="str">
-        <v>设备 → PCS</v>
+        <v>网格点</v>
       </c>
       <c r="C51" t="str">
-        <v>裝置 → PCS</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PCS → Device</v>
+        <v>Normalized</v>
       </c>
       <c r="B52" t="str">
-        <v>PCS → 设备</v>
+        <v>归一化</v>
       </c>
       <c r="C52" t="str">
-        <v>PCS → 裝置</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No CLUT grid</v>
+        <v>Human</v>
       </c>
       <c r="B53" t="str">
-        <v>无 CLUT 网格</v>
+        <v>可读值</v>
       </c>
       <c r="C53" t="str">
-        <v>無 CLUT 網格</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Loading…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B54" t="str">
-        <v>加载中…</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C54" t="str">
-        <v>載入中…</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B55" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C55" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Invalid profile URL:</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B56" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C56" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Loading…</v>
       </c>
       <c r="B57" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>加载中…</v>
       </c>
       <c r="C57" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B58" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C58" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B59" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C59" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B60" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C60" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Security</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B61" t="str">
-        <v>安全性</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C61" t="str">
-        <v>安全性</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Conformance</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B62" t="str">
-        <v>符合性</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C62" t="str">
-        <v>符合性</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Quality</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B63" t="str">
-        <v>质量</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C63" t="str">
-        <v>品質</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>REPORT</v>
+        <v>Security</v>
       </c>
       <c r="B64" t="str">
-        <v>报告</v>
+        <v>安全性</v>
       </c>
       <c r="C64" t="str">
-        <v>報告</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>FAIL</v>
+        <v>Conformance</v>
       </c>
       <c r="B65" t="str">
-        <v>失败</v>
+        <v>符合性</v>
       </c>
       <c r="C65" t="str">
-        <v>失敗</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>checks</v>
+        <v>Quality</v>
       </c>
       <c r="B66" t="str">
-        <v>项检查</v>
+        <v>质量</v>
       </c>
       <c r="C66" t="str">
-        <v>項檢查</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>REPORT</v>
       </c>
       <c r="B67" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>报告</v>
       </c>
       <c r="C67" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>FAIL</v>
       </c>
       <c r="B68" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>失败</v>
       </c>
       <c r="C68" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Error:</v>
+        <v>checks</v>
       </c>
       <c r="B69" t="str">
-        <v>错误：</v>
+        <v>项检查</v>
       </c>
       <c r="C69" t="str">
-        <v>錯誤：</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Convert to XML</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B70" t="str">
-        <v>转换为 XML</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C70" t="str">
-        <v>轉換為 XML</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to JSON</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B71" t="str">
-        <v>转换为 JSON</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C71" t="str">
-        <v>轉換為 JSON</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to ICC</v>
+        <v>Error:</v>
       </c>
       <c r="B72" t="str">
-        <v>转换为 ICC</v>
+        <v>错误：</v>
       </c>
       <c r="C72" t="str">
-        <v>轉換為 ICC</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B73" t="str">
-        <v>正在转换为 XML…</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C73" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B74" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C74" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B75" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C75" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B76" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C76" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B77" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C77" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Profile ID</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B78" t="str">
-        <v>配置文件 ID</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C78" t="str">
-        <v>設定檔 ID</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>No tags found.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B79" t="str">
-        <v>未找到标签。</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C79" t="str">
-        <v>找不到標籤。</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tag Name</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B80" t="str">
-        <v>标签名称</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C80" t="str">
-        <v>標籤名稱</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ID</v>
+        <v>Profile ID</v>
       </c>
       <c r="B81" t="str">
-        <v>ID</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C81" t="str">
-        <v>ID</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Offset</v>
+        <v>No tags found.</v>
       </c>
       <c r="B82" t="str">
-        <v>偏移</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C82" t="str">
-        <v>偏移</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Size</v>
+        <v>Tag Name</v>
       </c>
       <c r="B83" t="str">
-        <v>大小</v>
+        <v>标签名称</v>
       </c>
       <c r="C83" t="str">
-        <v>大小</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Pad</v>
+        <v>ID</v>
       </c>
       <c r="B84" t="str">
-        <v>填充</v>
+        <v>ID</v>
       </c>
       <c r="C84" t="str">
-        <v>填充</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bytes changed since load</v>
+        <v>Offset</v>
       </c>
       <c r="B85" t="str">
-        <v>加载后字节已更改</v>
+        <v>偏移</v>
       </c>
       <c r="C85" t="str">
-        <v>載入後位元組已變更</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Type</v>
+        <v>Size</v>
       </c>
       <c r="B86" t="str">
-        <v>类型</v>
+        <v>大小</v>
       </c>
       <c r="C86" t="str">
-        <v>類型</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Array of {type}</v>
+        <v>Pad</v>
       </c>
       <c r="B87" t="str">
-        <v>{type} 数组</v>
+        <v>填充</v>
       </c>
       <c r="C87" t="str">
-        <v>{type} 陣列</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>(No content)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B88" t="str">
-        <v>（无内容）</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C88" t="str">
-        <v>（無內容）</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>bytes</v>
+        <v>Type</v>
       </c>
       <c r="B89" t="str">
-        <v>字节</v>
+        <v>类型</v>
       </c>
       <c r="C89" t="str">
-        <v>位元組</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading full description…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B90" t="str">
-        <v>正在加载完整描述…</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C90" t="str">
-        <v>正在載入完整描述…</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Could not load full description:</v>
+        <v>(No content)</v>
       </c>
       <c r="B91" t="str">
-        <v>无法加载完整描述：</v>
+        <v>（无内容）</v>
       </c>
       <c r="C91" t="str">
-        <v>無法載入完整描述：</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>bytes</v>
       </c>
       <c r="B92" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>字节</v>
       </c>
       <c r="C92" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B93" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C93" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>No validation output</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B94" t="str">
-        <v>无验证输出</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C94" t="str">
-        <v>無驗證輸出</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Profile is valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B95" t="str">
-        <v>配置文件有效</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C95" t="str">
-        <v>設定檔有效</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B96" t="str">
-        <v>配置文件有警告</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C96" t="str">
-        <v>設定檔有警告</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile is non-compliant</v>
+        <v>No validation output</v>
       </c>
       <c r="B97" t="str">
-        <v>配置文件不合规</v>
+        <v>无验证输出</v>
       </c>
       <c r="C97" t="str">
-        <v>設定檔不符合規範</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B98" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C98" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B99" t="str">
-        <v>未知验证状态</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C99" t="str">
-        <v>未知驗證狀態</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B100" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C100" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B101" t="str">
-        <v>未发现警告或错误。</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C101" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Valid</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B102" t="str">
-        <v>有效</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C102" t="str">
-        <v>有效</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Warning</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B103" t="str">
-        <v>警告</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C103" t="str">
-        <v>警告</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B104" t="str">
-        <v>错误</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C104" t="str">
-        <v>錯誤</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Unknown</v>
+        <v>Valid</v>
       </c>
       <c r="B105" t="str">
-        <v>未知</v>
+        <v>有效</v>
       </c>
       <c r="C105" t="str">
-        <v>未知</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Pass</v>
+        <v>Warning</v>
       </c>
       <c r="B106" t="str">
-        <v>通过</v>
+        <v>警告</v>
       </c>
       <c r="C106" t="str">
-        <v>通過</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Fail</v>
+        <v>Error</v>
       </c>
       <c r="B107" t="str">
-        <v>失败</v>
+        <v>错误</v>
       </c>
       <c r="C107" t="str">
-        <v>失敗</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>View in context</v>
+        <v>Unknown</v>
       </c>
       <c r="B108" t="str">
-        <v>在上下文中查看</v>
+        <v>未知</v>
       </c>
       <c r="C108" t="str">
-        <v>在上下文中檢視</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Validation detail</v>
+        <v>Pass</v>
       </c>
       <c r="B109" t="str">
-        <v>验证详情</v>
+        <v>通过</v>
       </c>
       <c r="C109" t="str">
-        <v>驗證詳情</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Triggered by</v>
+        <v>Fail</v>
       </c>
       <c r="B110" t="str">
-        <v>触发字段</v>
+        <v>失败</v>
       </c>
       <c r="C110" t="str">
-        <v>觸發欄位</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Field</v>
+        <v>View in context</v>
       </c>
       <c r="B111" t="str">
-        <v>字段</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C111" t="str">
-        <v>欄位</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Current value</v>
+        <v>Validation detail</v>
       </c>
       <c r="B112" t="str">
-        <v>当前值</v>
+        <v>验证详情</v>
       </c>
       <c r="C112" t="str">
-        <v>目前值</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Required: 0</v>
+        <v>Triggered by</v>
       </c>
       <c r="B113" t="str">
-        <v>要求：0</v>
+        <v>触发字段</v>
       </c>
       <c r="C113" t="str">
-        <v>要求：0</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Expected: {value}</v>
+        <v>Field</v>
       </c>
       <c r="B114" t="str">
-        <v>预期：{value}</v>
+        <v>字段</v>
       </c>
       <c r="C114" t="str">
-        <v>預期：{value}</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Invalid</v>
+        <v>Current value</v>
       </c>
       <c r="B115" t="str">
-        <v>无效</v>
+        <v>当前值</v>
       </c>
       <c r="C115" t="str">
-        <v>無效</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B116" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>要求：0</v>
       </c>
       <c r="C116" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Close</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B117" t="str">
-        <v>关闭</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C117" t="str">
-        <v>關閉</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Loading XML editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B118" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>无效</v>
       </c>
       <c r="C118" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading JSON editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B119" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C119" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B120" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>关闭</v>
       </c>
       <c r="C120" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B121" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C121" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C122" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B123" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C123" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C124" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B125" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C125" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>indent</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B126" t="str">
-        <v>缩进</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C126" t="str">
-        <v>縮排</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B127" t="str">
-        <v>排序键</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C127" t="str">
-        <v>排序鍵</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B128" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C128" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B129" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C129" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B130" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C130" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B128" t="str">
+      <c r="B131" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C128" t="str">
+      <c r="C131" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C131"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C132"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1066,788 +1066,799 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B61" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C61" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B62" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C62" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B63" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C63" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B64" t="str">
-        <v>安全性</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C64" t="str">
-        <v>安全性</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B65" t="str">
-        <v>符合性</v>
+        <v>安全性</v>
       </c>
       <c r="C65" t="str">
-        <v>符合性</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B66" t="str">
-        <v>质量</v>
+        <v>符合性</v>
       </c>
       <c r="C66" t="str">
-        <v>品質</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B67" t="str">
-        <v>报告</v>
+        <v>质量</v>
       </c>
       <c r="C67" t="str">
-        <v>報告</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B68" t="str">
-        <v>失败</v>
+        <v>报告</v>
       </c>
       <c r="C68" t="str">
-        <v>失敗</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B69" t="str">
-        <v>项检查</v>
+        <v>失败</v>
       </c>
       <c r="C69" t="str">
-        <v>項檢查</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B70" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>项检查</v>
       </c>
       <c r="C70" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B71" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C71" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Error:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B72" t="str">
-        <v>错误：</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C72" t="str">
-        <v>錯誤：</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B73" t="str">
-        <v>转换为 XML</v>
+        <v>错误：</v>
       </c>
       <c r="C73" t="str">
-        <v>轉換為 XML</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B74" t="str">
-        <v>转换为 JSON</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C74" t="str">
-        <v>轉換為 JSON</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B75" t="str">
-        <v>转换为 ICC</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C75" t="str">
-        <v>轉換為 ICC</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B76" t="str">
-        <v>正在转换为 XML…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C76" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B77" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C77" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B78" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C78" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B79" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C79" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B80" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C80" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B81" t="str">
-        <v>配置文件 ID</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C81" t="str">
-        <v>設定檔 ID</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B82" t="str">
-        <v>未找到标签。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C82" t="str">
-        <v>找不到標籤。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B83" t="str">
-        <v>标签名称</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C83" t="str">
-        <v>標籤名稱</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B84" t="str">
-        <v>ID</v>
+        <v>标签名称</v>
       </c>
       <c r="C84" t="str">
-        <v>ID</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B85" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
       <c r="C85" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B86" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
       <c r="C86" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B87" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
       <c r="C87" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B88" t="str">
-        <v>加载后字节已更改</v>
+        <v>填充</v>
       </c>
       <c r="C88" t="str">
-        <v>載入後位元組已變更</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B89" t="str">
-        <v>类型</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C89" t="str">
-        <v>類型</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B90" t="str">
-        <v>{type} 数组</v>
+        <v>类型</v>
       </c>
       <c r="C90" t="str">
-        <v>{type} 陣列</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B91" t="str">
-        <v>（无内容）</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C91" t="str">
-        <v>（無內容）</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B92" t="str">
-        <v>字节</v>
+        <v>（无内容）</v>
       </c>
       <c r="C92" t="str">
-        <v>位元組</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B93" t="str">
-        <v>正在加载完整描述…</v>
+        <v>字节</v>
       </c>
       <c r="C93" t="str">
-        <v>正在載入完整描述…</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B94" t="str">
-        <v>无法加载完整描述：</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C94" t="str">
-        <v>無法載入完整描述：</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B95" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C95" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B96" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C96" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B97" t="str">
-        <v>无验证输出</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C97" t="str">
-        <v>無驗證輸出</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B98" t="str">
-        <v>配置文件有效</v>
+        <v>无验证输出</v>
       </c>
       <c r="C98" t="str">
-        <v>設定檔有效</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B99" t="str">
-        <v>配置文件有警告</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C99" t="str">
-        <v>設定檔有警告</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B100" t="str">
-        <v>配置文件不合规</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C100" t="str">
-        <v>設定檔不符合規範</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B101" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C101" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B102" t="str">
-        <v>未知验证状态</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C102" t="str">
-        <v>未知驗證狀態</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B103" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C103" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B104" t="str">
-        <v>未发现警告或错误。</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C104" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B105" t="str">
-        <v>有效</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C105" t="str">
-        <v>有效</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B106" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
       <c r="C106" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B107" t="str">
-        <v>错误</v>
+        <v>警告</v>
       </c>
       <c r="C107" t="str">
-        <v>錯誤</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B108" t="str">
-        <v>未知</v>
+        <v>错误</v>
       </c>
       <c r="C108" t="str">
-        <v>未知</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B109" t="str">
-        <v>通过</v>
+        <v>未知</v>
       </c>
       <c r="C109" t="str">
-        <v>通過</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B110" t="str">
-        <v>失败</v>
+        <v>通过</v>
       </c>
       <c r="C110" t="str">
-        <v>失敗</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B111" t="str">
-        <v>在上下文中查看</v>
+        <v>失败</v>
       </c>
       <c r="C111" t="str">
-        <v>在上下文中檢視</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B112" t="str">
-        <v>验证详情</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C112" t="str">
-        <v>驗證詳情</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B113" t="str">
-        <v>触发字段</v>
+        <v>验证详情</v>
       </c>
       <c r="C113" t="str">
-        <v>觸發欄位</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B114" t="str">
-        <v>字段</v>
+        <v>触发字段</v>
       </c>
       <c r="C114" t="str">
-        <v>欄位</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B115" t="str">
-        <v>当前值</v>
+        <v>字段</v>
       </c>
       <c r="C115" t="str">
-        <v>目前值</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B116" t="str">
-        <v>要求：0</v>
+        <v>当前值</v>
       </c>
       <c r="C116" t="str">
-        <v>要求：0</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B117" t="str">
-        <v>预期：{value}</v>
+        <v>要求：0</v>
       </c>
       <c r="C117" t="str">
-        <v>預期：{value}</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B118" t="str">
-        <v>无效</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C118" t="str">
-        <v>無效</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B119" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>无效</v>
       </c>
       <c r="C119" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B120" t="str">
-        <v>关闭</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C120" t="str">
-        <v>關閉</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B121" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>关闭</v>
       </c>
       <c r="C121" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C122" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B123" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C123" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C124" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B125" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C125" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B126" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C126" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B127" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C127" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B128" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C128" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B129" t="str">
-        <v>缩进</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C129" t="str">
-        <v>縮排</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B130" t="str">
-        <v>排序键</v>
+        <v>缩进</v>
       </c>
       <c r="C130" t="str">
-        <v>排序鍵</v>
+        <v>縮排</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B131" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C131" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B131" t="str">
+      <c r="B132" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C131" t="str">
+      <c r="C132" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C132"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C132"/>
+  <dimension ref="A1:C181"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -736,1129 +736,1668 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Plot</v>
+        <v>Analysis</v>
       </c>
       <c r="B31" t="str">
-        <v>绘图</v>
+        <v>分析</v>
       </c>
       <c r="C31" t="str">
-        <v>繪圖</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Raw Output</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B32" t="str">
-        <v>原始输出</v>
+        <v>中性轴墨量</v>
       </c>
       <c r="C32" t="str">
-        <v>原始輸出</v>
+        <v>中性軸墨量</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>XML</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B33" t="str">
-        <v>XML</v>
+        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
       </c>
       <c r="C33" t="str">
-        <v>XML</v>
+        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>JSON</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B34" t="str">
-        <v>JSON</v>
+        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C34" t="str">
-        <v>JSON</v>
+        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Curves</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B35" t="str">
-        <v>曲线</v>
+        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
       </c>
       <c r="C35" t="str">
-        <v>曲線</v>
+        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Input curves</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B36" t="str">
-        <v>输入曲线</v>
+        <v>渲染意图</v>
       </c>
       <c r="C36" t="str">
-        <v>輸入曲線</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Output curves</v>
+        <v>% ink</v>
       </c>
       <c r="B37" t="str">
-        <v>输出曲线</v>
+        <v>% 墨量</v>
       </c>
       <c r="C37" t="str">
-        <v>輸出曲線</v>
+        <v>% 墨量</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CLUT image</v>
+        <v>Perceptual</v>
       </c>
       <c r="B38" t="str">
-        <v>CLUT 图像</v>
+        <v>感知</v>
       </c>
       <c r="C38" t="str">
-        <v>CLUT 影像</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gamut image</v>
+        <v>Relative colorimetric</v>
       </c>
       <c r="B39" t="str">
-        <v>色域图像</v>
+        <v>相对比色</v>
       </c>
       <c r="C39" t="str">
-        <v>色域影像</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Chromaticity</v>
+        <v>Saturation</v>
       </c>
       <c r="B40" t="str">
-        <v>色度</v>
+        <v>饱和度</v>
       </c>
       <c r="C40" t="str">
-        <v>色度</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Scatter plot</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B41" t="str">
-        <v>散点图</v>
+        <v>反转较多的通道仅显示按 ΔL* 排序最大的 {shown} 个。</v>
       </c>
       <c r="C41" t="str">
-        <v>散佈圖</v>
+        <v>反轉較多的通道僅顯示依 ΔL* 排序最大的 {shown} 個。</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tone response curve</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B42" t="str">
-        <v>色调响应曲线</v>
+        <v>显示更多（{n}）</v>
       </c>
       <c r="C42" t="str">
-        <v>色調響應曲線</v>
+        <v>顯示更多（{n}）</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Curve table</v>
+        <v>All</v>
       </c>
       <c r="B43" t="str">
-        <v>曲线表</v>
+        <v>全部</v>
       </c>
       <c r="C43" t="str">
-        <v>曲線表</v>
+        <v>全部</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tables</v>
+        <v>Analysing…</v>
       </c>
       <c r="B44" t="str">
-        <v>表格</v>
+        <v>正在分析…</v>
       </c>
       <c r="C44" t="str">
-        <v>表格</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Data</v>
+        <v>Analysis</v>
       </c>
       <c r="B45" t="str">
-        <v>数据</v>
+        <v>分析</v>
       </c>
       <c r="C45" t="str">
-        <v>資料</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Evaluate</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B46" t="str">
-        <v>求值</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C46" t="str">
-        <v>求值</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Loading…</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B47" t="str">
-        <v>加载中…</v>
+        <v>L* 色调反转</v>
       </c>
       <c r="C47" t="str">
-        <v>載入中…</v>
+        <v>L* 色調反轉</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Input</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B48" t="str">
-        <v>输入</v>
+        <v>增加油墨不应使颜色变亮。逐一扫描每个设备通道并固定其他通道；凡 L* 上升的步骤都会被标记。该算法最初由 Harold Boll 提出。</v>
       </c>
       <c r="C48" t="str">
-        <v>輸入</v>
+        <v>增加油墨不應使顏色變亮。逐一掃描每個裝置通道並固定其他通道；凡 L* 上升的步驟都會被標記。此演算法最初由 Harold Boll 提出。</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Output</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B49" t="str">
-        <v>输出</v>
+        <v>此配置文件没有设备→PCS 的 CLUT，因此 L* 反转扫描不适用（例如矩阵/TRC 显示器配置文件）。</v>
       </c>
       <c r="C49" t="str">
-        <v>輸出</v>
+        <v>此設定檔沒有裝置→PCS 的 CLUT，因此 L* 反轉掃描不適用（例如矩陣/TRC 顯示器設定檔）。</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Floating point</v>
+        <v>LUT table</v>
       </c>
       <c r="B50" t="str">
-        <v>浮点值</v>
+        <v>LUT 表</v>
       </c>
       <c r="C50" t="str">
-        <v>浮點值</v>
+        <v>LUT 表</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Grid point</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B51" t="str">
-        <v>网格点</v>
+        <v>ΔL* 阈值 (ε)</v>
       </c>
       <c r="C51" t="str">
-        <v>網格點</v>
+        <v>ΔL* 閾值 (ε)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Normalized</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B52" t="str">
-        <v>归一化</v>
+        <v>超过 ε = {eps} 的反转：{n}</v>
       </c>
       <c r="C52" t="str">
-        <v>正規化</v>
+        <v>超過 ε = {eps} 的反轉：{n}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Human</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B53" t="str">
-        <v>可读值</v>
+        <v>没有超过 ε = {eps} 的 L* 反转</v>
       </c>
       <c r="C53" t="str">
-        <v>可讀值</v>
+        <v>沒有超過 ε = {eps} 的 L* 反轉</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Device → PCS</v>
+        <v>Channel</v>
       </c>
       <c r="B54" t="str">
-        <v>设备 → PCS</v>
+        <v>通道</v>
       </c>
       <c r="C54" t="str">
-        <v>裝置 → PCS</v>
+        <v>通道</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PCS → Device</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B55" t="str">
-        <v>PCS → 设备</v>
+        <v>油墨（低 → 高）</v>
       </c>
       <c r="C55" t="str">
-        <v>PCS → 裝置</v>
+        <v>油墨（低 → 高）</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No CLUT grid</v>
+        <v>Plot</v>
       </c>
       <c r="B56" t="str">
-        <v>无 CLUT 网格</v>
+        <v>绘图</v>
       </c>
       <c r="C56" t="str">
-        <v>無 CLUT 網格</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loading…</v>
+        <v>Raw Output</v>
       </c>
       <c r="B57" t="str">
-        <v>加载中…</v>
+        <v>原始输出</v>
       </c>
       <c r="C57" t="str">
-        <v>載入中…</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>XML</v>
       </c>
       <c r="B58" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>XML</v>
       </c>
       <c r="C58" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Invalid profile URL:</v>
+        <v>JSON</v>
       </c>
       <c r="B59" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>JSON</v>
       </c>
       <c r="C59" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curves</v>
       </c>
       <c r="B60" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>曲线</v>
       </c>
       <c r="C60" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Input curves</v>
       </c>
       <c r="B61" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>输入曲线</v>
       </c>
       <c r="C61" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Output curves</v>
       </c>
       <c r="B62" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>输出曲线</v>
       </c>
       <c r="C62" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B63" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C63" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Gamut image</v>
       </c>
       <c r="B64" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>色域图像</v>
       </c>
       <c r="C64" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Security</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B65" t="str">
-        <v>安全性</v>
+        <v>色度</v>
       </c>
       <c r="C65" t="str">
-        <v>安全性</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Conformance</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B66" t="str">
-        <v>符合性</v>
+        <v>散点图</v>
       </c>
       <c r="C66" t="str">
-        <v>符合性</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quality</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B67" t="str">
-        <v>质量</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C67" t="str">
-        <v>品質</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>REPORT</v>
+        <v>Curve table</v>
       </c>
       <c r="B68" t="str">
-        <v>报告</v>
+        <v>曲线表</v>
       </c>
       <c r="C68" t="str">
-        <v>報告</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FAIL</v>
+        <v>Tables</v>
       </c>
       <c r="B69" t="str">
-        <v>失败</v>
+        <v>表格</v>
       </c>
       <c r="C69" t="str">
-        <v>失敗</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>checks</v>
+        <v>Data</v>
       </c>
       <c r="B70" t="str">
-        <v>项检查</v>
+        <v>数据</v>
       </c>
       <c r="C70" t="str">
-        <v>項檢查</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B71" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>求值</v>
       </c>
       <c r="C71" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading…</v>
       </c>
       <c r="B72" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>加载中…</v>
       </c>
       <c r="C72" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Error:</v>
+        <v>Input</v>
       </c>
       <c r="B73" t="str">
-        <v>错误：</v>
+        <v>输入</v>
       </c>
       <c r="C73" t="str">
-        <v>錯誤：</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to XML</v>
+        <v>Output</v>
       </c>
       <c r="B74" t="str">
-        <v>转换为 XML</v>
+        <v>输出</v>
       </c>
       <c r="C74" t="str">
-        <v>轉換為 XML</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to JSON</v>
+        <v>Floating point</v>
       </c>
       <c r="B75" t="str">
-        <v>转换为 JSON</v>
+        <v>浮点值</v>
       </c>
       <c r="C75" t="str">
-        <v>轉換為 JSON</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Convert to ICC</v>
+        <v>Grid point</v>
       </c>
       <c r="B76" t="str">
-        <v>转换为 ICC</v>
+        <v>网格点</v>
       </c>
       <c r="C76" t="str">
-        <v>轉換為 ICC</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to XML…</v>
+        <v>Normalized</v>
       </c>
       <c r="B77" t="str">
-        <v>正在转换为 XML…</v>
+        <v>归一化</v>
       </c>
       <c r="C77" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to JSON…</v>
+        <v>Human</v>
       </c>
       <c r="B78" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>可读值</v>
       </c>
       <c r="C78" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B79" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C79" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Load ICC profile</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B80" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C80" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B81" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C81" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Profile ID</v>
+        <v>Loading…</v>
       </c>
       <c r="B82" t="str">
-        <v>配置文件 ID</v>
+        <v>加载中…</v>
       </c>
       <c r="C82" t="str">
-        <v>設定檔 ID</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>No tags found.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B83" t="str">
-        <v>未找到标签。</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C83" t="str">
-        <v>找不到標籤。</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Tag Name</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B84" t="str">
-        <v>标签名称</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C84" t="str">
-        <v>標籤名稱</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ID</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B85" t="str">
-        <v>ID</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C85" t="str">
-        <v>ID</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Offset</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B86" t="str">
-        <v>偏移</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C86" t="str">
-        <v>偏移</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Size</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B87" t="str">
-        <v>大小</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C87" t="str">
-        <v>大小</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pad</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B88" t="str">
-        <v>填充</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C88" t="str">
-        <v>填充</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B89" t="str">
-        <v>加载后字节已更改</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C89" t="str">
-        <v>載入後位元組已變更</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Type</v>
+        <v>Security</v>
       </c>
       <c r="B90" t="str">
-        <v>类型</v>
+        <v>安全性</v>
       </c>
       <c r="C90" t="str">
-        <v>類型</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Array of {type}</v>
+        <v>Conformance</v>
       </c>
       <c r="B91" t="str">
-        <v>{type} 数组</v>
+        <v>符合性</v>
       </c>
       <c r="C91" t="str">
-        <v>{type} 陣列</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>(No content)</v>
+        <v>Quality</v>
       </c>
       <c r="B92" t="str">
-        <v>（无内容）</v>
+        <v>质量</v>
       </c>
       <c r="C92" t="str">
-        <v>（無內容）</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>bytes</v>
+        <v>REPORT</v>
       </c>
       <c r="B93" t="str">
-        <v>字节</v>
+        <v>报告</v>
       </c>
       <c r="C93" t="str">
-        <v>位元組</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading full description…</v>
+        <v>FAIL</v>
       </c>
       <c r="B94" t="str">
-        <v>正在加载完整描述…</v>
+        <v>失败</v>
       </c>
       <c r="C94" t="str">
-        <v>正在載入完整描述…</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Could not load full description:</v>
+        <v>checks</v>
       </c>
       <c r="B95" t="str">
-        <v>无法加载完整描述：</v>
+        <v>项检查</v>
       </c>
       <c r="C95" t="str">
-        <v>無法載入完整描述：</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B96" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C96" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B97" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C97" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>No validation output</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B98" t="str">
-        <v>无验证输出</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C98" t="str">
-        <v>無驗證輸出</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile is valid</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B99" t="str">
-        <v>配置文件有效</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C99" t="str">
-        <v>設定檔有效</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B100" t="str">
-        <v>配置文件有警告</v>
+        <v>订阅</v>
       </c>
       <c r="C100" t="str">
-        <v>設定檔有警告</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B101" t="str">
-        <v>配置文件不合规</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C101" t="str">
-        <v>設定檔不符合規範</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Critical validation error</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B102" t="str">
-        <v>严重验证错误</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C102" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Unknown validation status</v>
+        <v>Close</v>
       </c>
       <c r="B103" t="str">
-        <v>未知验证状态</v>
+        <v>关闭</v>
       </c>
       <c r="C103" t="str">
-        <v>未知驗證狀態</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B104" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C104" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Email address</v>
       </c>
       <c r="B105" t="str">
-        <v>未发现警告或错误。</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C105" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Valid</v>
+        <v>you@example.com</v>
       </c>
       <c r="B106" t="str">
-        <v>有效</v>
+        <v>you@example.com</v>
       </c>
       <c r="C106" t="str">
-        <v>有效</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Warning</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B107" t="str">
-        <v>警告</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C107" t="str">
-        <v>警告</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Error</v>
+        <v>(optional)</v>
       </c>
       <c r="B108" t="str">
-        <v>错误</v>
+        <v>（选填）</v>
       </c>
       <c r="C108" t="str">
-        <v>錯誤</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Unknown</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B109" t="str">
-        <v>未知</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C109" t="str">
-        <v>未知</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Pass</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B110" t="str">
-        <v>通过</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C110" t="str">
-        <v>通過</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Fail</v>
+        <v>Cancel</v>
       </c>
       <c r="B111" t="str">
-        <v>失败</v>
+        <v>取消</v>
       </c>
       <c r="C111" t="str">
-        <v>失敗</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>View in context</v>
+        <v>Subscribe</v>
       </c>
       <c r="B112" t="str">
-        <v>在上下文中查看</v>
+        <v>订阅</v>
       </c>
       <c r="C112" t="str">
-        <v>在上下文中檢視</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Validation detail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B113" t="str">
-        <v>验证详情</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C113" t="str">
-        <v>驗證詳情</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Triggered by</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B114" t="str">
-        <v>触发字段</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C114" t="str">
-        <v>觸發欄位</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Field</v>
+        <v>Close</v>
       </c>
       <c r="B115" t="str">
-        <v>字段</v>
+        <v>关闭</v>
       </c>
       <c r="C115" t="str">
-        <v>欄位</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Current value</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B116" t="str">
-        <v>当前值</v>
+        <v>隐私声明</v>
       </c>
       <c r="C116" t="str">
-        <v>目前值</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Required: 0</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B117" t="str">
-        <v>要求：0</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C117" t="str">
-        <v>要求：0</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Expected: {value}</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B118" t="str">
-        <v>预期：{value}</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C118" t="str">
-        <v>預期：{value}</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Invalid</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B119" t="str">
-        <v>无效</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C119" t="str">
-        <v>無效</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B120" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C120" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Close</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B121" t="str">
-        <v>关闭</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C121" t="str">
-        <v>關閉</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading XML editor…</v>
+        <v>Error:</v>
       </c>
       <c r="B122" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>错误：</v>
       </c>
       <c r="C122" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B123" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C123" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B124" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C124" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B125" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C125" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B126" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C126" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B127" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C127" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B128" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C128" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B129" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C129" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>indent</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B130" t="str">
-        <v>缩进</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C130" t="str">
-        <v>縮排</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>sort keys</v>
+        <v>Profile ID</v>
       </c>
       <c r="B131" t="str">
-        <v>排序键</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C131" t="str">
-        <v>排序鍵</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B132" t="str">
+        <v>未找到标签。</v>
+      </c>
+      <c r="C132" t="str">
+        <v>找不到標籤。</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B133" t="str">
+        <v>标签名称</v>
+      </c>
+      <c r="C133" t="str">
+        <v>標籤名稱</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C134" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B135" t="str">
+        <v>偏移</v>
+      </c>
+      <c r="C135" t="str">
+        <v>偏移</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B136" t="str">
+        <v>大小</v>
+      </c>
+      <c r="C136" t="str">
+        <v>大小</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B137" t="str">
+        <v>填充</v>
+      </c>
+      <c r="C137" t="str">
+        <v>填充</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B138" t="str">
+        <v>加载后字节已更改</v>
+      </c>
+      <c r="C138" t="str">
+        <v>載入後位元組已變更</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B139" t="str">
+        <v>类型</v>
+      </c>
+      <c r="C139" t="str">
+        <v>類型</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B140" t="str">
+        <v>{type} 数组</v>
+      </c>
+      <c r="C140" t="str">
+        <v>{type} 陣列</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>（无内容）</v>
+      </c>
+      <c r="C141" t="str">
+        <v>（無內容）</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B142" t="str">
+        <v>字节</v>
+      </c>
+      <c r="C142" t="str">
+        <v>位元組</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B143" t="str">
+        <v>正在加载完整描述…</v>
+      </c>
+      <c r="C143" t="str">
+        <v>正在載入完整描述…</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B144" t="str">
+        <v>无法加载完整描述：</v>
+      </c>
+      <c r="C144" t="str">
+        <v>無法載入完整描述：</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B145" t="str">
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+      </c>
+      <c r="C145" t="str">
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B146" t="str">
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+      </c>
+      <c r="C146" t="str">
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B147" t="str">
+        <v>无验证输出</v>
+      </c>
+      <c r="C147" t="str">
+        <v>無驗證輸出</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B148" t="str">
+        <v>配置文件有效</v>
+      </c>
+      <c r="C148" t="str">
+        <v>設定檔有效</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>配置文件有警告</v>
+      </c>
+      <c r="C149" t="str">
+        <v>設定檔有警告</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B150" t="str">
+        <v>配置文件不合规</v>
+      </c>
+      <c r="C150" t="str">
+        <v>設定檔不符合規範</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B151" t="str">
+        <v>严重验证错误</v>
+      </c>
+      <c r="C151" t="str">
+        <v>嚴重驗證錯誤</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B152" t="str">
+        <v>未知验证状态</v>
+      </c>
+      <c r="C152" t="str">
+        <v>未知驗證狀態</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B153" t="str">
+        <v>严重 — 仅供检查显示</v>
+      </c>
+      <c r="C153" t="str">
+        <v>嚴重 — 僅供檢視顯示</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B154" t="str">
+        <v>未发现警告或错误。</v>
+      </c>
+      <c r="C154" t="str">
+        <v>未發現警告或錯誤。</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B155" t="str">
+        <v>有效</v>
+      </c>
+      <c r="C155" t="str">
+        <v>有效</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B156" t="str">
+        <v>警告</v>
+      </c>
+      <c r="C156" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B157" t="str">
+        <v>错误</v>
+      </c>
+      <c r="C157" t="str">
+        <v>錯誤</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B158" t="str">
+        <v>未知</v>
+      </c>
+      <c r="C158" t="str">
+        <v>未知</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B159" t="str">
+        <v>通过</v>
+      </c>
+      <c r="C159" t="str">
+        <v>通過</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B160" t="str">
+        <v>失败</v>
+      </c>
+      <c r="C160" t="str">
+        <v>失敗</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B161" t="str">
+        <v>在上下文中查看</v>
+      </c>
+      <c r="C161" t="str">
+        <v>在上下文中檢視</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B162" t="str">
+        <v>验证详情</v>
+      </c>
+      <c r="C162" t="str">
+        <v>驗證詳情</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B163" t="str">
+        <v>触发字段</v>
+      </c>
+      <c r="C163" t="str">
+        <v>觸發欄位</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B164" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C164" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B165" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C165" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B166" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C166" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B167" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C167" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B168" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C168" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B169" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C169" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B170" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C170" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B171" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C171" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B172" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C172" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B173" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C173" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B174" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C174" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B175" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C175" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B176" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C176" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B177" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C177" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B178" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C178" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B179" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C179" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B180" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C180" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B181" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C132" t="str">
+      <c r="C181" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C181"/>
+  <dimension ref="A1:C190"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -560,1844 +560,1943 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ICC Profile Tool</v>
+        <v>User guide</v>
       </c>
       <c r="B15" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>用户指南</v>
       </c>
       <c r="C15" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>使用者指南</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Search guide</v>
       </c>
       <c r="B16" t="str">
-        <v>上传一个 ICC 配置文件，依据</v>
+        <v>搜索指南</v>
       </c>
       <c r="C16" t="str">
-        <v>上傳一個 ICC 設定檔，依據</v>
+        <v>搜尋指南</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>specification using the</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B17" t="str">
-        <v>规范使用</v>
+        <v>搜索用户指南</v>
       </c>
       <c r="C17" t="str">
-        <v>規範使用</v>
+        <v>搜尋使用者指南</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>demo implementation.</v>
+        <v>Previous match</v>
       </c>
       <c r="B18" t="str">
-        <v>演示实现进行验证。</v>
+        <v>上一个匹配项</v>
       </c>
       <c r="C18" t="str">
-        <v>示範實作進行驗證。</v>
+        <v>上一個相符項目</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Based on</v>
+        <v>Next match</v>
       </c>
       <c r="B19" t="str">
-        <v>基于</v>
+        <v>下一个匹配项</v>
       </c>
       <c r="C19" t="str">
-        <v>基於</v>
+        <v>下一個相符項目</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>demo implementation</v>
+        <v>Close user guide</v>
       </c>
       <c r="B20" t="str">
-        <v>演示实现</v>
+        <v>关闭用户指南</v>
       </c>
       <c r="C20" t="str">
-        <v>示範實作</v>
+        <v>關閉使用者指南</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Validating…</v>
+        <v>Loading…</v>
       </c>
       <c r="B21" t="str">
-        <v>正在验证…</v>
+        <v>加载中…</v>
       </c>
       <c r="C21" t="str">
-        <v>驗證中…</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Save ICC profile</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B22" t="str">
-        <v>保存 ICC 配置文件</v>
+        <v>无法加载用户指南。</v>
       </c>
       <c r="C22" t="str">
-        <v>儲存 ICC 設定檔</v>
+        <v>無法載入使用者指南。</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>None</v>
       </c>
       <c r="B23" t="str">
-        <v>● 已修改 — 尚未保存</v>
+        <v>无</v>
       </c>
       <c r="C23" t="str">
-        <v>● 已修改 — 尚未儲存</v>
+        <v>無</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B24" t="str">
-        <v>将 ICC 配置文件拖到此处</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C24" t="str">
-        <v>將 ICC 設定檔拖到此處</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>or</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B25" t="str">
-        <v>或</v>
+        <v>上传一个 ICC 配置文件，依据</v>
       </c>
       <c r="C25" t="str">
-        <v>或</v>
+        <v>上傳一個 ICC 設定檔，依據</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Choose file</v>
+        <v>specification using the</v>
       </c>
       <c r="B26" t="str">
-        <v>选择文件</v>
+        <v>规范使用</v>
       </c>
       <c r="C26" t="str">
-        <v>選擇檔案</v>
+        <v>規範使用</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>.icc and .icm files</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B27" t="str">
-        <v>.icc 和 .icm 文件</v>
+        <v>演示实现进行验证。</v>
       </c>
       <c r="C27" t="str">
-        <v>.icc 與 .icm 檔案</v>
+        <v>示範實作進行驗證。</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Header</v>
+        <v>Based on</v>
       </c>
       <c r="B28" t="str">
-        <v>标头</v>
+        <v>基于</v>
       </c>
       <c r="C28" t="str">
-        <v>標頭</v>
+        <v>基於</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tags</v>
+        <v>demo implementation</v>
       </c>
       <c r="B29" t="str">
-        <v>标签</v>
+        <v>演示实现</v>
       </c>
       <c r="C29" t="str">
-        <v>標籤</v>
+        <v>示範實作</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validation</v>
+        <v>Validating…</v>
       </c>
       <c r="B30" t="str">
-        <v>验证</v>
+        <v>正在验证…</v>
       </c>
       <c r="C30" t="str">
-        <v>驗證</v>
+        <v>驗證中…</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Analysis</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B31" t="str">
-        <v>分析</v>
+        <v>保存 ICC 配置文件</v>
       </c>
       <c r="C31" t="str">
-        <v>分析</v>
+        <v>儲存 ICC 設定檔</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B32" t="str">
-        <v>中性轴墨量</v>
+        <v>● 已修改 — 尚未保存</v>
       </c>
       <c r="C32" t="str">
-        <v>中性軸墨量</v>
+        <v>● 已修改 — 尚未儲存</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B33" t="str">
-        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
+        <v>将 ICC 配置文件拖到此处</v>
       </c>
       <c r="C33" t="str">
-        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
+        <v>將 ICC 設定檔拖到此處</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>or</v>
       </c>
       <c r="B34" t="str">
-        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
+        <v>或</v>
       </c>
       <c r="C34" t="str">
-        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
+        <v>或</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Choose file</v>
       </c>
       <c r="B35" t="str">
-        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
+        <v>选择文件</v>
       </c>
       <c r="C35" t="str">
-        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
+        <v>選擇檔案</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Rendering intent</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B36" t="str">
-        <v>渲染意图</v>
+        <v>.icc 和 .icm 文件</v>
       </c>
       <c r="C36" t="str">
-        <v>轉換意圖</v>
+        <v>.icc 與 .icm 檔案</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>% ink</v>
+        <v>Header</v>
       </c>
       <c r="B37" t="str">
-        <v>% 墨量</v>
+        <v>标头</v>
       </c>
       <c r="C37" t="str">
-        <v>% 墨量</v>
+        <v>標頭</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Perceptual</v>
+        <v>Tags</v>
       </c>
       <c r="B38" t="str">
-        <v>感知</v>
+        <v>标签</v>
       </c>
       <c r="C38" t="str">
-        <v>感知</v>
+        <v>標籤</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Relative colorimetric</v>
+        <v>Validation</v>
       </c>
       <c r="B39" t="str">
-        <v>相对比色</v>
+        <v>验证</v>
       </c>
       <c r="C39" t="str">
-        <v>相對比色</v>
+        <v>驗證</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Saturation</v>
+        <v>Analysis</v>
       </c>
       <c r="B40" t="str">
-        <v>饱和度</v>
+        <v>分析</v>
       </c>
       <c r="C40" t="str">
-        <v>飽和度</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B41" t="str">
-        <v>反转较多的通道仅显示按 ΔL* 排序最大的 {shown} 个。</v>
+        <v>中性轴墨量</v>
       </c>
       <c r="C41" t="str">
-        <v>反轉較多的通道僅顯示依 ΔL* 排序最大的 {shown} 個。</v>
+        <v>中性軸墨量</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Show more ({n})</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B42" t="str">
-        <v>显示更多（{n}）</v>
+        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
       </c>
       <c r="C42" t="str">
-        <v>顯示更多（{n}）</v>
+        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>All</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B43" t="str">
-        <v>全部</v>
+        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C43" t="str">
-        <v>全部</v>
+        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Analysing…</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B44" t="str">
-        <v>正在分析…</v>
+        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
       </c>
       <c r="C44" t="str">
-        <v>正在分析…</v>
+        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B45" t="str">
-        <v>分析</v>
+        <v>渲染意图</v>
       </c>
       <c r="C45" t="str">
-        <v>分析</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>% ink</v>
       </c>
       <c r="B46" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>% 墨量</v>
       </c>
       <c r="C46" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>% 墨量</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Perceptual</v>
       </c>
       <c r="B47" t="str">
-        <v>L* 色调反转</v>
+        <v>感知</v>
       </c>
       <c r="C47" t="str">
-        <v>L* 色調反轉</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B48" t="str">
-        <v>增加油墨不应使颜色变亮。逐一扫描每个设备通道并固定其他通道；凡 L* 上升的步骤都会被标记。该算法最初由 Harold Boll 提出。</v>
+        <v>相对比色</v>
       </c>
       <c r="C48" t="str">
-        <v>增加油墨不應使顏色變亮。逐一掃描每個裝置通道並固定其他通道；凡 L* 上升的步驟都會被標記。此演算法最初由 Harold Boll 提出。</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B49" t="str">
-        <v>此配置文件没有设备→PCS 的 CLUT，因此 L* 反转扫描不适用（例如矩阵/TRC 显示器配置文件）。</v>
+        <v>饱和度</v>
       </c>
       <c r="C49" t="str">
-        <v>此設定檔沒有裝置→PCS 的 CLUT，因此 L* 反轉掃描不適用（例如矩陣/TRC 顯示器設定檔）。</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LUT table</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B50" t="str">
-        <v>LUT 表</v>
+        <v>反转较多的通道仅显示按 ΔL* 排序最大的 {shown} 个。</v>
       </c>
       <c r="C50" t="str">
-        <v>LUT 表</v>
+        <v>反轉較多的通道僅顯示依 ΔL* 排序最大的 {shown} 個。</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B51" t="str">
-        <v>ΔL* 阈值 (ε)</v>
+        <v>显示更多（{n}）</v>
       </c>
       <c r="C51" t="str">
-        <v>ΔL* 閾值 (ε)</v>
+        <v>顯示更多（{n}）</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B52" t="str">
-        <v>超过 ε = {eps} 的反转：{n}</v>
+        <v>全部</v>
       </c>
       <c r="C52" t="str">
-        <v>超過 ε = {eps} 的反轉：{n}</v>
+        <v>全部</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Analysing…</v>
       </c>
       <c r="B53" t="str">
-        <v>没有超过 ε = {eps} 的 L* 反转</v>
+        <v>正在分析…</v>
       </c>
       <c r="C53" t="str">
-        <v>沒有超過 ε = {eps} 的 L* 反轉</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Channel</v>
+        <v>Analysis</v>
       </c>
       <c r="B54" t="str">
-        <v>通道</v>
+        <v>分析</v>
       </c>
       <c r="C54" t="str">
-        <v>通道</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ink (low → high)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B55" t="str">
-        <v>油墨（低 → 高）</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C55" t="str">
-        <v>油墨（低 → 高）</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Plot</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B56" t="str">
-        <v>绘图</v>
+        <v>L* 色调反转</v>
       </c>
       <c r="C56" t="str">
-        <v>繪圖</v>
+        <v>L* 色調反轉</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Raw Output</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B57" t="str">
-        <v>原始输出</v>
+        <v>增加油墨不应使颜色变亮。逐一扫描每个设备通道并固定其他通道；凡 L* 上升的步骤都会被标记。该算法最初由 Harold Boll 提出。</v>
       </c>
       <c r="C57" t="str">
-        <v>原始輸出</v>
+        <v>增加油墨不應使顏色變亮。逐一掃描每個裝置通道並固定其他通道；凡 L* 上升的步驟都會被標記。此演算法最初由 Harold Boll 提出。</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>XML</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B58" t="str">
-        <v>XML</v>
+        <v>此配置文件没有设备→PCS 的 CLUT，因此 L* 反转扫描不适用（例如矩阵/TRC 显示器配置文件）。</v>
       </c>
       <c r="C58" t="str">
-        <v>XML</v>
+        <v>此設定檔沒有裝置→PCS 的 CLUT，因此 L* 反轉掃描不適用（例如矩陣/TRC 顯示器設定檔）。</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>JSON</v>
+        <v>LUT table</v>
       </c>
       <c r="B59" t="str">
-        <v>JSON</v>
+        <v>LUT 表</v>
       </c>
       <c r="C59" t="str">
-        <v>JSON</v>
+        <v>LUT 表</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B60" t="str">
-        <v>曲线</v>
+        <v>ΔL* 阈值 (ε)</v>
       </c>
       <c r="C60" t="str">
-        <v>曲線</v>
+        <v>ΔL* 閾值 (ε)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Input curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B61" t="str">
-        <v>输入曲线</v>
+        <v>超过 ε = {eps} 的反转：{n}</v>
       </c>
       <c r="C61" t="str">
-        <v>輸入曲線</v>
+        <v>超過 ε = {eps} 的反轉：{n}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Output curves</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B62" t="str">
-        <v>输出曲线</v>
+        <v>没有超过 ε = {eps} 的 L* 反转</v>
       </c>
       <c r="C62" t="str">
-        <v>輸出曲線</v>
+        <v>沒有超過 ε = {eps} 的 L* 反轉</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CLUT image</v>
+        <v>Channel</v>
       </c>
       <c r="B63" t="str">
-        <v>CLUT 图像</v>
+        <v>通道</v>
       </c>
       <c r="C63" t="str">
-        <v>CLUT 影像</v>
+        <v>通道</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Gamut image</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B64" t="str">
-        <v>色域图像</v>
+        <v>油墨（低 → 高）</v>
       </c>
       <c r="C64" t="str">
-        <v>色域影像</v>
+        <v>油墨（低 → 高）</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chromaticity</v>
+        <v>Plot</v>
       </c>
       <c r="B65" t="str">
-        <v>色度</v>
+        <v>绘图</v>
       </c>
       <c r="C65" t="str">
-        <v>色度</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Scatter plot</v>
+        <v>Raw Output</v>
       </c>
       <c r="B66" t="str">
-        <v>散点图</v>
+        <v>原始输出</v>
       </c>
       <c r="C66" t="str">
-        <v>散佈圖</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tone response curve</v>
+        <v>XML</v>
       </c>
       <c r="B67" t="str">
-        <v>色调响应曲线</v>
+        <v>XML</v>
       </c>
       <c r="C67" t="str">
-        <v>色調響應曲線</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curve table</v>
+        <v>JSON</v>
       </c>
       <c r="B68" t="str">
-        <v>曲线表</v>
+        <v>JSON</v>
       </c>
       <c r="C68" t="str">
-        <v>曲線表</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tables</v>
+        <v>Curves</v>
       </c>
       <c r="B69" t="str">
-        <v>表格</v>
+        <v>曲线</v>
       </c>
       <c r="C69" t="str">
-        <v>表格</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Data</v>
+        <v>Input curves</v>
       </c>
       <c r="B70" t="str">
-        <v>数据</v>
+        <v>输入曲线</v>
       </c>
       <c r="C70" t="str">
-        <v>資料</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Evaluate</v>
+        <v>Output curves</v>
       </c>
       <c r="B71" t="str">
-        <v>求值</v>
+        <v>输出曲线</v>
       </c>
       <c r="C71" t="str">
-        <v>求值</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B72" t="str">
-        <v>加载中…</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C72" t="str">
-        <v>載入中…</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Input</v>
+        <v>Gamut image</v>
       </c>
       <c r="B73" t="str">
-        <v>输入</v>
+        <v>色域图像</v>
       </c>
       <c r="C73" t="str">
-        <v>輸入</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Output</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B74" t="str">
-        <v>输出</v>
+        <v>色度</v>
       </c>
       <c r="C74" t="str">
-        <v>輸出</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Floating point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B75" t="str">
-        <v>浮点值</v>
+        <v>散点图</v>
       </c>
       <c r="C75" t="str">
-        <v>浮點值</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Grid point</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B76" t="str">
-        <v>网格点</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C76" t="str">
-        <v>網格點</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Normalized</v>
+        <v>Curve table</v>
       </c>
       <c r="B77" t="str">
-        <v>归一化</v>
+        <v>曲线表</v>
       </c>
       <c r="C77" t="str">
-        <v>正規化</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Human</v>
+        <v>Tables</v>
       </c>
       <c r="B78" t="str">
-        <v>可读值</v>
+        <v>表格</v>
       </c>
       <c r="C78" t="str">
-        <v>可讀值</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Device → PCS</v>
+        <v>Data</v>
       </c>
       <c r="B79" t="str">
-        <v>设备 → PCS</v>
+        <v>数据</v>
       </c>
       <c r="C79" t="str">
-        <v>裝置 → PCS</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PCS → Device</v>
+        <v>Evaluate</v>
       </c>
       <c r="B80" t="str">
-        <v>PCS → 设备</v>
+        <v>求值</v>
       </c>
       <c r="C80" t="str">
-        <v>PCS → 裝置</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>No CLUT grid</v>
+        <v>Loading…</v>
       </c>
       <c r="B81" t="str">
-        <v>无 CLUT 网格</v>
+        <v>加载中…</v>
       </c>
       <c r="C81" t="str">
-        <v>無 CLUT 網格</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Loading…</v>
+        <v>Input</v>
       </c>
       <c r="B82" t="str">
-        <v>加载中…</v>
+        <v>输入</v>
       </c>
       <c r="C82" t="str">
-        <v>載入中…</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Output</v>
       </c>
       <c r="B83" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>输出</v>
       </c>
       <c r="C83" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Floating point</v>
       </c>
       <c r="B84" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>浮点值</v>
       </c>
       <c r="C84" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Grid point</v>
       </c>
       <c r="B85" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>网格点</v>
       </c>
       <c r="C85" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Normalized</v>
       </c>
       <c r="B86" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>归一化</v>
       </c>
       <c r="C86" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Human</v>
       </c>
       <c r="B87" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>可读值</v>
       </c>
       <c r="C87" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B88" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C88" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B89" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C89" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Security</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B90" t="str">
-        <v>安全性</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C90" t="str">
-        <v>安全性</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Conformance</v>
+        <v>Loading…</v>
       </c>
       <c r="B91" t="str">
-        <v>符合性</v>
+        <v>加载中…</v>
       </c>
       <c r="C91" t="str">
-        <v>符合性</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Quality</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B92" t="str">
-        <v>质量</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C92" t="str">
-        <v>品質</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>REPORT</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B93" t="str">
-        <v>报告</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C93" t="str">
-        <v>報告</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FAIL</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B94" t="str">
-        <v>失败</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C94" t="str">
-        <v>失敗</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>checks</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B95" t="str">
-        <v>项检查</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C95" t="str">
-        <v>項檢查</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B96" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C96" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B97" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C97" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B98" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C98" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Powered by {lib}</v>
+        <v>Security</v>
       </c>
       <c r="B99" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>安全性</v>
       </c>
       <c r="C99" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Subscribe</v>
+        <v>Conformance</v>
       </c>
       <c r="B100" t="str">
-        <v>订阅</v>
+        <v>符合性</v>
       </c>
       <c r="C100" t="str">
-        <v>訂閱</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Quality</v>
       </c>
       <c r="B101" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>质量</v>
       </c>
       <c r="C101" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Get notified about new releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B102" t="str">
-        <v>订阅新版本通知</v>
+        <v>报告</v>
       </c>
       <c r="C102" t="str">
-        <v>訂閱新版本通知</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Close</v>
+        <v>FAIL</v>
       </c>
       <c r="B103" t="str">
-        <v>关闭</v>
+        <v>失败</v>
       </c>
       <c r="C103" t="str">
-        <v>關閉</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>checks</v>
       </c>
       <c r="B104" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>项检查</v>
       </c>
       <c r="C104" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Email address</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B105" t="str">
-        <v>电子邮件地址</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C105" t="str">
-        <v>電子郵件地址</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B106" t="str">
-        <v>you@example.com</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C106" t="str">
-        <v>you@example.com</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B107" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C107" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>(optional)</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B108" t="str">
-        <v>（选填）</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C108" t="str">
-        <v>（選填）</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B109" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>订阅</v>
       </c>
       <c r="C109" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B110" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C110" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B111" t="str">
-        <v>取消</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C111" t="str">
-        <v>取消</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B112" t="str">
-        <v>订阅</v>
+        <v>关闭</v>
       </c>
       <c r="C112" t="str">
-        <v>訂閱</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B113" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C113" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Email address</v>
       </c>
       <c r="B114" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C114" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B115" t="str">
-        <v>关闭</v>
+        <v>you@example.com</v>
       </c>
       <c r="C115" t="str">
-        <v>關閉</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Privacy notice</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B116" t="str">
-        <v>隐私声明</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C116" t="str">
-        <v>隱私聲明</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>(optional)</v>
       </c>
       <c r="B117" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>（选填）</v>
       </c>
       <c r="C117" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B118" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C118" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Please check the form and try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B119" t="str">
-        <v>请检查表单后重试。</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C119" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B120" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>取消</v>
       </c>
       <c r="C120" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B121" t="str">
-        <v>网络错误，请重试。</v>
+        <v>订阅</v>
       </c>
       <c r="C121" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Error:</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B122" t="str">
-        <v>错误：</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C122" t="str">
-        <v>錯誤：</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Convert to XML</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B123" t="str">
-        <v>转换为 XML</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C123" t="str">
-        <v>轉換為 XML</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Convert to JSON</v>
+        <v>Close</v>
       </c>
       <c r="B124" t="str">
-        <v>转换为 JSON</v>
+        <v>关闭</v>
       </c>
       <c r="C124" t="str">
-        <v>轉換為 JSON</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Convert to ICC</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B125" t="str">
-        <v>转换为 ICC</v>
+        <v>隐私声明</v>
       </c>
       <c r="C125" t="str">
-        <v>轉換為 ICC</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Converting to XML…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B126" t="str">
-        <v>正在转换为 XML…</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C126" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Converting to JSON…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B127" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C127" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C128" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Load ICC profile</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C129" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B130" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C130" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Profile ID</v>
+        <v>Error:</v>
       </c>
       <c r="B131" t="str">
-        <v>配置文件 ID</v>
+        <v>错误：</v>
       </c>
       <c r="C131" t="str">
-        <v>設定檔 ID</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>No tags found.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B132" t="str">
-        <v>未找到标签。</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C132" t="str">
-        <v>找不到標籤。</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Tag Name</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B133" t="str">
-        <v>标签名称</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C133" t="str">
-        <v>標籤名稱</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ID</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B134" t="str">
-        <v>ID</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C134" t="str">
-        <v>ID</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Offset</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B135" t="str">
-        <v>偏移</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C135" t="str">
-        <v>偏移</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Size</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B136" t="str">
-        <v>大小</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C136" t="str">
-        <v>大小</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pad</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B137" t="str">
-        <v>填充</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C137" t="str">
-        <v>填充</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Bytes changed since load</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B138" t="str">
-        <v>加载后字节已更改</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C138" t="str">
-        <v>載入後位元組已變更</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Type</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B139" t="str">
-        <v>类型</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C139" t="str">
-        <v>類型</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Array of {type}</v>
+        <v>Profile ID</v>
       </c>
       <c r="B140" t="str">
-        <v>{type} 数组</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C140" t="str">
-        <v>{type} 陣列</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(No content)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B141" t="str">
-        <v>（无内容）</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C141" t="str">
-        <v>（無內容）</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>bytes</v>
+        <v>Tag Name</v>
       </c>
       <c r="B142" t="str">
-        <v>字节</v>
+        <v>标签名称</v>
       </c>
       <c r="C142" t="str">
-        <v>位元組</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Loading full description…</v>
+        <v>ID</v>
       </c>
       <c r="B143" t="str">
-        <v>正在加载完整描述…</v>
+        <v>ID</v>
       </c>
       <c r="C143" t="str">
-        <v>正在載入完整描述…</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Could not load full description:</v>
+        <v>Offset</v>
       </c>
       <c r="B144" t="str">
-        <v>无法加载完整描述：</v>
+        <v>偏移</v>
       </c>
       <c r="C144" t="str">
-        <v>無法載入完整描述：</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Size</v>
       </c>
       <c r="B145" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>大小</v>
       </c>
       <c r="C145" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Pad</v>
       </c>
       <c r="B146" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>填充</v>
       </c>
       <c r="C146" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>No validation output</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B147" t="str">
-        <v>无验证输出</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C147" t="str">
-        <v>無驗證輸出</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Profile is valid</v>
+        <v>Type</v>
       </c>
       <c r="B148" t="str">
-        <v>配置文件有效</v>
+        <v>类型</v>
       </c>
       <c r="C148" t="str">
-        <v>設定檔有效</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B149" t="str">
-        <v>配置文件有警告</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C149" t="str">
-        <v>設定檔有警告</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile is non-compliant</v>
+        <v>(No content)</v>
       </c>
       <c r="B150" t="str">
-        <v>配置文件不合规</v>
+        <v>（无内容）</v>
       </c>
       <c r="C150" t="str">
-        <v>設定檔不符合規範</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Critical validation error</v>
+        <v>bytes</v>
       </c>
       <c r="B151" t="str">
-        <v>严重验证错误</v>
+        <v>字节</v>
       </c>
       <c r="C151" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Unknown validation status</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B152" t="str">
-        <v>未知验证状态</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C152" t="str">
-        <v>未知驗證狀態</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B153" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C153" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No warnings or errors found.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B154" t="str">
-        <v>未发现警告或错误。</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C154" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B155" t="str">
-        <v>有效</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C155" t="str">
-        <v>有效</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Warning</v>
+        <v>No validation output</v>
       </c>
       <c r="B156" t="str">
-        <v>警告</v>
+        <v>无验证输出</v>
       </c>
       <c r="C156" t="str">
-        <v>警告</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B157" t="str">
-        <v>错误</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C157" t="str">
-        <v>錯誤</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Unknown</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B158" t="str">
-        <v>未知</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C158" t="str">
-        <v>未知</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Pass</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B159" t="str">
-        <v>通过</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C159" t="str">
-        <v>通過</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B160" t="str">
-        <v>失败</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C160" t="str">
-        <v>失敗</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>View in context</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B161" t="str">
-        <v>在上下文中查看</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C161" t="str">
-        <v>在上下文中檢視</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Validation detail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B162" t="str">
-        <v>验证详情</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C162" t="str">
-        <v>驗證詳情</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Triggered by</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B163" t="str">
-        <v>触发字段</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C163" t="str">
-        <v>觸發欄位</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Field</v>
+        <v>Valid</v>
       </c>
       <c r="B164" t="str">
-        <v>字段</v>
+        <v>有效</v>
       </c>
       <c r="C164" t="str">
-        <v>欄位</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Current value</v>
+        <v>Warning</v>
       </c>
       <c r="B165" t="str">
-        <v>当前值</v>
+        <v>警告</v>
       </c>
       <c r="C165" t="str">
-        <v>目前值</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Required: 0</v>
+        <v>Error</v>
       </c>
       <c r="B166" t="str">
-        <v>要求：0</v>
+        <v>错误</v>
       </c>
       <c r="C166" t="str">
-        <v>要求：0</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Expected: {value}</v>
+        <v>Unknown</v>
       </c>
       <c r="B167" t="str">
-        <v>预期：{value}</v>
+        <v>未知</v>
       </c>
       <c r="C167" t="str">
-        <v>預期：{value}</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Invalid</v>
+        <v>Pass</v>
       </c>
       <c r="B168" t="str">
-        <v>无效</v>
+        <v>通过</v>
       </c>
       <c r="C168" t="str">
-        <v>無效</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Fail</v>
       </c>
       <c r="B169" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>失败</v>
       </c>
       <c r="C169" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>View in context</v>
       </c>
       <c r="B170" t="str">
-        <v>关闭</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C170" t="str">
-        <v>關閉</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Loading XML editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B171" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>验证详情</v>
       </c>
       <c r="C171" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B172" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>触发字段</v>
       </c>
       <c r="C172" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B173" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>字段</v>
       </c>
       <c r="C173" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B174" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>当前值</v>
       </c>
       <c r="C174" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B175" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>要求：0</v>
       </c>
       <c r="C175" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B176" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C176" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B177" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>无效</v>
       </c>
       <c r="C177" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B178" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C178" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>indent</v>
+        <v>Close</v>
       </c>
       <c r="B179" t="str">
-        <v>缩进</v>
+        <v>关闭</v>
       </c>
       <c r="C179" t="str">
-        <v>縮排</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>sort keys</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>排序键</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C180" t="str">
-        <v>排序鍵</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B181" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C181" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B182" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C182" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B183" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C183" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B184" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C184" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B185" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C185" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C186" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C187" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B188" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C188" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B189" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C189" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B181" t="str">
+      <c r="B190" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C181" t="str">
+      <c r="C190" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C190"/>
+  <dimension ref="A1:C200"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -945,453 +945,453 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B50" t="str">
-        <v>反转较多的通道仅显示按 ΔL* 排序最大的 {shown} 个。</v>
+        <v>绝对比色</v>
       </c>
       <c r="C50" t="str">
-        <v>反轉較多的通道僅顯示依 ΔL* 排序最大的 {shown} 個。</v>
+        <v>絕對比色</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Show more ({n})</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B51" t="str">
-        <v>显示更多（{n}）</v>
+        <v>特性文件统计</v>
       </c>
       <c r="C51" t="str">
-        <v>顯示更多（{n}）</v>
+        <v>特性檔統計</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>All</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B52" t="str">
-        <v>全部</v>
+        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
       </c>
       <c r="C52" t="str">
-        <v>全部</v>
+        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Analysing…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B53" t="str">
-        <v>正在分析…</v>
+        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
       </c>
       <c r="C53" t="str">
-        <v>正在分析…</v>
+        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B54" t="str">
-        <v>分析</v>
+        <v>渲染意图</v>
       </c>
       <c r="C54" t="str">
-        <v>分析</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B55" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>色域体积 (ΔE³)</v>
       </c>
       <c r="C55" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>色域體積 (ΔE³)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B56" t="str">
-        <v>L* 色调反转</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C56" t="str">
-        <v>L* 色調反轉</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>mean</v>
       </c>
       <c r="B57" t="str">
-        <v>增加油墨不应使颜色变亮。逐一扫描每个设备通道并固定其他通道；凡 L* 上升的步骤都会被标记。该算法最初由 Harold Boll 提出。</v>
+        <v>均值</v>
       </c>
       <c r="C57" t="str">
-        <v>增加油墨不應使顏色變亮。逐一掃描每個裝置通道並固定其他通道；凡 L* 上升的步驟都會被標記。此演算法最初由 Harold Boll 提出。</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>P90</v>
       </c>
       <c r="B58" t="str">
-        <v>此配置文件没有设备→PCS 的 CLUT，因此 L* 反转扫描不适用（例如矩阵/TRC 显示器配置文件）。</v>
+        <v>P90</v>
       </c>
       <c r="C58" t="str">
-        <v>此設定檔沒有裝置→PCS 的 CLUT，因此 L* 反轉掃描不適用（例如矩陣/TRC 顯示器設定檔）。</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>LUT table</v>
+        <v>max</v>
       </c>
       <c r="B59" t="str">
-        <v>LUT 表</v>
+        <v>最大</v>
       </c>
       <c r="C59" t="str">
-        <v>LUT 表</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B60" t="str">
-        <v>ΔL* 阈值 (ε)</v>
+        <v>反转较多的通道仅显示按 ΔL* 排序最大的 {shown} 个。</v>
       </c>
       <c r="C60" t="str">
-        <v>ΔL* 閾值 (ε)</v>
+        <v>反轉較多的通道僅顯示依 ΔL* 排序最大的 {shown} 個。</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B61" t="str">
-        <v>超过 ε = {eps} 的反转：{n}</v>
+        <v>显示更多（{n}）</v>
       </c>
       <c r="C61" t="str">
-        <v>超過 ε = {eps} 的反轉：{n}</v>
+        <v>顯示更多（{n}）</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B62" t="str">
-        <v>没有超过 ε = {eps} 的 L* 反转</v>
+        <v>全部</v>
       </c>
       <c r="C62" t="str">
-        <v>沒有超過 ε = {eps} 的 L* 反轉</v>
+        <v>全部</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Channel</v>
+        <v>Analysing…</v>
       </c>
       <c r="B63" t="str">
-        <v>通道</v>
+        <v>正在分析…</v>
       </c>
       <c r="C63" t="str">
-        <v>通道</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ink (low → high)</v>
+        <v>Analysis</v>
       </c>
       <c r="B64" t="str">
-        <v>油墨（低 → 高）</v>
+        <v>分析</v>
       </c>
       <c r="C64" t="str">
-        <v>油墨（低 → 高）</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B65" t="str">
-        <v>绘图</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C65" t="str">
-        <v>繪圖</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Raw Output</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B66" t="str">
-        <v>原始输出</v>
+        <v>L* 色调反转</v>
       </c>
       <c r="C66" t="str">
-        <v>原始輸出</v>
+        <v>L* 色調反轉</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>XML</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B67" t="str">
-        <v>XML</v>
+        <v>增加油墨不应使颜色变亮。逐一扫描每个设备通道并固定其他通道；凡 L* 上升的步骤都会被标记。该算法最初由 Harold Boll 提出。</v>
       </c>
       <c r="C67" t="str">
-        <v>XML</v>
+        <v>增加油墨不應使顏色變亮。逐一掃描每個裝置通道並固定其他通道；凡 L* 上升的步驟都會被標記。此演算法最初由 Harold Boll 提出。</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>JSON</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B68" t="str">
-        <v>JSON</v>
+        <v>此配置文件没有设备→PCS 的 CLUT，因此 L* 反转扫描不适用（例如矩阵/TRC 显示器配置文件）。</v>
       </c>
       <c r="C68" t="str">
-        <v>JSON</v>
+        <v>此設定檔沒有裝置→PCS 的 CLUT，因此 L* 反轉掃描不適用（例如矩陣/TRC 顯示器設定檔）。</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Curves</v>
+        <v>LUT table</v>
       </c>
       <c r="B69" t="str">
-        <v>曲线</v>
+        <v>LUT 表</v>
       </c>
       <c r="C69" t="str">
-        <v>曲線</v>
+        <v>LUT 表</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Input curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B70" t="str">
-        <v>输入曲线</v>
+        <v>ΔL* 阈值 (ε)</v>
       </c>
       <c r="C70" t="str">
-        <v>輸入曲線</v>
+        <v>ΔL* 閾值 (ε)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Output curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B71" t="str">
-        <v>输出曲线</v>
+        <v>超过 ε = {eps} 的反转：{n}</v>
       </c>
       <c r="C71" t="str">
-        <v>輸出曲線</v>
+        <v>超過 ε = {eps} 的反轉：{n}</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CLUT image</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B72" t="str">
-        <v>CLUT 图像</v>
+        <v>没有超过 ε = {eps} 的 L* 反转</v>
       </c>
       <c r="C72" t="str">
-        <v>CLUT 影像</v>
+        <v>沒有超過 ε = {eps} 的 L* 反轉</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut image</v>
+        <v>Channel</v>
       </c>
       <c r="B73" t="str">
-        <v>色域图像</v>
+        <v>通道</v>
       </c>
       <c r="C73" t="str">
-        <v>色域影像</v>
+        <v>通道</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Chromaticity</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B74" t="str">
-        <v>色度</v>
+        <v>油墨（低 → 高）</v>
       </c>
       <c r="C74" t="str">
-        <v>色度</v>
+        <v>油墨（低 → 高）</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Scatter plot</v>
+        <v>Plot</v>
       </c>
       <c r="B75" t="str">
-        <v>散点图</v>
+        <v>绘图</v>
       </c>
       <c r="C75" t="str">
-        <v>散佈圖</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tone response curve</v>
+        <v>Raw Output</v>
       </c>
       <c r="B76" t="str">
-        <v>色调响应曲线</v>
+        <v>原始输出</v>
       </c>
       <c r="C76" t="str">
-        <v>色調響應曲線</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Curve table</v>
+        <v>XML</v>
       </c>
       <c r="B77" t="str">
-        <v>曲线表</v>
+        <v>XML</v>
       </c>
       <c r="C77" t="str">
-        <v>曲線表</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tables</v>
+        <v>JSON</v>
       </c>
       <c r="B78" t="str">
-        <v>表格</v>
+        <v>JSON</v>
       </c>
       <c r="C78" t="str">
-        <v>表格</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Data</v>
+        <v>Curves</v>
       </c>
       <c r="B79" t="str">
-        <v>数据</v>
+        <v>曲线</v>
       </c>
       <c r="C79" t="str">
-        <v>資料</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Evaluate</v>
+        <v>Input curves</v>
       </c>
       <c r="B80" t="str">
-        <v>求值</v>
+        <v>输入曲线</v>
       </c>
       <c r="C80" t="str">
-        <v>求值</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Loading…</v>
+        <v>Output curves</v>
       </c>
       <c r="B81" t="str">
-        <v>加载中…</v>
+        <v>输出曲线</v>
       </c>
       <c r="C81" t="str">
-        <v>載入中…</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Input</v>
+        <v>CLUT image</v>
       </c>
       <c r="B82" t="str">
-        <v>输入</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C82" t="str">
-        <v>輸入</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B83" t="str">
-        <v>输出</v>
+        <v>色域图像</v>
       </c>
       <c r="C83" t="str">
-        <v>輸出</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Floating point</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B84" t="str">
-        <v>浮点值</v>
+        <v>色度</v>
       </c>
       <c r="C84" t="str">
-        <v>浮點值</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Grid point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B85" t="str">
-        <v>网格点</v>
+        <v>散点图</v>
       </c>
       <c r="C85" t="str">
-        <v>網格點</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Normalized</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B86" t="str">
-        <v>归一化</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C86" t="str">
-        <v>正規化</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Human</v>
+        <v>Curve table</v>
       </c>
       <c r="B87" t="str">
-        <v>可读值</v>
+        <v>曲线表</v>
       </c>
       <c r="C87" t="str">
-        <v>可讀值</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Device → PCS</v>
+        <v>Tables</v>
       </c>
       <c r="B88" t="str">
-        <v>设备 → PCS</v>
+        <v>表格</v>
       </c>
       <c r="C88" t="str">
-        <v>裝置 → PCS</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PCS → Device</v>
+        <v>Data</v>
       </c>
       <c r="B89" t="str">
-        <v>PCS → 设备</v>
+        <v>数据</v>
       </c>
       <c r="C89" t="str">
-        <v>PCS → 裝置</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>No CLUT grid</v>
+        <v>Evaluate</v>
       </c>
       <c r="B90" t="str">
-        <v>无 CLUT 网格</v>
+        <v>求值</v>
       </c>
       <c r="C90" t="str">
-        <v>無 CLUT 網格</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="91">
@@ -1407,1096 +1407,1206 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Input</v>
       </c>
       <c r="B92" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>输入</v>
       </c>
       <c r="C92" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Output</v>
       </c>
       <c r="B93" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>输出</v>
       </c>
       <c r="C93" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Floating point</v>
       </c>
       <c r="B94" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>浮点值</v>
       </c>
       <c r="C94" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Grid point</v>
       </c>
       <c r="B95" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>网格点</v>
       </c>
       <c r="C95" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Normalized</v>
       </c>
       <c r="B96" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>归一化</v>
       </c>
       <c r="C96" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Human</v>
       </c>
       <c r="B97" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>可读值</v>
       </c>
       <c r="C97" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B98" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C98" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Security</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B99" t="str">
-        <v>安全性</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C99" t="str">
-        <v>安全性</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Conformance</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B100" t="str">
-        <v>符合性</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C100" t="str">
-        <v>符合性</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Quality</v>
+        <v>Loading…</v>
       </c>
       <c r="B101" t="str">
-        <v>质量</v>
+        <v>加载中…</v>
       </c>
       <c r="C101" t="str">
-        <v>品質</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>REPORT</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B102" t="str">
-        <v>报告</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C102" t="str">
-        <v>報告</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>FAIL</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B103" t="str">
-        <v>失败</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C103" t="str">
-        <v>失敗</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>checks</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B104" t="str">
-        <v>项检查</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C104" t="str">
-        <v>項檢查</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B105" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C105" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B106" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C106" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B107" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C107" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Powered by {lib}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B108" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C108" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Subscribe</v>
+        <v>Security</v>
       </c>
       <c r="B109" t="str">
-        <v>订阅</v>
+        <v>安全性</v>
       </c>
       <c r="C109" t="str">
-        <v>訂閱</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Conformance</v>
       </c>
       <c r="B110" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>符合性</v>
       </c>
       <c r="C110" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Get notified about new releases</v>
+        <v>Quality</v>
       </c>
       <c r="B111" t="str">
-        <v>订阅新版本通知</v>
+        <v>质量</v>
       </c>
       <c r="C111" t="str">
-        <v>訂閱新版本通知</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B112" t="str">
-        <v>关闭</v>
+        <v>报告</v>
       </c>
       <c r="C112" t="str">
-        <v>關閉</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B113" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>失败</v>
       </c>
       <c r="C113" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B114" t="str">
-        <v>电子邮件地址</v>
+        <v>项检查</v>
       </c>
       <c r="C114" t="str">
-        <v>電子郵件地址</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B115" t="str">
-        <v>you@example.com</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C115" t="str">
-        <v>you@example.com</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B116" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C116" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B117" t="str">
-        <v>（选填）</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C117" t="str">
-        <v>（選填）</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B118" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C118" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B119" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>订阅</v>
       </c>
       <c r="C119" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B120" t="str">
-        <v>取消</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C120" t="str">
-        <v>取消</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B121" t="str">
-        <v>订阅</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C121" t="str">
-        <v>訂閱</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B122" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>关闭</v>
       </c>
       <c r="C122" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B123" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C123" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B124" t="str">
-        <v>关闭</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C124" t="str">
-        <v>關閉</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B125" t="str">
-        <v>隐私声明</v>
+        <v>you@example.com</v>
       </c>
       <c r="C125" t="str">
-        <v>隱私聲明</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B126" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C126" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B127" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>（选填）</v>
       </c>
       <c r="C127" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B128" t="str">
-        <v>请检查表单后重试。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C128" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B129" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C129" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B130" t="str">
-        <v>网络错误，请重试。</v>
+        <v>取消</v>
       </c>
       <c r="C130" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B131" t="str">
-        <v>错误：</v>
+        <v>订阅</v>
       </c>
       <c r="C131" t="str">
-        <v>錯誤：</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B132" t="str">
-        <v>转换为 XML</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C132" t="str">
-        <v>轉換為 XML</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B133" t="str">
-        <v>转换为 JSON</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C133" t="str">
-        <v>轉換為 JSON</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B134" t="str">
-        <v>转换为 ICC</v>
+        <v>关闭</v>
       </c>
       <c r="C134" t="str">
-        <v>轉換為 ICC</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B135" t="str">
-        <v>正在转换为 XML…</v>
+        <v>隐私声明</v>
       </c>
       <c r="C135" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B136" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C136" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B137" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C137" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B138" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C138" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B139" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C139" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B140" t="str">
-        <v>配置文件 ID</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C140" t="str">
-        <v>設定檔 ID</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B141" t="str">
-        <v>未找到标签。</v>
+        <v>错误：</v>
       </c>
       <c r="C141" t="str">
-        <v>找不到標籤。</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B142" t="str">
-        <v>标签名称</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C142" t="str">
-        <v>標籤名稱</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B143" t="str">
-        <v>ID</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C143" t="str">
-        <v>ID</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B144" t="str">
-        <v>偏移</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C144" t="str">
-        <v>偏移</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B145" t="str">
-        <v>大小</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C145" t="str">
-        <v>大小</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B146" t="str">
-        <v>填充</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C146" t="str">
-        <v>填充</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B147" t="str">
-        <v>加载后字节已更改</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C147" t="str">
-        <v>載入後位元組已變更</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B148" t="str">
-        <v>类型</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C148" t="str">
-        <v>類型</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B149" t="str">
-        <v>{type} 数组</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C149" t="str">
-        <v>{type} 陣列</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B150" t="str">
-        <v>（无内容）</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C150" t="str">
-        <v>（無內容）</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B151" t="str">
-        <v>字节</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C151" t="str">
-        <v>位元組</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B152" t="str">
-        <v>正在加载完整描述…</v>
+        <v>标签名称</v>
       </c>
       <c r="C152" t="str">
-        <v>正在載入完整描述…</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B153" t="str">
-        <v>无法加载完整描述：</v>
+        <v>ID</v>
       </c>
       <c r="C153" t="str">
-        <v>無法載入完整描述：</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B154" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>偏移</v>
       </c>
       <c r="C154" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B155" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>大小</v>
       </c>
       <c r="C155" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B156" t="str">
-        <v>无验证输出</v>
+        <v>填充</v>
       </c>
       <c r="C156" t="str">
-        <v>無驗證輸出</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B157" t="str">
-        <v>配置文件有效</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C157" t="str">
-        <v>設定檔有效</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B158" t="str">
-        <v>配置文件有警告</v>
+        <v>类型</v>
       </c>
       <c r="C158" t="str">
-        <v>設定檔有警告</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B159" t="str">
-        <v>配置文件不合规</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C159" t="str">
-        <v>設定檔不符合規範</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B160" t="str">
-        <v>严重验证错误</v>
+        <v>（无内容）</v>
       </c>
       <c r="C160" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B161" t="str">
-        <v>未知验证状态</v>
+        <v>字节</v>
       </c>
       <c r="C161" t="str">
-        <v>未知驗證狀態</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B162" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C162" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B163" t="str">
-        <v>未发现警告或错误。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C163" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B164" t="str">
-        <v>有效</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C164" t="str">
-        <v>有效</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B165" t="str">
-        <v>警告</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C165" t="str">
-        <v>警告</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B166" t="str">
-        <v>错误</v>
+        <v>无验证输出</v>
       </c>
       <c r="C166" t="str">
-        <v>錯誤</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B167" t="str">
-        <v>未知</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C167" t="str">
-        <v>未知</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B168" t="str">
-        <v>通过</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C168" t="str">
-        <v>通過</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B169" t="str">
-        <v>失败</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C169" t="str">
-        <v>失敗</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B170" t="str">
-        <v>在上下文中查看</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C170" t="str">
-        <v>在上下文中檢視</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B171" t="str">
-        <v>验证详情</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C171" t="str">
-        <v>驗證詳情</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B172" t="str">
-        <v>触发字段</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C172" t="str">
-        <v>觸發欄位</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B173" t="str">
-        <v>字段</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C173" t="str">
-        <v>欄位</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B174" t="str">
-        <v>当前值</v>
+        <v>有效</v>
       </c>
       <c r="C174" t="str">
-        <v>目前值</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B175" t="str">
-        <v>要求：0</v>
+        <v>警告</v>
       </c>
       <c r="C175" t="str">
-        <v>要求：0</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B176" t="str">
-        <v>预期：{value}</v>
+        <v>错误</v>
       </c>
       <c r="C176" t="str">
-        <v>預期：{value}</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B177" t="str">
-        <v>无效</v>
+        <v>未知</v>
       </c>
       <c r="C177" t="str">
-        <v>無效</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B178" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>通过</v>
       </c>
       <c r="C178" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B179" t="str">
-        <v>关闭</v>
+        <v>失败</v>
       </c>
       <c r="C179" t="str">
-        <v>關閉</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B180" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C180" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B181" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>验证详情</v>
       </c>
       <c r="C181" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B182" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>触发字段</v>
       </c>
       <c r="C182" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B183" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>字段</v>
       </c>
       <c r="C183" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B184" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>当前值</v>
       </c>
       <c r="C184" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B185" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>要求：0</v>
       </c>
       <c r="C185" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B186" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C186" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B187" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>无效</v>
       </c>
       <c r="C187" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B188" t="str">
-        <v>缩进</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C188" t="str">
-        <v>縮排</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B189" t="str">
-        <v>排序键</v>
+        <v>关闭</v>
       </c>
       <c r="C189" t="str">
-        <v>排序鍵</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B190" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C190" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B191" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C191" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B192" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C192" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B193" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C193" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B194" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C194" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B195" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C195" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B196" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C196" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B197" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C197" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B198" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C198" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B199" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C199" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B190" t="str">
+      <c r="B200" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C190" t="str">
+      <c r="C200" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C200"/>
+  <dimension ref="A1:C188"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1055,651 +1055,651 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Analysing…</v>
       </c>
       <c r="B60" t="str">
-        <v>反转较多的通道仅显示按 ΔL* 排序最大的 {shown} 个。</v>
+        <v>正在分析…</v>
       </c>
       <c r="C60" t="str">
-        <v>反轉較多的通道僅顯示依 ΔL* 排序最大的 {shown} 個。</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Show more ({n})</v>
+        <v>Analysis</v>
       </c>
       <c r="B61" t="str">
-        <v>显示更多（{n}）</v>
+        <v>分析</v>
       </c>
       <c r="C61" t="str">
-        <v>顯示更多（{n}）</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>All</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B62" t="str">
-        <v>全部</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C62" t="str">
-        <v>全部</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B63" t="str">
-        <v>正在分析…</v>
+        <v>绘图</v>
       </c>
       <c r="C63" t="str">
-        <v>正在分析…</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B64" t="str">
-        <v>分析</v>
+        <v>原始输出</v>
       </c>
       <c r="C64" t="str">
-        <v>分析</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B65" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>XML</v>
       </c>
       <c r="C65" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>L* Tone Reversal</v>
+        <v>JSON</v>
       </c>
       <c r="B66" t="str">
-        <v>L* 色调反转</v>
+        <v>JSON</v>
       </c>
       <c r="C66" t="str">
-        <v>L* 色調反轉</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Curves</v>
       </c>
       <c r="B67" t="str">
-        <v>增加油墨不应使颜色变亮。逐一扫描每个设备通道并固定其他通道；凡 L* 上升的步骤都会被标记。该算法最初由 Harold Boll 提出。</v>
+        <v>曲线</v>
       </c>
       <c r="C67" t="str">
-        <v>增加油墨不應使顏色變亮。逐一掃描每個裝置通道並固定其他通道；凡 L* 上升的步驟都會被標記。此演算法最初由 Harold Boll 提出。</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Input curves</v>
       </c>
       <c r="B68" t="str">
-        <v>此配置文件没有设备→PCS 的 CLUT，因此 L* 反转扫描不适用（例如矩阵/TRC 显示器配置文件）。</v>
+        <v>输入曲线</v>
       </c>
       <c r="C68" t="str">
-        <v>此設定檔沒有裝置→PCS 的 CLUT，因此 L* 反轉掃描不適用（例如矩陣/TRC 顯示器設定檔）。</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>LUT table</v>
+        <v>Output curves</v>
       </c>
       <c r="B69" t="str">
-        <v>LUT 表</v>
+        <v>输出曲线</v>
       </c>
       <c r="C69" t="str">
-        <v>LUT 表</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>CLUT image</v>
       </c>
       <c r="B70" t="str">
-        <v>ΔL* 阈值 (ε)</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C70" t="str">
-        <v>ΔL* 閾值 (ε)</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Gamut image</v>
       </c>
       <c r="B71" t="str">
-        <v>超过 ε = {eps} 的反转：{n}</v>
+        <v>色域图像</v>
       </c>
       <c r="C71" t="str">
-        <v>超過 ε = {eps} 的反轉：{n}</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B72" t="str">
-        <v>没有超过 ε = {eps} 的 L* 反转</v>
+        <v>色度</v>
       </c>
       <c r="C72" t="str">
-        <v>沒有超過 ε = {eps} 的 L* 反轉</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Channel</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B73" t="str">
-        <v>通道</v>
+        <v>散点图</v>
       </c>
       <c r="C73" t="str">
-        <v>通道</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ink (low → high)</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B74" t="str">
-        <v>油墨（低 → 高）</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C74" t="str">
-        <v>油墨（低 → 高）</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Plot</v>
+        <v>Curve table</v>
       </c>
       <c r="B75" t="str">
-        <v>绘图</v>
+        <v>曲线表</v>
       </c>
       <c r="C75" t="str">
-        <v>繪圖</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Raw Output</v>
+        <v>Tables</v>
       </c>
       <c r="B76" t="str">
-        <v>原始输出</v>
+        <v>表格</v>
       </c>
       <c r="C76" t="str">
-        <v>原始輸出</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>XML</v>
+        <v>Data</v>
       </c>
       <c r="B77" t="str">
-        <v>XML</v>
+        <v>数据</v>
       </c>
       <c r="C77" t="str">
-        <v>XML</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>JSON</v>
+        <v>Evaluate</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON</v>
+        <v>求值</v>
       </c>
       <c r="C78" t="str">
-        <v>JSON</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Curves</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>曲线</v>
+        <v>加载中…</v>
       </c>
       <c r="C79" t="str">
-        <v>曲線</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input curves</v>
+        <v>Input</v>
       </c>
       <c r="B80" t="str">
-        <v>输入曲线</v>
+        <v>输入</v>
       </c>
       <c r="C80" t="str">
-        <v>輸入曲線</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output curves</v>
+        <v>Output</v>
       </c>
       <c r="B81" t="str">
-        <v>输出曲线</v>
+        <v>输出</v>
       </c>
       <c r="C81" t="str">
-        <v>輸出曲線</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CLUT image</v>
+        <v>Floating point</v>
       </c>
       <c r="B82" t="str">
-        <v>CLUT 图像</v>
+        <v>浮点值</v>
       </c>
       <c r="C82" t="str">
-        <v>CLUT 影像</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Gamut image</v>
+        <v>Grid point</v>
       </c>
       <c r="B83" t="str">
-        <v>色域图像</v>
+        <v>网格点</v>
       </c>
       <c r="C83" t="str">
-        <v>色域影像</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chromaticity</v>
+        <v>Normalized</v>
       </c>
       <c r="B84" t="str">
-        <v>色度</v>
+        <v>归一化</v>
       </c>
       <c r="C84" t="str">
-        <v>色度</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Scatter plot</v>
+        <v>Human</v>
       </c>
       <c r="B85" t="str">
-        <v>散点图</v>
+        <v>可读值</v>
       </c>
       <c r="C85" t="str">
-        <v>散佈圖</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tone response curve</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B86" t="str">
-        <v>色调响应曲线</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C86" t="str">
-        <v>色調響應曲線</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Curve table</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B87" t="str">
-        <v>曲线表</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C87" t="str">
-        <v>曲線表</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Tables</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B88" t="str">
-        <v>表格</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C88" t="str">
-        <v>表格</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Data</v>
+        <v>Loading…</v>
       </c>
       <c r="B89" t="str">
-        <v>数据</v>
+        <v>加载中…</v>
       </c>
       <c r="C89" t="str">
-        <v>資料</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Evaluate</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B90" t="str">
-        <v>求值</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C90" t="str">
-        <v>求值</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B91" t="str">
-        <v>加载中…</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C91" t="str">
-        <v>載入中…</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Input</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B92" t="str">
-        <v>输入</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C92" t="str">
-        <v>輸入</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Output</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B93" t="str">
-        <v>输出</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C93" t="str">
-        <v>輸出</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Floating point</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B94" t="str">
-        <v>浮点值</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C94" t="str">
-        <v>浮點值</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grid point</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B95" t="str">
-        <v>网格点</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C95" t="str">
-        <v>網格點</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Normalized</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B96" t="str">
-        <v>归一化</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C96" t="str">
-        <v>正規化</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Human</v>
+        <v>Security</v>
       </c>
       <c r="B97" t="str">
-        <v>可读值</v>
+        <v>安全性</v>
       </c>
       <c r="C97" t="str">
-        <v>可讀值</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Device → PCS</v>
+        <v>Conformance</v>
       </c>
       <c r="B98" t="str">
-        <v>设备 → PCS</v>
+        <v>符合性</v>
       </c>
       <c r="C98" t="str">
-        <v>裝置 → PCS</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PCS → Device</v>
+        <v>Quality</v>
       </c>
       <c r="B99" t="str">
-        <v>PCS → 设备</v>
+        <v>质量</v>
       </c>
       <c r="C99" t="str">
-        <v>PCS → 裝置</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No CLUT grid</v>
+        <v>REPORT</v>
       </c>
       <c r="B100" t="str">
-        <v>无 CLUT 网格</v>
+        <v>报告</v>
       </c>
       <c r="C100" t="str">
-        <v>無 CLUT 網格</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Loading…</v>
+        <v>FAIL</v>
       </c>
       <c r="B101" t="str">
-        <v>加载中…</v>
+        <v>失败</v>
       </c>
       <c r="C101" t="str">
-        <v>載入中…</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>checks</v>
       </c>
       <c r="B102" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>项检查</v>
       </c>
       <c r="C102" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B103" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C103" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B104" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C104" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B105" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C105" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B106" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C106" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Subscribe</v>
       </c>
       <c r="B107" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>订阅</v>
       </c>
       <c r="C107" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B108" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C108" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Security</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B109" t="str">
-        <v>安全性</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C109" t="str">
-        <v>安全性</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Conformance</v>
+        <v>Close</v>
       </c>
       <c r="B110" t="str">
-        <v>符合性</v>
+        <v>关闭</v>
       </c>
       <c r="C110" t="str">
-        <v>符合性</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Quality</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B111" t="str">
-        <v>质量</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C111" t="str">
-        <v>品質</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>REPORT</v>
+        <v>Email address</v>
       </c>
       <c r="B112" t="str">
-        <v>报告</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C112" t="str">
-        <v>報告</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>FAIL</v>
+        <v>you@example.com</v>
       </c>
       <c r="B113" t="str">
-        <v>失败</v>
+        <v>you@example.com</v>
       </c>
       <c r="C113" t="str">
-        <v>失敗</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>checks</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B114" t="str">
-        <v>项检查</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C114" t="str">
-        <v>項檢查</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>(optional)</v>
       </c>
       <c r="B115" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>（选填）</v>
       </c>
       <c r="C115" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B116" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C116" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ICC Profile Tool</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B117" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C117" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Powered by {lib}</v>
+        <v>Cancel</v>
       </c>
       <c r="B118" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>取消</v>
       </c>
       <c r="C118" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="119">
@@ -1715,24 +1715,24 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B120" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C120" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Get notified about new releases</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B121" t="str">
-        <v>订阅新版本通知</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C121" t="str">
-        <v>訂閱新版本通知</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="122">
@@ -1748,865 +1748,733 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B123" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C123" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Email address</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B124" t="str">
-        <v>电子邮件地址</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C124" t="str">
-        <v>電子郵件地址</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>you@example.com</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B125" t="str">
-        <v>you@example.com</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C125" t="str">
-        <v>you@example.com</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B126" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C126" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>(optional)</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>（选填）</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C127" t="str">
-        <v>（選填）</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C128" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Error:</v>
       </c>
       <c r="B129" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>错误：</v>
       </c>
       <c r="C129" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Cancel</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B130" t="str">
-        <v>取消</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C130" t="str">
-        <v>取消</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Subscribe</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B131" t="str">
-        <v>订阅</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C131" t="str">
-        <v>訂閱</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B132" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C132" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B133" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C133" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Close</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B134" t="str">
-        <v>关闭</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C134" t="str">
-        <v>關閉</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Privacy notice</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B135" t="str">
-        <v>隐私声明</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C135" t="str">
-        <v>隱私聲明</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B136" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C136" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B137" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C137" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B138" t="str">
-        <v>请检查表单后重试。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C138" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B139" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C139" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B140" t="str">
-        <v>网络错误，请重试。</v>
+        <v>标签名称</v>
       </c>
       <c r="C140" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Error:</v>
+        <v>ID</v>
       </c>
       <c r="B141" t="str">
-        <v>错误：</v>
+        <v>ID</v>
       </c>
       <c r="C141" t="str">
-        <v>錯誤：</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Convert to XML</v>
+        <v>Offset</v>
       </c>
       <c r="B142" t="str">
-        <v>转换为 XML</v>
+        <v>偏移</v>
       </c>
       <c r="C142" t="str">
-        <v>轉換為 XML</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Convert to JSON</v>
+        <v>Size</v>
       </c>
       <c r="B143" t="str">
-        <v>转换为 JSON</v>
+        <v>大小</v>
       </c>
       <c r="C143" t="str">
-        <v>轉換為 JSON</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Convert to ICC</v>
+        <v>Pad</v>
       </c>
       <c r="B144" t="str">
-        <v>转换为 ICC</v>
+        <v>填充</v>
       </c>
       <c r="C144" t="str">
-        <v>轉換為 ICC</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Converting to XML…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B145" t="str">
-        <v>正在转换为 XML…</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C145" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Converting to JSON…</v>
+        <v>Type</v>
       </c>
       <c r="B146" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>类型</v>
       </c>
       <c r="C146" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Converting to ICC…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B147" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C147" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Load ICC profile</v>
+        <v>(No content)</v>
       </c>
       <c r="B148" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>（无内容）</v>
       </c>
       <c r="C148" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>bytes</v>
       </c>
       <c r="B149" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>字节</v>
       </c>
       <c r="C149" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile ID</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B150" t="str">
-        <v>配置文件 ID</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C150" t="str">
-        <v>設定檔 ID</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>No tags found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B151" t="str">
-        <v>未找到标签。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C151" t="str">
-        <v>找不到標籤。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tag Name</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B152" t="str">
-        <v>标签名称</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C152" t="str">
-        <v>標籤名稱</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ID</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B153" t="str">
-        <v>ID</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C153" t="str">
-        <v>ID</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Offset</v>
+        <v>No validation output</v>
       </c>
       <c r="B154" t="str">
-        <v>偏移</v>
+        <v>无验证输出</v>
       </c>
       <c r="C154" t="str">
-        <v>偏移</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Size</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B155" t="str">
-        <v>大小</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C155" t="str">
-        <v>大小</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Pad</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B156" t="str">
-        <v>填充</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C156" t="str">
-        <v>填充</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B157" t="str">
-        <v>加载后字节已更改</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C157" t="str">
-        <v>載入後位元組已變更</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Type</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B158" t="str">
-        <v>类型</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C158" t="str">
-        <v>類型</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Array of {type}</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B159" t="str">
-        <v>{type} 数组</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C159" t="str">
-        <v>{type} 陣列</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>(No content)</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B160" t="str">
-        <v>（无内容）</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C160" t="str">
-        <v>（無內容）</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>bytes</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B161" t="str">
-        <v>字节</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C161" t="str">
-        <v>位元組</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Loading full description…</v>
+        <v>Valid</v>
       </c>
       <c r="B162" t="str">
-        <v>正在加载完整描述…</v>
+        <v>有效</v>
       </c>
       <c r="C162" t="str">
-        <v>正在載入完整描述…</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Could not load full description:</v>
+        <v>Warning</v>
       </c>
       <c r="B163" t="str">
-        <v>无法加载完整描述：</v>
+        <v>警告</v>
       </c>
       <c r="C163" t="str">
-        <v>無法載入完整描述：</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error</v>
       </c>
       <c r="B164" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>错误</v>
       </c>
       <c r="C164" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Unknown</v>
       </c>
       <c r="B165" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>未知</v>
       </c>
       <c r="C165" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>No validation output</v>
+        <v>Pass</v>
       </c>
       <c r="B166" t="str">
-        <v>无验证输出</v>
+        <v>通过</v>
       </c>
       <c r="C166" t="str">
-        <v>無驗證輸出</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Profile is valid</v>
+        <v>Fail</v>
       </c>
       <c r="B167" t="str">
-        <v>配置文件有效</v>
+        <v>失败</v>
       </c>
       <c r="C167" t="str">
-        <v>設定檔有效</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Profile has warning(s)</v>
+        <v>View in context</v>
       </c>
       <c r="B168" t="str">
-        <v>配置文件有警告</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C168" t="str">
-        <v>設定檔有警告</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Validation detail</v>
       </c>
       <c r="B169" t="str">
-        <v>配置文件不合规</v>
+        <v>验证详情</v>
       </c>
       <c r="C169" t="str">
-        <v>設定檔不符合規範</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Critical validation error</v>
+        <v>Triggered by</v>
       </c>
       <c r="B170" t="str">
-        <v>严重验证错误</v>
+        <v>触发字段</v>
       </c>
       <c r="C170" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Unknown validation status</v>
+        <v>Field</v>
       </c>
       <c r="B171" t="str">
-        <v>未知验证状态</v>
+        <v>字段</v>
       </c>
       <c r="C171" t="str">
-        <v>未知驗證狀態</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Current value</v>
       </c>
       <c r="B172" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>当前值</v>
       </c>
       <c r="C172" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B173" t="str">
-        <v>未发现警告或错误。</v>
+        <v>要求：0</v>
       </c>
       <c r="C173" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Valid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B174" t="str">
-        <v>有效</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C174" t="str">
-        <v>有效</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Warning</v>
+        <v>Invalid</v>
       </c>
       <c r="B175" t="str">
-        <v>警告</v>
+        <v>无效</v>
       </c>
       <c r="C175" t="str">
-        <v>警告</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Error</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B176" t="str">
-        <v>错误</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C176" t="str">
-        <v>錯誤</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Unknown</v>
+        <v>Close</v>
       </c>
       <c r="B177" t="str">
-        <v>未知</v>
+        <v>关闭</v>
       </c>
       <c r="C177" t="str">
-        <v>未知</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Pass</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B178" t="str">
-        <v>通过</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C178" t="str">
-        <v>通過</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Fail</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>失败</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C179" t="str">
-        <v>失敗</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>View in context</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B180" t="str">
-        <v>在上下文中查看</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C180" t="str">
-        <v>在上下文中檢視</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Validation detail</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>验证详情</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C181" t="str">
-        <v>驗證詳情</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Triggered by</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B182" t="str">
-        <v>触发字段</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C182" t="str">
-        <v>觸發欄位</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Field</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B183" t="str">
-        <v>字段</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C183" t="str">
-        <v>欄位</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Current value</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B184" t="str">
-        <v>当前值</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C184" t="str">
-        <v>目前值</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Required: 0</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>要求：0</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C185" t="str">
-        <v>要求：0</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Expected: {value}</v>
+        <v>indent</v>
       </c>
       <c r="B186" t="str">
-        <v>预期：{value}</v>
+        <v>缩进</v>
       </c>
       <c r="C186" t="str">
-        <v>預期：{value}</v>
+        <v>縮排</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Invalid</v>
+        <v>sort keys</v>
       </c>
       <c r="B187" t="str">
-        <v>无效</v>
+        <v>排序键</v>
       </c>
       <c r="C187" t="str">
-        <v>無效</v>
+        <v>排序鍵</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B188" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
       <c r="C188" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Close</v>
-      </c>
-      <c r="B189" t="str">
-        <v>关闭</v>
-      </c>
-      <c r="C189" t="str">
-        <v>關閉</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Loading XML editor…</v>
-      </c>
-      <c r="B190" t="str">
-        <v>正在加载 XML 编辑器…</v>
-      </c>
-      <c r="C190" t="str">
-        <v>正在載入 XML 編輯器…</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Loading JSON editor…</v>
-      </c>
-      <c r="B191" t="str">
-        <v>正在加载 JSON 编辑器…</v>
-      </c>
-      <c r="C191" t="str">
-        <v>正在載入 JSON 編輯器…</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B192" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
-      </c>
-      <c r="C192" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B193" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
-      </c>
-      <c r="C193" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>● unsaved XML edits</v>
-      </c>
-      <c r="B194" t="str">
-        <v>● 未保存的 XML 修改</v>
-      </c>
-      <c r="C194" t="str">
-        <v>● 未儲存的 XML 修改</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>● unsaved JSON edits</v>
-      </c>
-      <c r="B195" t="str">
-        <v>● 未保存的 JSON 修改</v>
-      </c>
-      <c r="C195" t="str">
-        <v>● 未儲存的 JSON 修改</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B196" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
-      </c>
-      <c r="C196" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B197" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
-      </c>
-      <c r="C197" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B198" t="str">
-        <v>缩进</v>
-      </c>
-      <c r="C198" t="str">
-        <v>縮排</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B199" t="str">
-        <v>排序键</v>
-      </c>
-      <c r="C199" t="str">
-        <v>排序鍵</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B200" t="str">
-        <v>已从编辑写入配置文件，但重新验证失败：</v>
-      </c>
-      <c r="C200" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C188"/>
+  <dimension ref="A1:C189"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1022,1459 +1022,1470 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B57" t="str">
-        <v>均值</v>
+        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
       </c>
       <c r="C57" t="str">
-        <v>平均</v>
+        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B58" t="str">
-        <v>P90</v>
+        <v>均值</v>
       </c>
       <c r="C58" t="str">
-        <v>P90</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B59" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
       <c r="C59" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B60" t="str">
-        <v>正在分析…</v>
+        <v>最大</v>
       </c>
       <c r="C60" t="str">
-        <v>正在分析…</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B61" t="str">
-        <v>分析</v>
+        <v>正在分析…</v>
       </c>
       <c r="C61" t="str">
-        <v>分析</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B62" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>分析</v>
       </c>
       <c r="C62" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B63" t="str">
-        <v>绘图</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C63" t="str">
-        <v>繪圖</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B64" t="str">
-        <v>原始输出</v>
+        <v>绘图</v>
       </c>
       <c r="C64" t="str">
-        <v>原始輸出</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B65" t="str">
-        <v>XML</v>
+        <v>原始输出</v>
       </c>
       <c r="C65" t="str">
-        <v>XML</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="C66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B67" t="str">
-        <v>曲线</v>
+        <v>JSON</v>
       </c>
       <c r="C67" t="str">
-        <v>曲線</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B68" t="str">
-        <v>输入曲线</v>
+        <v>曲线</v>
       </c>
       <c r="C68" t="str">
-        <v>輸入曲線</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B69" t="str">
-        <v>输出曲线</v>
+        <v>输入曲线</v>
       </c>
       <c r="C69" t="str">
-        <v>輸出曲線</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B70" t="str">
-        <v>CLUT 图像</v>
+        <v>输出曲线</v>
       </c>
       <c r="C70" t="str">
-        <v>CLUT 影像</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B71" t="str">
-        <v>色域图像</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C71" t="str">
-        <v>色域影像</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B72" t="str">
-        <v>色度</v>
+        <v>色域图像</v>
       </c>
       <c r="C72" t="str">
-        <v>色度</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B73" t="str">
-        <v>散点图</v>
+        <v>色度</v>
       </c>
       <c r="C73" t="str">
-        <v>散佈圖</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B74" t="str">
-        <v>色调响应曲线</v>
+        <v>散点图</v>
       </c>
       <c r="C74" t="str">
-        <v>色調響應曲線</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B75" t="str">
-        <v>曲线表</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C75" t="str">
-        <v>曲線表</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B76" t="str">
-        <v>表格</v>
+        <v>曲线表</v>
       </c>
       <c r="C76" t="str">
-        <v>表格</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B77" t="str">
-        <v>数据</v>
+        <v>表格</v>
       </c>
       <c r="C77" t="str">
-        <v>資料</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B78" t="str">
-        <v>求值</v>
+        <v>数据</v>
       </c>
       <c r="C78" t="str">
-        <v>求值</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B79" t="str">
-        <v>加载中…</v>
+        <v>求值</v>
       </c>
       <c r="C79" t="str">
-        <v>載入中…</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B80" t="str">
-        <v>输入</v>
+        <v>加载中…</v>
       </c>
       <c r="C80" t="str">
-        <v>輸入</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B81" t="str">
-        <v>输出</v>
+        <v>输入</v>
       </c>
       <c r="C81" t="str">
-        <v>輸出</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B82" t="str">
-        <v>浮点值</v>
+        <v>输出</v>
       </c>
       <c r="C82" t="str">
-        <v>浮點值</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B83" t="str">
-        <v>网格点</v>
+        <v>浮点值</v>
       </c>
       <c r="C83" t="str">
-        <v>網格點</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B84" t="str">
-        <v>归一化</v>
+        <v>网格点</v>
       </c>
       <c r="C84" t="str">
-        <v>正規化</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B85" t="str">
-        <v>可读值</v>
+        <v>归一化</v>
       </c>
       <c r="C85" t="str">
-        <v>可讀值</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B86" t="str">
-        <v>设备 → PCS</v>
+        <v>可读值</v>
       </c>
       <c r="C86" t="str">
-        <v>裝置 → PCS</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B87" t="str">
-        <v>PCS → 设备</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C87" t="str">
-        <v>PCS → 裝置</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B88" t="str">
-        <v>无 CLUT 网格</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C88" t="str">
-        <v>無 CLUT 網格</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B89" t="str">
-        <v>加载中…</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C89" t="str">
-        <v>載入中…</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B90" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>加载中…</v>
       </c>
       <c r="C90" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B91" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C91" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B92" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C92" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B93" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C93" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B94" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C94" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B95" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C95" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B96" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C96" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B97" t="str">
-        <v>安全性</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C97" t="str">
-        <v>安全性</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B98" t="str">
-        <v>符合性</v>
+        <v>安全性</v>
       </c>
       <c r="C98" t="str">
-        <v>符合性</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B99" t="str">
-        <v>质量</v>
+        <v>符合性</v>
       </c>
       <c r="C99" t="str">
-        <v>品質</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B100" t="str">
-        <v>报告</v>
+        <v>质量</v>
       </c>
       <c r="C100" t="str">
-        <v>報告</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B101" t="str">
-        <v>失败</v>
+        <v>报告</v>
       </c>
       <c r="C101" t="str">
-        <v>失敗</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B102" t="str">
-        <v>项检查</v>
+        <v>失败</v>
       </c>
       <c r="C102" t="str">
-        <v>項檢查</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B103" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>项检查</v>
       </c>
       <c r="C103" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B104" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C104" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B105" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C105" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B106" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C106" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B107" t="str">
-        <v>订阅</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C107" t="str">
-        <v>訂閱</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B108" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>订阅</v>
       </c>
       <c r="C108" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B109" t="str">
-        <v>订阅新版本通知</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C109" t="str">
-        <v>訂閱新版本通知</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B110" t="str">
-        <v>关闭</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C110" t="str">
-        <v>關閉</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B111" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>关闭</v>
       </c>
       <c r="C111" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B112" t="str">
-        <v>电子邮件地址</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C112" t="str">
-        <v>電子郵件地址</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B113" t="str">
-        <v>you@example.com</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C113" t="str">
-        <v>you@example.com</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B114" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
       <c r="C114" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B115" t="str">
-        <v>（选填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C115" t="str">
-        <v>（選填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B116" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>（选填）</v>
       </c>
       <c r="C116" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B117" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C117" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B118" t="str">
-        <v>取消</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C118" t="str">
-        <v>取消</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B119" t="str">
-        <v>订阅</v>
+        <v>取消</v>
       </c>
       <c r="C119" t="str">
-        <v>訂閱</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B120" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>订阅</v>
       </c>
       <c r="C120" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B121" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C121" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B122" t="str">
-        <v>关闭</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C122" t="str">
-        <v>關閉</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B123" t="str">
-        <v>隐私声明</v>
+        <v>关闭</v>
       </c>
       <c r="C123" t="str">
-        <v>隱私聲明</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B124" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C124" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B125" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C125" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B126" t="str">
-        <v>请检查表单后重试。</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C126" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C127" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>网络错误，请重试。</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C128" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>错误：</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C129" t="str">
-        <v>錯誤：</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B130" t="str">
-        <v>转换为 XML</v>
+        <v>错误：</v>
       </c>
       <c r="C130" t="str">
-        <v>轉換為 XML</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B131" t="str">
-        <v>转换为 JSON</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C131" t="str">
-        <v>轉換為 JSON</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B132" t="str">
-        <v>转换为 ICC</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C132" t="str">
-        <v>轉換為 ICC</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B133" t="str">
-        <v>正在转换为 XML…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C133" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B134" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C134" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B135" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C135" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B136" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C136" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B137" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C137" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B138" t="str">
-        <v>配置文件 ID</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C138" t="str">
-        <v>設定檔 ID</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B139" t="str">
-        <v>未找到标签。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C139" t="str">
-        <v>找不到標籤。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B140" t="str">
-        <v>标签名称</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C140" t="str">
-        <v>標籤名稱</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B141" t="str">
-        <v>ID</v>
+        <v>标签名称</v>
       </c>
       <c r="C141" t="str">
-        <v>ID</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B142" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
       <c r="C142" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B143" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
       <c r="C143" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B144" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
       <c r="C144" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B145" t="str">
-        <v>加载后字节已更改</v>
+        <v>填充</v>
       </c>
       <c r="C145" t="str">
-        <v>載入後位元組已變更</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B146" t="str">
-        <v>类型</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C146" t="str">
-        <v>類型</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B147" t="str">
-        <v>{type} 数组</v>
+        <v>类型</v>
       </c>
       <c r="C147" t="str">
-        <v>{type} 陣列</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B148" t="str">
-        <v>（无内容）</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C148" t="str">
-        <v>（無內容）</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B149" t="str">
-        <v>字节</v>
+        <v>（无内容）</v>
       </c>
       <c r="C149" t="str">
-        <v>位元組</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B150" t="str">
-        <v>正在加载完整描述…</v>
+        <v>字节</v>
       </c>
       <c r="C150" t="str">
-        <v>正在載入完整描述…</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B151" t="str">
-        <v>无法加载完整描述：</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C151" t="str">
-        <v>無法載入完整描述：</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B152" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C152" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B153" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C153" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B154" t="str">
-        <v>无验证输出</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C154" t="str">
-        <v>無驗證輸出</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B155" t="str">
-        <v>配置文件有效</v>
+        <v>无验证输出</v>
       </c>
       <c r="C155" t="str">
-        <v>設定檔有效</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B156" t="str">
-        <v>配置文件有警告</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C156" t="str">
-        <v>設定檔有警告</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B157" t="str">
-        <v>配置文件不合规</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C157" t="str">
-        <v>設定檔不符合規範</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B158" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C158" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B159" t="str">
-        <v>未知验证状态</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C159" t="str">
-        <v>未知驗證狀態</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B160" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C160" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B161" t="str">
-        <v>未发现警告或错误。</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C161" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B162" t="str">
-        <v>有效</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C162" t="str">
-        <v>有效</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B163" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
       <c r="C163" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B164" t="str">
-        <v>错误</v>
+        <v>警告</v>
       </c>
       <c r="C164" t="str">
-        <v>錯誤</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B165" t="str">
-        <v>未知</v>
+        <v>错误</v>
       </c>
       <c r="C165" t="str">
-        <v>未知</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B166" t="str">
-        <v>通过</v>
+        <v>未知</v>
       </c>
       <c r="C166" t="str">
-        <v>通過</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B167" t="str">
-        <v>失败</v>
+        <v>通过</v>
       </c>
       <c r="C167" t="str">
-        <v>失敗</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B168" t="str">
-        <v>在上下文中查看</v>
+        <v>失败</v>
       </c>
       <c r="C168" t="str">
-        <v>在上下文中檢視</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B169" t="str">
-        <v>验证详情</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C169" t="str">
-        <v>驗證詳情</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B170" t="str">
-        <v>触发字段</v>
+        <v>验证详情</v>
       </c>
       <c r="C170" t="str">
-        <v>觸發欄位</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B171" t="str">
-        <v>字段</v>
+        <v>触发字段</v>
       </c>
       <c r="C171" t="str">
-        <v>欄位</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B172" t="str">
-        <v>当前值</v>
+        <v>字段</v>
       </c>
       <c r="C172" t="str">
-        <v>目前值</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B173" t="str">
-        <v>要求：0</v>
+        <v>当前值</v>
       </c>
       <c r="C173" t="str">
-        <v>要求：0</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B174" t="str">
-        <v>预期：{value}</v>
+        <v>要求：0</v>
       </c>
       <c r="C174" t="str">
-        <v>預期：{value}</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B175" t="str">
-        <v>无效</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C175" t="str">
-        <v>無效</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B176" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>无效</v>
       </c>
       <c r="C176" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B177" t="str">
-        <v>关闭</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C177" t="str">
-        <v>關閉</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B178" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>关闭</v>
       </c>
       <c r="C178" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C179" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C180" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C181" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B182" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C182" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B183" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C183" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B184" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C184" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C185" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B186" t="str">
-        <v>缩进</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C186" t="str">
-        <v>縮排</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B187" t="str">
-        <v>排序键</v>
+        <v>缩进</v>
       </c>
       <c r="C187" t="str">
-        <v>排序鍵</v>
+        <v>縮排</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B188" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C188" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B188" t="str">
+      <c r="B189" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C188" t="str">
+      <c r="C189" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C189"/>
+  <dimension ref="A1:C236"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -417,2075 +417,2592 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Settings</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B2" t="str">
-        <v>设置</v>
+        <v>往返 (PRMG)</v>
       </c>
       <c r="C2" t="str">
-        <v>設定</v>
+        <v>往返 (PRMG)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Display</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B3" t="str">
-        <v>显示</v>
+        <v>按照参考工具 iccRoundTrip 对配置文件的设备立方体进行往返计算。往返 1 是设备→PCS→设备的误差 (ΔE*ab)；往返 2 衡量 PCS 往返的稳定性。PRMG 直方图显示与感知参考媒介色域 (Perceptual Reference Medium Gamut) 的互操作性。</v>
       </c>
       <c r="C3" t="str">
-        <v>顯示</v>
+        <v>依照參考工具 iccRoundTrip 對描述檔的裝置立方體進行往返計算。往返 1 是裝置→PCS→裝置的誤差 (ΔE*ab)；往返 2 衡量 PCS 往返的穩定性。PRMG 長條圖顯示與感知參考媒體色域 (Perceptual Reference Medium Gamut) 的互通性。</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Background</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B4" t="str">
-        <v>背景</v>
+        <v>使用 MPE（颜色）标签</v>
       </c>
       <c r="C4" t="str">
-        <v>背景</v>
+        <v>使用 MPE（色彩）標籤</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Language</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B5" t="str">
-        <v>语言</v>
+        <v>此配置文件无法往返——缺少该指标所需的设备↔PCS 转换（例如单向或抽象配置文件）。</v>
       </c>
       <c r="C5" t="str">
-        <v>語言</v>
+        <v>此描述檔無法往返——缺少此指標所需的裝置↔PCS 轉換（例如單向或抽象描述檔）。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>System</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B6" t="str">
-        <v>系统</v>
+        <v>已跳过往返：设备色彩空间太大，无法评估（样本过多）。</v>
       </c>
       <c r="C6" t="str">
-        <v>系統</v>
+        <v>已略過往返：裝置色彩空間太大，無法評估（樣本過多）。</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Light</v>
+        <v>Metric</v>
       </c>
       <c r="B7" t="str">
-        <v>浅色</v>
+        <v>指标</v>
       </c>
       <c r="C7" t="str">
-        <v>淺色</v>
+        <v>指標</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dark</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B8" t="str">
-        <v>深色</v>
+        <v>往返 1</v>
       </c>
       <c r="C8" t="str">
-        <v>深色</v>
+        <v>往返 1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>System default</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B9" t="str">
-        <v>系统默认</v>
+        <v>往返 2</v>
       </c>
       <c r="C9" t="str">
-        <v>系統預設</v>
+        <v>往返 2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Number format</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B10" t="str">
-        <v>数字格式</v>
+        <v>设备 → PCS → 设备</v>
       </c>
       <c r="C10" t="str">
-        <v>數字格式</v>
+        <v>裝置 → PCS → 裝置</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hexadecimal</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B11" t="str">
-        <v>十六进制</v>
+        <v>PCS 往返稳定性</v>
       </c>
       <c r="C11" t="str">
-        <v>十六進位</v>
+        <v>PCS 往返穩定性</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Decimal</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B12" t="str">
-        <v>十进制</v>
+        <v>最小 ΔE</v>
       </c>
       <c r="C12" t="str">
-        <v>十進位</v>
+        <v>最小 ΔE</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Help</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>帮助</v>
+        <v>平均 ΔE</v>
       </c>
       <c r="C13" t="str">
-        <v>說明</v>
+        <v>平均 ΔE</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Contact</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>联系</v>
+        <v>最大 ΔE</v>
       </c>
       <c r="C14" t="str">
-        <v>聯絡</v>
+        <v>最大 ΔE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>User guide</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B15" t="str">
-        <v>用户指南</v>
+        <v>最差 L, a, b</v>
       </c>
       <c r="C15" t="str">
-        <v>使用者指南</v>
+        <v>最差 L, a, b</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Search guide</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B16" t="str">
-        <v>搜索指南</v>
+        <v>指定色域</v>
       </c>
       <c r="C16" t="str">
-        <v>搜尋指南</v>
+        <v>指定色域</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Search the user guide</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>搜索用户指南</v>
+        <v>感知参考媒介色域</v>
       </c>
       <c r="C17" t="str">
-        <v>搜尋使用者指南</v>
+        <v>感知參考媒體色域</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Previous match</v>
+        <v>Not specified</v>
       </c>
       <c r="B18" t="str">
-        <v>上一个匹配项</v>
+        <v>未指定</v>
       </c>
       <c r="C18" t="str">
-        <v>上一個相符項目</v>
+        <v>未指定</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Next match</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B19" t="str">
-        <v>下一个匹配项</v>
+        <v>未评估</v>
       </c>
       <c r="C19" t="str">
-        <v>下一個相符項目</v>
+        <v>未評估</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Close user guide</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B20" t="str">
-        <v>关闭用户指南</v>
+        <v>PRMG 互操作性</v>
       </c>
       <c r="C20" t="str">
-        <v>關閉使用者指南</v>
+        <v>PRMG 互通性</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B21" t="str">
-        <v>加载中…</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C21" t="str">
-        <v>載入中…</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Count</v>
       </c>
       <c r="B22" t="str">
-        <v>无法加载用户指南。</v>
+        <v>数量</v>
       </c>
       <c r="C22" t="str">
-        <v>無法載入使用者指南。</v>
+        <v>數量</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>None</v>
+        <v>Share</v>
       </c>
       <c r="B23" t="str">
-        <v>无</v>
+        <v>占比</v>
       </c>
       <c r="C23" t="str">
-        <v>無</v>
+        <v>占比</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Total</v>
       </c>
       <c r="B24" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>总计</v>
       </c>
       <c r="C24" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>總計</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B25" t="str">
-        <v>上传一个 ICC 配置文件，依据</v>
+        <v>未评估 PRMG</v>
       </c>
       <c r="C25" t="str">
-        <v>上傳一個 ICC 設定檔，依據</v>
+        <v>未評估 PRMG</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>specification using the</v>
+        <v>Settings</v>
       </c>
       <c r="B26" t="str">
-        <v>规范使用</v>
+        <v>设置</v>
       </c>
       <c r="C26" t="str">
-        <v>規範使用</v>
+        <v>設定</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>demo implementation.</v>
+        <v>Display</v>
       </c>
       <c r="B27" t="str">
-        <v>演示实现进行验证。</v>
+        <v>显示</v>
       </c>
       <c r="C27" t="str">
-        <v>示範實作進行驗證。</v>
+        <v>顯示</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Based on</v>
+        <v>Background</v>
       </c>
       <c r="B28" t="str">
-        <v>基于</v>
+        <v>背景</v>
       </c>
       <c r="C28" t="str">
-        <v>基於</v>
+        <v>背景</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>demo implementation</v>
+        <v>Language</v>
       </c>
       <c r="B29" t="str">
-        <v>演示实现</v>
+        <v>语言</v>
       </c>
       <c r="C29" t="str">
-        <v>示範實作</v>
+        <v>語言</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validating…</v>
+        <v>System</v>
       </c>
       <c r="B30" t="str">
-        <v>正在验证…</v>
+        <v>系统</v>
       </c>
       <c r="C30" t="str">
-        <v>驗證中…</v>
+        <v>系統</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Save ICC profile</v>
+        <v>Light</v>
       </c>
       <c r="B31" t="str">
-        <v>保存 ICC 配置文件</v>
+        <v>浅色</v>
       </c>
       <c r="C31" t="str">
-        <v>儲存 ICC 設定檔</v>
+        <v>淺色</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Dark</v>
       </c>
       <c r="B32" t="str">
-        <v>● 已修改 — 尚未保存</v>
+        <v>深色</v>
       </c>
       <c r="C32" t="str">
-        <v>● 已修改 — 尚未儲存</v>
+        <v>深色</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>System default</v>
       </c>
       <c r="B33" t="str">
-        <v>将 ICC 配置文件拖到此处</v>
+        <v>系统默认</v>
       </c>
       <c r="C33" t="str">
-        <v>將 ICC 設定檔拖到此處</v>
+        <v>系統預設</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>or</v>
+        <v>Number format</v>
       </c>
       <c r="B34" t="str">
-        <v>或</v>
+        <v>数字格式</v>
       </c>
       <c r="C34" t="str">
-        <v>或</v>
+        <v>數字格式</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Choose file</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B35" t="str">
-        <v>选择文件</v>
+        <v>十六进制</v>
       </c>
       <c r="C35" t="str">
-        <v>選擇檔案</v>
+        <v>十六進位</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>.icc and .icm files</v>
+        <v>Decimal</v>
       </c>
       <c r="B36" t="str">
-        <v>.icc 和 .icm 文件</v>
+        <v>十进制</v>
       </c>
       <c r="C36" t="str">
-        <v>.icc 與 .icm 檔案</v>
+        <v>十進位</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Header</v>
+        <v>Help</v>
       </c>
       <c r="B37" t="str">
-        <v>标头</v>
+        <v>帮助</v>
       </c>
       <c r="C37" t="str">
-        <v>標頭</v>
+        <v>說明</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tags</v>
+        <v>Contact</v>
       </c>
       <c r="B38" t="str">
-        <v>标签</v>
+        <v>联系</v>
       </c>
       <c r="C38" t="str">
-        <v>標籤</v>
+        <v>聯絡</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Validation</v>
+        <v>User guide</v>
       </c>
       <c r="B39" t="str">
-        <v>验证</v>
+        <v>用户指南</v>
       </c>
       <c r="C39" t="str">
-        <v>驗證</v>
+        <v>使用者指南</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Analysis</v>
+        <v>Search guide</v>
       </c>
       <c r="B40" t="str">
-        <v>分析</v>
+        <v>搜索指南</v>
       </c>
       <c r="C40" t="str">
-        <v>分析</v>
+        <v>搜尋指南</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B41" t="str">
-        <v>中性轴墨量</v>
+        <v>搜索用户指南</v>
       </c>
       <c r="C41" t="str">
-        <v>中性軸墨量</v>
+        <v>搜尋使用者指南</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Previous match</v>
       </c>
       <c r="B42" t="str">
-        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
+        <v>上一个匹配项</v>
       </c>
       <c r="C42" t="str">
-        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
+        <v>上一個相符項目</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Next match</v>
       </c>
       <c r="B43" t="str">
-        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
+        <v>下一个匹配项</v>
       </c>
       <c r="C43" t="str">
-        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
+        <v>下一個相符項目</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Close user guide</v>
       </c>
       <c r="B44" t="str">
-        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
+        <v>关闭用户指南</v>
       </c>
       <c r="C44" t="str">
-        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
+        <v>關閉使用者指南</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Rendering intent</v>
+        <v>Loading…</v>
       </c>
       <c r="B45" t="str">
-        <v>渲染意图</v>
+        <v>加载中…</v>
       </c>
       <c r="C45" t="str">
-        <v>轉換意圖</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>% ink</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B46" t="str">
-        <v>% 墨量</v>
+        <v>无法加载用户指南。</v>
       </c>
       <c r="C46" t="str">
-        <v>% 墨量</v>
+        <v>無法載入使用者指南。</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Perceptual</v>
+        <v>None</v>
       </c>
       <c r="B47" t="str">
-        <v>感知</v>
+        <v>无</v>
       </c>
       <c r="C47" t="str">
-        <v>感知</v>
+        <v>無</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Relative Colorimetric</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B48" t="str">
-        <v>相对比色</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C48" t="str">
-        <v>相對比色</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Saturation</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B49" t="str">
-        <v>饱和度</v>
+        <v>上传一个 ICC 配置文件，依据</v>
       </c>
       <c r="C49" t="str">
-        <v>飽和度</v>
+        <v>上傳一個 ICC 設定檔，依據</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>specification using the</v>
       </c>
       <c r="B50" t="str">
-        <v>绝对比色</v>
+        <v>规范使用</v>
       </c>
       <c r="C50" t="str">
-        <v>絕對比色</v>
+        <v>規範使用</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Profile Statistics</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B51" t="str">
-        <v>特性文件统计</v>
+        <v>演示实现进行验证。</v>
       </c>
       <c r="C51" t="str">
-        <v>特性檔統計</v>
+        <v>示範實作進行驗證。</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Based on</v>
       </c>
       <c r="B52" t="str">
-        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
+        <v>基于</v>
       </c>
       <c r="C52" t="str">
-        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
+        <v>基於</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>demo implementation</v>
       </c>
       <c r="B53" t="str">
-        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
+        <v>演示实现</v>
       </c>
       <c r="C53" t="str">
-        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
+        <v>示範實作</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Rendering intent</v>
+        <v>Validating…</v>
       </c>
       <c r="B54" t="str">
-        <v>渲染意图</v>
+        <v>正在验证…</v>
       </c>
       <c r="C54" t="str">
-        <v>轉換意圖</v>
+        <v>驗證中…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B55" t="str">
-        <v>色域体积 (ΔE³)</v>
+        <v>保存 ICC 配置文件</v>
       </c>
       <c r="C55" t="str">
-        <v>色域體積 (ΔE³)</v>
+        <v>儲存 ICC 設定檔</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Round-trip ΔE</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B56" t="str">
-        <v>往返 ΔE</v>
+        <v>● 已修改 — 尚未保存</v>
       </c>
       <c r="C56" t="str">
-        <v>往返 ΔE</v>
+        <v>● 已修改 — 尚未儲存</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Profiles</v>
       </c>
       <c r="B57" t="str">
-        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
+        <v/>
       </c>
       <c r="C57" t="str">
-        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mean</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B58" t="str">
-        <v>均值</v>
+        <v/>
       </c>
       <c r="C58" t="str">
-        <v>平均</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>P90</v>
+        <v>Collapse</v>
       </c>
       <c r="B59" t="str">
-        <v>P90</v>
+        <v/>
       </c>
       <c r="C59" t="str">
-        <v>P90</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>max</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B60" t="str">
-        <v>最大</v>
+        <v/>
       </c>
       <c r="C60" t="str">
-        <v>最大</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysing…</v>
+        <v>Remove</v>
       </c>
       <c r="B61" t="str">
-        <v>正在分析…</v>
+        <v/>
       </c>
       <c r="C61" t="str">
-        <v>正在分析…</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Analysis</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B62" t="str">
-        <v>分析</v>
+        <v/>
       </c>
       <c r="C62" t="str">
-        <v>分析</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>or use “Load Profiles” — files stay on your device.</v>
       </c>
       <c r="B63" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v/>
       </c>
       <c r="C63" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Plot</v>
+        <v>Profile</v>
       </c>
       <c r="B64" t="str">
-        <v>绘图</v>
+        <v/>
       </c>
       <c r="C64" t="str">
-        <v>繪圖</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Raw Output</v>
+        <v>Compare</v>
       </c>
       <c r="B65" t="str">
-        <v>原始输出</v>
+        <v/>
       </c>
       <c r="C65" t="str">
-        <v>原始輸出</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>XML</v>
+        <v>Link</v>
       </c>
       <c r="B66" t="str">
-        <v>XML</v>
+        <v/>
       </c>
       <c r="C66" t="str">
-        <v>XML</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>JSON</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B67" t="str">
-        <v>JSON</v>
+        <v/>
       </c>
       <c r="C67" t="str">
-        <v>JSON</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curves</v>
+        <v>Remove</v>
       </c>
       <c r="B68" t="str">
-        <v>曲线</v>
+        <v/>
       </c>
       <c r="C68" t="str">
-        <v>曲線</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Input curves</v>
+        <v>No profile selected</v>
       </c>
       <c r="B69" t="str">
-        <v>输入曲线</v>
+        <v/>
       </c>
       <c r="C69" t="str">
-        <v>輸入曲線</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Output curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B70" t="str">
-        <v>输出曲线</v>
+        <v/>
       </c>
       <c r="C70" t="str">
-        <v>輸出曲線</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CLUT image</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B71" t="str">
-        <v>CLUT 图像</v>
+        <v/>
       </c>
       <c r="C71" t="str">
-        <v>CLUT 影像</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Gamut image</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B72" t="str">
-        <v>色域图像</v>
+        <v/>
       </c>
       <c r="C72" t="str">
-        <v>色域影像</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B73" t="str">
-        <v>色度</v>
+        <v/>
       </c>
       <c r="C73" t="str">
-        <v>色度</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Scatter plot</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B74" t="str">
-        <v>散点图</v>
+        <v/>
       </c>
       <c r="C74" t="str">
-        <v>散佈圖</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tone response curve</v>
+        <v>Linking</v>
       </c>
       <c r="B75" t="str">
-        <v>色调响应曲线</v>
+        <v/>
       </c>
       <c r="C75" t="str">
-        <v>色調響應曲線</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Curve table</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B76" t="str">
-        <v>曲线表</v>
+        <v/>
       </c>
       <c r="C76" t="str">
-        <v>曲線表</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Tables</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B77" t="str">
-        <v>表格</v>
+        <v/>
       </c>
       <c r="C77" t="str">
-        <v>表格</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Data</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B78" t="str">
-        <v>数据</v>
+        <v/>
       </c>
       <c r="C78" t="str">
-        <v>資料</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Evaluate</v>
+        <v>OK</v>
       </c>
       <c r="B79" t="str">
-        <v>求值</v>
+        <v/>
       </c>
       <c r="C79" t="str">
-        <v>求值</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Loading…</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B80" t="str">
-        <v>加载中…</v>
+        <v>将 ICC 配置文件拖到此处</v>
       </c>
       <c r="C80" t="str">
-        <v>載入中…</v>
+        <v>將 ICC 設定檔拖到此處</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Input</v>
+        <v>or</v>
       </c>
       <c r="B81" t="str">
-        <v>输入</v>
+        <v>或</v>
       </c>
       <c r="C81" t="str">
-        <v>輸入</v>
+        <v>或</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Output</v>
+        <v>Choose file</v>
       </c>
       <c r="B82" t="str">
-        <v>输出</v>
+        <v>选择文件</v>
       </c>
       <c r="C82" t="str">
-        <v>輸出</v>
+        <v>選擇檔案</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Floating point</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B83" t="str">
-        <v>浮点值</v>
+        <v>.icc 和 .icm 文件</v>
       </c>
       <c r="C83" t="str">
-        <v>浮點值</v>
+        <v>.icc 與 .icm 檔案</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Grid point</v>
+        <v>Header</v>
       </c>
       <c r="B84" t="str">
-        <v>网格点</v>
+        <v>标头</v>
       </c>
       <c r="C84" t="str">
-        <v>網格點</v>
+        <v>標頭</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Normalized</v>
+        <v>Tags</v>
       </c>
       <c r="B85" t="str">
-        <v>归一化</v>
+        <v>标签</v>
       </c>
       <c r="C85" t="str">
-        <v>正規化</v>
+        <v>標籤</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Human</v>
+        <v>Validation</v>
       </c>
       <c r="B86" t="str">
-        <v>可读值</v>
+        <v>验证</v>
       </c>
       <c r="C86" t="str">
-        <v>可讀值</v>
+        <v>驗證</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Device → PCS</v>
+        <v>Analysis</v>
       </c>
       <c r="B87" t="str">
-        <v>设备 → PCS</v>
+        <v>分析</v>
       </c>
       <c r="C87" t="str">
-        <v>裝置 → PCS</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B88" t="str">
-        <v>PCS → 设备</v>
+        <v>中性轴墨量</v>
       </c>
       <c r="C88" t="str">
-        <v>PCS → 裝置</v>
+        <v>中性軸墨量</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>No CLUT grid</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B89" t="str">
-        <v>无 CLUT 网格</v>
+        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
       </c>
       <c r="C89" t="str">
-        <v>無 CLUT 網格</v>
+        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading…</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B90" t="str">
-        <v>加载中…</v>
+        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C90" t="str">
-        <v>載入中…</v>
+        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B91" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
       </c>
       <c r="C91" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B92" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>渲染意图</v>
       </c>
       <c r="C92" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>% ink</v>
       </c>
       <c r="B93" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>% 墨量</v>
       </c>
       <c r="C93" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>% 墨量</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Perceptual</v>
       </c>
       <c r="B94" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>感知</v>
       </c>
       <c r="C94" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B95" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>相对比色</v>
       </c>
       <c r="C95" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Saturation</v>
       </c>
       <c r="B96" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>饱和度</v>
       </c>
       <c r="C96" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B97" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>绝对比色</v>
       </c>
       <c r="C97" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>絕對比色</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Security</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B98" t="str">
-        <v>安全性</v>
+        <v>特性文件统计</v>
       </c>
       <c r="C98" t="str">
-        <v>安全性</v>
+        <v>特性檔統計</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Conformance</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B99" t="str">
-        <v>符合性</v>
+        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
       </c>
       <c r="C99" t="str">
-        <v>符合性</v>
+        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quality</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B100" t="str">
-        <v>质量</v>
+        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
       </c>
       <c r="C100" t="str">
-        <v>品質</v>
+        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>REPORT</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B101" t="str">
-        <v>报告</v>
+        <v>渲染意图</v>
       </c>
       <c r="C101" t="str">
-        <v>報告</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>FAIL</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B102" t="str">
-        <v>失败</v>
+        <v>色域体积 (ΔE³)</v>
       </c>
       <c r="C102" t="str">
-        <v>失敗</v>
+        <v>色域體積 (ΔE³)</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>checks</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B103" t="str">
-        <v>项检查</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C103" t="str">
-        <v>項檢查</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B104" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
       </c>
       <c r="C104" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>mean</v>
       </c>
       <c r="B105" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>均值</v>
       </c>
       <c r="C105" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool</v>
+        <v>P90</v>
       </c>
       <c r="B106" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>P90</v>
       </c>
       <c r="C106" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Powered by {lib}</v>
+        <v>max</v>
       </c>
       <c r="B107" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>最大</v>
       </c>
       <c r="C107" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Subscribe</v>
+        <v>Analysing…</v>
       </c>
       <c r="B108" t="str">
-        <v>订阅</v>
+        <v>正在分析…</v>
       </c>
       <c r="C108" t="str">
-        <v>訂閱</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Analysis</v>
       </c>
       <c r="B109" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>分析</v>
       </c>
       <c r="C109" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new releases</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B110" t="str">
-        <v>订阅新版本通知</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C110" t="str">
-        <v>訂閱新版本通知</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Close</v>
+        <v>Plot</v>
       </c>
       <c r="B111" t="str">
-        <v>关闭</v>
+        <v>绘图</v>
       </c>
       <c r="C111" t="str">
-        <v>關閉</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Raw Output</v>
       </c>
       <c r="B112" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>原始输出</v>
       </c>
       <c r="C112" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Email address</v>
+        <v>XML</v>
       </c>
       <c r="B113" t="str">
-        <v>电子邮件地址</v>
+        <v>XML</v>
       </c>
       <c r="C113" t="str">
-        <v>電子郵件地址</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
       <c r="B114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
       <c r="C114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Curves</v>
       </c>
       <c r="B115" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>曲线</v>
       </c>
       <c r="C115" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>(optional)</v>
+        <v>Input curves</v>
       </c>
       <c r="B116" t="str">
-        <v>（选填）</v>
+        <v>输入曲线</v>
       </c>
       <c r="C116" t="str">
-        <v>（選填）</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Output curves</v>
       </c>
       <c r="B117" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>输出曲线</v>
       </c>
       <c r="C117" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B118" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C118" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Cancel</v>
+        <v>Gamut image</v>
       </c>
       <c r="B119" t="str">
-        <v>取消</v>
+        <v>色域图像</v>
       </c>
       <c r="C119" t="str">
-        <v>取消</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Subscribe</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B120" t="str">
-        <v>订阅</v>
+        <v>色度</v>
       </c>
       <c r="C120" t="str">
-        <v>訂閱</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B121" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>散点图</v>
       </c>
       <c r="C121" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B122" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C122" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Close</v>
+        <v>Curve table</v>
       </c>
       <c r="B123" t="str">
-        <v>关闭</v>
+        <v>曲线表</v>
       </c>
       <c r="C123" t="str">
-        <v>關閉</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Privacy notice</v>
+        <v>Tables</v>
       </c>
       <c r="B124" t="str">
-        <v>隐私声明</v>
+        <v>表格</v>
       </c>
       <c r="C124" t="str">
-        <v>隱私聲明</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Data</v>
       </c>
       <c r="B125" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>数据</v>
       </c>
       <c r="C125" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B126" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>求值</v>
       </c>
       <c r="C126" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Loading…</v>
       </c>
       <c r="B127" t="str">
-        <v>请检查表单后重试。</v>
+        <v>加载中…</v>
       </c>
       <c r="C127" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Input</v>
       </c>
       <c r="B128" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>输入</v>
       </c>
       <c r="C128" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Output</v>
       </c>
       <c r="B129" t="str">
-        <v>网络错误，请重试。</v>
+        <v>输出</v>
       </c>
       <c r="C129" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Error:</v>
+        <v>Floating point</v>
       </c>
       <c r="B130" t="str">
-        <v>错误：</v>
+        <v>浮点值</v>
       </c>
       <c r="C130" t="str">
-        <v>錯誤：</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to XML</v>
+        <v>Grid point</v>
       </c>
       <c r="B131" t="str">
-        <v>转换为 XML</v>
+        <v>网格点</v>
       </c>
       <c r="C131" t="str">
-        <v>轉換為 XML</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to JSON</v>
+        <v>Normalized</v>
       </c>
       <c r="B132" t="str">
-        <v>转换为 JSON</v>
+        <v>归一化</v>
       </c>
       <c r="C132" t="str">
-        <v>轉換為 JSON</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to ICC</v>
+        <v>Human</v>
       </c>
       <c r="B133" t="str">
-        <v>转换为 ICC</v>
+        <v>可读值</v>
       </c>
       <c r="C133" t="str">
-        <v>轉換為 ICC</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to XML…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B134" t="str">
-        <v>正在转换为 XML…</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C134" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to JSON…</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B135" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C135" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to ICC…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B136" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C136" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Load ICC profile</v>
+        <v>Loading…</v>
       </c>
       <c r="B137" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>加载中…</v>
       </c>
       <c r="C137" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B138" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C138" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Profile ID</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B139" t="str">
-        <v>配置文件 ID</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C139" t="str">
-        <v>設定檔 ID</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>No tags found.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B140" t="str">
-        <v>未找到标签。</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C140" t="str">
-        <v>找不到標籤。</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Tag Name</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B141" t="str">
-        <v>标签名称</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C141" t="str">
-        <v>標籤名稱</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ID</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B142" t="str">
-        <v>ID</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C142" t="str">
-        <v>ID</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Offset</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B143" t="str">
-        <v>偏移</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C143" t="str">
-        <v>偏移</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Size</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B144" t="str">
-        <v>大小</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C144" t="str">
-        <v>大小</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pad</v>
+        <v>Security</v>
       </c>
       <c r="B145" t="str">
-        <v>填充</v>
+        <v>安全性</v>
       </c>
       <c r="C145" t="str">
-        <v>填充</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Bytes changed since load</v>
+        <v>Conformance</v>
       </c>
       <c r="B146" t="str">
-        <v>加载后字节已更改</v>
+        <v>符合性</v>
       </c>
       <c r="C146" t="str">
-        <v>載入後位元組已變更</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Type</v>
+        <v>Quality</v>
       </c>
       <c r="B147" t="str">
-        <v>类型</v>
+        <v>质量</v>
       </c>
       <c r="C147" t="str">
-        <v>類型</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Array of {type}</v>
+        <v>REPORT</v>
       </c>
       <c r="B148" t="str">
-        <v>{type} 数组</v>
+        <v>报告</v>
       </c>
       <c r="C148" t="str">
-        <v>{type} 陣列</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>(No content)</v>
+        <v>FAIL</v>
       </c>
       <c r="B149" t="str">
-        <v>（无内容）</v>
+        <v>失败</v>
       </c>
       <c r="C149" t="str">
-        <v>（無內容）</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>bytes</v>
+        <v>checks</v>
       </c>
       <c r="B150" t="str">
-        <v>字节</v>
+        <v>项检查</v>
       </c>
       <c r="C150" t="str">
-        <v>位元組</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Loading full description…</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B151" t="str">
-        <v>正在加载完整描述…</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C151" t="str">
-        <v>正在載入完整描述…</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Could not load full description:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B152" t="str">
-        <v>无法加载完整描述：</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C152" t="str">
-        <v>無法載入完整描述：</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B153" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C153" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B154" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C154" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No validation output</v>
+        <v>Subscribe</v>
       </c>
       <c r="B155" t="str">
-        <v>无验证输出</v>
+        <v>订阅</v>
       </c>
       <c r="C155" t="str">
-        <v>無驗證輸出</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile is valid</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B156" t="str">
-        <v>配置文件有效</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C156" t="str">
-        <v>設定檔有效</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B157" t="str">
-        <v>配置文件有警告</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C157" t="str">
-        <v>設定檔有警告</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Close</v>
       </c>
       <c r="B158" t="str">
-        <v>配置文件不合规</v>
+        <v>关闭</v>
       </c>
       <c r="C158" t="str">
-        <v>設定檔不符合規範</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Critical validation error</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B159" t="str">
-        <v>严重验证错误</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C159" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Unknown validation status</v>
+        <v>Email address</v>
       </c>
       <c r="B160" t="str">
-        <v>未知验证状态</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C160" t="str">
-        <v>未知驗證狀態</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>you@example.com</v>
       </c>
       <c r="B161" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>you@example.com</v>
       </c>
       <c r="C161" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>No warnings or errors found.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B162" t="str">
-        <v>未发现警告或错误。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C162" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Valid</v>
+        <v>(optional)</v>
       </c>
       <c r="B163" t="str">
-        <v>有效</v>
+        <v>（选填）</v>
       </c>
       <c r="C163" t="str">
-        <v>有效</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Warning</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B164" t="str">
-        <v>警告</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C164" t="str">
-        <v>警告</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Error</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B165" t="str">
-        <v>错误</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C165" t="str">
-        <v>錯誤</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Unknown</v>
+        <v>Cancel</v>
       </c>
       <c r="B166" t="str">
-        <v>未知</v>
+        <v>取消</v>
       </c>
       <c r="C166" t="str">
-        <v>未知</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Pass</v>
+        <v>Subscribe</v>
       </c>
       <c r="B167" t="str">
-        <v>通过</v>
+        <v>订阅</v>
       </c>
       <c r="C167" t="str">
-        <v>通過</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B168" t="str">
-        <v>失败</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C168" t="str">
-        <v>失敗</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>View in context</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B169" t="str">
-        <v>在上下文中查看</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C169" t="str">
-        <v>在上下文中檢視</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Validation detail</v>
+        <v>Close</v>
       </c>
       <c r="B170" t="str">
-        <v>验证详情</v>
+        <v>关闭</v>
       </c>
       <c r="C170" t="str">
-        <v>驗證詳情</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Triggered by</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B171" t="str">
-        <v>触发字段</v>
+        <v>隐私声明</v>
       </c>
       <c r="C171" t="str">
-        <v>觸發欄位</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Field</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B172" t="str">
-        <v>字段</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C172" t="str">
-        <v>欄位</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Current value</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B173" t="str">
-        <v>当前值</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C173" t="str">
-        <v>目前值</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Required: 0</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B174" t="str">
-        <v>要求：0</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C174" t="str">
-        <v>要求：0</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B175" t="str">
-        <v>预期：{value}</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C175" t="str">
-        <v>預期：{value}</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Invalid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B176" t="str">
-        <v>无效</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C176" t="str">
-        <v>無效</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error:</v>
       </c>
       <c r="B177" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>错误：</v>
       </c>
       <c r="C177" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Close</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B178" t="str">
-        <v>关闭</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C178" t="str">
-        <v>關閉</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading XML editor…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B179" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C179" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B180" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C180" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B181" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C181" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B182" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C182" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B183" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C183" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B184" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C184" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B185" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C185" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B186" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C186" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>indent</v>
+        <v>No tags found.</v>
       </c>
       <c r="B187" t="str">
-        <v>缩进</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C187" t="str">
-        <v>縮排</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>sort keys</v>
+        <v>Tag Name</v>
       </c>
       <c r="B188" t="str">
-        <v>排序键</v>
+        <v>标签名称</v>
       </c>
       <c r="C188" t="str">
-        <v>排序鍵</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C189" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B190" t="str">
+        <v>偏移</v>
+      </c>
+      <c r="C190" t="str">
+        <v>偏移</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B191" t="str">
+        <v>大小</v>
+      </c>
+      <c r="C191" t="str">
+        <v>大小</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B192" t="str">
+        <v>填充</v>
+      </c>
+      <c r="C192" t="str">
+        <v>填充</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B193" t="str">
+        <v>加载后字节已更改</v>
+      </c>
+      <c r="C193" t="str">
+        <v>載入後位元組已變更</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B194" t="str">
+        <v>类型</v>
+      </c>
+      <c r="C194" t="str">
+        <v>類型</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B195" t="str">
+        <v>{type} 数组</v>
+      </c>
+      <c r="C195" t="str">
+        <v>{type} 陣列</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>（无内容）</v>
+      </c>
+      <c r="C196" t="str">
+        <v>（無內容）</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B197" t="str">
+        <v>字节</v>
+      </c>
+      <c r="C197" t="str">
+        <v>位元組</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B198" t="str">
+        <v>正在加载完整描述…</v>
+      </c>
+      <c r="C198" t="str">
+        <v>正在載入完整描述…</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B199" t="str">
+        <v>无法加载完整描述：</v>
+      </c>
+      <c r="C199" t="str">
+        <v>無法載入完整描述：</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B200" t="str">
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+      </c>
+      <c r="C200" t="str">
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B201" t="str">
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+      </c>
+      <c r="C201" t="str">
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B202" t="str">
+        <v>无验证输出</v>
+      </c>
+      <c r="C202" t="str">
+        <v>無驗證輸出</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B203" t="str">
+        <v>配置文件有效</v>
+      </c>
+      <c r="C203" t="str">
+        <v>設定檔有效</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>配置文件有警告</v>
+      </c>
+      <c r="C204" t="str">
+        <v>設定檔有警告</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B205" t="str">
+        <v>配置文件不合规</v>
+      </c>
+      <c r="C205" t="str">
+        <v>設定檔不符合規範</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B206" t="str">
+        <v>严重验证错误</v>
+      </c>
+      <c r="C206" t="str">
+        <v>嚴重驗證錯誤</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B207" t="str">
+        <v>未知验证状态</v>
+      </c>
+      <c r="C207" t="str">
+        <v>未知驗證狀態</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B208" t="str">
+        <v>严重 — 仅供检查显示</v>
+      </c>
+      <c r="C208" t="str">
+        <v>嚴重 — 僅供檢視顯示</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>未发现警告或错误。</v>
+      </c>
+      <c r="C209" t="str">
+        <v>未發現警告或錯誤。</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B210" t="str">
+        <v>有效</v>
+      </c>
+      <c r="C210" t="str">
+        <v>有效</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B211" t="str">
+        <v>警告</v>
+      </c>
+      <c r="C211" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B212" t="str">
+        <v>错误</v>
+      </c>
+      <c r="C212" t="str">
+        <v>錯誤</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B213" t="str">
+        <v>未知</v>
+      </c>
+      <c r="C213" t="str">
+        <v>未知</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B214" t="str">
+        <v>通过</v>
+      </c>
+      <c r="C214" t="str">
+        <v>通過</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B215" t="str">
+        <v>失败</v>
+      </c>
+      <c r="C215" t="str">
+        <v>失敗</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B216" t="str">
+        <v>在上下文中查看</v>
+      </c>
+      <c r="C216" t="str">
+        <v>在上下文中檢視</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B217" t="str">
+        <v>验证详情</v>
+      </c>
+      <c r="C217" t="str">
+        <v>驗證詳情</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B218" t="str">
+        <v>触发字段</v>
+      </c>
+      <c r="C218" t="str">
+        <v>觸發欄位</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B219" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C219" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B220" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C220" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B221" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C221" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B222" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C222" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B223" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C223" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C224" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B225" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C225" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B226" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C226" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B227" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C227" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B228" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C228" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B229" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C229" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B230" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C230" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B231" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C231" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B232" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C232" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B233" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C233" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B234" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C234" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B235" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C235" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B189" t="str">
+      <c r="B236" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C189" t="str">
+      <c r="C236" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C236"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C236"/>
+  <dimension ref="A1:C319"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -681,2328 +681,3250 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Settings</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B26" t="str">
-        <v>设置</v>
+        <v>针对某一渲染意图的整份配置文件指标：由设备→PCS 变换所包围的色域体积 (ΔE*ab³)，以及往返精度指标。选择渲染意图和往返类型 — 表格和直方图会相应更新。</v>
       </c>
       <c r="C26" t="str">
-        <v>設定</v>
+        <v>針對某一轉換意圖的整份設定檔指標：由裝置→PCS 轉換所包圍的色域體積 (ΔE*ab³)，以及往返精度指標。選擇轉換意圖與往返類型 — 表格與長條圖會隨之更新。</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Display</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B27" t="str">
-        <v>显示</v>
+        <v>往返类型</v>
       </c>
       <c r="C27" t="str">
-        <v>顯示</v>
+        <v>往返類型</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Background</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>背景</v>
+        <v>对此往返类型无影响</v>
       </c>
       <c r="C28" t="str">
-        <v>背景</v>
+        <v>對此往返類型無影響</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Language</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B29" t="str">
-        <v>语言</v>
+        <v>此往返类型不适用于该配置文件。</v>
       </c>
       <c r="C29" t="str">
-        <v>語言</v>
+        <v>此往返類型不適用於此設定檔。</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>System</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B30" t="str">
-        <v>系统</v>
+        <v>往返 ΔE 分布</v>
       </c>
       <c r="C30" t="str">
-        <v>系統</v>
+        <v>往返 ΔE 分佈</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Light</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B31" t="str">
-        <v>浅色</v>
+        <v>没有往返样本落在评估区域内。</v>
       </c>
       <c r="C31" t="str">
-        <v>淺色</v>
+        <v>沒有往返樣本落在評估區域內。</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dark</v>
+        <v>Std Dev</v>
       </c>
       <c r="B32" t="str">
-        <v>深色</v>
+        <v>标准差</v>
       </c>
       <c r="C32" t="str">
-        <v>深色</v>
+        <v>標準差</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>System default</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B33" t="str">
-        <v>系统默认</v>
+        <v>相对频率</v>
       </c>
       <c r="C33" t="str">
-        <v>系統預設</v>
+        <v>相對頻率</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Number format</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>数字格式</v>
+        <v>累积频率</v>
       </c>
       <c r="C34" t="str">
-        <v>數字格式</v>
+        <v>累積頻率</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Hexadecimal</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B35" t="str">
-        <v>十六进制</v>
+        <v>水平刻度</v>
       </c>
       <c r="C35" t="str">
-        <v>十六進位</v>
+        <v>水平刻度</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Decimal</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B36" t="str">
-        <v>十进制</v>
+        <v>整数 ΔE</v>
       </c>
       <c r="C36" t="str">
-        <v>十進位</v>
+        <v>整數 ΔE</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Help</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B37" t="str">
-        <v>帮助</v>
+        <v>自动缩放</v>
       </c>
       <c r="C37" t="str">
-        <v>說明</v>
+        <v>自動縮放</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Contact</v>
+        <v>Bins</v>
       </c>
       <c r="B38" t="str">
-        <v>联系</v>
+        <v>分组</v>
       </c>
       <c r="C38" t="str">
-        <v>聯絡</v>
+        <v>分組</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>User guide</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B39" t="str">
-        <v>用户指南</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C39" t="str">
-        <v>使用者指南</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Search guide</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B40" t="str">
-        <v>搜索指南</v>
+        <v>设备↔PCS 变换的颜色查找表 (CLUT)，平铺成一幅图像。选择要查看的渲染意图表。</v>
       </c>
       <c r="C40" t="str">
-        <v>搜尋指南</v>
+        <v>裝置↔PCS 轉換的色彩查找表 (CLUT)，平鋪成一幅影像。選擇要檢視的轉換意圖表。</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Search the user guide</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B41" t="str">
-        <v>搜索用户指南</v>
+        <v>此配置文件没有可供可视化的基于 CLUT 的设备↔PCS 表。</v>
       </c>
       <c r="C41" t="str">
-        <v>搜尋使用者指南</v>
+        <v>此設定檔沒有可供視覺化的基於 CLUT 的裝置↔PCS 表。</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Previous match</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B42" t="str">
-        <v>上一个匹配项</v>
+        <v>色域图像</v>
       </c>
       <c r="C42" t="str">
-        <v>上一個相符項目</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Next match</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B43" t="str">
-        <v>下一个匹配项</v>
+        <v>色域标签的色域内/外映射：PCS 颜色可再现处为中性色，落在设备色域之外处为红色。</v>
       </c>
       <c r="C43" t="str">
-        <v>下一個相符項目</v>
+        <v>色域標籤的色域內/外對應：PCS 色彩可重現處為中性色，落在裝置色域之外處為紅色。</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Close user guide</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B44" t="str">
-        <v>关闭用户指南</v>
+        <v>此配置文件没有可供可视化的色域标签。</v>
       </c>
       <c r="C44" t="str">
-        <v>關閉使用者指南</v>
+        <v>此設定檔沒有可供視覺化的色域標籤。</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Loading…</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B45" t="str">
-        <v>加载中…</v>
+        <v>垂直刻度</v>
       </c>
       <c r="C45" t="str">
-        <v>載入中…</v>
+        <v>垂直刻度</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Could not load the user guide.</v>
+        <v>X–Y</v>
       </c>
       <c r="B46" t="str">
-        <v>无法加载用户指南。</v>
+        <v>X–Y</v>
       </c>
       <c r="C46" t="str">
-        <v>無法載入使用者指南。</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>None</v>
+        <v>Tone increase</v>
       </c>
       <c r="B47" t="str">
-        <v>无</v>
+        <v>色调增益</v>
       </c>
       <c r="C47" t="str">
-        <v>無</v>
+        <v>色調增益</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B48" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>色调增益（输出 − 输入）</v>
       </c>
       <c r="C48" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>色調增益（輸出 − 輸入）</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Show full dump</v>
       </c>
       <c r="B49" t="str">
-        <v>上传一个 ICC 配置文件，依据</v>
+        <v>显示完整转储</v>
       </c>
       <c r="C49" t="str">
-        <v>上傳一個 ICC 設定檔，依據</v>
+        <v>顯示完整傾印</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>specification using the</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B50" t="str">
-        <v>规范使用</v>
+        <v>为提升性能，输出已截断。</v>
       </c>
       <c r="C50" t="str">
-        <v>規範使用</v>
+        <v>為提升效能，輸出已截斷。</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>demo implementation.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B51" t="str">
-        <v>演示实现进行验证。</v>
+        <v>色域内概览 (RT0)</v>
       </c>
       <c r="C51" t="str">
-        <v>示範實作進行驗證。</v>
+        <v>色域內概覽 (RT0)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Based on</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B52" t="str">
-        <v>基于</v>
+        <v>反演 + 色域 (RT1)</v>
       </c>
       <c r="C52" t="str">
-        <v>基於</v>
+        <v>反演 + 色域 (RT1)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>demo implementation</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B53" t="str">
-        <v>演示实现</v>
+        <v>可重现性 (RT2)</v>
       </c>
       <c r="C53" t="str">
-        <v>示範實作</v>
+        <v>可重現性 (RT2)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Validating…</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B54" t="str">
-        <v>正在验证…</v>
+        <v>PRMG 互操作性</v>
       </c>
       <c r="C54" t="str">
-        <v>驗證中…</v>
+        <v>PRMG 互操作性</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Save ICC profile</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B55" t="str">
-        <v>保存 ICC 配置文件</v>
+        <v>iccviz 概览：设备值网格被转换到 PCS、再回到设备、再次到 PCS；在两次 PCS 结果之间测量 ΔE*ab。这是一次快速的色域内稳定性检查。</v>
       </c>
       <c r="C55" t="str">
-        <v>儲存 ICC 設定檔</v>
+        <v>iccviz 概覽：裝置值網格被轉換到 PCS、再回到裝置、再次到 PCS；在兩次 PCS 結果之間測量 ΔE*ab。這是一次快速的色域內穩定性檢查。</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B56" t="str">
-        <v>● 已修改 — 尚未保存</v>
+        <v>iccRoundTrip 往返 1：每个设备颜色的 PCS 与其经过一次 Lab → 设备 → Lab 往返后的 PCS 之间的 ΔE*ab。反映反演精度和色域映射。</v>
       </c>
       <c r="C56" t="str">
-        <v>● 已修改 — 尚未儲存</v>
+        <v>iccRoundTrip 往返 1：每個裝置色彩的 PCS 與其經過一次 Lab → 裝置 → Lab 往返後的 PCS 之間的 ΔE*ab。反映反演精度與色域對應。</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profiles</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>iccRoundTrip 往返 2：第一次与第二次往返之间的 ΔE*ab — 重复的 PCS 往返有多稳定（可重现性，与第一次往返的色域裁剪无关）。</v>
       </c>
       <c r="C57" t="str">
-        <v/>
+        <v>iccRoundTrip 往返 2：第一次與第二次往返之間的 ΔE*ab — 重複的 PCS 往返有多穩定（可重現性，與第一次往返的色域裁剪無關）。</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Show profile pool</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 内的 PCS 颜色进行一次往返（Lab → 设备 → Lab）；ΔE*ab 分布可指示跨配置文件的互操作性。</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 內的 PCS 色彩進行一次往返（Lab → 裝置 → Lab）；ΔE*ab 分佈可指示跨設定檔的互操作性。</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Collapse</v>
+        <v>Settings</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>设置</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>設定</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Load Profiles</v>
+        <v>Display</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>显示</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>顯示</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Remove</v>
+        <v>Background</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>背景</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>背景</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Language</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>语言</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>語言</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>or use “Load Profiles” — files stay on your device.</v>
+        <v>System</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>系统</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>系統</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile</v>
+        <v>Light</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>浅色</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>淺色</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Compare</v>
+        <v>Dark</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>深色</v>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>深色</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Link</v>
+        <v>System default</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>系统默认</v>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>系統預設</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Number format</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>数字格式</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>數字格式</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Remove</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>十六进制</v>
       </c>
       <c r="C68" t="str">
-        <v/>
+        <v>十六進位</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>No profile selected</v>
+        <v>Decimal</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>十进制</v>
       </c>
       <c r="C69" t="str">
-        <v/>
+        <v>十進位</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Help</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>帮助</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>說明</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Contact</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>联系</v>
       </c>
       <c r="C71" t="str">
-        <v/>
+        <v>聯絡</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>User guide</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>用户指南</v>
       </c>
       <c r="C72" t="str">
-        <v/>
+        <v>使用者指南</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut comparison</v>
+        <v>Search guide</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>搜索指南</v>
       </c>
       <c r="C73" t="str">
-        <v/>
+        <v>搜尋指南</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>搜索用户指南</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>搜尋使用者指南</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Linking</v>
+        <v>Previous match</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>上一个匹配项</v>
       </c>
       <c r="C75" t="str">
-        <v/>
+        <v>上一個相符項目</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Next match</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>下一个匹配项</v>
       </c>
       <c r="C76" t="str">
-        <v/>
+        <v>下一個相符項目</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Close user guide</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>关闭用户指南</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>關閉使用者指南</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Loading…</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>加载中…</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>OK</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>无法加载用户指南。</v>
       </c>
       <c r="C79" t="str">
-        <v/>
+        <v>無法載入使用者指南。</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>None</v>
       </c>
       <c r="B80" t="str">
-        <v>将 ICC 配置文件拖到此处</v>
+        <v>无</v>
       </c>
       <c r="C80" t="str">
-        <v>將 ICC 設定檔拖到此處</v>
+        <v>無</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>or</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B81" t="str">
-        <v>或</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C81" t="str">
-        <v>或</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Choose file</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B82" t="str">
-        <v>选择文件</v>
+        <v>上传一个 ICC 配置文件，依据</v>
       </c>
       <c r="C82" t="str">
-        <v>選擇檔案</v>
+        <v>上傳一個 ICC 設定檔，依據</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>.icc and .icm files</v>
+        <v>specification using the</v>
       </c>
       <c r="B83" t="str">
-        <v>.icc 和 .icm 文件</v>
+        <v>规范使用</v>
       </c>
       <c r="C83" t="str">
-        <v>.icc 與 .icm 檔案</v>
+        <v>規範使用</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Header</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B84" t="str">
-        <v>标头</v>
+        <v>演示实现进行验证。</v>
       </c>
       <c r="C84" t="str">
-        <v>標頭</v>
+        <v>示範實作進行驗證。</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tags</v>
+        <v>Based on</v>
       </c>
       <c r="B85" t="str">
-        <v>标签</v>
+        <v>基于</v>
       </c>
       <c r="C85" t="str">
-        <v>標籤</v>
+        <v>基於</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Validation</v>
+        <v>demo implementation</v>
       </c>
       <c r="B86" t="str">
-        <v>验证</v>
+        <v>演示实现</v>
       </c>
       <c r="C86" t="str">
-        <v>驗證</v>
+        <v>示範實作</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Analysis</v>
+        <v>Validating…</v>
       </c>
       <c r="B87" t="str">
-        <v>分析</v>
+        <v>正在验证…</v>
       </c>
       <c r="C87" t="str">
-        <v>分析</v>
+        <v>驗證中…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B88" t="str">
-        <v>中性轴墨量</v>
+        <v>保存 ICC 配置文件</v>
       </c>
       <c r="C88" t="str">
-        <v>中性軸墨量</v>
+        <v>儲存 ICC 設定檔</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B89" t="str">
-        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
+        <v>● 已修改 — 尚未保存</v>
       </c>
       <c r="C89" t="str">
-        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
+        <v>● 已修改 — 尚未儲存</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
+        <v>配置文件</v>
       </c>
       <c r="C90" t="str">
-        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
+        <v>設定檔</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B91" t="str">
-        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
+        <v>显示配置文件池</v>
       </c>
       <c r="C91" t="str">
-        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
+        <v>顯示設定檔集區</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Rendering intent</v>
+        <v>Collapse</v>
       </c>
       <c r="B92" t="str">
-        <v>渲染意图</v>
+        <v>收起</v>
       </c>
       <c r="C92" t="str">
-        <v>轉換意圖</v>
+        <v>收合</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>% ink</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B93" t="str">
-        <v>% 墨量</v>
+        <v>加载配置文件</v>
       </c>
       <c r="C93" t="str">
-        <v>% 墨量</v>
+        <v>載入設定檔</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Perceptual</v>
+        <v>Remove</v>
       </c>
       <c r="B94" t="str">
-        <v>感知</v>
+        <v>移除</v>
       </c>
       <c r="C94" t="str">
-        <v>感知</v>
+        <v>移除</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B95" t="str">
-        <v>相对比色</v>
+        <v>将 ICC 配置文件拖放到此处</v>
       </c>
       <c r="C95" t="str">
-        <v>相對比色</v>
+        <v>將 ICC 設定檔拖放到此處</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Saturation</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B96" t="str">
-        <v>饱和度</v>
+        <v>或拖入图像 (TIFF/PNG/JPEG) 以提取其嵌入的配置文件 — 文件保留在您的设备上。</v>
       </c>
       <c r="C96" t="str">
-        <v>飽和度</v>
+        <v>或拖入影像 (TIFF/PNG/JPEG) 以擷取其內嵌設定檔 — 檔案會保留在您的裝置上。</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>New from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>绝对比色</v>
+        <v>从 .cube 新建</v>
       </c>
       <c r="C97" t="str">
-        <v>絕對比色</v>
+        <v>從 .cube 新建</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Statistics</v>
+        <v>Sort by name</v>
       </c>
       <c r="B98" t="str">
-        <v>特性文件统计</v>
+        <v>按名称排序</v>
       </c>
       <c r="C98" t="str">
-        <v>特性檔統計</v>
+        <v>依名稱排序</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>A–Z</v>
       </c>
       <c r="B99" t="str">
-        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
+        <v>A–Z</v>
       </c>
       <c r="C99" t="str">
-        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B100" t="str">
-        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
+        <v>从 .cube 新建配置文件</v>
       </c>
       <c r="C100" t="str">
-        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
+        <v>從 .cube 新建設定檔</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Rendering intent</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B101" t="str">
-        <v>渲染意图</v>
+        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并下载。</v>
       </c>
       <c r="C101" t="str">
-        <v>轉換意圖</v>
+        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並下載。</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B102" t="str">
-        <v>色域体积 (ΔE³)</v>
+        <v>选择 .cube 文件</v>
       </c>
       <c r="C102" t="str">
-        <v>色域體積 (ΔE³)</v>
+        <v>選擇 .cube 檔案</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Round-trip ΔE</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B103" t="str">
-        <v>往返 ΔE</v>
+        <v>或拖放到此处，或在下方粘贴</v>
       </c>
       <c r="C103" t="str">
-        <v>往返 ΔE</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
-      </c>
-      <c r="B104" t="str">
-        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
-      </c>
-      <c r="C104" t="str">
-        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
+        <v>或拖放到此處，或在下方貼上</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
+      </c>
+      <c r="C104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>mean</v>
+        <v>Cancel</v>
       </c>
       <c r="B105" t="str">
-        <v>均值</v>
+        <v>取消</v>
       </c>
       <c r="C105" t="str">
-        <v>平均</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>P90</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B106" t="str">
-        <v>P90</v>
+        <v>创建 DeviceLink</v>
       </c>
       <c r="C106" t="str">
-        <v>P90</v>
+        <v>建立 DeviceLink</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>max</v>
+        <v>Creating…</v>
       </c>
       <c r="B107" t="str">
-        <v>最大</v>
+        <v>正在创建…</v>
       </c>
       <c r="C107" t="str">
-        <v>最大</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Analysing…</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B108" t="str">
-        <v>正在分析…</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C108" t="str">
-        <v>正在分析…</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Analysis</v>
+        <v>Profile</v>
       </c>
       <c r="B109" t="str">
-        <v>分析</v>
+        <v>配置文件</v>
       </c>
       <c r="C109" t="str">
-        <v>分析</v>
+        <v>設定檔</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Compare</v>
       </c>
       <c r="B110" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>比较</v>
       </c>
       <c r="C110" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Plot</v>
+        <v>Link</v>
       </c>
       <c r="B111" t="str">
-        <v>绘图</v>
+        <v>链接</v>
       </c>
       <c r="C111" t="str">
-        <v>繪圖</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Raw Output</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B112" t="str">
-        <v>原始输出</v>
+        <v>将配置文件从池中拖到此选项卡</v>
       </c>
       <c r="C112" t="str">
-        <v>原始輸出</v>
+        <v>將設定檔從集區拖到此分頁</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>XML</v>
+        <v>Remove</v>
       </c>
       <c r="B113" t="str">
-        <v>XML</v>
+        <v>移除</v>
       </c>
       <c r="C113" t="str">
-        <v>XML</v>
+        <v>移除</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>JSON</v>
+        <v>No profile selected</v>
       </c>
       <c r="B114" t="str">
-        <v>JSON</v>
+        <v>未选择配置文件</v>
       </c>
       <c r="C114" t="str">
-        <v>JSON</v>
+        <v>未選擇設定檔</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B115" t="str">
-        <v>曲线</v>
+        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
       </c>
       <c r="C115" t="str">
-        <v>曲線</v>
+        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Input curves</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B116" t="str">
-        <v>输入曲线</v>
+        <v>暂无可比较的内容</v>
       </c>
       <c r="C116" t="str">
-        <v>輸入曲線</v>
+        <v>尚無可比較的內容</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Output curves</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B117" t="str">
-        <v>输出曲线</v>
+        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
       </c>
       <c r="C117" t="str">
-        <v>輸出曲線</v>
+        <v>將一個或多個設定檔拖到「比較」分頁。</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>CLUT image</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B118" t="str">
-        <v>CLUT 图像</v>
+        <v>色域比较</v>
       </c>
       <c r="C118" t="str">
-        <v>CLUT 影像</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut image</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B119" t="str">
-        <v>色域图像</v>
+        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
       </c>
       <c r="C119" t="str">
-        <v>色域影像</v>
+        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Chromaticity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B120" t="str">
-        <v>色度</v>
+        <v>渲染意图</v>
       </c>
       <c r="C120" t="str">
-        <v>色度</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Scatter plot</v>
+        <v>Shell</v>
       </c>
       <c r="B121" t="str">
-        <v>散点图</v>
+        <v>外壳</v>
       </c>
       <c r="C121" t="str">
-        <v>散佈圖</v>
+        <v>外殼</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tone response curve</v>
+        <v>Wireframe</v>
       </c>
       <c r="B122" t="str">
-        <v>色调响应曲线</v>
+        <v>线框</v>
       </c>
       <c r="C122" t="str">
-        <v>色調響應曲線</v>
+        <v>線框</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Curve table</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>曲线表</v>
+        <v>不透明度</v>
       </c>
       <c r="C123" t="str">
-        <v>曲線表</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tables</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>表格</v>
+        <v>颜色</v>
       </c>
       <c r="C124" t="str">
-        <v>表格</v>
+        <v>色彩</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Data</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>数据</v>
+        <v>纯色</v>
       </c>
       <c r="C125" t="str">
-        <v>資料</v>
+        <v>純色</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Evaluate</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>求值</v>
+        <v>按数值</v>
       </c>
       <c r="C126" t="str">
-        <v>求值</v>
+        <v>依數值</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Loading…</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>加载中…</v>
+        <v>按色相</v>
       </c>
       <c r="C127" t="str">
-        <v>載入中…</v>
+        <v>依色相</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Input</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>输入</v>
+        <v>旋转</v>
       </c>
       <c r="C128" t="str">
-        <v>輸入</v>
+        <v>旋轉</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Output</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>输出</v>
+        <v>转盘</v>
       </c>
       <c r="C129" t="str">
-        <v>輸出</v>
+        <v>轉盤</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Floating point</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>浮点值</v>
+        <v>轨道</v>
       </c>
       <c r="C130" t="str">
-        <v>浮點值</v>
+        <v>軌道</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Grid point</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>网格点</v>
+        <v>拖动速度</v>
       </c>
       <c r="C131" t="str">
-        <v>網格點</v>
+        <v>拖曳速度</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Normalized</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>归一化</v>
+        <v>翻滚</v>
       </c>
       <c r="C132" t="str">
-        <v>正規化</v>
+        <v>翻滾</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Human</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>可读值</v>
+        <v>翻滚速度</v>
       </c>
       <c r="C133" t="str">
-        <v>可讀值</v>
+        <v>翻滾速度</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Device → PCS</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>设备 → PCS</v>
+        <v>正在构建色域…</v>
       </c>
       <c r="C134" t="str">
-        <v>裝置 → PCS</v>
+        <v>正在建構色域…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PCS → Device</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>PCS → 设备</v>
+        <v>无色域</v>
       </c>
       <c r="C135" t="str">
-        <v>PCS → 裝置</v>
+        <v>無色域</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>No CLUT grid</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>无 CLUT 网格</v>
+        <v>显示/隐藏</v>
       </c>
       <c r="C136" t="str">
-        <v>無 CLUT 網格</v>
+        <v>顯示/隱藏</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Loading…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>加载中…</v>
+        <v>3D 色域外壳</v>
       </c>
       <c r="C137" t="str">
-        <v>載入中…</v>
+        <v>3D 色域外殼</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>2D 色域切片</v>
       </c>
       <c r="C138" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>2D 色域切片</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>平面</v>
       </c>
       <c r="C139" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>L*</v>
       </c>
       <c r="C140" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>a*</v>
       </c>
       <c r="C141" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>b*</v>
       </c>
       <c r="C142" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
       </c>
       <c r="C143" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>链接</v>
       </c>
       <c r="C144" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Security</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>安全性</v>
+        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
       </c>
       <c r="C145" t="str">
-        <v>安全性</v>
+        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Conformance</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>符合性</v>
+        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
       </c>
       <c r="C146" t="str">
-        <v>符合性</v>
+        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Quality</v>
+        <v>V4 Display Maker</v>
       </c>
       <c r="B147" t="str">
-        <v>质量</v>
+        <v>V4 显示器生成器</v>
       </c>
       <c r="C147" t="str">
-        <v>品質</v>
+        <v>V4 顯示器產生器</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REPORT</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>报告</v>
+        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
       </c>
       <c r="C148" t="str">
-        <v>報告</v>
+        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FAIL</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>失败</v>
+        <v>V5 RGB 显示器</v>
       </c>
       <c r="C149" t="str">
-        <v>失敗</v>
+        <v>V5 RGB 顯示器</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>checks</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>项检查</v>
+        <v>拖入显示器配置文件</v>
       </c>
       <c r="C150" t="str">
-        <v>項檢查</v>
+        <v>拖入顯示器設定檔</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>V5 观察者 (PCC)</v>
       </c>
       <c r="C151" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>V5 觀察者 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>拖入观察者配置文件</v>
       </c>
       <c r="C152" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>拖入觀察者設定檔</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
       </c>
       <c r="C153" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Powered by {lib}</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>创建 V4 显示器配置文件</v>
       </c>
       <c r="C154" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>建立 V4 顯示器設定檔</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Subscribe</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>订阅</v>
+        <v>配置文件名称</v>
       </c>
       <c r="C155" t="str">
-        <v>訂閱</v>
+        <v>設定檔名稱</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>创建</v>
       </c>
       <c r="C156" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>建立</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Get notified about new releases</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>订阅新版本通知</v>
+        <v>正在创建…</v>
       </c>
       <c r="C157" t="str">
-        <v>訂閱新版本通知</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Close</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>关闭</v>
+        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
       </c>
       <c r="C158" t="str">
-        <v>關閉</v>
+        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Cancel</v>
       </c>
       <c r="B159" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>取消</v>
       </c>
       <c r="C159" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Email address</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B160" t="str">
-        <v>电子邮件地址</v>
+        <v>有 {n} 个文件未加载</v>
       </c>
       <c r="C160" t="str">
-        <v>電子郵件地址</v>
+        <v>有 {n} 個檔案未載入</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>you@example.com</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B161" t="str">
-        <v>you@example.com</v>
+        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
       </c>
       <c r="C161" t="str">
-        <v>you@example.com</v>
+        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>How will you use profiletool?</v>
+        <v>OK</v>
       </c>
       <c r="B162" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>确定</v>
       </c>
       <c r="C162" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>確定</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>(optional)</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B163" t="str">
-        <v>（选填）</v>
+        <v>将 ICC 配置文件拖到此处</v>
       </c>
       <c r="C163" t="str">
-        <v>（選填）</v>
+        <v>將 ICC 設定檔拖到此處</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>or</v>
       </c>
       <c r="B164" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>或</v>
       </c>
       <c r="C164" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>或</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Choose file</v>
       </c>
       <c r="B165" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>选择文件</v>
       </c>
       <c r="C165" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>選擇檔案</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cancel</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B166" t="str">
-        <v>取消</v>
+        <v>.icc 和 .icm 文件</v>
       </c>
       <c r="C166" t="str">
-        <v>取消</v>
+        <v>.icc 與 .icm 檔案</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Subscribe</v>
+        <v>Header</v>
       </c>
       <c r="B167" t="str">
-        <v>订阅</v>
+        <v>标头</v>
       </c>
       <c r="C167" t="str">
-        <v>訂閱</v>
+        <v>標頭</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Tags</v>
       </c>
       <c r="B168" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>标签</v>
       </c>
       <c r="C168" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>標籤</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Validation</v>
       </c>
       <c r="B169" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>验证</v>
       </c>
       <c r="C169" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>驗證</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>Analysis</v>
       </c>
       <c r="B170" t="str">
-        <v>关闭</v>
+        <v>分析</v>
       </c>
       <c r="C170" t="str">
-        <v>關閉</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Privacy notice</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B171" t="str">
-        <v>隐私声明</v>
+        <v>中性轴墨量</v>
       </c>
       <c r="C171" t="str">
-        <v>隱私聲明</v>
+        <v>中性軸墨量</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B172" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
       </c>
       <c r="C172" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B173" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C173" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Please check the form and try again.</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B174" t="str">
-        <v>请检查表单后重试。</v>
+        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
       </c>
       <c r="C174" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B175" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>渲染意图</v>
       </c>
       <c r="C175" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Network error. Please try again.</v>
+        <v>% ink</v>
       </c>
       <c r="B176" t="str">
-        <v>网络错误，请重试。</v>
+        <v>% 墨量</v>
       </c>
       <c r="C176" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>% 墨量</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Error:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B177" t="str">
-        <v>错误：</v>
+        <v>感知</v>
       </c>
       <c r="C177" t="str">
-        <v>錯誤：</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Convert to XML</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B178" t="str">
-        <v>转换为 XML</v>
+        <v>相对比色</v>
       </c>
       <c r="C178" t="str">
-        <v>轉換為 XML</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Convert to JSON</v>
+        <v>Saturation</v>
       </c>
       <c r="B179" t="str">
-        <v>转换为 JSON</v>
+        <v>饱和度</v>
       </c>
       <c r="C179" t="str">
-        <v>轉換為 JSON</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Convert to ICC</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B180" t="str">
-        <v>转换为 ICC</v>
+        <v>绝对比色</v>
       </c>
       <c r="C180" t="str">
-        <v>轉換為 ICC</v>
+        <v>絕對比色</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Converting to XML…</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B181" t="str">
-        <v>正在转换为 XML…</v>
+        <v>特性文件统计</v>
       </c>
       <c r="C181" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>特性檔統計</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Converting to JSON…</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B182" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
       </c>
       <c r="C182" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Converting to ICC…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B183" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
       </c>
       <c r="C183" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Load ICC profile</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B184" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>渲染意图</v>
       </c>
       <c r="C184" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B185" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>色域体积 (ΔE³)</v>
       </c>
       <c r="C185" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>色域體積 (ΔE³)</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Profile ID</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B186" t="str">
-        <v>配置文件 ID</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C186" t="str">
-        <v>設定檔 ID</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>No tags found.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B187" t="str">
-        <v>未找到标签。</v>
+        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
       </c>
       <c r="C187" t="str">
-        <v>找不到標籤。</v>
+        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tag Name</v>
+        <v>mean</v>
       </c>
       <c r="B188" t="str">
-        <v>标签名称</v>
+        <v>均值</v>
       </c>
       <c r="C188" t="str">
-        <v>標籤名稱</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
       <c r="B189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
       <c r="C189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Offset</v>
+        <v>max</v>
       </c>
       <c r="B190" t="str">
-        <v>偏移</v>
+        <v>最大</v>
       </c>
       <c r="C190" t="str">
-        <v>偏移</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Size</v>
+        <v>Analysing…</v>
       </c>
       <c r="B191" t="str">
-        <v>大小</v>
+        <v>正在分析…</v>
       </c>
       <c r="C191" t="str">
-        <v>大小</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Pad</v>
+        <v>Analysis</v>
       </c>
       <c r="B192" t="str">
-        <v>填充</v>
+        <v>分析</v>
       </c>
       <c r="C192" t="str">
-        <v>填充</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B193" t="str">
-        <v>加载后字节已更改</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C193" t="str">
-        <v>載入後位元組已變更</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Type</v>
+        <v>Plot</v>
       </c>
       <c r="B194" t="str">
-        <v>类型</v>
+        <v>绘图</v>
       </c>
       <c r="C194" t="str">
-        <v>類型</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Array of {type}</v>
+        <v>Raw Output</v>
       </c>
       <c r="B195" t="str">
-        <v>{type} 数组</v>
+        <v>原始输出</v>
       </c>
       <c r="C195" t="str">
-        <v>{type} 陣列</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>(No content)</v>
+        <v>XML</v>
       </c>
       <c r="B196" t="str">
-        <v>（无内容）</v>
+        <v>XML</v>
       </c>
       <c r="C196" t="str">
-        <v>（無內容）</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
       <c r="B197" t="str">
-        <v>字节</v>
+        <v>JSON</v>
       </c>
       <c r="C197" t="str">
-        <v>位元組</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Loading full description…</v>
+        <v>Curves</v>
       </c>
       <c r="B198" t="str">
-        <v>正在加载完整描述…</v>
+        <v>曲线</v>
       </c>
       <c r="C198" t="str">
-        <v>正在載入完整描述…</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not load full description:</v>
+        <v>Input curves</v>
       </c>
       <c r="B199" t="str">
-        <v>无法加载完整描述：</v>
+        <v>输入曲线</v>
       </c>
       <c r="C199" t="str">
-        <v>無法載入完整描述：</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Output curves</v>
       </c>
       <c r="B200" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>输出曲线</v>
       </c>
       <c r="C200" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B201" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C201" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>No validation output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B202" t="str">
-        <v>无验证输出</v>
+        <v>色域图像</v>
       </c>
       <c r="C202" t="str">
-        <v>無驗證輸出</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Profile is valid</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B203" t="str">
-        <v>配置文件有效</v>
+        <v>色度</v>
       </c>
       <c r="C203" t="str">
-        <v>設定檔有效</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B204" t="str">
-        <v>配置文件有警告</v>
+        <v>散点图</v>
       </c>
       <c r="C204" t="str">
-        <v>設定檔有警告</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B205" t="str">
-        <v>配置文件不合规</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C205" t="str">
-        <v>設定檔不符合規範</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Critical validation error</v>
+        <v>Curve table</v>
       </c>
       <c r="B206" t="str">
-        <v>严重验证错误</v>
+        <v>曲线表</v>
       </c>
       <c r="C206" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Unknown validation status</v>
+        <v>Tables</v>
       </c>
       <c r="B207" t="str">
-        <v>未知验证状态</v>
+        <v>表格</v>
       </c>
       <c r="C207" t="str">
-        <v>未知驗證狀態</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Data</v>
       </c>
       <c r="B208" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>数据</v>
       </c>
       <c r="C208" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B209" t="str">
-        <v>未发现警告或错误。</v>
+        <v>求值</v>
       </c>
       <c r="C209" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Valid</v>
+        <v>Loading…</v>
       </c>
       <c r="B210" t="str">
-        <v>有效</v>
+        <v>加载中…</v>
       </c>
       <c r="C210" t="str">
-        <v>有效</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Warning</v>
+        <v>Input</v>
       </c>
       <c r="B211" t="str">
-        <v>警告</v>
+        <v>输入</v>
       </c>
       <c r="C211" t="str">
-        <v>警告</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Error</v>
+        <v>Output</v>
       </c>
       <c r="B212" t="str">
-        <v>错误</v>
+        <v>输出</v>
       </c>
       <c r="C212" t="str">
-        <v>錯誤</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Unknown</v>
+        <v>Floating point</v>
       </c>
       <c r="B213" t="str">
-        <v>未知</v>
+        <v>浮点值</v>
       </c>
       <c r="C213" t="str">
-        <v>未知</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Pass</v>
+        <v>Grid point</v>
       </c>
       <c r="B214" t="str">
-        <v>通过</v>
+        <v>网格点</v>
       </c>
       <c r="C214" t="str">
-        <v>通過</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Fail</v>
+        <v>Normalized</v>
       </c>
       <c r="B215" t="str">
-        <v>失败</v>
+        <v>归一化</v>
       </c>
       <c r="C215" t="str">
-        <v>失敗</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>View in context</v>
+        <v>Human</v>
       </c>
       <c r="B216" t="str">
-        <v>在上下文中查看</v>
+        <v>可读值</v>
       </c>
       <c r="C216" t="str">
-        <v>在上下文中檢視</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Validation detail</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B217" t="str">
-        <v>验证详情</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C217" t="str">
-        <v>驗證詳情</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Triggered by</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B218" t="str">
-        <v>触发字段</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C218" t="str">
-        <v>觸發欄位</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Field</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B219" t="str">
-        <v>字段</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C219" t="str">
-        <v>欄位</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Current value</v>
+        <v>Loading…</v>
       </c>
       <c r="B220" t="str">
-        <v>当前值</v>
+        <v>加载中…</v>
       </c>
       <c r="C220" t="str">
-        <v>目前值</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Required: 0</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B221" t="str">
-        <v>要求：0</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C221" t="str">
-        <v>要求：0</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B222" t="str">
-        <v>预期：{value}</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C222" t="str">
-        <v>預期：{value}</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invalid</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B223" t="str">
-        <v>无效</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C223" t="str">
-        <v>無效</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B224" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C224" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B225" t="str">
-        <v>关闭</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C225" t="str">
-        <v>關閉</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Loading XML editor…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B226" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C226" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B227" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C227" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Security</v>
       </c>
       <c r="B228" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>安全性</v>
       </c>
       <c r="C228" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Conformance</v>
       </c>
       <c r="B229" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>符合性</v>
       </c>
       <c r="C229" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Quality</v>
       </c>
       <c r="B230" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>质量</v>
       </c>
       <c r="C230" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>REPORT</v>
       </c>
       <c r="B231" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>报告</v>
       </c>
       <c r="C231" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>FAIL</v>
       </c>
       <c r="B232" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>失败</v>
       </c>
       <c r="C232" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>checks</v>
       </c>
       <c r="B233" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>项检查</v>
       </c>
       <c r="C233" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>indent</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B234" t="str">
-        <v>缩进</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C234" t="str">
-        <v>縮排</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sort keys</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B235" t="str">
-        <v>排序键</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C235" t="str">
-        <v>排序鍵</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B236" t="str">
+        <v>ICC 配置文件工具</v>
+      </c>
+      <c r="C236" t="str">
+        <v>ICC 設定檔工具</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B237" t="str">
+        <v>由 {lib} 提供支持</v>
+      </c>
+      <c r="C237" t="str">
+        <v>由 {lib} 提供支援</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B238" t="str">
+        <v>订阅</v>
+      </c>
+      <c r="C238" t="str">
+        <v>訂閱</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B239" t="str">
+        <v>在 profiletool 新版本发布时收到通知</v>
+      </c>
+      <c r="C239" t="str">
+        <v>在 profiletool 新版本發佈時收到通知</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B240" t="str">
+        <v>订阅新版本通知</v>
+      </c>
+      <c r="C240" t="str">
+        <v>訂閱新版本通知</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B241" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C241" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B242" t="str">
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+      </c>
+      <c r="C242" t="str">
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B243" t="str">
+        <v>电子邮件地址</v>
+      </c>
+      <c r="C243" t="str">
+        <v>電子郵件地址</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B244" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="C244" t="str">
+        <v>you@example.com</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B245" t="str">
+        <v>您打算如何使用 profiletool？</v>
+      </c>
+      <c r="C245" t="str">
+        <v>您打算如何使用 profiletool？</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B246" t="str">
+        <v>（选填）</v>
+      </c>
+      <c r="C246" t="str">
+        <v>（選填）</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B247" t="str">
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+      </c>
+      <c r="C247" t="str">
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B248" t="str">
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+      </c>
+      <c r="C248" t="str">
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B249" t="str">
+        <v>取消</v>
+      </c>
+      <c r="C249" t="str">
+        <v>取消</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B250" t="str">
+        <v>订阅</v>
+      </c>
+      <c r="C250" t="str">
+        <v>訂閱</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B251" t="str">
+        <v>谢谢 — 我们会再联系您。</v>
+      </c>
+      <c r="C251" t="str">
+        <v>感謝 — 我們會再聯絡您。</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B252" t="str">
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+      </c>
+      <c r="C252" t="str">
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B253" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C253" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B254" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="C254" t="str">
+        <v>隱私聲明</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B255" t="str">
+        <v>请输入有效的电子邮件地址。</v>
+      </c>
+      <c r="C255" t="str">
+        <v>請輸入有效的電子郵件地址。</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B256" t="str">
+        <v>请求过多，请稍后再试。</v>
+      </c>
+      <c r="C256" t="str">
+        <v>請求過多，請稍後再試。</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B257" t="str">
+        <v>请检查表单后重试。</v>
+      </c>
+      <c r="C257" t="str">
+        <v>請檢查表單後重試。</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B258" t="str">
+        <v>无法发送您的请求，请重试。</v>
+      </c>
+      <c r="C258" t="str">
+        <v>無法傳送您的請求，請重試。</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>网络错误，请重试。</v>
+      </c>
+      <c r="C259" t="str">
+        <v>網路錯誤，請重試。</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B260" t="str">
+        <v>错误：</v>
+      </c>
+      <c r="C260" t="str">
+        <v>錯誤：</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B261" t="str">
+        <v>转换为 XML</v>
+      </c>
+      <c r="C261" t="str">
+        <v>轉換為 XML</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B262" t="str">
+        <v>转换为 JSON</v>
+      </c>
+      <c r="C262" t="str">
+        <v>轉換為 JSON</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B263" t="str">
+        <v>转换为 ICC</v>
+      </c>
+      <c r="C263" t="str">
+        <v>轉換為 ICC</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B264" t="str">
+        <v>正在转换为 XML…</v>
+      </c>
+      <c r="C264" t="str">
+        <v>正在轉換為 XML…</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B265" t="str">
+        <v>正在转换为 JSON…</v>
+      </c>
+      <c r="C265" t="str">
+        <v>正在轉換為 JSON…</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B266" t="str">
+        <v>正在转换为 ICC…</v>
+      </c>
+      <c r="C266" t="str">
+        <v>正在轉換為 ICC…</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B267" t="str">
+        <v>加载 ICC 配置文件</v>
+      </c>
+      <c r="C267" t="str">
+        <v>載入 ICC 設定檔</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B268" t="str">
+        <v>ICC 配置文件拖放区</v>
+      </c>
+      <c r="C268" t="str">
+        <v>ICC 設定檔拖放區</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B269" t="str">
+        <v>配置文件 ID</v>
+      </c>
+      <c r="C269" t="str">
+        <v>設定檔 ID</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B270" t="str">
+        <v>未找到标签。</v>
+      </c>
+      <c r="C270" t="str">
+        <v>找不到標籤。</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B271" t="str">
+        <v>标签名称</v>
+      </c>
+      <c r="C271" t="str">
+        <v>標籤名稱</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B272" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C272" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B273" t="str">
+        <v>偏移</v>
+      </c>
+      <c r="C273" t="str">
+        <v>偏移</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B274" t="str">
+        <v>大小</v>
+      </c>
+      <c r="C274" t="str">
+        <v>大小</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B275" t="str">
+        <v>填充</v>
+      </c>
+      <c r="C275" t="str">
+        <v>填充</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B276" t="str">
+        <v>加载后字节已更改</v>
+      </c>
+      <c r="C276" t="str">
+        <v>載入後位元組已變更</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B277" t="str">
+        <v>类型</v>
+      </c>
+      <c r="C277" t="str">
+        <v>類型</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B278" t="str">
+        <v>{type} 数组</v>
+      </c>
+      <c r="C278" t="str">
+        <v>{type} 陣列</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B279" t="str">
+        <v>（无内容）</v>
+      </c>
+      <c r="C279" t="str">
+        <v>（無內容）</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B280" t="str">
+        <v>字节</v>
+      </c>
+      <c r="C280" t="str">
+        <v>位元組</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B281" t="str">
+        <v>正在加载完整描述…</v>
+      </c>
+      <c r="C281" t="str">
+        <v>正在載入完整描述…</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B282" t="str">
+        <v>无法加载完整描述：</v>
+      </c>
+      <c r="C282" t="str">
+        <v>無法載入完整描述：</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B283" t="str">
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+      </c>
+      <c r="C283" t="str">
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B284" t="str">
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+      </c>
+      <c r="C284" t="str">
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B285" t="str">
+        <v>无验证输出</v>
+      </c>
+      <c r="C285" t="str">
+        <v>無驗證輸出</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B286" t="str">
+        <v>配置文件有效</v>
+      </c>
+      <c r="C286" t="str">
+        <v>設定檔有效</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B287" t="str">
+        <v>配置文件有警告</v>
+      </c>
+      <c r="C287" t="str">
+        <v>設定檔有警告</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B288" t="str">
+        <v>配置文件不合规</v>
+      </c>
+      <c r="C288" t="str">
+        <v>設定檔不符合規範</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B289" t="str">
+        <v>严重验证错误</v>
+      </c>
+      <c r="C289" t="str">
+        <v>嚴重驗證錯誤</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B290" t="str">
+        <v>未知验证状态</v>
+      </c>
+      <c r="C290" t="str">
+        <v>未知驗證狀態</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B291" t="str">
+        <v>严重 — 仅供检查显示</v>
+      </c>
+      <c r="C291" t="str">
+        <v>嚴重 — 僅供檢視顯示</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B292" t="str">
+        <v>未发现警告或错误。</v>
+      </c>
+      <c r="C292" t="str">
+        <v>未發現警告或錯誤。</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B293" t="str">
+        <v>有效</v>
+      </c>
+      <c r="C293" t="str">
+        <v>有效</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B294" t="str">
+        <v>警告</v>
+      </c>
+      <c r="C294" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B295" t="str">
+        <v>错误</v>
+      </c>
+      <c r="C295" t="str">
+        <v>錯誤</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B296" t="str">
+        <v>未知</v>
+      </c>
+      <c r="C296" t="str">
+        <v>未知</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B297" t="str">
+        <v>通过</v>
+      </c>
+      <c r="C297" t="str">
+        <v>通過</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B298" t="str">
+        <v>失败</v>
+      </c>
+      <c r="C298" t="str">
+        <v>失敗</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B299" t="str">
+        <v>在上下文中查看</v>
+      </c>
+      <c r="C299" t="str">
+        <v>在上下文中檢視</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B300" t="str">
+        <v>验证详情</v>
+      </c>
+      <c r="C300" t="str">
+        <v>驗證詳情</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B301" t="str">
+        <v>触发字段</v>
+      </c>
+      <c r="C301" t="str">
+        <v>觸發欄位</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B302" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C302" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B303" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C303" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B304" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C304" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B305" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C305" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B306" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C306" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B307" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C307" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B308" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C308" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B309" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C309" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B310" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C310" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B311" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C311" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B312" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C312" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B313" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C313" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B314" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C314" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C315" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B316" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C316" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B317" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C317" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B318" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C318" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B236" t="str">
+      <c r="B319" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C236" t="str">
+      <c r="C319" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C319"/>
+  <dimension ref="A1:C413"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Link</v>
+        <v>Combine</v>
       </c>
       <c r="B111" t="str">
         <v>链接</v>
@@ -1636,2295 +1636,3329 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B112" t="str">
-        <v>将配置文件从池中拖到此选项卡</v>
+        <v>光谱</v>
       </c>
       <c r="C112" t="str">
-        <v>將設定檔從集區拖到此分頁</v>
+        <v>光譜</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B113" t="str">
-        <v>移除</v>
+        <v>将配置文件从池中拖到此选项卡</v>
       </c>
       <c r="C113" t="str">
-        <v>移除</v>
+        <v>將設定檔從集區拖到此分頁</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B114" t="str">
-        <v>未选择配置文件</v>
+        <v>移除</v>
       </c>
       <c r="C114" t="str">
-        <v>未選擇設定檔</v>
+        <v>移除</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B115" t="str">
-        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
+        <v>未选择配置文件</v>
       </c>
       <c r="C115" t="str">
-        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
+        <v>未選擇設定檔</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B116" t="str">
-        <v>暂无可比较的内容</v>
+        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
       </c>
       <c r="C116" t="str">
-        <v>尚無可比較的內容</v>
+        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B117" t="str">
-        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
+        <v>暂无可比较的内容</v>
       </c>
       <c r="C117" t="str">
-        <v>將一個或多個設定檔拖到「比較」分頁。</v>
+        <v>尚無可比較的內容</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B118" t="str">
-        <v>色域比较</v>
+        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
       </c>
       <c r="C118" t="str">
-        <v>色域比較</v>
+        <v>將一個或多個設定檔拖到「比較」分頁。</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B119" t="str">
-        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
+        <v>色域比较</v>
       </c>
       <c r="C119" t="str">
-        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B120" t="str">
-        <v>渲染意图</v>
+        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
       </c>
       <c r="C120" t="str">
-        <v>轉換意圖</v>
+        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B121" t="str">
-        <v>外壳</v>
+        <v>渲染意图</v>
       </c>
       <c r="C121" t="str">
-        <v>外殼</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B122" t="str">
-        <v>线框</v>
+        <v>外壳</v>
       </c>
       <c r="C122" t="str">
-        <v>線框</v>
+        <v>外殼</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Wireframe</v>
       </c>
       <c r="B123" t="str">
-        <v>不透明度</v>
+        <v>线框</v>
       </c>
       <c r="C123" t="str">
-        <v>不透明度</v>
+        <v>線框</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B124" t="str">
-        <v>颜色</v>
+        <v>轴编号</v>
       </c>
       <c r="C124" t="str">
-        <v>色彩</v>
+        <v>軸編號</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Opacity</v>
       </c>
       <c r="B125" t="str">
-        <v>纯色</v>
+        <v>不透明度</v>
       </c>
       <c r="C125" t="str">
-        <v>純色</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Colour</v>
       </c>
       <c r="B126" t="str">
-        <v>按数值</v>
+        <v>颜色</v>
       </c>
       <c r="C126" t="str">
-        <v>依數值</v>
+        <v>色彩</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Solid</v>
       </c>
       <c r="B127" t="str">
-        <v>按色相</v>
+        <v>纯色</v>
       </c>
       <c r="C127" t="str">
-        <v>依色相</v>
+        <v>純色</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>By value</v>
       </c>
       <c r="B128" t="str">
-        <v>旋转</v>
+        <v>按数值</v>
       </c>
       <c r="C128" t="str">
-        <v>旋轉</v>
+        <v>依數值</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>By hue</v>
       </c>
       <c r="B129" t="str">
-        <v>转盘</v>
+        <v>按色相</v>
       </c>
       <c r="C129" t="str">
-        <v>轉盤</v>
+        <v>依色相</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>Rotation</v>
       </c>
       <c r="B130" t="str">
-        <v>轨道</v>
+        <v>旋转</v>
       </c>
       <c r="C130" t="str">
-        <v>軌道</v>
+        <v>旋轉</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B131" t="str">
-        <v>拖动速度</v>
+        <v>转盘</v>
       </c>
       <c r="C131" t="str">
-        <v>拖曳速度</v>
+        <v>轉盤</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Orbit</v>
       </c>
       <c r="B132" t="str">
-        <v>翻滚</v>
+        <v>轨道</v>
       </c>
       <c r="C132" t="str">
-        <v>翻滾</v>
+        <v>軌道</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Drag speed</v>
       </c>
       <c r="B133" t="str">
-        <v>翻滚速度</v>
+        <v>拖动速度</v>
       </c>
       <c r="C133" t="str">
-        <v>翻滾速度</v>
+        <v>拖曳速度</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Roll</v>
       </c>
       <c r="B134" t="str">
-        <v>正在构建色域…</v>
+        <v>翻滚</v>
       </c>
       <c r="C134" t="str">
-        <v>正在建構色域…</v>
+        <v>翻滾</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Roll speed</v>
       </c>
       <c r="B135" t="str">
-        <v>无色域</v>
+        <v>翻滚速度</v>
       </c>
       <c r="C135" t="str">
-        <v>無色域</v>
+        <v>翻滾速度</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B136" t="str">
-        <v>显示/隐藏</v>
+        <v>正在构建色域…</v>
       </c>
       <c r="C136" t="str">
-        <v>顯示/隱藏</v>
+        <v>正在建構色域…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>no gamut</v>
       </c>
       <c r="B137" t="str">
-        <v>3D 色域外壳</v>
+        <v>无色域</v>
       </c>
       <c r="C137" t="str">
-        <v>3D 色域外殼</v>
+        <v>無色域</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Show / hide</v>
       </c>
       <c r="B138" t="str">
-        <v>2D 色域切片</v>
+        <v>显示/隐藏</v>
       </c>
       <c r="C138" t="str">
-        <v>2D 色域切片</v>
+        <v>顯示/隱藏</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B139" t="str">
-        <v>平面</v>
+        <v>3D 色域外壳</v>
       </c>
       <c r="C139" t="str">
-        <v>平面</v>
+        <v>3D 色域外殼</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>2D 色域切片</v>
       </c>
       <c r="C140" t="str">
-        <v>L*</v>
+        <v>2D 色域切片</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>Plane</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>平面</v>
       </c>
       <c r="C141" t="str">
-        <v>a*</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
       <c r="C142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>a*</v>
       </c>
       <c r="B143" t="str">
-        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
+        <v>a*</v>
       </c>
       <c r="C143" t="str">
-        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>b*</v>
       </c>
       <c r="B144" t="str">
-        <v>链接</v>
+        <v>b*</v>
       </c>
       <c r="C144" t="str">
-        <v>連結</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B145" t="str">
-        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
+        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
       </c>
       <c r="C145" t="str">
-        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
+        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>Linking</v>
       </c>
       <c r="B146" t="str">
-        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
+        <v>链接</v>
       </c>
       <c r="C146" t="str">
-        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>V4 Display Maker</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B147" t="str">
-        <v>V4 显示器生成器</v>
+        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
       </c>
       <c r="C147" t="str">
-        <v>V4 顯示器產生器</v>
+        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B148" t="str">
-        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
+        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
       </c>
       <c r="C148" t="str">
-        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
+        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>Observer Change</v>
       </c>
       <c r="B149" t="str">
-        <v>V5 RGB 显示器</v>
+        <v>V4 显示器生成器</v>
       </c>
       <c r="C149" t="str">
-        <v>V5 RGB 顯示器</v>
+        <v>V4 顯示器產生器</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B150" t="str">
-        <v>拖入显示器配置文件</v>
+        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
       </c>
       <c r="C150" t="str">
-        <v>拖入顯示器設定檔</v>
+        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B151" t="str">
-        <v>V5 观察者 (PCC)</v>
+        <v>V5 RGB 显示器</v>
       </c>
       <c r="C151" t="str">
-        <v>V5 觀察者 (PCC)</v>
+        <v>V5 RGB 顯示器</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B152" t="str">
-        <v>拖入观察者配置文件</v>
+        <v>拖入显示器配置文件</v>
       </c>
       <c r="C152" t="str">
-        <v>拖入觀察者設定檔</v>
+        <v>拖入顯示器設定檔</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B153" t="str">
-        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
+        <v>V5 观察者 (PCC)</v>
       </c>
       <c r="C153" t="str">
-        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
+        <v>V5 觀察者 (PCC)</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B154" t="str">
-        <v>创建 V4 显示器配置文件</v>
+        <v>拖入观察者配置文件</v>
       </c>
       <c r="C154" t="str">
-        <v>建立 V4 顯示器設定檔</v>
+        <v>拖入觀察者設定檔</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B155" t="str">
-        <v>配置文件名称</v>
+        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
       </c>
       <c r="C155" t="str">
-        <v>設定檔名稱</v>
+        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B156" t="str">
-        <v>创建</v>
+        <v>创建 V4 显示器配置文件</v>
       </c>
       <c r="C156" t="str">
-        <v>建立</v>
+        <v>建立 V4 顯示器設定檔</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Profile name</v>
       </c>
       <c r="B157" t="str">
-        <v>正在创建…</v>
+        <v>配置文件名称</v>
       </c>
       <c r="C157" t="str">
-        <v>正在建立…</v>
+        <v>設定檔名稱</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Create</v>
       </c>
       <c r="B158" t="str">
-        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
+        <v>创建</v>
       </c>
       <c r="C158" t="str">
-        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
+        <v>建立</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Cancel</v>
+        <v>Making…</v>
       </c>
       <c r="B159" t="str">
-        <v>取消</v>
+        <v>正在创建…</v>
       </c>
       <c r="C159" t="str">
-        <v>取消</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B160" t="str">
-        <v>有 {n} 个文件未加载</v>
+        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
       </c>
       <c r="C160" t="str">
-        <v>有 {n} 個檔案未載入</v>
+        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B161" t="str">
-        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
+        <v>链接流水线</v>
       </c>
       <c r="C161" t="str">
-        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
+        <v>連結管線</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>OK</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B162" t="str">
-        <v>确定</v>
+        <v>构建一条配置文件链，然后生成 DeviceLink、转换图像，或通过它转换色彩数据集。</v>
       </c>
       <c r="C162" t="str">
-        <v>確定</v>
+        <v>建立一條描述檔鏈，然後產生 DeviceLink、轉換影像，或透過它轉換色彩資料集。</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Done</v>
       </c>
       <c r="B163" t="str">
-        <v>将 ICC 配置文件拖到此处</v>
+        <v>完成</v>
       </c>
       <c r="C163" t="str">
-        <v>將 ICC 設定檔拖到此處</v>
+        <v>完成</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>or</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B164" t="str">
-        <v>或</v>
+        <v>拖放图像以进行转换（TIFF/PNG/JPEG）</v>
       </c>
       <c r="C164" t="str">
-        <v>或</v>
+        <v>拖放影像以進行轉換（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Choose file</v>
+        <v>Checking image…</v>
       </c>
       <c r="B165" t="str">
-        <v>选择文件</v>
+        <v>正在检查图像…</v>
       </c>
       <c r="C165" t="str">
-        <v>選擇檔案</v>
+        <v>正在檢查影像…</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>.icc and .icm files</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B166" t="str">
-        <v>.icc 和 .icm 文件</v>
+        <v>不受支持的图像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C166" t="str">
-        <v>.icc 與 .icm 檔案</v>
+        <v>不受支援的影像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Header</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B167" t="str">
-        <v>标头</v>
+        <v>图像过大（{mp} MP；上限 {max} MP）。</v>
       </c>
       <c r="C167" t="str">
-        <v>標頭</v>
+        <v>影像過大（{mp} MP；上限 {max} MP）。</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Tags</v>
+        <v>Transform Image</v>
       </c>
       <c r="B168" t="str">
-        <v>标签</v>
+        <v>转换图像</v>
       </c>
       <c r="C168" t="str">
-        <v>標籤</v>
+        <v>轉換影像</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation</v>
+        <v>Transforming…</v>
       </c>
       <c r="B169" t="str">
-        <v>验证</v>
+        <v>正在转换…</v>
       </c>
       <c r="C169" t="str">
-        <v>驗證</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Analysis</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B170" t="str">
-        <v>分析</v>
+        <v>拖放配置文件以开始链条</v>
       </c>
       <c r="C170" t="str">
-        <v>分析</v>
+        <v>拖放描述檔以開始鏈條</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>removed</v>
       </c>
       <c r="B171" t="str">
-        <v>中性轴墨量</v>
+        <v>已移除</v>
       </c>
       <c r="C171" t="str">
-        <v>中性軸墨量</v>
+        <v>已移除</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Move earlier</v>
       </c>
       <c r="B172" t="str">
-        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
+        <v>前移</v>
       </c>
       <c r="C172" t="str">
-        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
+        <v>前移</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Move later</v>
       </c>
       <c r="B173" t="str">
-        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
+        <v>后移</v>
       </c>
       <c r="C173" t="str">
-        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
+        <v>後移</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Move up</v>
       </c>
       <c r="B174" t="str">
-        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
+        <v>上移</v>
       </c>
       <c r="C174" t="str">
-        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
+        <v>上移</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent</v>
+        <v>Move down</v>
       </c>
       <c r="B175" t="str">
-        <v>渲染意图</v>
+        <v>下移</v>
       </c>
       <c r="C175" t="str">
-        <v>轉換意圖</v>
+        <v>下移</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>% ink</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B176" t="str">
-        <v>% 墨量</v>
+        <v>渲染意图（全部）</v>
       </c>
       <c r="C176" t="str">
-        <v>% 墨量</v>
+        <v>演算意圖（全部）</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Perceptual</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B177" t="str">
-        <v>感知</v>
+        <v>此转换的渲染意图</v>
       </c>
       <c r="C177" t="str">
-        <v>感知</v>
+        <v>此轉換的演算意圖</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B178" t="str">
-        <v>相对比色</v>
+        <v>各转换使用了不同的渲染意图</v>
       </c>
       <c r="C178" t="str">
-        <v>相對比色</v>
+        <v>各轉換使用了不同的演算意圖</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Saturation</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B179" t="str">
-        <v>饱和度</v>
+        <v>翻转链条方向（反转首个转换，并影响整条链）</v>
       </c>
       <c r="C179" t="str">
-        <v>飽和度</v>
+        <v>翻轉鏈條方向（反轉首個轉換，並影響整條鏈）</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B180" t="str">
-        <v>绝对比色</v>
+        <v>链条中的某个配置文件已从池中移除——请将其移除以继续。</v>
       </c>
       <c r="C180" t="str">
-        <v>絕對比色</v>
+        <v>鏈條中的某個描述檔已從集區中移除——請將其移除以繼續。</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Profile Statistics</v>
+        <v>Chain</v>
       </c>
       <c r="B181" t="str">
-        <v>特性文件统计</v>
+        <v>链条</v>
       </c>
       <c r="C181" t="str">
-        <v>特性檔統計</v>
+        <v>鏈條</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B182" t="str">
-        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
+        <v>无法分析该链条。</v>
       </c>
       <c r="C182" t="str">
-        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
+        <v>無法分析該鏈條。</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B183" t="str">
-        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
+        <v>正在检查链条…</v>
       </c>
       <c r="C183" t="str">
-        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
+        <v>正在檢查鏈條…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Rendering intent</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B184" t="str">
-        <v>渲染意图</v>
+        <v>链条未能衔接（{detail}）。</v>
       </c>
       <c r="C184" t="str">
-        <v>轉換意圖</v>
+        <v>鏈條未能銜接（{detail}）。</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B185" t="str">
-        <v>色域体积 (ΔE³)</v>
+        <v>配置文件 {n} 未能与上一阶段衔接（{detail}）。</v>
       </c>
       <c r="C185" t="str">
-        <v>色域體積 (ΔE³)</v>
+        <v>描述檔 {n} 未能與上一階段銜接（{detail}）。</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B186" t="str">
-        <v>往返 ΔE</v>
+        <v>请先修复链条，再处理图像</v>
       </c>
       <c r="C186" t="str">
-        <v>往返 ΔE</v>
+        <v>請先修正鏈條，再處理影像</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Clear</v>
       </c>
       <c r="B187" t="str">
-        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
+        <v>清除</v>
       </c>
       <c r="C187" t="str">
-        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
+        <v>清除</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mean</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B188" t="str">
-        <v>均值</v>
+        <v>生成 DeviceLink</v>
       </c>
       <c r="C188" t="str">
-        <v>平均</v>
+        <v>產生 DeviceLink</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>P90</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B189" t="str">
-        <v>P90</v>
+        <v>DeviceLink 名称</v>
       </c>
       <c r="C189" t="str">
-        <v>P90</v>
+        <v>DeviceLink 名稱</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>max</v>
+        <v>Making…</v>
       </c>
       <c r="B190" t="str">
-        <v>最大</v>
+        <v>正在生成…</v>
       </c>
       <c r="C190" t="str">
-        <v>最大</v>
+        <v>正在產生…</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Analysing…</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B191" t="str">
-        <v>正在分析…</v>
+        <v>已创建“{name}”——已添加到池和此标签页。</v>
       </c>
       <c r="C191" t="str">
-        <v>正在分析…</v>
+        <v>已建立「{name}」——已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Analysis</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B192" t="str">
-        <v>分析</v>
+        <v>拖放 {src} 图像以转换为 {dst}——结果将下载，不会被存储。</v>
       </c>
       <c r="C192" t="str">
-        <v>分析</v>
+        <v>拖放 {src} 影像以轉換為 {dst}——結果將下載，不會被儲存。</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B193" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>构建链条以处理图像</v>
       </c>
       <c r="C193" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>建立鏈條以處理影像</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Plot</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B194" t="str">
-        <v>绘图</v>
+        <v>此链条的首尾并非图像色彩空间</v>
       </c>
       <c r="C194" t="str">
-        <v>繪圖</v>
+        <v>此鏈條的首尾並非影像色彩空間</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Raw Output</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B195" t="str">
-        <v>原始输出</v>
+        <v>已保存转换后的图像。</v>
       </c>
       <c r="C195" t="str">
-        <v>原始輸出</v>
+        <v>已儲存轉換後的影像。</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>XML</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B196" t="str">
-        <v>XML</v>
+        <v>拖放色彩数据集（CGATS/CSV/CxF/JSON）</v>
       </c>
       <c r="C196" t="str">
-        <v>XML</v>
+        <v>拖放色彩資料集（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>JSON</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B197" t="str">
-        <v>JSON</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C197" t="str">
-        <v>JSON</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Curves</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B198" t="str">
-        <v>曲线</v>
+        <v>数据文件过大。</v>
       </c>
       <c r="C198" t="str">
-        <v>曲線</v>
+        <v>資料檔案過大。</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Input curves</v>
+        <v>Transform Data</v>
       </c>
       <c r="B199" t="str">
-        <v>输入曲线</v>
+        <v>转换数据</v>
       </c>
       <c r="C199" t="str">
-        <v>輸入曲線</v>
+        <v>轉換資料</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Output curves</v>
+        <v>Transforming…</v>
       </c>
       <c r="B200" t="str">
-        <v>输出曲线</v>
+        <v>正在转换…</v>
       </c>
       <c r="C200" t="str">
-        <v>輸出曲線</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>CLUT image</v>
+        <v>Prefer</v>
       </c>
       <c r="B201" t="str">
-        <v>CLUT 图像</v>
+        <v>偏好</v>
       </c>
       <c r="C201" t="str">
-        <v>CLUT 影像</v>
+        <v>偏好</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Gamut image</v>
+        <v>Observer</v>
       </c>
       <c r="B202" t="str">
-        <v>色域图像</v>
+        <v>观察者</v>
       </c>
       <c r="C202" t="str">
-        <v>色域影像</v>
+        <v>觀察者</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Chromaticity</v>
+        <v>Illuminant</v>
       </c>
       <c r="B203" t="str">
-        <v>色度</v>
+        <v>光源</v>
       </c>
       <c r="C203" t="str">
-        <v>色度</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Scatter plot</v>
+        <v>Condition</v>
       </c>
       <c r="B204" t="str">
-        <v>散点图</v>
+        <v>条件</v>
       </c>
       <c r="C204" t="str">
-        <v>散佈圖</v>
+        <v>條件</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Tone response curve</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B205" t="str">
-        <v>色调响应曲线</v>
+        <v>过滤 {n} 个重复项</v>
       </c>
       <c r="C205" t="str">
-        <v>色調響應曲線</v>
+        <v>篩選 {n} 個重複項</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Curve table</v>
+        <v>median</v>
       </c>
       <c r="B206" t="str">
-        <v>曲线表</v>
+        <v>中位数</v>
       </c>
       <c r="C206" t="str">
-        <v>曲線表</v>
+        <v>中位數</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Tables</v>
+        <v>mean</v>
       </c>
       <c r="B207" t="str">
-        <v>表格</v>
+        <v>平均值</v>
       </c>
       <c r="C207" t="str">
-        <v>表格</v>
+        <v>平均值</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Data</v>
+        <v>patches</v>
       </c>
       <c r="B208" t="str">
-        <v>数据</v>
+        <v>色块</v>
       </c>
       <c r="C208" t="str">
-        <v>資料</v>
+        <v>色塊</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Evaluate</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B209" t="str">
-        <v>求值</v>
+        <v>{n} 个重复项</v>
       </c>
       <c r="C209" t="str">
-        <v>求值</v>
+        <v>{n} 個重複項</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Loading…</v>
+        <v>Transform result</v>
       </c>
       <c r="B210" t="str">
-        <v>加载中…</v>
+        <v>转换结果</v>
       </c>
       <c r="C210" t="str">
-        <v>載入中…</v>
+        <v>轉換結果</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Input</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B211" t="str">
-        <v>输入</v>
+        <v>{src} → {dst} · {n} 个色块</v>
       </c>
       <c r="C211" t="str">
-        <v>輸入</v>
+        <v>{src} → {dst} · {n} 個色塊</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Output</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B212" t="str">
-        <v>输出</v>
+        <v>显示前 {shown} 项，共 {total} 项——保存将写入全部数据。</v>
       </c>
       <c r="C212" t="str">
-        <v>輸出</v>
+        <v>顯示前 {shown} 項，共 {total} 項——儲存將寫入全部資料。</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Floating point</v>
+        <v>Save as</v>
       </c>
       <c r="B213" t="str">
-        <v>浮点值</v>
+        <v>另存为</v>
       </c>
       <c r="C213" t="str">
-        <v>浮點值</v>
+        <v>另存新檔</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Grid point</v>
+        <v>Save</v>
       </c>
       <c r="B214" t="str">
-        <v>网格点</v>
+        <v>保存</v>
       </c>
       <c r="C214" t="str">
-        <v>網格點</v>
+        <v>儲存</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Normalized</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B215" t="str">
-        <v>归一化</v>
+        <v>反向转换</v>
       </c>
       <c r="C215" t="str">
-        <v>正規化</v>
+        <v>反向轉換</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Human</v>
+        <v>Inverting…</v>
       </c>
       <c r="B216" t="str">
-        <v>可读值</v>
+        <v>正在反向计算…</v>
       </c>
       <c r="C216" t="str">
-        <v>可讀值</v>
+        <v>正在反向計算…</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Device → PCS</v>
+        <v>Invert</v>
       </c>
       <c r="B217" t="str">
-        <v>设备 → PCS</v>
+        <v>反转</v>
       </c>
       <c r="C217" t="str">
-        <v>裝置 → PCS</v>
+        <v>反轉</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PCS → Device</v>
+        <v>last stage</v>
       </c>
       <c r="B218" t="str">
-        <v>PCS → 设备</v>
+        <v>最后阶段</v>
       </c>
       <c r="C218" t="str">
-        <v>PCS → 裝置</v>
+        <v>最後階段</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>No CLUT grid</v>
+        <v>first stage</v>
       </c>
       <c r="B219" t="str">
-        <v>无 CLUT 网格</v>
+        <v>第一阶段</v>
       </c>
       <c r="C219" t="str">
-        <v>無 CLUT 網格</v>
+        <v>第一階段</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Loading…</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B220" t="str">
-        <v>加载中…</v>
+        <v>输入数据为 {in} → 搜索 {out}</v>
       </c>
       <c r="C220" t="str">
-        <v>載入中…</v>
+        <v>輸入資料為 {in} → 搜尋 {out}</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B221" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>反转需要 2–3 个配置文件组成的链条</v>
       </c>
       <c r="C221" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>反轉需要 2–3 個描述檔組成的鏈條</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Invalid profile URL:</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B222" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>数据集必须为 {in}；反向搜索将生成 {out}，并附带每个色块的可逆性代价。</v>
       </c>
       <c r="C222" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>資料集必須為 {in}；反向搜尋將產生 {out}，並附帶每個色塊的可逆性代價。</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B223" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>ΔE 代价</v>
       </c>
       <c r="C223" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>ΔE 代價</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B224" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>此图像嵌入了 ICC 配置文件。</v>
       </c>
       <c r="C224" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>此影像內嵌了 ICC 描述檔。</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B225" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>提取并添加到链条</v>
       </c>
       <c r="C225" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>擷取並加入鏈條</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Extracting…</v>
       </c>
       <c r="B226" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>正在提取…</v>
       </c>
       <c r="C226" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>正在擷取…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Dismiss</v>
       </c>
       <c r="B227" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>忽略</v>
       </c>
       <c r="C227" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>忽略</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Security</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B228" t="str">
-        <v>安全性</v>
+        <v>已提取嵌入的配置文件——已添加到池中并置于链条首位。</v>
       </c>
       <c r="C228" t="str">
-        <v>安全性</v>
+        <v>已擷取內嵌的描述檔——已加入集區並置於鏈條首位。</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Conformance</v>
+        <v>Image output options</v>
       </c>
       <c r="B229" t="str">
-        <v>符合性</v>
+        <v>图像输出选项</v>
       </c>
       <c r="C229" t="str">
-        <v>符合性</v>
+        <v>影像輸出選項</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Quality</v>
+        <v>Encoding</v>
       </c>
       <c r="B230" t="str">
-        <v>质量</v>
+        <v>编码</v>
       </c>
       <c r="C230" t="str">
-        <v>品質</v>
+        <v>編碼</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>REPORT</v>
+        <v>Same as source</v>
       </c>
       <c r="B231" t="str">
-        <v>报告</v>
+        <v>与源相同</v>
       </c>
       <c r="C231" t="str">
-        <v>報告</v>
+        <v>與來源相同</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>FAIL</v>
+        <v>8-bit</v>
       </c>
       <c r="B232" t="str">
-        <v>失败</v>
+        <v>8 位</v>
       </c>
       <c r="C232" t="str">
-        <v>失敗</v>
+        <v>8 位元</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>checks</v>
+        <v>16-bit</v>
       </c>
       <c r="B233" t="str">
-        <v>项检查</v>
+        <v>16 位</v>
       </c>
       <c r="C233" t="str">
-        <v>項檢查</v>
+        <v>16 位元</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B234" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>浮点（32 位）</v>
       </c>
       <c r="C234" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>浮點（32 位元）</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Compression</v>
       </c>
       <c r="B235" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>压缩</v>
       </c>
       <c r="C235" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>壓縮</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B236" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>无</v>
       </c>
       <c r="C236" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>無</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Powered by {lib}</v>
+        <v>Planar</v>
       </c>
       <c r="B237" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>平面格式</v>
       </c>
       <c r="C237" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>平面格式</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Subscribe</v>
+        <v>Composite</v>
       </c>
       <c r="B238" t="str">
-        <v>订阅</v>
+        <v>交错</v>
       </c>
       <c r="C238" t="str">
-        <v>訂閱</v>
+        <v>交錯</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Separated</v>
       </c>
       <c r="B239" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>分离</v>
       </c>
       <c r="C239" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>分離</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Get notified about new releases</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B240" t="str">
-        <v>订阅新版本通知</v>
+        <v>CMM 插值</v>
       </c>
       <c r="C240" t="str">
-        <v>訂閱新版本通知</v>
+        <v>CMM 內插</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Close</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B241" t="str">
-        <v>关闭</v>
+        <v>四面体</v>
       </c>
       <c r="C241" t="str">
-        <v>關閉</v>
+        <v>四面體</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Linear</v>
       </c>
       <c r="B242" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>线性</v>
       </c>
       <c r="C242" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>線性</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Email address</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B243" t="str">
-        <v>电子邮件地址</v>
+        <v>嵌入 ICC</v>
       </c>
       <c r="C243" t="str">
-        <v>電子郵件地址</v>
+        <v>內嵌 ICC</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>you@example.com</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B244" t="str">
-        <v>you@example.com</v>
+        <v>编码、压缩和平面格式会影响保存的 TIFF。除非设置了仅限 TIFF 的选项（浮点、LZW/ZIP、分离），否则 RGB/Gray 输出仍为 PNG。</v>
       </c>
       <c r="C244" t="str">
-        <v>you@example.com</v>
+        <v>編碼、壓縮和平面格式會影響儲存的 TIFF。除非設定了僅限 TIFF 的選項（浮點、LZW/ZIP、分離），否則 RGB/Gray 輸出仍為 PNG。</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B245" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>组装光谱 TIFF</v>
       </c>
       <c r="C245" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>組裝光譜 TIFF</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>(optional)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B246" t="str">
-        <v>（选填）</v>
+        <v>按通道顺序拖放单通道光谱图像，然后将其组装为一个多通道 TIFF。</v>
       </c>
       <c r="C246" t="str">
-        <v>（選填）</v>
+        <v>依通道順序拖放單通道光譜影像，然後將其組裝為一個多通道 TIFF。</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B247" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>将光谱图像拖放到此处（或点击选择）</v>
       </c>
       <c r="C247" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>將光譜影像拖放到此處（或點擊選擇）</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ch</v>
       </c>
       <c r="B248" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>通道</v>
       </c>
       <c r="C248" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>通道</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B249" t="str">
-        <v>取消</v>
+        <v>组装并保存</v>
       </c>
       <c r="C249" t="str">
-        <v>取消</v>
+        <v>組裝並儲存</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Subscribe</v>
+        <v>Assembling…</v>
       </c>
       <c r="B250" t="str">
-        <v>订阅</v>
+        <v>正在组装…</v>
       </c>
       <c r="C250" t="str">
-        <v>訂閱</v>
+        <v>正在組裝…</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B251" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>已组装 {n} 个通道。</v>
       </c>
       <c r="C251" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>已組裝 {n} 個通道。</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B252" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>这些文件似乎都不是图像（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C252" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>這些檔案似乎都不是影像（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B253" t="str">
-        <v>关闭</v>
+        <v>取消</v>
       </c>
       <c r="C253" t="str">
-        <v>關閉</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Privacy notice</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B254" t="str">
-        <v>隐私声明</v>
+        <v>有 {n} 个文件未加载</v>
       </c>
       <c r="C254" t="str">
-        <v>隱私聲明</v>
+        <v>有 {n} 個檔案未載入</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B255" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
       </c>
       <c r="C255" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>OK</v>
       </c>
       <c r="B256" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>确定</v>
       </c>
       <c r="C256" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>確定</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B257" t="str">
-        <v>请检查表单后重试。</v>
+        <v>将 ICC 配置文件拖到此处</v>
       </c>
       <c r="C257" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>將 ICC 設定檔拖到此處</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>or</v>
       </c>
       <c r="B258" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>或</v>
       </c>
       <c r="C258" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>或</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Choose file</v>
       </c>
       <c r="B259" t="str">
-        <v>网络错误，请重试。</v>
+        <v>选择文件</v>
       </c>
       <c r="C259" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>選擇檔案</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Error:</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B260" t="str">
-        <v>错误：</v>
+        <v>.icc 和 .icm 文件</v>
       </c>
       <c r="C260" t="str">
-        <v>錯誤：</v>
+        <v>.icc 與 .icm 檔案</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Convert to XML</v>
+        <v>Header</v>
       </c>
       <c r="B261" t="str">
-        <v>转换为 XML</v>
+        <v>标头</v>
       </c>
       <c r="C261" t="str">
-        <v>轉換為 XML</v>
+        <v>標頭</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Convert to JSON</v>
+        <v>Tags</v>
       </c>
       <c r="B262" t="str">
-        <v>转换为 JSON</v>
+        <v>标签</v>
       </c>
       <c r="C262" t="str">
-        <v>轉換為 JSON</v>
+        <v>標籤</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Convert to ICC</v>
+        <v>Validation</v>
       </c>
       <c r="B263" t="str">
-        <v>转换为 ICC</v>
+        <v>验证</v>
       </c>
       <c r="C263" t="str">
-        <v>轉換為 ICC</v>
+        <v>驗證</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Converting to XML…</v>
+        <v>Analysis</v>
       </c>
       <c r="B264" t="str">
-        <v>正在转换为 XML…</v>
+        <v>分析</v>
       </c>
       <c r="C264" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Converting to JSON…</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B265" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>中性轴墨量</v>
       </c>
       <c r="C265" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>中性軸墨量</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B266" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
       </c>
       <c r="C266" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Load ICC profile</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B267" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C267" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B268" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
       </c>
       <c r="C268" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Profile ID</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B269" t="str">
-        <v>配置文件 ID</v>
+        <v>渲染意图</v>
       </c>
       <c r="C269" t="str">
-        <v>設定檔 ID</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>No tags found.</v>
+        <v>% ink</v>
       </c>
       <c r="B270" t="str">
-        <v>未找到标签。</v>
+        <v>% 墨量</v>
       </c>
       <c r="C270" t="str">
-        <v>找不到標籤。</v>
+        <v>% 墨量</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Tag Name</v>
+        <v>Perceptual</v>
       </c>
       <c r="B271" t="str">
-        <v>标签名称</v>
+        <v>感知</v>
       </c>
       <c r="C271" t="str">
-        <v>標籤名稱</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>ID</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>ID</v>
+        <v>相对比色</v>
       </c>
       <c r="C272" t="str">
-        <v>ID</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Offset</v>
+        <v>Saturation</v>
       </c>
       <c r="B273" t="str">
-        <v>偏移</v>
+        <v>饱和度</v>
       </c>
       <c r="C273" t="str">
-        <v>偏移</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Size</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B274" t="str">
-        <v>大小</v>
+        <v>绝对比色</v>
       </c>
       <c r="C274" t="str">
-        <v>大小</v>
+        <v>絕對比色</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Pad</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B275" t="str">
-        <v>填充</v>
+        <v>特性文件统计</v>
       </c>
       <c r="C275" t="str">
-        <v>填充</v>
+        <v>特性檔統計</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Bytes changed since load</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B276" t="str">
-        <v>加载后字节已更改</v>
+        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
       </c>
       <c r="C276" t="str">
-        <v>載入後位元組已變更</v>
+        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Type</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B277" t="str">
-        <v>类型</v>
+        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
       </c>
       <c r="C277" t="str">
-        <v>類型</v>
+        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Array of {type}</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B278" t="str">
-        <v>{type} 数组</v>
+        <v>渲染意图</v>
       </c>
       <c r="C278" t="str">
-        <v>{type} 陣列</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>(No content)</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B279" t="str">
-        <v>（无内容）</v>
+        <v>色域体积 (ΔE³)</v>
       </c>
       <c r="C279" t="str">
-        <v>（無內容）</v>
+        <v>色域體積 (ΔE³)</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>bytes</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B280" t="str">
-        <v>字节</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C280" t="str">
-        <v>位元組</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Loading full description…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B281" t="str">
-        <v>正在加载完整描述…</v>
+        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
       </c>
       <c r="C281" t="str">
-        <v>正在載入完整描述…</v>
+        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Could not load full description:</v>
+        <v>mean</v>
       </c>
       <c r="B282" t="str">
-        <v>无法加载完整描述：</v>
+        <v>均值</v>
       </c>
       <c r="C282" t="str">
-        <v>無法載入完整描述：</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>P90</v>
       </c>
       <c r="B283" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>P90</v>
       </c>
       <c r="C283" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>max</v>
       </c>
       <c r="B284" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>最大</v>
       </c>
       <c r="C284" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>No validation output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B285" t="str">
-        <v>无验证输出</v>
+        <v>正在分析…</v>
       </c>
       <c r="C285" t="str">
-        <v>無驗證輸出</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Profile is valid</v>
+        <v>Analysis</v>
       </c>
       <c r="B286" t="str">
-        <v>配置文件有效</v>
+        <v>分析</v>
       </c>
       <c r="C286" t="str">
-        <v>設定檔有效</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B287" t="str">
-        <v>配置文件有警告</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C287" t="str">
-        <v>設定檔有警告</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Plot</v>
       </c>
       <c r="B288" t="str">
-        <v>配置文件不合规</v>
+        <v>绘图</v>
       </c>
       <c r="C288" t="str">
-        <v>設定檔不符合規範</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Critical validation error</v>
+        <v>Raw Output</v>
       </c>
       <c r="B289" t="str">
-        <v>严重验证错误</v>
+        <v>原始输出</v>
       </c>
       <c r="C289" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Unknown validation status</v>
+        <v>XML</v>
       </c>
       <c r="B290" t="str">
-        <v>未知验证状态</v>
+        <v>XML</v>
       </c>
       <c r="C290" t="str">
-        <v>未知驗證狀態</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>JSON</v>
       </c>
       <c r="B291" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>JSON</v>
       </c>
       <c r="C291" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Curves</v>
       </c>
       <c r="B292" t="str">
-        <v>未发现警告或错误。</v>
+        <v>曲线</v>
       </c>
       <c r="C292" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Valid</v>
+        <v>Input curves</v>
       </c>
       <c r="B293" t="str">
-        <v>有效</v>
+        <v>输入曲线</v>
       </c>
       <c r="C293" t="str">
-        <v>有效</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Warning</v>
+        <v>Output curves</v>
       </c>
       <c r="B294" t="str">
-        <v>警告</v>
+        <v>输出曲线</v>
       </c>
       <c r="C294" t="str">
-        <v>警告</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Error</v>
+        <v>CLUT image</v>
       </c>
       <c r="B295" t="str">
-        <v>错误</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C295" t="str">
-        <v>錯誤</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Unknown</v>
+        <v>Gamut image</v>
       </c>
       <c r="B296" t="str">
-        <v>未知</v>
+        <v>色域图像</v>
       </c>
       <c r="C296" t="str">
-        <v>未知</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Pass</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B297" t="str">
-        <v>通过</v>
+        <v>色度</v>
       </c>
       <c r="C297" t="str">
-        <v>通過</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Fail</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B298" t="str">
-        <v>失败</v>
+        <v>散点图</v>
       </c>
       <c r="C298" t="str">
-        <v>失敗</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>View in context</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B299" t="str">
-        <v>在上下文中查看</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C299" t="str">
-        <v>在上下文中檢視</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Validation detail</v>
+        <v>Curve table</v>
       </c>
       <c r="B300" t="str">
-        <v>验证详情</v>
+        <v>曲线表</v>
       </c>
       <c r="C300" t="str">
-        <v>驗證詳情</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Triggered by</v>
+        <v>Tables</v>
       </c>
       <c r="B301" t="str">
-        <v>触发字段</v>
+        <v>表格</v>
       </c>
       <c r="C301" t="str">
-        <v>觸發欄位</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Field</v>
+        <v>Data</v>
       </c>
       <c r="B302" t="str">
-        <v>字段</v>
+        <v>数据</v>
       </c>
       <c r="C302" t="str">
-        <v>欄位</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Current value</v>
+        <v>Evaluate</v>
       </c>
       <c r="B303" t="str">
-        <v>当前值</v>
+        <v>求值</v>
       </c>
       <c r="C303" t="str">
-        <v>目前值</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Required: 0</v>
+        <v>Loading…</v>
       </c>
       <c r="B304" t="str">
-        <v>要求：0</v>
+        <v>加载中…</v>
       </c>
       <c r="C304" t="str">
-        <v>要求：0</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Expected: {value}</v>
+        <v>Input</v>
       </c>
       <c r="B305" t="str">
-        <v>预期：{value}</v>
+        <v>输入</v>
       </c>
       <c r="C305" t="str">
-        <v>預期：{value}</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Invalid</v>
+        <v>Output</v>
       </c>
       <c r="B306" t="str">
-        <v>无效</v>
+        <v>输出</v>
       </c>
       <c r="C306" t="str">
-        <v>無效</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Floating point</v>
       </c>
       <c r="B307" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>浮点值</v>
       </c>
       <c r="C307" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Close</v>
+        <v>Grid point</v>
       </c>
       <c r="B308" t="str">
-        <v>关闭</v>
+        <v>网格点</v>
       </c>
       <c r="C308" t="str">
-        <v>關閉</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Loading XML editor…</v>
+        <v>Normalized</v>
       </c>
       <c r="B309" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>归一化</v>
       </c>
       <c r="C309" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Human</v>
       </c>
       <c r="B310" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>可读值</v>
       </c>
       <c r="C310" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B311" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C311" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B312" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C312" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>● unsaved XML edits</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B313" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C313" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading…</v>
       </c>
       <c r="B314" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>加载中…</v>
       </c>
       <c r="C314" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B315" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C315" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B316" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C316" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>indent</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B317" t="str">
-        <v>缩进</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C317" t="str">
-        <v>縮排</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>sort keys</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B318" t="str">
-        <v>排序键</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C318" t="str">
-        <v>排序鍵</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
+        <v>Loading Profile Assessment WG report…</v>
+      </c>
+      <c r="B319" t="str">
+        <v>正在加载 Profile Assessment WG 报告…</v>
+      </c>
+      <c r="C319" t="str">
+        <v>正在載入 Profile Assessment WG 報告…</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Running Profile Assessment WG checks…</v>
+      </c>
+      <c r="B320" t="str">
+        <v>正在运行 Profile Assessment WG 检查…</v>
+      </c>
+      <c r="C320" t="str">
+        <v>正在執行 Profile Assessment WG 檢查…</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Profile Assessment WG Report</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Profile Assessment WG 报告</v>
+      </c>
+      <c r="C321" t="str">
+        <v>Profile Assessment WG 報告</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Security</v>
+      </c>
+      <c r="B322" t="str">
+        <v>安全性</v>
+      </c>
+      <c r="C322" t="str">
+        <v>安全性</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Conformance</v>
+      </c>
+      <c r="B323" t="str">
+        <v>符合性</v>
+      </c>
+      <c r="C323" t="str">
+        <v>符合性</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Quality</v>
+      </c>
+      <c r="B324" t="str">
+        <v>质量</v>
+      </c>
+      <c r="C324" t="str">
+        <v>品質</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>REPORT</v>
+      </c>
+      <c r="B325" t="str">
+        <v>报告</v>
+      </c>
+      <c r="C325" t="str">
+        <v>報告</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="B326" t="str">
+        <v>失败</v>
+      </c>
+      <c r="C326" t="str">
+        <v>失敗</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>checks</v>
+      </c>
+      <c r="B327" t="str">
+        <v>项检查</v>
+      </c>
+      <c r="C327" t="str">
+        <v>項檢查</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+      </c>
+      <c r="B328" t="str">
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+      </c>
+      <c r="C328" t="str">
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>ICC Profile Tool · powered by IccProfLib</v>
+      </c>
+      <c r="B329" t="str">
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+      </c>
+      <c r="C329" t="str">
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B330" t="str">
+        <v>ICC 配置文件工具</v>
+      </c>
+      <c r="C330" t="str">
+        <v>ICC 設定檔工具</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B331" t="str">
+        <v>由 {lib} 提供支持</v>
+      </c>
+      <c r="C331" t="str">
+        <v>由 {lib} 提供支援</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B332" t="str">
+        <v>订阅</v>
+      </c>
+      <c r="C332" t="str">
+        <v>訂閱</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B333" t="str">
+        <v>在 profiletool 新版本发布时收到通知</v>
+      </c>
+      <c r="C333" t="str">
+        <v>在 profiletool 新版本發佈時收到通知</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B334" t="str">
+        <v>订阅新版本通知</v>
+      </c>
+      <c r="C334" t="str">
+        <v>訂閱新版本通知</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B335" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C335" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B336" t="str">
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+      </c>
+      <c r="C336" t="str">
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B337" t="str">
+        <v>电子邮件地址</v>
+      </c>
+      <c r="C337" t="str">
+        <v>電子郵件地址</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B338" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="C338" t="str">
+        <v>you@example.com</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B339" t="str">
+        <v>您打算如何使用 profiletool？</v>
+      </c>
+      <c r="C339" t="str">
+        <v>您打算如何使用 profiletool？</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B340" t="str">
+        <v>（选填）</v>
+      </c>
+      <c r="C340" t="str">
+        <v>（選填）</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B341" t="str">
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+      </c>
+      <c r="C341" t="str">
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B342" t="str">
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+      </c>
+      <c r="C342" t="str">
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B343" t="str">
+        <v>取消</v>
+      </c>
+      <c r="C343" t="str">
+        <v>取消</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B344" t="str">
+        <v>订阅</v>
+      </c>
+      <c r="C344" t="str">
+        <v>訂閱</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B345" t="str">
+        <v>谢谢 — 我们会再联系您。</v>
+      </c>
+      <c r="C345" t="str">
+        <v>感謝 — 我們會再聯絡您。</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B346" t="str">
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+      </c>
+      <c r="C346" t="str">
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B347" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C347" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B348" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="C348" t="str">
+        <v>隱私聲明</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B349" t="str">
+        <v>请输入有效的电子邮件地址。</v>
+      </c>
+      <c r="C349" t="str">
+        <v>請輸入有效的電子郵件地址。</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B350" t="str">
+        <v>请求过多，请稍后再试。</v>
+      </c>
+      <c r="C350" t="str">
+        <v>請求過多，請稍後再試。</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>请检查表单后重试。</v>
+      </c>
+      <c r="C351" t="str">
+        <v>請檢查表單後重試。</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>无法发送您的请求，请重试。</v>
+      </c>
+      <c r="C352" t="str">
+        <v>無法傳送您的請求，請重試。</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B353" t="str">
+        <v>网络错误，请重试。</v>
+      </c>
+      <c r="C353" t="str">
+        <v>網路錯誤，請重試。</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B354" t="str">
+        <v>错误：</v>
+      </c>
+      <c r="C354" t="str">
+        <v>錯誤：</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B355" t="str">
+        <v>转换为 XML</v>
+      </c>
+      <c r="C355" t="str">
+        <v>轉換為 XML</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B356" t="str">
+        <v>转换为 JSON</v>
+      </c>
+      <c r="C356" t="str">
+        <v>轉換為 JSON</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B357" t="str">
+        <v>转换为 ICC</v>
+      </c>
+      <c r="C357" t="str">
+        <v>轉換為 ICC</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B358" t="str">
+        <v>正在转换为 XML…</v>
+      </c>
+      <c r="C358" t="str">
+        <v>正在轉換為 XML…</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B359" t="str">
+        <v>正在转换为 JSON…</v>
+      </c>
+      <c r="C359" t="str">
+        <v>正在轉換為 JSON…</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B360" t="str">
+        <v>正在转换为 ICC…</v>
+      </c>
+      <c r="C360" t="str">
+        <v>正在轉換為 ICC…</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B361" t="str">
+        <v>加载 ICC 配置文件</v>
+      </c>
+      <c r="C361" t="str">
+        <v>載入 ICC 設定檔</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B362" t="str">
+        <v>ICC 配置文件拖放区</v>
+      </c>
+      <c r="C362" t="str">
+        <v>ICC 設定檔拖放區</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B363" t="str">
+        <v>配置文件 ID</v>
+      </c>
+      <c r="C363" t="str">
+        <v>設定檔 ID</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B364" t="str">
+        <v>未找到标签。</v>
+      </c>
+      <c r="C364" t="str">
+        <v>找不到標籤。</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B365" t="str">
+        <v>标签名称</v>
+      </c>
+      <c r="C365" t="str">
+        <v>標籤名稱</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B366" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C366" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B367" t="str">
+        <v>偏移</v>
+      </c>
+      <c r="C367" t="str">
+        <v>偏移</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B368" t="str">
+        <v>大小</v>
+      </c>
+      <c r="C368" t="str">
+        <v>大小</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B369" t="str">
+        <v>填充</v>
+      </c>
+      <c r="C369" t="str">
+        <v>填充</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B370" t="str">
+        <v>加载后字节已更改</v>
+      </c>
+      <c r="C370" t="str">
+        <v>載入後位元組已變更</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B371" t="str">
+        <v>类型</v>
+      </c>
+      <c r="C371" t="str">
+        <v>類型</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B372" t="str">
+        <v>{type} 数组</v>
+      </c>
+      <c r="C372" t="str">
+        <v>{type} 陣列</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B373" t="str">
+        <v>（无内容）</v>
+      </c>
+      <c r="C373" t="str">
+        <v>（無內容）</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B374" t="str">
+        <v>字节</v>
+      </c>
+      <c r="C374" t="str">
+        <v>位元組</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B375" t="str">
+        <v>正在加载完整描述…</v>
+      </c>
+      <c r="C375" t="str">
+        <v>正在載入完整描述…</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B376" t="str">
+        <v>无法加载完整描述：</v>
+      </c>
+      <c r="C376" t="str">
+        <v>無法載入完整描述：</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+      </c>
+      <c r="C377" t="str">
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B378" t="str">
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+      </c>
+      <c r="C378" t="str">
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B379" t="str">
+        <v>无验证输出</v>
+      </c>
+      <c r="C379" t="str">
+        <v>無驗證輸出</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B380" t="str">
+        <v>配置文件有效</v>
+      </c>
+      <c r="C380" t="str">
+        <v>設定檔有效</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B381" t="str">
+        <v>配置文件有警告</v>
+      </c>
+      <c r="C381" t="str">
+        <v>設定檔有警告</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B382" t="str">
+        <v>配置文件不合规</v>
+      </c>
+      <c r="C382" t="str">
+        <v>設定檔不符合規範</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B383" t="str">
+        <v>严重验证错误</v>
+      </c>
+      <c r="C383" t="str">
+        <v>嚴重驗證錯誤</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B384" t="str">
+        <v>未知验证状态</v>
+      </c>
+      <c r="C384" t="str">
+        <v>未知驗證狀態</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B385" t="str">
+        <v>严重 — 仅供检查显示</v>
+      </c>
+      <c r="C385" t="str">
+        <v>嚴重 — 僅供檢視顯示</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B386" t="str">
+        <v>未发现警告或错误。</v>
+      </c>
+      <c r="C386" t="str">
+        <v>未發現警告或錯誤。</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B387" t="str">
+        <v>有效</v>
+      </c>
+      <c r="C387" t="str">
+        <v>有效</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B388" t="str">
+        <v>警告</v>
+      </c>
+      <c r="C388" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B389" t="str">
+        <v>错误</v>
+      </c>
+      <c r="C389" t="str">
+        <v>錯誤</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B390" t="str">
+        <v>未知</v>
+      </c>
+      <c r="C390" t="str">
+        <v>未知</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B391" t="str">
+        <v>通过</v>
+      </c>
+      <c r="C391" t="str">
+        <v>通過</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B392" t="str">
+        <v>失败</v>
+      </c>
+      <c r="C392" t="str">
+        <v>失敗</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B393" t="str">
+        <v>在上下文中查看</v>
+      </c>
+      <c r="C393" t="str">
+        <v>在上下文中檢視</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B394" t="str">
+        <v>验证详情</v>
+      </c>
+      <c r="C394" t="str">
+        <v>驗證詳情</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B395" t="str">
+        <v>触发字段</v>
+      </c>
+      <c r="C395" t="str">
+        <v>觸發欄位</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B396" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C396" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B397" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C397" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B398" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C398" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B399" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C399" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B400" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C400" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B401" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C401" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B402" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C402" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B403" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C403" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B404" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C404" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B405" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C405" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B406" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C406" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B407" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C407" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B408" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C408" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B409" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C409" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B410" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C410" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B411" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C411" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B412" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C412" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B319" t="str">
+      <c r="B413" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C319" t="str">
+      <c r="C413" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C413"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C413"/>
+  <dimension ref="A1:C410"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1297,3668 +1297,3635 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Based on</v>
       </c>
       <c r="B82" t="str">
-        <v>上传一个 ICC 配置文件，依据</v>
+        <v>基于</v>
       </c>
       <c r="C82" t="str">
-        <v>上傳一個 ICC 設定檔，依據</v>
+        <v>基於</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>specification using the</v>
+        <v>demo implementation</v>
       </c>
       <c r="B83" t="str">
-        <v>规范使用</v>
+        <v>演示实现</v>
       </c>
       <c r="C83" t="str">
-        <v>規範使用</v>
+        <v>示範實作</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation.</v>
+        <v>Validating…</v>
       </c>
       <c r="B84" t="str">
-        <v>演示实现进行验证。</v>
+        <v>正在验证…</v>
       </c>
       <c r="C84" t="str">
-        <v>示範實作進行驗證。</v>
+        <v>驗證中…</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Based on</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B85" t="str">
-        <v>基于</v>
+        <v>保存 ICC 配置文件</v>
       </c>
       <c r="C85" t="str">
-        <v>基於</v>
+        <v>儲存 ICC 設定檔</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>demo implementation</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B86" t="str">
-        <v>演示实现</v>
+        <v>● 已修改 — 尚未保存</v>
       </c>
       <c r="C86" t="str">
-        <v>示範實作</v>
+        <v>● 已修改 — 尚未儲存</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Validating…</v>
+        <v>Profiles</v>
       </c>
       <c r="B87" t="str">
-        <v>正在验证…</v>
+        <v>配置文件</v>
       </c>
       <c r="C87" t="str">
-        <v>驗證中…</v>
+        <v>設定檔</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Save ICC profile</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B88" t="str">
-        <v>保存 ICC 配置文件</v>
+        <v>显示配置文件池</v>
       </c>
       <c r="C88" t="str">
-        <v>儲存 ICC 設定檔</v>
+        <v>顯示設定檔集區</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Collapse</v>
       </c>
       <c r="B89" t="str">
-        <v>● 已修改 — 尚未保存</v>
+        <v>收起</v>
       </c>
       <c r="C89" t="str">
-        <v>● 已修改 — 尚未儲存</v>
+        <v>收合</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Profiles</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>配置文件</v>
+        <v>加载配置文件</v>
       </c>
       <c r="C90" t="str">
-        <v>設定檔</v>
+        <v>載入設定檔</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Show profile pool</v>
+        <v>Remove</v>
       </c>
       <c r="B91" t="str">
-        <v>显示配置文件池</v>
+        <v>移除</v>
       </c>
       <c r="C91" t="str">
-        <v>顯示設定檔集區</v>
+        <v>移除</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Collapse</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B92" t="str">
-        <v>收起</v>
+        <v>将 ICC 配置文件拖放到此处</v>
       </c>
       <c r="C92" t="str">
-        <v>收合</v>
+        <v>將 ICC 設定檔拖放到此處</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load Profiles</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B93" t="str">
-        <v>加载配置文件</v>
+        <v>或拖入图像 (TIFF/PNG/JPEG) 以提取其嵌入的配置文件 — 文件保留在您的设备上。</v>
       </c>
       <c r="C93" t="str">
-        <v>載入設定檔</v>
+        <v>或拖入影像 (TIFF/PNG/JPEG) 以擷取其內嵌設定檔 — 檔案會保留在您的裝置上。</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Remove</v>
+        <v>New from .cube</v>
       </c>
       <c r="B94" t="str">
-        <v>移除</v>
+        <v>从 .cube 新建</v>
       </c>
       <c r="C94" t="str">
-        <v>移除</v>
+        <v>從 .cube 新建</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Sort by name</v>
       </c>
       <c r="B95" t="str">
-        <v>将 ICC 配置文件拖放到此处</v>
+        <v>按名称排序</v>
       </c>
       <c r="C95" t="str">
-        <v>將 ICC 設定檔拖放到此處</v>
+        <v>依名稱排序</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>A–Z</v>
       </c>
       <c r="B96" t="str">
-        <v>或拖入图像 (TIFF/PNG/JPEG) 以提取其嵌入的配置文件 — 文件保留在您的设备上。</v>
+        <v>A–Z</v>
       </c>
       <c r="C96" t="str">
-        <v>或拖入影像 (TIFF/PNG/JPEG) 以擷取其內嵌設定檔 — 檔案會保留在您的裝置上。</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New from .cube</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>从 .cube 新建</v>
+        <v>从 .cube 新建配置文件</v>
       </c>
       <c r="C97" t="str">
-        <v>從 .cube 新建</v>
+        <v>從 .cube 新建設定檔</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sort by name</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B98" t="str">
-        <v>按名称排序</v>
+        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并下载。</v>
       </c>
       <c r="C98" t="str">
-        <v>依名稱排序</v>
+        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並下載。</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>A–Z</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B99" t="str">
-        <v>A–Z</v>
+        <v>选择 .cube 文件</v>
       </c>
       <c r="C99" t="str">
-        <v>A–Z</v>
+        <v>選擇 .cube 檔案</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>New profile from .cube</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B100" t="str">
-        <v>从 .cube 新建配置文件</v>
+        <v>或拖放到此处，或在下方粘贴</v>
       </c>
       <c r="C100" t="str">
-        <v>從 .cube 新建設定檔</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
-      </c>
-      <c r="B101" t="str">
-        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并下载。</v>
-      </c>
-      <c r="C101" t="str">
-        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並下載。</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Choose .cube file</v>
-      </c>
-      <c r="B102" t="str">
-        <v>选择 .cube 文件</v>
-      </c>
-      <c r="C102" t="str">
-        <v>選擇 .cube 檔案</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>or drop it here, or paste below</v>
-      </c>
-      <c r="B103" t="str">
-        <v>或拖放到此处，或在下方粘贴</v>
-      </c>
-      <c r="C103" t="str">
         <v>或拖放到此處，或在下方貼上</v>
       </c>
     </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str" xml:space="preserve">
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B104" t="str" xml:space="preserve">
+      <c r="B101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="C104" t="str" xml:space="preserve">
+      <c r="C101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B102" t="str">
+        <v>取消</v>
+      </c>
+      <c r="C102" t="str">
+        <v>取消</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Create DeviceLink</v>
+      </c>
+      <c r="B103" t="str">
+        <v>创建 DeviceLink</v>
+      </c>
+      <c r="C103" t="str">
+        <v>建立 DeviceLink</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Creating…</v>
+      </c>
+      <c r="B104" t="str">
+        <v>正在创建…</v>
+      </c>
+      <c r="C104" t="str">
+        <v>正在建立…</v>
+      </c>
+    </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Cancel</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B105" t="str">
-        <v>取消</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C105" t="str">
-        <v>取消</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Create DeviceLink</v>
+        <v>Profile</v>
       </c>
       <c r="B106" t="str">
-        <v>创建 DeviceLink</v>
+        <v>配置文件</v>
       </c>
       <c r="C106" t="str">
-        <v>建立 DeviceLink</v>
+        <v>設定檔</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Creating…</v>
+        <v>Compare</v>
       </c>
       <c r="B107" t="str">
-        <v>正在创建…</v>
+        <v>比较</v>
       </c>
       <c r="C107" t="str">
-        <v>正在建立…</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Could not read that file.</v>
+        <v>Combine</v>
       </c>
       <c r="B108" t="str">
-        <v>无法读取该文件。</v>
+        <v>链接</v>
       </c>
       <c r="C108" t="str">
-        <v>無法讀取該檔案。</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Profile</v>
+        <v>Spectral</v>
       </c>
       <c r="B109" t="str">
-        <v>配置文件</v>
+        <v>光谱</v>
       </c>
       <c r="C109" t="str">
-        <v>設定檔</v>
+        <v>光譜</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Compare</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B110" t="str">
-        <v>比较</v>
+        <v>将配置文件从池中拖到此选项卡</v>
       </c>
       <c r="C110" t="str">
-        <v>比較</v>
+        <v>將設定檔從集區拖到此分頁</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Combine</v>
+        <v>Remove</v>
       </c>
       <c r="B111" t="str">
-        <v>链接</v>
+        <v>移除</v>
       </c>
       <c r="C111" t="str">
-        <v>連結</v>
+        <v>移除</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Spectral</v>
+        <v>No profile selected</v>
       </c>
       <c r="B112" t="str">
-        <v>光谱</v>
+        <v>未选择配置文件</v>
       </c>
       <c r="C112" t="str">
-        <v>光譜</v>
+        <v>未選擇設定檔</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B113" t="str">
-        <v>将配置文件从池中拖到此选项卡</v>
+        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
       </c>
       <c r="C113" t="str">
-        <v>將設定檔從集區拖到此分頁</v>
+        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Remove</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B114" t="str">
-        <v>移除</v>
+        <v>暂无可比较的内容</v>
       </c>
       <c r="C114" t="str">
-        <v>移除</v>
+        <v>尚無可比較的內容</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>No profile selected</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B115" t="str">
-        <v>未选择配置文件</v>
+        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
       </c>
       <c r="C115" t="str">
-        <v>未選擇設定檔</v>
+        <v>將一個或多個設定檔拖到「比較」分頁。</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B116" t="str">
-        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
+        <v>色域比较</v>
       </c>
       <c r="C116" t="str">
-        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing to compare yet</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B117" t="str">
-        <v>暂无可比较的内容</v>
+        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
       </c>
       <c r="C117" t="str">
-        <v>尚無可比較的內容</v>
+        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B118" t="str">
-        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
+        <v>渲染意图</v>
       </c>
       <c r="C118" t="str">
-        <v>將一個或多個設定檔拖到「比較」分頁。</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut comparison</v>
+        <v>Shell</v>
       </c>
       <c r="B119" t="str">
-        <v>色域比较</v>
+        <v>外壳</v>
       </c>
       <c r="C119" t="str">
-        <v>色域比較</v>
+        <v>外殼</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Wireframe</v>
       </c>
       <c r="B120" t="str">
-        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
+        <v>线框</v>
       </c>
       <c r="C120" t="str">
-        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
+        <v>線框</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Rendering intent</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B121" t="str">
-        <v>渲染意图</v>
+        <v>轴编号</v>
       </c>
       <c r="C121" t="str">
-        <v>轉換意圖</v>
+        <v>軸編號</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Shell</v>
+        <v>Opacity</v>
       </c>
       <c r="B122" t="str">
-        <v>外壳</v>
+        <v>不透明度</v>
       </c>
       <c r="C122" t="str">
-        <v>外殼</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Wireframe</v>
+        <v>Colour</v>
       </c>
       <c r="B123" t="str">
-        <v>线框</v>
+        <v>颜色</v>
       </c>
       <c r="C123" t="str">
-        <v>線框</v>
+        <v>色彩</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Axis numbers</v>
+        <v>Solid</v>
       </c>
       <c r="B124" t="str">
-        <v>轴编号</v>
+        <v>纯色</v>
       </c>
       <c r="C124" t="str">
-        <v>軸編號</v>
+        <v>純色</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Opacity</v>
+        <v>By value</v>
       </c>
       <c r="B125" t="str">
-        <v>不透明度</v>
+        <v>按数值</v>
       </c>
       <c r="C125" t="str">
-        <v>不透明度</v>
+        <v>依數值</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Colour</v>
+        <v>By hue</v>
       </c>
       <c r="B126" t="str">
-        <v>颜色</v>
+        <v>按色相</v>
       </c>
       <c r="C126" t="str">
-        <v>色彩</v>
+        <v>依色相</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Solid</v>
+        <v>Rotation</v>
       </c>
       <c r="B127" t="str">
-        <v>纯色</v>
+        <v>旋转</v>
       </c>
       <c r="C127" t="str">
-        <v>純色</v>
+        <v>旋轉</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>By value</v>
+        <v>Turntable</v>
       </c>
       <c r="B128" t="str">
-        <v>按数值</v>
+        <v>转盘</v>
       </c>
       <c r="C128" t="str">
-        <v>依數值</v>
+        <v>轉盤</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>By hue</v>
+        <v>Orbit</v>
       </c>
       <c r="B129" t="str">
-        <v>按色相</v>
+        <v>轨道</v>
       </c>
       <c r="C129" t="str">
-        <v>依色相</v>
+        <v>軌道</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Rotation</v>
+        <v>Drag speed</v>
       </c>
       <c r="B130" t="str">
-        <v>旋转</v>
+        <v>拖动速度</v>
       </c>
       <c r="C130" t="str">
-        <v>旋轉</v>
+        <v>拖曳速度</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turntable</v>
+        <v>Roll</v>
       </c>
       <c r="B131" t="str">
-        <v>转盘</v>
+        <v>翻滚</v>
       </c>
       <c r="C131" t="str">
-        <v>轉盤</v>
+        <v>翻滾</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Orbit</v>
+        <v>Roll speed</v>
       </c>
       <c r="B132" t="str">
-        <v>轨道</v>
+        <v>翻滚速度</v>
       </c>
       <c r="C132" t="str">
-        <v>軌道</v>
+        <v>翻滾速度</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Drag speed</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B133" t="str">
-        <v>拖动速度</v>
+        <v>正在构建色域…</v>
       </c>
       <c r="C133" t="str">
-        <v>拖曳速度</v>
+        <v>正在建構色域…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Roll</v>
+        <v>no gamut</v>
       </c>
       <c r="B134" t="str">
-        <v>翻滚</v>
+        <v>无色域</v>
       </c>
       <c r="C134" t="str">
-        <v>翻滾</v>
+        <v>無色域</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Roll speed</v>
+        <v>Show / hide</v>
       </c>
       <c r="B135" t="str">
-        <v>翻滚速度</v>
+        <v>显示/隐藏</v>
       </c>
       <c r="C135" t="str">
-        <v>翻滾速度</v>
+        <v>顯示/隱藏</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Building gamut…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B136" t="str">
-        <v>正在构建色域…</v>
+        <v>3D 色域外壳</v>
       </c>
       <c r="C136" t="str">
-        <v>正在建構色域…</v>
+        <v>3D 色域外殼</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>no gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B137" t="str">
-        <v>无色域</v>
+        <v>2D 色域切片</v>
       </c>
       <c r="C137" t="str">
-        <v>無色域</v>
+        <v>2D 色域切片</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Show / hide</v>
+        <v>Plane</v>
       </c>
       <c r="B138" t="str">
-        <v>显示/隐藏</v>
+        <v>平面</v>
       </c>
       <c r="C138" t="str">
-        <v>顯示/隱藏</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>3-D gamut shell</v>
+        <v>L*</v>
       </c>
       <c r="B139" t="str">
-        <v>3D 色域外壳</v>
+        <v>L*</v>
       </c>
       <c r="C139" t="str">
-        <v>3D 色域外殼</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2-D gamut slice</v>
+        <v>a*</v>
       </c>
       <c r="B140" t="str">
-        <v>2D 色域切片</v>
+        <v>a*</v>
       </c>
       <c r="C140" t="str">
-        <v>2D 色域切片</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Plane</v>
+        <v>b*</v>
       </c>
       <c r="B141" t="str">
-        <v>平面</v>
+        <v>b*</v>
       </c>
       <c r="C141" t="str">
-        <v>平面</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L*</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B142" t="str">
-        <v>L*</v>
+        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
       </c>
       <c r="C142" t="str">
-        <v>L*</v>
+        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>a*</v>
+        <v>Linking</v>
       </c>
       <c r="B143" t="str">
-        <v>a*</v>
+        <v>链接</v>
       </c>
       <c r="C143" t="str">
-        <v>a*</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>b*</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B144" t="str">
-        <v>b*</v>
+        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
       </c>
       <c r="C144" t="str">
-        <v>b*</v>
+        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B145" t="str">
-        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
+        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
       </c>
       <c r="C145" t="str">
-        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
+        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Linking</v>
+        <v>Observer Change</v>
       </c>
       <c r="B146" t="str">
-        <v>链接</v>
+        <v>V4 显示器生成器</v>
       </c>
       <c r="C146" t="str">
-        <v>連結</v>
+        <v>V4 顯示器產生器</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B147" t="str">
-        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
+        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
       </c>
       <c r="C147" t="str">
-        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
+        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B148" t="str">
-        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
+        <v>V5 RGB 显示器</v>
       </c>
       <c r="C148" t="str">
-        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
+        <v>V5 RGB 顯示器</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Observer Change</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B149" t="str">
-        <v>V4 显示器生成器</v>
+        <v>拖入显示器配置文件</v>
       </c>
       <c r="C149" t="str">
-        <v>V4 顯示器產生器</v>
+        <v>拖入顯示器設定檔</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B150" t="str">
-        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
+        <v>V5 观察者 (PCC)</v>
       </c>
       <c r="C150" t="str">
-        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
+        <v>V5 觀察者 (PCC)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 RGB display</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B151" t="str">
-        <v>V5 RGB 显示器</v>
+        <v>拖入观察者配置文件</v>
       </c>
       <c r="C151" t="str">
-        <v>V5 RGB 顯示器</v>
+        <v>拖入觀察者設定檔</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop a display profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B152" t="str">
-        <v>拖入显示器配置文件</v>
+        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
       </c>
       <c r="C152" t="str">
-        <v>拖入顯示器設定檔</v>
+        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B153" t="str">
-        <v>V5 观察者 (PCC)</v>
+        <v>创建 V4 显示器配置文件</v>
       </c>
       <c r="C153" t="str">
-        <v>V5 觀察者 (PCC)</v>
+        <v>建立 V4 顯示器設定檔</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop an observer profile</v>
+        <v>Profile name</v>
       </c>
       <c r="B154" t="str">
-        <v>拖入观察者配置文件</v>
+        <v>配置文件名称</v>
       </c>
       <c r="C154" t="str">
-        <v>拖入觀察者設定檔</v>
+        <v>設定檔名稱</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>Create</v>
       </c>
       <c r="B155" t="str">
-        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
+        <v>创建</v>
       </c>
       <c r="C155" t="str">
-        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
+        <v>建立</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Making…</v>
       </c>
       <c r="B156" t="str">
-        <v>创建 V4 显示器配置文件</v>
+        <v>正在创建…</v>
       </c>
       <c r="C156" t="str">
-        <v>建立 V4 顯示器設定檔</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile name</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B157" t="str">
-        <v>配置文件名称</v>
+        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
       </c>
       <c r="C157" t="str">
-        <v>設定檔名稱</v>
+        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Create</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B158" t="str">
-        <v>创建</v>
+        <v>链接流水线</v>
       </c>
       <c r="C158" t="str">
-        <v>建立</v>
+        <v>連結管線</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Making…</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B159" t="str">
-        <v>正在创建…</v>
+        <v>构建一条配置文件链，然后生成 DeviceLink、转换图像，或通过它转换色彩数据集。</v>
       </c>
       <c r="C159" t="str">
-        <v>正在建立…</v>
+        <v>建立一條描述檔鏈，然後產生 DeviceLink、轉換影像，或透過它轉換色彩資料集。</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Done</v>
       </c>
       <c r="B160" t="str">
-        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
+        <v>完成</v>
       </c>
       <c r="C160" t="str">
-        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
+        <v>完成</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Link Pipeline</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B161" t="str">
-        <v>链接流水线</v>
+        <v>拖放图像以进行转换（TIFF/PNG/JPEG）</v>
       </c>
       <c r="C161" t="str">
-        <v>連結管線</v>
+        <v>拖放影像以進行轉換（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Checking image…</v>
       </c>
       <c r="B162" t="str">
-        <v>构建一条配置文件链，然后生成 DeviceLink、转换图像，或通过它转换色彩数据集。</v>
+        <v>正在检查图像…</v>
       </c>
       <c r="C162" t="str">
-        <v>建立一條描述檔鏈，然後產生 DeviceLink、轉換影像，或透過它轉換色彩資料集。</v>
+        <v>正在檢查影像…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Done</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B163" t="str">
-        <v>完成</v>
+        <v>不受支持的图像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C163" t="str">
-        <v>完成</v>
+        <v>不受支援的影像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B164" t="str">
-        <v>拖放图像以进行转换（TIFF/PNG/JPEG）</v>
+        <v>图像过大（{mp} MP；上限 {max} MP）。</v>
       </c>
       <c r="C164" t="str">
-        <v>拖放影像以進行轉換（TIFF/PNG/JPEG）</v>
+        <v>影像過大（{mp} MP；上限 {max} MP）。</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Checking image…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B165" t="str">
-        <v>正在检查图像…</v>
+        <v>转换图像</v>
       </c>
       <c r="C165" t="str">
-        <v>正在檢查影像…</v>
+        <v>轉換影像</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Transforming…</v>
       </c>
       <c r="B166" t="str">
-        <v>不受支持的图像格式（TIFF、PNG 或 JPEG）。</v>
+        <v>正在转换…</v>
       </c>
       <c r="C166" t="str">
-        <v>不受支援的影像格式（TIFF、PNG 或 JPEG）。</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B167" t="str">
-        <v>图像过大（{mp} MP；上限 {max} MP）。</v>
+        <v>拖放配置文件以开始链条</v>
       </c>
       <c r="C167" t="str">
-        <v>影像過大（{mp} MP；上限 {max} MP）。</v>
+        <v>拖放描述檔以開始鏈條</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Transform Image</v>
+        <v>removed</v>
       </c>
       <c r="B168" t="str">
-        <v>转换图像</v>
+        <v>已移除</v>
       </c>
       <c r="C168" t="str">
-        <v>轉換影像</v>
+        <v>已移除</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Transforming…</v>
+        <v>Move earlier</v>
       </c>
       <c r="B169" t="str">
-        <v>正在转换…</v>
+        <v>前移</v>
       </c>
       <c r="C169" t="str">
-        <v>正在轉換…</v>
+        <v>前移</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Move later</v>
       </c>
       <c r="B170" t="str">
-        <v>拖放配置文件以开始链条</v>
+        <v>后移</v>
       </c>
       <c r="C170" t="str">
-        <v>拖放描述檔以開始鏈條</v>
+        <v>後移</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>removed</v>
+        <v>Move up</v>
       </c>
       <c r="B171" t="str">
-        <v>已移除</v>
+        <v>上移</v>
       </c>
       <c r="C171" t="str">
-        <v>已移除</v>
+        <v>上移</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move earlier</v>
+        <v>Move down</v>
       </c>
       <c r="B172" t="str">
-        <v>前移</v>
+        <v>下移</v>
       </c>
       <c r="C172" t="str">
-        <v>前移</v>
+        <v>下移</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move later</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B173" t="str">
-        <v>后移</v>
+        <v>渲染意图（全部）</v>
       </c>
       <c r="C173" t="str">
-        <v>後移</v>
+        <v>演算意圖（全部）</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move up</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B174" t="str">
-        <v>上移</v>
+        <v>此转换的渲染意图</v>
       </c>
       <c r="C174" t="str">
-        <v>上移</v>
+        <v>此轉換的演算意圖</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move down</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B175" t="str">
-        <v>下移</v>
+        <v>各转换使用了不同的渲染意图</v>
       </c>
       <c r="C175" t="str">
-        <v>下移</v>
+        <v>各轉換使用了不同的演算意圖</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B176" t="str">
-        <v>渲染意图（全部）</v>
+        <v>翻转链条方向（反转首个转换，并影响整条链）</v>
       </c>
       <c r="C176" t="str">
-        <v>演算意圖（全部）</v>
+        <v>翻轉鏈條方向（反轉首個轉換，並影響整條鏈）</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B177" t="str">
-        <v>此转换的渲染意图</v>
+        <v>链条中的某个配置文件已从池中移除——请将其移除以继续。</v>
       </c>
       <c r="C177" t="str">
-        <v>此轉換的演算意圖</v>
+        <v>鏈條中的某個描述檔已從集區中移除——請將其移除以繼續。</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Chain</v>
       </c>
       <c r="B178" t="str">
-        <v>各转换使用了不同的渲染意图</v>
+        <v>链条</v>
       </c>
       <c r="C178" t="str">
-        <v>各轉換使用了不同的演算意圖</v>
+        <v>鏈條</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B179" t="str">
-        <v>翻转链条方向（反转首个转换，并影响整条链）</v>
+        <v>无法分析该链条。</v>
       </c>
       <c r="C179" t="str">
-        <v>翻轉鏈條方向（反轉首個轉換，並影響整條鏈）</v>
+        <v>無法分析該鏈條。</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B180" t="str">
-        <v>链条中的某个配置文件已从池中移除——请将其移除以继续。</v>
+        <v>正在检查链条…</v>
       </c>
       <c r="C180" t="str">
-        <v>鏈條中的某個描述檔已從集區中移除——請將其移除以繼續。</v>
+        <v>正在檢查鏈條…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Chain</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B181" t="str">
-        <v>链条</v>
+        <v>链条未能衔接（{detail}）。</v>
       </c>
       <c r="C181" t="str">
-        <v>鏈條</v>
+        <v>鏈條未能銜接（{detail}）。</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>无法分析该链条。</v>
+        <v>配置文件 {n} 未能与上一阶段衔接（{detail}）。</v>
       </c>
       <c r="C182" t="str">
-        <v>無法分析該鏈條。</v>
+        <v>描述檔 {n} 未能與上一階段銜接（{detail}）。</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Checking chain…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B183" t="str">
-        <v>正在检查链条…</v>
+        <v>请先修复链条，再处理图像</v>
       </c>
       <c r="C183" t="str">
-        <v>正在檢查鏈條…</v>
+        <v>請先修正鏈條，再處理影像</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Clear</v>
       </c>
       <c r="B184" t="str">
-        <v>链条未能衔接（{detail}）。</v>
+        <v>清除</v>
       </c>
       <c r="C184" t="str">
-        <v>鏈條未能銜接（{detail}）。</v>
+        <v>清除</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B185" t="str">
-        <v>配置文件 {n} 未能与上一阶段衔接（{detail}）。</v>
+        <v>生成 DeviceLink</v>
       </c>
       <c r="C185" t="str">
-        <v>描述檔 {n} 未能與上一階段銜接（{detail}）。</v>
+        <v>產生 DeviceLink</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B186" t="str">
-        <v>请先修复链条，再处理图像</v>
+        <v>DeviceLink 名称</v>
       </c>
       <c r="C186" t="str">
-        <v>請先修正鏈條，再處理影像</v>
+        <v>DeviceLink 名稱</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Clear</v>
+        <v>Making…</v>
       </c>
       <c r="B187" t="str">
-        <v>清除</v>
+        <v>正在生成…</v>
       </c>
       <c r="C187" t="str">
-        <v>清除</v>
+        <v>正在產生…</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Make DeviceLink</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B188" t="str">
-        <v>生成 DeviceLink</v>
+        <v>已创建“{name}”——已添加到池和此标签页。</v>
       </c>
       <c r="C188" t="str">
-        <v>產生 DeviceLink</v>
+        <v>已建立「{name}」——已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DeviceLink name</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B189" t="str">
-        <v>DeviceLink 名称</v>
+        <v>拖放 {src} 图像以转换为 {dst}——结果将下载，不会被存储。</v>
       </c>
       <c r="C189" t="str">
-        <v>DeviceLink 名稱</v>
+        <v>拖放 {src} 影像以轉換為 {dst}——結果將下載，不會被儲存。</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Making…</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B190" t="str">
-        <v>正在生成…</v>
+        <v>构建链条以处理图像</v>
       </c>
       <c r="C190" t="str">
-        <v>正在產生…</v>
+        <v>建立鏈條以處理影像</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B191" t="str">
-        <v>已创建“{name}”——已添加到池和此标签页。</v>
+        <v>此链条的首尾并非图像色彩空间</v>
       </c>
       <c r="C191" t="str">
-        <v>已建立「{name}」——已加入集區與此分頁。</v>
+        <v>此鏈條的首尾並非影像色彩空間</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B192" t="str">
-        <v>拖放 {src} 图像以转换为 {dst}——结果将下载，不会被存储。</v>
+        <v>已保存转换后的图像。</v>
       </c>
       <c r="C192" t="str">
-        <v>拖放 {src} 影像以轉換為 {dst}——結果將下載，不會被儲存。</v>
+        <v>已儲存轉換後的影像。</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B193" t="str">
-        <v>构建链条以处理图像</v>
+        <v>拖放色彩数据集（CGATS/CSV/CxF/JSON）</v>
       </c>
       <c r="C193" t="str">
-        <v>建立鏈條以處理影像</v>
+        <v>拖放色彩資料集（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B194" t="str">
-        <v>此链条的首尾并非图像色彩空间</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C194" t="str">
-        <v>此鏈條的首尾並非影像色彩空間</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B195" t="str">
-        <v>已保存转换后的图像。</v>
+        <v>数据文件过大。</v>
       </c>
       <c r="C195" t="str">
-        <v>已儲存轉換後的影像。</v>
+        <v>資料檔案過大。</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Transform Data</v>
       </c>
       <c r="B196" t="str">
-        <v>拖放色彩数据集（CGATS/CSV/CxF/JSON）</v>
+        <v>转换数据</v>
       </c>
       <c r="C196" t="str">
-        <v>拖放色彩資料集（CGATS/CSV/CxF/JSON）</v>
+        <v>轉換資料</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Could not read that file.</v>
+        <v>Transforming…</v>
       </c>
       <c r="B197" t="str">
-        <v>无法读取该文件。</v>
+        <v>正在转换…</v>
       </c>
       <c r="C197" t="str">
-        <v>無法讀取該檔案。</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Data file too large.</v>
+        <v>Prefer</v>
       </c>
       <c r="B198" t="str">
-        <v>数据文件过大。</v>
+        <v>偏好</v>
       </c>
       <c r="C198" t="str">
-        <v>資料檔案過大。</v>
+        <v>偏好</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Transform Data</v>
+        <v>Observer</v>
       </c>
       <c r="B199" t="str">
-        <v>转换数据</v>
+        <v>观察者</v>
       </c>
       <c r="C199" t="str">
-        <v>轉換資料</v>
+        <v>觀察者</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Transforming…</v>
+        <v>Illuminant</v>
       </c>
       <c r="B200" t="str">
-        <v>正在转换…</v>
+        <v>光源</v>
       </c>
       <c r="C200" t="str">
-        <v>正在轉換…</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Prefer</v>
+        <v>Condition</v>
       </c>
       <c r="B201" t="str">
-        <v>偏好</v>
+        <v>条件</v>
       </c>
       <c r="C201" t="str">
-        <v>偏好</v>
+        <v>條件</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Observer</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B202" t="str">
-        <v>观察者</v>
+        <v>过滤 {n} 个重复项</v>
       </c>
       <c r="C202" t="str">
-        <v>觀察者</v>
+        <v>篩選 {n} 個重複項</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Illuminant</v>
+        <v>median</v>
       </c>
       <c r="B203" t="str">
-        <v>光源</v>
+        <v>中位数</v>
       </c>
       <c r="C203" t="str">
-        <v>光源</v>
+        <v>中位數</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Condition</v>
+        <v>mean</v>
       </c>
       <c r="B204" t="str">
-        <v>条件</v>
+        <v>平均值</v>
       </c>
       <c r="C204" t="str">
-        <v>條件</v>
+        <v>平均值</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>patches</v>
       </c>
       <c r="B205" t="str">
-        <v>过滤 {n} 个重复项</v>
+        <v>色块</v>
       </c>
       <c r="C205" t="str">
-        <v>篩選 {n} 個重複項</v>
+        <v>色塊</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>median</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B206" t="str">
-        <v>中位数</v>
+        <v>{n} 个重复项</v>
       </c>
       <c r="C206" t="str">
-        <v>中位數</v>
+        <v>{n} 個重複項</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>mean</v>
+        <v>Transform result</v>
       </c>
       <c r="B207" t="str">
-        <v>平均值</v>
+        <v>转换结果</v>
       </c>
       <c r="C207" t="str">
-        <v>平均值</v>
+        <v>轉換結果</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>patches</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B208" t="str">
-        <v>色块</v>
+        <v>{src} → {dst} · {n} 个色块</v>
       </c>
       <c r="C208" t="str">
-        <v>色塊</v>
+        <v>{src} → {dst} · {n} 個色塊</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{n} duplicates</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B209" t="str">
-        <v>{n} 个重复项</v>
+        <v>显示前 {shown} 项，共 {total} 项——保存将写入全部数据。</v>
       </c>
       <c r="C209" t="str">
-        <v>{n} 個重複項</v>
+        <v>顯示前 {shown} 項，共 {total} 項——儲存將寫入全部資料。</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Transform result</v>
+        <v>Save as</v>
       </c>
       <c r="B210" t="str">
-        <v>转换结果</v>
+        <v>另存为</v>
       </c>
       <c r="C210" t="str">
-        <v>轉換結果</v>
+        <v>另存新檔</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Save</v>
       </c>
       <c r="B211" t="str">
-        <v>{src} → {dst} · {n} 个色块</v>
+        <v>保存</v>
       </c>
       <c r="C211" t="str">
-        <v>{src} → {dst} · {n} 個色塊</v>
+        <v>儲存</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B212" t="str">
-        <v>显示前 {shown} 项，共 {total} 项——保存将写入全部数据。</v>
+        <v>反向转换</v>
       </c>
       <c r="C212" t="str">
-        <v>顯示前 {shown} 項，共 {total} 項——儲存將寫入全部資料。</v>
+        <v>反向轉換</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Save as</v>
+        <v>Inverting…</v>
       </c>
       <c r="B213" t="str">
-        <v>另存为</v>
+        <v>正在反向计算…</v>
       </c>
       <c r="C213" t="str">
-        <v>另存新檔</v>
+        <v>正在反向計算…</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Save</v>
+        <v>Invert</v>
       </c>
       <c r="B214" t="str">
-        <v>保存</v>
+        <v>反转</v>
       </c>
       <c r="C214" t="str">
-        <v>儲存</v>
+        <v>反轉</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert Transform</v>
+        <v>last stage</v>
       </c>
       <c r="B215" t="str">
-        <v>反向转换</v>
+        <v>最后阶段</v>
       </c>
       <c r="C215" t="str">
-        <v>反向轉換</v>
+        <v>最後階段</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Inverting…</v>
+        <v>first stage</v>
       </c>
       <c r="B216" t="str">
-        <v>正在反向计算…</v>
+        <v>第一阶段</v>
       </c>
       <c r="C216" t="str">
-        <v>正在反向計算…</v>
+        <v>第一階段</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B217" t="str">
-        <v>反转</v>
+        <v>输入数据为 {in} → 搜索 {out}</v>
       </c>
       <c r="C217" t="str">
-        <v>反轉</v>
+        <v>輸入資料為 {in} → 搜尋 {out}</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>last stage</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B218" t="str">
-        <v>最后阶段</v>
+        <v>反转需要 2–3 个配置文件组成的链条</v>
       </c>
       <c r="C218" t="str">
-        <v>最後階段</v>
+        <v>反轉需要 2–3 個描述檔組成的鏈條</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>first stage</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B219" t="str">
-        <v>第一阶段</v>
+        <v>数据集必须为 {in}；反向搜索将生成 {out}，并附带每个色块的可逆性代价。</v>
       </c>
       <c r="C219" t="str">
-        <v>第一階段</v>
+        <v>資料集必須為 {in}；反向搜尋將產生 {out}，並附帶每個色塊的可逆性代價。</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B220" t="str">
-        <v>输入数据为 {in} → 搜索 {out}</v>
+        <v>ΔE 代价</v>
       </c>
       <c r="C220" t="str">
-        <v>輸入資料為 {in} → 搜尋 {out}</v>
+        <v>ΔE 代價</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B221" t="str">
-        <v>反转需要 2–3 个配置文件组成的链条</v>
+        <v>此图像嵌入了 ICC 配置文件。</v>
       </c>
       <c r="C221" t="str">
-        <v>反轉需要 2–3 個描述檔組成的鏈條</v>
+        <v>此影像內嵌了 ICC 描述檔。</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B222" t="str">
-        <v>数据集必须为 {in}；反向搜索将生成 {out}，并附带每个色块的可逆性代价。</v>
+        <v>提取并添加到链条</v>
       </c>
       <c r="C222" t="str">
-        <v>資料集必須為 {in}；反向搜尋將產生 {out}，並附帶每個色塊的可逆性代價。</v>
+        <v>擷取並加入鏈條</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>ΔE cost</v>
+        <v>Extracting…</v>
       </c>
       <c r="B223" t="str">
-        <v>ΔE 代价</v>
+        <v>正在提取…</v>
       </c>
       <c r="C223" t="str">
-        <v>ΔE 代價</v>
+        <v>正在擷取…</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B224" t="str">
-        <v>此图像嵌入了 ICC 配置文件。</v>
+        <v>忽略</v>
       </c>
       <c r="C224" t="str">
-        <v>此影像內嵌了 ICC 描述檔。</v>
+        <v>忽略</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B225" t="str">
-        <v>提取并添加到链条</v>
+        <v>已提取嵌入的配置文件——已添加到池中并置于链条首位。</v>
       </c>
       <c r="C225" t="str">
-        <v>擷取並加入鏈條</v>
+        <v>已擷取內嵌的描述檔——已加入集區並置於鏈條首位。</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracting…</v>
+        <v>Image output options</v>
       </c>
       <c r="B226" t="str">
-        <v>正在提取…</v>
+        <v>图像输出选项</v>
       </c>
       <c r="C226" t="str">
-        <v>正在擷取…</v>
+        <v>影像輸出選項</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Dismiss</v>
+        <v>Encoding</v>
       </c>
       <c r="B227" t="str">
-        <v>忽略</v>
+        <v>编码</v>
       </c>
       <c r="C227" t="str">
-        <v>忽略</v>
+        <v>編碼</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Same as source</v>
       </c>
       <c r="B228" t="str">
-        <v>已提取嵌入的配置文件——已添加到池中并置于链条首位。</v>
+        <v>与源相同</v>
       </c>
       <c r="C228" t="str">
-        <v>已擷取內嵌的描述檔——已加入集區並置於鏈條首位。</v>
+        <v>與來源相同</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Image output options</v>
+        <v>8-bit</v>
       </c>
       <c r="B229" t="str">
-        <v>图像输出选项</v>
+        <v>8 位</v>
       </c>
       <c r="C229" t="str">
-        <v>影像輸出選項</v>
+        <v>8 位元</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Encoding</v>
+        <v>16-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>编码</v>
+        <v>16 位</v>
       </c>
       <c r="C230" t="str">
-        <v>編碼</v>
+        <v>16 位元</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Same as source</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B231" t="str">
-        <v>与源相同</v>
+        <v>浮点（32 位）</v>
       </c>
       <c r="C231" t="str">
-        <v>與來源相同</v>
+        <v>浮點（32 位元）</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>8-bit</v>
+        <v>Compression</v>
       </c>
       <c r="B232" t="str">
-        <v>8 位</v>
+        <v>压缩</v>
       </c>
       <c r="C232" t="str">
-        <v>8 位元</v>
+        <v>壓縮</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>16-bit</v>
+        <v>None</v>
       </c>
       <c r="B233" t="str">
-        <v>16 位</v>
+        <v>无</v>
       </c>
       <c r="C233" t="str">
-        <v>16 位元</v>
+        <v>無</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Float (32-bit)</v>
+        <v>Planar</v>
       </c>
       <c r="B234" t="str">
-        <v>浮点（32 位）</v>
+        <v>平面格式</v>
       </c>
       <c r="C234" t="str">
-        <v>浮點（32 位元）</v>
+        <v>平面格式</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Compression</v>
+        <v>Composite</v>
       </c>
       <c r="B235" t="str">
-        <v>压缩</v>
+        <v>交错</v>
       </c>
       <c r="C235" t="str">
-        <v>壓縮</v>
+        <v>交錯</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>None</v>
+        <v>Separated</v>
       </c>
       <c r="B236" t="str">
-        <v>无</v>
+        <v>分离</v>
       </c>
       <c r="C236" t="str">
-        <v>無</v>
+        <v>分離</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Planar</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B237" t="str">
-        <v>平面格式</v>
+        <v>CMM 插值</v>
       </c>
       <c r="C237" t="str">
-        <v>平面格式</v>
+        <v>CMM 內插</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Composite</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B238" t="str">
-        <v>交错</v>
+        <v>四面体</v>
       </c>
       <c r="C238" t="str">
-        <v>交錯</v>
+        <v>四面體</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Separated</v>
+        <v>Linear</v>
       </c>
       <c r="B239" t="str">
-        <v>分离</v>
+        <v>线性</v>
       </c>
       <c r="C239" t="str">
-        <v>分離</v>
+        <v>線性</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>CMM interpolation</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B240" t="str">
-        <v>CMM 插值</v>
+        <v>嵌入 ICC</v>
       </c>
       <c r="C240" t="str">
-        <v>CMM 內插</v>
+        <v>內嵌 ICC</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Tetrahedral</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B241" t="str">
-        <v>四面体</v>
+        <v>编码、压缩和平面格式会影响保存的 TIFF。除非设置了仅限 TIFF 的选项（浮点、LZW/ZIP、分离），否则 RGB/Gray 输出仍为 PNG。</v>
       </c>
       <c r="C241" t="str">
-        <v>四面體</v>
+        <v>編碼、壓縮和平面格式會影響儲存的 TIFF。除非設定了僅限 TIFF 的選項（浮點、LZW/ZIP、分離），否則 RGB/Gray 輸出仍為 PNG。</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Linear</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B242" t="str">
-        <v>线性</v>
+        <v>组装光谱 TIFF</v>
       </c>
       <c r="C242" t="str">
-        <v>線性</v>
+        <v>組裝光譜 TIFF</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Embed ICC</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B243" t="str">
-        <v>嵌入 ICC</v>
+        <v>按通道顺序拖放单通道光谱图像，然后将其组装为一个多通道 TIFF。</v>
       </c>
       <c r="C243" t="str">
-        <v>內嵌 ICC</v>
+        <v>依通道順序拖放單通道光譜影像，然後將其組裝為一個多通道 TIFF。</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B244" t="str">
-        <v>编码、压缩和平面格式会影响保存的 TIFF。除非设置了仅限 TIFF 的选项（浮点、LZW/ZIP、分离），否则 RGB/Gray 输出仍为 PNG。</v>
+        <v>将光谱图像拖放到此处（或点击选择）</v>
       </c>
       <c r="C244" t="str">
-        <v>編碼、壓縮和平面格式會影響儲存的 TIFF。除非設定了僅限 TIFF 的選項（浮點、LZW/ZIP、分離），否則 RGB/Gray 輸出仍為 PNG。</v>
+        <v>將光譜影像拖放到此處（或點擊選擇）</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>ch</v>
       </c>
       <c r="B245" t="str">
-        <v>组装光谱 TIFF</v>
+        <v>通道</v>
       </c>
       <c r="C245" t="str">
-        <v>組裝光譜 TIFF</v>
+        <v>通道</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B246" t="str">
-        <v>按通道顺序拖放单通道光谱图像，然后将其组装为一个多通道 TIFF。</v>
+        <v>组装并保存</v>
       </c>
       <c r="C246" t="str">
-        <v>依通道順序拖放單通道光譜影像，然後將其組裝為一個多通道 TIFF。</v>
+        <v>組裝並儲存</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Assembling…</v>
       </c>
       <c r="B247" t="str">
-        <v>将光谱图像拖放到此处（或点击选择）</v>
+        <v>正在组装…</v>
       </c>
       <c r="C247" t="str">
-        <v>將光譜影像拖放到此處（或點擊選擇）</v>
+        <v>正在組裝…</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ch</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B248" t="str">
-        <v>通道</v>
+        <v>已组装 {n} 个通道。</v>
       </c>
       <c r="C248" t="str">
-        <v>通道</v>
+        <v>已組裝 {n} 個通道。</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B249" t="str">
-        <v>组装并保存</v>
+        <v>这些文件似乎都不是图像（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C249" t="str">
-        <v>組裝並儲存</v>
+        <v>這些檔案似乎都不是影像（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Assembling…</v>
+        <v>Cancel</v>
       </c>
       <c r="B250" t="str">
-        <v>正在组装…</v>
+        <v>取消</v>
       </c>
       <c r="C250" t="str">
-        <v>正在組裝…</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B251" t="str">
-        <v>已组装 {n} 个通道。</v>
+        <v>有 {n} 个文件未加载</v>
       </c>
       <c r="C251" t="str">
-        <v>已組裝 {n} 個通道。</v>
+        <v>有 {n} 個檔案未載入</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B252" t="str">
-        <v>这些文件似乎都不是图像（TIFF、PNG 或 JPEG）。</v>
+        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
       </c>
       <c r="C252" t="str">
-        <v>這些檔案似乎都不是影像（TIFF、PNG 或 JPEG）。</v>
+        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Cancel</v>
+        <v>OK</v>
       </c>
       <c r="B253" t="str">
-        <v>取消</v>
+        <v>确定</v>
       </c>
       <c r="C253" t="str">
-        <v>取消</v>
+        <v>確定</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B254" t="str">
-        <v>有 {n} 个文件未加载</v>
+        <v>将 ICC 配置文件拖到此处</v>
       </c>
       <c r="C254" t="str">
-        <v>有 {n} 個檔案未載入</v>
+        <v>將 ICC 設定檔拖到此處</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>or</v>
       </c>
       <c r="B255" t="str">
-        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
+        <v>或</v>
       </c>
       <c r="C255" t="str">
-        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
+        <v>或</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>OK</v>
+        <v>Choose file</v>
       </c>
       <c r="B256" t="str">
-        <v>确定</v>
+        <v>选择文件</v>
       </c>
       <c r="C256" t="str">
-        <v>確定</v>
+        <v>選擇檔案</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B257" t="str">
-        <v>将 ICC 配置文件拖到此处</v>
+        <v>.icc 和 .icm 文件</v>
       </c>
       <c r="C257" t="str">
-        <v>將 ICC 設定檔拖到此處</v>
+        <v>.icc 與 .icm 檔案</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>or</v>
+        <v>Header</v>
       </c>
       <c r="B258" t="str">
-        <v>或</v>
+        <v>标头</v>
       </c>
       <c r="C258" t="str">
-        <v>或</v>
+        <v>標頭</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Choose file</v>
+        <v>Tags</v>
       </c>
       <c r="B259" t="str">
-        <v>选择文件</v>
+        <v>标签</v>
       </c>
       <c r="C259" t="str">
-        <v>選擇檔案</v>
+        <v>標籤</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>.icc and .icm files</v>
+        <v>Validation</v>
       </c>
       <c r="B260" t="str">
-        <v>.icc 和 .icm 文件</v>
+        <v>验证</v>
       </c>
       <c r="C260" t="str">
-        <v>.icc 與 .icm 檔案</v>
+        <v>驗證</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Header</v>
+        <v>Analysis</v>
       </c>
       <c r="B261" t="str">
-        <v>标头</v>
+        <v>分析</v>
       </c>
       <c r="C261" t="str">
-        <v>標頭</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Tags</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B262" t="str">
-        <v>标签</v>
+        <v>中性轴墨量</v>
       </c>
       <c r="C262" t="str">
-        <v>標籤</v>
+        <v>中性軸墨量</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Validation</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B263" t="str">
-        <v>验证</v>
+        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
       </c>
       <c r="C263" t="str">
-        <v>驗證</v>
+        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Analysis</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B264" t="str">
-        <v>分析</v>
+        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C264" t="str">
-        <v>分析</v>
+        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B265" t="str">
-        <v>中性轴墨量</v>
+        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
       </c>
       <c r="C265" t="str">
-        <v>中性軸墨量</v>
+        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B266" t="str">
-        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
+        <v>渲染意图</v>
       </c>
       <c r="C266" t="str">
-        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>% ink</v>
       </c>
       <c r="B267" t="str">
-        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
+        <v>% 墨量</v>
       </c>
       <c r="C267" t="str">
-        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
+        <v>% 墨量</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Perceptual</v>
       </c>
       <c r="B268" t="str">
-        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
+        <v>感知</v>
       </c>
       <c r="C268" t="str">
-        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Rendering intent</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B269" t="str">
-        <v>渲染意图</v>
+        <v>相对比色</v>
       </c>
       <c r="C269" t="str">
-        <v>轉換意圖</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>% ink</v>
+        <v>Saturation</v>
       </c>
       <c r="B270" t="str">
-        <v>% 墨量</v>
+        <v>饱和度</v>
       </c>
       <c r="C270" t="str">
-        <v>% 墨量</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Perceptual</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B271" t="str">
-        <v>感知</v>
+        <v>绝对比色</v>
       </c>
       <c r="C271" t="str">
-        <v>感知</v>
+        <v>絕對比色</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B272" t="str">
-        <v>相对比色</v>
+        <v>特性文件统计</v>
       </c>
       <c r="C272" t="str">
-        <v>相對比色</v>
+        <v>特性檔統計</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Saturation</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B273" t="str">
-        <v>饱和度</v>
+        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
       </c>
       <c r="C273" t="str">
-        <v>飽和度</v>
+        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B274" t="str">
-        <v>绝对比色</v>
+        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
       </c>
       <c r="C274" t="str">
-        <v>絕對比色</v>
+        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Profile Statistics</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B275" t="str">
-        <v>特性文件统计</v>
+        <v>渲染意图</v>
       </c>
       <c r="C275" t="str">
-        <v>特性檔統計</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B276" t="str">
-        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
+        <v>色域体积 (ΔE³)</v>
       </c>
       <c r="C276" t="str">
-        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
+        <v>色域體積 (ΔE³)</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B277" t="str">
-        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C277" t="str">
-        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Rendering intent</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B278" t="str">
-        <v>渲染意图</v>
+        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
       </c>
       <c r="C278" t="str">
-        <v>轉換意圖</v>
+        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>mean</v>
       </c>
       <c r="B279" t="str">
-        <v>色域体积 (ΔE³)</v>
+        <v>均值</v>
       </c>
       <c r="C279" t="str">
-        <v>色域體積 (ΔE³)</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Round-trip ΔE</v>
+        <v>P90</v>
       </c>
       <c r="B280" t="str">
-        <v>往返 ΔE</v>
+        <v>P90</v>
       </c>
       <c r="C280" t="str">
-        <v>往返 ΔE</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>max</v>
       </c>
       <c r="B281" t="str">
-        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
+        <v>最大</v>
       </c>
       <c r="C281" t="str">
-        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>mean</v>
+        <v>Analysing…</v>
       </c>
       <c r="B282" t="str">
-        <v>均值</v>
+        <v>正在分析…</v>
       </c>
       <c r="C282" t="str">
-        <v>平均</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>P90</v>
+        <v>Analysis</v>
       </c>
       <c r="B283" t="str">
-        <v>P90</v>
+        <v>分析</v>
       </c>
       <c r="C283" t="str">
-        <v>P90</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>max</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B284" t="str">
-        <v>最大</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C284" t="str">
-        <v>最大</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B285" t="str">
-        <v>正在分析…</v>
+        <v>绘图</v>
       </c>
       <c r="C285" t="str">
-        <v>正在分析…</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B286" t="str">
-        <v>分析</v>
+        <v>原始输出</v>
       </c>
       <c r="C286" t="str">
-        <v>分析</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B287" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>XML</v>
       </c>
       <c r="C287" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Plot</v>
+        <v>JSON</v>
       </c>
       <c r="B288" t="str">
-        <v>绘图</v>
+        <v>JSON</v>
       </c>
       <c r="C288" t="str">
-        <v>繪圖</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Raw Output</v>
+        <v>Curves</v>
       </c>
       <c r="B289" t="str">
-        <v>原始输出</v>
+        <v>曲线</v>
       </c>
       <c r="C289" t="str">
-        <v>原始輸出</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>XML</v>
+        <v>Input curves</v>
       </c>
       <c r="B290" t="str">
-        <v>XML</v>
+        <v>输入曲线</v>
       </c>
       <c r="C290" t="str">
-        <v>XML</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>JSON</v>
+        <v>Output curves</v>
       </c>
       <c r="B291" t="str">
-        <v>JSON</v>
+        <v>输出曲线</v>
       </c>
       <c r="C291" t="str">
-        <v>JSON</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Curves</v>
+        <v>CLUT image</v>
       </c>
       <c r="B292" t="str">
-        <v>曲线</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C292" t="str">
-        <v>曲線</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Input curves</v>
+        <v>Gamut image</v>
       </c>
       <c r="B293" t="str">
-        <v>输入曲线</v>
+        <v>色域图像</v>
       </c>
       <c r="C293" t="str">
-        <v>輸入曲線</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Output curves</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B294" t="str">
-        <v>输出曲线</v>
+        <v>色度</v>
       </c>
       <c r="C294" t="str">
-        <v>輸出曲線</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>CLUT image</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B295" t="str">
-        <v>CLUT 图像</v>
+        <v>散点图</v>
       </c>
       <c r="C295" t="str">
-        <v>CLUT 影像</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Gamut image</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B296" t="str">
-        <v>色域图像</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C296" t="str">
-        <v>色域影像</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Chromaticity</v>
+        <v>Curve table</v>
       </c>
       <c r="B297" t="str">
-        <v>色度</v>
+        <v>曲线表</v>
       </c>
       <c r="C297" t="str">
-        <v>色度</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Scatter plot</v>
+        <v>Tables</v>
       </c>
       <c r="B298" t="str">
-        <v>散点图</v>
+        <v>表格</v>
       </c>
       <c r="C298" t="str">
-        <v>散佈圖</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tone response curve</v>
+        <v>Data</v>
       </c>
       <c r="B299" t="str">
-        <v>色调响应曲线</v>
+        <v>数据</v>
       </c>
       <c r="C299" t="str">
-        <v>色調響應曲線</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Curve table</v>
+        <v>Evaluate</v>
       </c>
       <c r="B300" t="str">
-        <v>曲线表</v>
+        <v>求值</v>
       </c>
       <c r="C300" t="str">
-        <v>曲線表</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Tables</v>
+        <v>Loading…</v>
       </c>
       <c r="B301" t="str">
-        <v>表格</v>
+        <v>加载中…</v>
       </c>
       <c r="C301" t="str">
-        <v>表格</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Data</v>
+        <v>Input</v>
       </c>
       <c r="B302" t="str">
-        <v>数据</v>
+        <v>输入</v>
       </c>
       <c r="C302" t="str">
-        <v>資料</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Evaluate</v>
+        <v>Output</v>
       </c>
       <c r="B303" t="str">
-        <v>求值</v>
+        <v>输出</v>
       </c>
       <c r="C303" t="str">
-        <v>求值</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Loading…</v>
+        <v>Floating point</v>
       </c>
       <c r="B304" t="str">
-        <v>加载中…</v>
+        <v>浮点值</v>
       </c>
       <c r="C304" t="str">
-        <v>載入中…</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Input</v>
+        <v>Grid point</v>
       </c>
       <c r="B305" t="str">
-        <v>输入</v>
+        <v>网格点</v>
       </c>
       <c r="C305" t="str">
-        <v>輸入</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Output</v>
+        <v>Normalized</v>
       </c>
       <c r="B306" t="str">
-        <v>输出</v>
+        <v>归一化</v>
       </c>
       <c r="C306" t="str">
-        <v>輸出</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Floating point</v>
+        <v>Human</v>
       </c>
       <c r="B307" t="str">
-        <v>浮点值</v>
+        <v>可读值</v>
       </c>
       <c r="C307" t="str">
-        <v>浮點值</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Grid point</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B308" t="str">
-        <v>网格点</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C308" t="str">
-        <v>網格點</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Normalized</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B309" t="str">
-        <v>归一化</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C309" t="str">
-        <v>正規化</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Human</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B310" t="str">
-        <v>可读值</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C310" t="str">
-        <v>可讀值</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Device → PCS</v>
+        <v>Loading…</v>
       </c>
       <c r="B311" t="str">
-        <v>设备 → PCS</v>
+        <v>加载中…</v>
       </c>
       <c r="C311" t="str">
-        <v>裝置 → PCS</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B312" t="str">
-        <v>PCS → 设备</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C312" t="str">
-        <v>PCS → 裝置</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No CLUT grid</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B313" t="str">
-        <v>无 CLUT 网格</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C313" t="str">
-        <v>無 CLUT 網格</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Loading…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B314" t="str">
-        <v>加载中…</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C314" t="str">
-        <v>載入中…</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B315" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C315" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B316" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C316" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B317" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C317" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B318" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C318" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Security</v>
       </c>
       <c r="B319" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>安全性</v>
       </c>
       <c r="C319" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Conformance</v>
       </c>
       <c r="B320" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>符合性</v>
       </c>
       <c r="C320" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Quality</v>
       </c>
       <c r="B321" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>质量</v>
       </c>
       <c r="C321" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Security</v>
+        <v>REPORT</v>
       </c>
       <c r="B322" t="str">
-        <v>安全性</v>
+        <v>报告</v>
       </c>
       <c r="C322" t="str">
-        <v>安全性</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Conformance</v>
+        <v>FAIL</v>
       </c>
       <c r="B323" t="str">
-        <v>符合性</v>
+        <v>失败</v>
       </c>
       <c r="C323" t="str">
-        <v>符合性</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Quality</v>
+        <v>checks</v>
       </c>
       <c r="B324" t="str">
-        <v>质量</v>
+        <v>项检查</v>
       </c>
       <c r="C324" t="str">
-        <v>品質</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>REPORT</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B325" t="str">
-        <v>报告</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C325" t="str">
-        <v>報告</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>FAIL</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B326" t="str">
-        <v>失败</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C326" t="str">
-        <v>失敗</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>checks</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B327" t="str">
-        <v>项检查</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C327" t="str">
-        <v>項檢查</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B328" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C328" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Subscribe</v>
       </c>
       <c r="B329" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>订阅</v>
       </c>
       <c r="C329" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B330" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C330" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Powered by {lib}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B331" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C331" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B332" t="str">
-        <v>订阅</v>
+        <v>关闭</v>
       </c>
       <c r="C332" t="str">
-        <v>訂閱</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B333" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C333" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Get notified about new releases</v>
+        <v>Email address</v>
       </c>
       <c r="B334" t="str">
-        <v>订阅新版本通知</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C334" t="str">
-        <v>訂閱新版本通知</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B335" t="str">
-        <v>关闭</v>
+        <v>you@example.com</v>
       </c>
       <c r="C335" t="str">
-        <v>關閉</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B336" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C336" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Email address</v>
+        <v>(optional)</v>
       </c>
       <c r="B337" t="str">
-        <v>电子邮件地址</v>
+        <v>（选填）</v>
       </c>
       <c r="C337" t="str">
-        <v>電子郵件地址</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>you@example.com</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B338" t="str">
-        <v>you@example.com</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C338" t="str">
-        <v>you@example.com</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>How will you use profiletool?</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B339" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C339" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>(optional)</v>
+        <v>Cancel</v>
       </c>
       <c r="B340" t="str">
-        <v>（选填）</v>
+        <v>取消</v>
       </c>
       <c r="C340" t="str">
-        <v>（選填）</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B341" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>订阅</v>
       </c>
       <c r="C341" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B342" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C342" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Cancel</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B343" t="str">
-        <v>取消</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C343" t="str">
-        <v>取消</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B344" t="str">
-        <v>订阅</v>
+        <v>关闭</v>
       </c>
       <c r="C344" t="str">
-        <v>訂閱</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B345" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C345" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B346" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C346" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Close</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B347" t="str">
-        <v>关闭</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C347" t="str">
-        <v>關閉</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Privacy notice</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B348" t="str">
-        <v>隐私声明</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C348" t="str">
-        <v>隱私聲明</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C349" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C350" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Error:</v>
       </c>
       <c r="B351" t="str">
-        <v>请检查表单后重试。</v>
+        <v>错误：</v>
       </c>
       <c r="C351" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B352" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C352" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B353" t="str">
-        <v>网络错误，请重试。</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C353" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Error:</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B354" t="str">
-        <v>错误：</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C354" t="str">
-        <v>錯誤：</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to XML</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B355" t="str">
-        <v>转换为 XML</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C355" t="str">
-        <v>轉換為 XML</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Convert to JSON</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B356" t="str">
-        <v>转换为 JSON</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C356" t="str">
-        <v>轉換為 JSON</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B357" t="str">
-        <v>转换为 ICC</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C357" t="str">
-        <v>轉換為 ICC</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to XML…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B358" t="str">
-        <v>正在转换为 XML…</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C358" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Converting to JSON…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B359" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C359" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Converting to ICC…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B360" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C360" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Load ICC profile</v>
+        <v>No tags found.</v>
       </c>
       <c r="B361" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C361" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Tag Name</v>
       </c>
       <c r="B362" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>标签名称</v>
       </c>
       <c r="C362" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Profile ID</v>
+        <v>ID</v>
       </c>
       <c r="B363" t="str">
-        <v>配置文件 ID</v>
+        <v>ID</v>
       </c>
       <c r="C363" t="str">
-        <v>設定檔 ID</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>No tags found.</v>
+        <v>Offset</v>
       </c>
       <c r="B364" t="str">
-        <v>未找到标签。</v>
+        <v>偏移</v>
       </c>
       <c r="C364" t="str">
-        <v>找不到標籤。</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Tag Name</v>
+        <v>Size</v>
       </c>
       <c r="B365" t="str">
-        <v>标签名称</v>
+        <v>大小</v>
       </c>
       <c r="C365" t="str">
-        <v>標籤名稱</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ID</v>
+        <v>Pad</v>
       </c>
       <c r="B366" t="str">
-        <v>ID</v>
+        <v>填充</v>
       </c>
       <c r="C366" t="str">
-        <v>ID</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Offset</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B367" t="str">
-        <v>偏移</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C367" t="str">
-        <v>偏移</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Size</v>
+        <v>Type</v>
       </c>
       <c r="B368" t="str">
-        <v>大小</v>
+        <v>类型</v>
       </c>
       <c r="C368" t="str">
-        <v>大小</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Pad</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B369" t="str">
-        <v>填充</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C369" t="str">
-        <v>填充</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Bytes changed since load</v>
+        <v>(No content)</v>
       </c>
       <c r="B370" t="str">
-        <v>加载后字节已更改</v>
+        <v>（无内容）</v>
       </c>
       <c r="C370" t="str">
-        <v>載入後位元組已變更</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Type</v>
+        <v>bytes</v>
       </c>
       <c r="B371" t="str">
-        <v>类型</v>
+        <v>字节</v>
       </c>
       <c r="C371" t="str">
-        <v>類型</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Array of {type}</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B372" t="str">
-        <v>{type} 数组</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C372" t="str">
-        <v>{type} 陣列</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>(No content)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B373" t="str">
-        <v>（无内容）</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C373" t="str">
-        <v>（無內容）</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>bytes</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B374" t="str">
-        <v>字节</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C374" t="str">
-        <v>位元組</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Loading full description…</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B375" t="str">
-        <v>正在加载完整描述…</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C375" t="str">
-        <v>正在載入完整描述…</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Could not load full description:</v>
+        <v>No validation output</v>
       </c>
       <c r="B376" t="str">
-        <v>无法加载完整描述：</v>
+        <v>无验证输出</v>
       </c>
       <c r="C376" t="str">
-        <v>無法載入完整描述：</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B377" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C377" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B378" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C378" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>No validation output</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B379" t="str">
-        <v>无验证输出</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C379" t="str">
-        <v>無驗證輸出</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B380" t="str">
-        <v>配置文件有效</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C380" t="str">
-        <v>設定檔有效</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B381" t="str">
-        <v>配置文件有警告</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C381" t="str">
-        <v>設定檔有警告</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B382" t="str">
-        <v>配置文件不合规</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C382" t="str">
-        <v>設定檔不符合規範</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical validation error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B383" t="str">
-        <v>严重验证错误</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C383" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Unknown validation status</v>
+        <v>Valid</v>
       </c>
       <c r="B384" t="str">
-        <v>未知验证状态</v>
+        <v>有效</v>
       </c>
       <c r="C384" t="str">
-        <v>未知驗證狀態</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Warning</v>
       </c>
       <c r="B385" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>警告</v>
       </c>
       <c r="C385" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Error</v>
       </c>
       <c r="B386" t="str">
-        <v>未发现警告或错误。</v>
+        <v>错误</v>
       </c>
       <c r="C386" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Valid</v>
+        <v>Unknown</v>
       </c>
       <c r="B387" t="str">
-        <v>有效</v>
+        <v>未知</v>
       </c>
       <c r="C387" t="str">
-        <v>有效</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Warning</v>
+        <v>Pass</v>
       </c>
       <c r="B388" t="str">
-        <v>警告</v>
+        <v>通过</v>
       </c>
       <c r="C388" t="str">
-        <v>警告</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Error</v>
+        <v>Fail</v>
       </c>
       <c r="B389" t="str">
-        <v>错误</v>
+        <v>失败</v>
       </c>
       <c r="C389" t="str">
-        <v>錯誤</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Unknown</v>
+        <v>View in context</v>
       </c>
       <c r="B390" t="str">
-        <v>未知</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C390" t="str">
-        <v>未知</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Pass</v>
+        <v>Validation detail</v>
       </c>
       <c r="B391" t="str">
-        <v>通过</v>
+        <v>验证详情</v>
       </c>
       <c r="C391" t="str">
-        <v>通過</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Fail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B392" t="str">
-        <v>失败</v>
+        <v>触发字段</v>
       </c>
       <c r="C392" t="str">
-        <v>失敗</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>View in context</v>
+        <v>Field</v>
       </c>
       <c r="B393" t="str">
-        <v>在上下文中查看</v>
+        <v>字段</v>
       </c>
       <c r="C393" t="str">
-        <v>在上下文中檢視</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Validation detail</v>
+        <v>Current value</v>
       </c>
       <c r="B394" t="str">
-        <v>验证详情</v>
+        <v>当前值</v>
       </c>
       <c r="C394" t="str">
-        <v>驗證詳情</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Triggered by</v>
+        <v>Required: 0</v>
       </c>
       <c r="B395" t="str">
-        <v>触发字段</v>
+        <v>要求：0</v>
       </c>
       <c r="C395" t="str">
-        <v>觸發欄位</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Field</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B396" t="str">
-        <v>字段</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C396" t="str">
-        <v>欄位</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Current value</v>
+        <v>Invalid</v>
       </c>
       <c r="B397" t="str">
-        <v>当前值</v>
+        <v>无效</v>
       </c>
       <c r="C397" t="str">
-        <v>目前值</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Required: 0</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B398" t="str">
-        <v>要求：0</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C398" t="str">
-        <v>要求：0</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Expected: {value}</v>
+        <v>Close</v>
       </c>
       <c r="B399" t="str">
-        <v>预期：{value}</v>
+        <v>关闭</v>
       </c>
       <c r="C399" t="str">
-        <v>預期：{value}</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Invalid</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B400" t="str">
-        <v>无效</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C400" t="str">
-        <v>無效</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C401" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Close</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B402" t="str">
-        <v>关闭</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C402" t="str">
-        <v>關閉</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Loading XML editor…</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C403" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Loading JSON editor…</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B404" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C404" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B405" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C405" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B406" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C406" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C407" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>indent</v>
       </c>
       <c r="B408" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>缩进</v>
       </c>
       <c r="C408" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>縮排</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>sort keys</v>
       </c>
       <c r="B409" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>排序键</v>
       </c>
       <c r="C409" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>排序鍵</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B410" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
       <c r="C410" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B411" t="str">
-        <v>缩进</v>
-      </c>
-      <c r="C411" t="str">
-        <v>縮排</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B412" t="str">
-        <v>排序键</v>
-      </c>
-      <c r="C412" t="str">
-        <v>排序鍵</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B413" t="str">
-        <v>已从编辑写入配置文件，但重新验证失败：</v>
-      </c>
-      <c r="C413" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C413"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C410"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C410"/>
+  <dimension ref="A1:C411"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -417,4515 +417,4526 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Round-Trip (PRMG)</v>
+        <v>{pct}% of samples were out of range and were clamped.</v>
       </c>
       <c r="B2" t="str">
-        <v>往返 (PRMG)</v>
+        <v>{pct}% 的采样值超出范围，已被裁剪。</v>
       </c>
       <c r="C2" t="str">
-        <v>往返 (PRMG)</v>
+        <v>{pct}% 的取樣值超出範圍，已被裁剪。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B3" t="str">
-        <v>按照参考工具 iccRoundTrip 对配置文件的设备立方体进行往返计算。往返 1 是设备→PCS→设备的误差 (ΔE*ab)；往返 2 衡量 PCS 往返的稳定性。PRMG 直方图显示与感知参考媒介色域 (Perceptual Reference Medium Gamut) 的互操作性。</v>
+        <v>往返 (PRMG)</v>
       </c>
       <c r="C3" t="str">
-        <v>依照參考工具 iccRoundTrip 對描述檔的裝置立方體進行往返計算。往返 1 是裝置→PCS→裝置的誤差 (ΔE*ab)；往返 2 衡量 PCS 往返的穩定性。PRMG 長條圖顯示與感知參考媒體色域 (Perceptual Reference Medium Gamut) 的互通性。</v>
+        <v>往返 (PRMG)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Use MPE (color) tags</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B4" t="str">
-        <v>使用 MPE（颜色）标签</v>
+        <v>按照参考工具 iccRoundTrip 对配置文件的设备立方体进行往返计算。往返 1 是设备→PCS→设备的误差 (ΔE*ab)；往返 2 衡量 PCS 往返的稳定性。PRMG 直方图显示与感知参考媒介色域 (Perceptual Reference Medium Gamut) 的互操作性。</v>
       </c>
       <c r="C4" t="str">
-        <v>使用 MPE（色彩）標籤</v>
+        <v>依照參考工具 iccRoundTrip 對描述檔的裝置立方體進行往返計算。往返 1 是裝置→PCS→裝置的誤差 (ΔE*ab)；往返 2 衡量 PCS 往返的穩定性。PRMG 長條圖顯示與感知參考媒體色域 (Perceptual Reference Medium Gamut) 的互通性。</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B5" t="str">
-        <v>此配置文件无法往返——缺少该指标所需的设备↔PCS 转换（例如单向或抽象配置文件）。</v>
+        <v>使用 MPE（颜色）标签</v>
       </c>
       <c r="C5" t="str">
-        <v>此描述檔無法往返——缺少此指標所需的裝置↔PCS 轉換（例如單向或抽象描述檔）。</v>
+        <v>使用 MPE（色彩）標籤</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B6" t="str">
-        <v>已跳过往返：设备色彩空间太大，无法评估（样本过多）。</v>
+        <v>此配置文件无法往返——缺少该指标所需的设备↔PCS 转换（例如单向或抽象配置文件）。</v>
       </c>
       <c r="C6" t="str">
-        <v>已略過往返：裝置色彩空間太大，無法評估（樣本過多）。</v>
+        <v>此描述檔無法往返——缺少此指標所需的裝置↔PCS 轉換（例如單向或抽象描述檔）。</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Metric</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B7" t="str">
-        <v>指标</v>
+        <v>已跳过往返：设备色彩空间太大，无法评估（样本过多）。</v>
       </c>
       <c r="C7" t="str">
-        <v>指標</v>
+        <v>已略過往返：裝置色彩空間太大，無法評估（樣本過多）。</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Round Trip 1</v>
+        <v>Metric</v>
       </c>
       <c r="B8" t="str">
-        <v>往返 1</v>
+        <v>指标</v>
       </c>
       <c r="C8" t="str">
-        <v>往返 1</v>
+        <v>指標</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Round Trip 2</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B9" t="str">
-        <v>往返 2</v>
+        <v>往返 1</v>
       </c>
       <c r="C9" t="str">
-        <v>往返 2</v>
+        <v>往返 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>device → PCS → device</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B10" t="str">
-        <v>设备 → PCS → 设备</v>
+        <v>往返 2</v>
       </c>
       <c r="C10" t="str">
-        <v>裝置 → PCS → 裝置</v>
+        <v>往返 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>PCS round-trip stability</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B11" t="str">
-        <v>PCS 往返稳定性</v>
+        <v>设备 → PCS → 设备</v>
       </c>
       <c r="C11" t="str">
-        <v>PCS 往返穩定性</v>
+        <v>裝置 → PCS → 裝置</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Min ΔE</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B12" t="str">
-        <v>最小 ΔE</v>
+        <v>PCS 往返稳定性</v>
       </c>
       <c r="C12" t="str">
-        <v>最小 ΔE</v>
+        <v>PCS 往返穩定性</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mean ΔE</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>平均 ΔE</v>
+        <v>最小 ΔE</v>
       </c>
       <c r="C13" t="str">
-        <v>平均 ΔE</v>
+        <v>最小 ΔE</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max ΔE</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>最大 ΔE</v>
+        <v>平均 ΔE</v>
       </c>
       <c r="C14" t="str">
-        <v>最大 ΔE</v>
+        <v>平均 ΔE</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Worst L, a, b</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B15" t="str">
-        <v>最差 L, a, b</v>
+        <v>最大 ΔE</v>
       </c>
       <c r="C15" t="str">
-        <v>最差 L, a, b</v>
+        <v>最大 ΔE</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Specified gamut</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B16" t="str">
-        <v>指定色域</v>
+        <v>最差 L, a, b</v>
       </c>
       <c r="C16" t="str">
-        <v>指定色域</v>
+        <v>最差 L, a, b</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>感知参考媒介色域</v>
+        <v>指定色域</v>
       </c>
       <c r="C17" t="str">
-        <v>感知參考媒體色域</v>
+        <v>指定色域</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Not specified</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B18" t="str">
-        <v>未指定</v>
+        <v>感知参考媒介色域</v>
       </c>
       <c r="C18" t="str">
-        <v>未指定</v>
+        <v>感知參考媒體色域</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not evaluated</v>
+        <v>Not specified</v>
       </c>
       <c r="B19" t="str">
-        <v>未评估</v>
+        <v>未指定</v>
       </c>
       <c r="C19" t="str">
-        <v>未評估</v>
+        <v>未指定</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PRMG interoperability</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B20" t="str">
-        <v>PRMG 互操作性</v>
+        <v>未评估</v>
       </c>
       <c r="C20" t="str">
-        <v>PRMG 互通性</v>
+        <v>未評估</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Round-trip ΔE</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B21" t="str">
-        <v>往返 ΔE</v>
+        <v>PRMG 互操作性</v>
       </c>
       <c r="C21" t="str">
-        <v>往返 ΔE</v>
+        <v>PRMG 互通性</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Count</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B22" t="str">
-        <v>数量</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C22" t="str">
-        <v>數量</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Share</v>
+        <v>Count</v>
       </c>
       <c r="B23" t="str">
-        <v>占比</v>
+        <v>数量</v>
       </c>
       <c r="C23" t="str">
-        <v>占比</v>
+        <v>數量</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Total</v>
+        <v>Share</v>
       </c>
       <c r="B24" t="str">
-        <v>总计</v>
+        <v>占比</v>
       </c>
       <c r="C24" t="str">
-        <v>總計</v>
+        <v>占比</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Total</v>
       </c>
       <c r="B25" t="str">
-        <v>未评估 PRMG</v>
+        <v>总计</v>
       </c>
       <c r="C25" t="str">
-        <v>未評估 PRMG</v>
+        <v>總計</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B26" t="str">
-        <v>针对某一渲染意图的整份配置文件指标：由设备→PCS 变换所包围的色域体积 (ΔE*ab³)，以及往返精度指标。选择渲染意图和往返类型 — 表格和直方图会相应更新。</v>
+        <v>未评估 PRMG</v>
       </c>
       <c r="C26" t="str">
-        <v>針對某一轉換意圖的整份設定檔指標：由裝置→PCS 轉換所包圍的色域體積 (ΔE*ab³)，以及往返精度指標。選擇轉換意圖與往返類型 — 表格與長條圖會隨之更新。</v>
+        <v>未評估 PRMG</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Round-trip type</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B27" t="str">
-        <v>往返类型</v>
+        <v>针对某一渲染意图的整份配置文件指标：由设备→PCS 变换所包围的色域体积 (ΔE*ab³)，以及往返精度指标。选择渲染意图和往返类型 — 表格和直方图会相应更新。</v>
       </c>
       <c r="C27" t="str">
-        <v>往返類型</v>
+        <v>針對某一轉換意圖的整份設定檔指標：由裝置→PCS 轉換所包圍的色域體積 (ΔE*ab³)，以及往返精度指標。選擇轉換意圖與往返類型 — 表格與長條圖會隨之更新。</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>对此往返类型无影响</v>
+        <v>往返类型</v>
       </c>
       <c r="C28" t="str">
-        <v>對此往返類型無影響</v>
+        <v>往返類型</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B29" t="str">
-        <v>此往返类型不适用于该配置文件。</v>
+        <v>对此往返类型无影响</v>
       </c>
       <c r="C29" t="str">
-        <v>此往返類型不適用於此設定檔。</v>
+        <v>對此往返類型無影響</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B30" t="str">
-        <v>往返 ΔE 分布</v>
+        <v>此往返类型不适用于该配置文件。</v>
       </c>
       <c r="C30" t="str">
-        <v>往返 ΔE 分佈</v>
+        <v>此往返類型不適用於此設定檔。</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B31" t="str">
-        <v>没有往返样本落在评估区域内。</v>
+        <v>往返 ΔE 分布</v>
       </c>
       <c r="C31" t="str">
-        <v>沒有往返樣本落在評估區域內。</v>
+        <v>往返 ΔE 分佈</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Std Dev</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B32" t="str">
-        <v>标准差</v>
+        <v>没有往返样本落在评估区域内。</v>
       </c>
       <c r="C32" t="str">
-        <v>標準差</v>
+        <v>沒有往返樣本落在評估區域內。</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Relative frequency</v>
+        <v>Std Dev</v>
       </c>
       <c r="B33" t="str">
-        <v>相对频率</v>
+        <v>标准差</v>
       </c>
       <c r="C33" t="str">
-        <v>相對頻率</v>
+        <v>標準差</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cumulative frequency</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>累积频率</v>
+        <v>相对频率</v>
       </c>
       <c r="C34" t="str">
-        <v>累積頻率</v>
+        <v>相對頻率</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Horizontal scale</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B35" t="str">
-        <v>水平刻度</v>
+        <v>累积频率</v>
       </c>
       <c r="C35" t="str">
-        <v>水平刻度</v>
+        <v>累積頻率</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Integer ΔE</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B36" t="str">
-        <v>整数 ΔE</v>
+        <v>水平刻度</v>
       </c>
       <c r="C36" t="str">
-        <v>整數 ΔE</v>
+        <v>水平刻度</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Auto-scale</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B37" t="str">
-        <v>自动缩放</v>
+        <v>整数 ΔE</v>
       </c>
       <c r="C37" t="str">
-        <v>自動縮放</v>
+        <v>整數 ΔE</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bins</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B38" t="str">
-        <v>分组</v>
+        <v>自动缩放</v>
       </c>
       <c r="C38" t="str">
-        <v>分組</v>
+        <v>自動縮放</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CLUT Image</v>
+        <v>Bins</v>
       </c>
       <c r="B39" t="str">
-        <v>CLUT 图像</v>
+        <v>分组</v>
       </c>
       <c r="C39" t="str">
-        <v>CLUT 影像</v>
+        <v>分組</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B40" t="str">
-        <v>设备↔PCS 变换的颜色查找表 (CLUT)，平铺成一幅图像。选择要查看的渲染意图表。</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C40" t="str">
-        <v>裝置↔PCS 轉換的色彩查找表 (CLUT)，平鋪成一幅影像。選擇要檢視的轉換意圖表。</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B41" t="str">
-        <v>此配置文件没有可供可视化的基于 CLUT 的设备↔PCS 表。</v>
+        <v>设备↔PCS 变换的颜色查找表 (CLUT)，平铺成一幅图像。选择要查看的渲染意图表。</v>
       </c>
       <c r="C41" t="str">
-        <v>此設定檔沒有可供視覺化的基於 CLUT 的裝置↔PCS 表。</v>
+        <v>裝置↔PCS 轉換的色彩查找表 (CLUT)，平鋪成一幅影像。選擇要檢視的轉換意圖表。</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Gamut Image</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B42" t="str">
-        <v>色域图像</v>
+        <v>此配置文件没有可供可视化的基于 CLUT 的设备↔PCS 表。</v>
       </c>
       <c r="C42" t="str">
-        <v>色域影像</v>
+        <v>此設定檔沒有可供視覺化的基於 CLUT 的裝置↔PCS 表。</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B43" t="str">
-        <v>色域标签的色域内/外映射：PCS 颜色可再现处为中性色，落在设备色域之外处为红色。</v>
+        <v>色域图像</v>
       </c>
       <c r="C43" t="str">
-        <v>色域標籤的色域內/外對應：PCS 色彩可重現處為中性色，落在裝置色域之外處為紅色。</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B44" t="str">
-        <v>此配置文件没有可供可视化的色域标签。</v>
+        <v>色域标签的色域内/外映射：PCS 颜色可再现处为中性色，落在设备色域之外处为红色。</v>
       </c>
       <c r="C44" t="str">
-        <v>此設定檔沒有可供視覺化的色域標籤。</v>
+        <v>色域標籤的色域內/外對應：PCS 色彩可重現處為中性色，落在裝置色域之外處為紅色。</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B45" t="str">
-        <v>垂直刻度</v>
+        <v>此配置文件没有可供可视化的色域标签。</v>
       </c>
       <c r="C45" t="str">
-        <v>垂直刻度</v>
+        <v>此設定檔沒有可供視覺化的色域標籤。</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>X–Y</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B46" t="str">
-        <v>X–Y</v>
+        <v>垂直刻度</v>
       </c>
       <c r="C46" t="str">
-        <v>X–Y</v>
+        <v>垂直刻度</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Tone increase</v>
+        <v>X–Y</v>
       </c>
       <c r="B47" t="str">
-        <v>色调增益</v>
+        <v>X–Y</v>
       </c>
       <c r="C47" t="str">
-        <v>色調增益</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B48" t="str">
-        <v>色调增益（输出 − 输入）</v>
+        <v>色调增益</v>
       </c>
       <c r="C48" t="str">
-        <v>色調增益（輸出 − 輸入）</v>
+        <v>色調增益</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Show full dump</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B49" t="str">
-        <v>显示完整转储</v>
+        <v>色调增益（输出 − 输入）</v>
       </c>
       <c r="C49" t="str">
-        <v>顯示完整傾印</v>
+        <v>色調增益（輸出 − 輸入）</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Output truncated for performance.</v>
+        <v>Show full dump</v>
       </c>
       <c r="B50" t="str">
-        <v>为提升性能，输出已截断。</v>
+        <v>显示完整转储</v>
       </c>
       <c r="C50" t="str">
-        <v>為提升效能，輸出已截斷。</v>
+        <v>顯示完整傾印</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B51" t="str">
-        <v>色域内概览 (RT0)</v>
+        <v>为提升性能，输出已截断。</v>
       </c>
       <c r="C51" t="str">
-        <v>色域內概覽 (RT0)</v>
+        <v>為提升效能，輸出已截斷。</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B52" t="str">
-        <v>反演 + 色域 (RT1)</v>
+        <v>色域内概览 (RT0)</v>
       </c>
       <c r="C52" t="str">
-        <v>反演 + 色域 (RT1)</v>
+        <v>色域內概覽 (RT0)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B53" t="str">
-        <v>可重现性 (RT2)</v>
+        <v>反演 + 色域 (RT1)</v>
       </c>
       <c r="C53" t="str">
-        <v>可重現性 (RT2)</v>
+        <v>反演 + 色域 (RT1)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PRMG interoperability</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B54" t="str">
-        <v>PRMG 互操作性</v>
+        <v>可重现性 (RT2)</v>
       </c>
       <c r="C54" t="str">
-        <v>PRMG 互操作性</v>
+        <v>可重現性 (RT2)</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B55" t="str">
-        <v>iccviz 概览：设备值网格被转换到 PCS、再回到设备、再次到 PCS；在两次 PCS 结果之间测量 ΔE*ab。这是一次快速的色域内稳定性检查。</v>
+        <v>PRMG 互操作性</v>
       </c>
       <c r="C55" t="str">
-        <v>iccviz 概覽：裝置值網格被轉換到 PCS、再回到裝置、再次到 PCS；在兩次 PCS 結果之間測量 ΔE*ab。這是一次快速的色域內穩定性檢查。</v>
+        <v>PRMG 互操作性</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B56" t="str">
-        <v>iccRoundTrip 往返 1：每个设备颜色的 PCS 与其经过一次 Lab → 设备 → Lab 往返后的 PCS 之间的 ΔE*ab。反映反演精度和色域映射。</v>
+        <v>iccviz 概览：设备值网格被转换到 PCS、再回到设备、再次到 PCS；在两次 PCS 结果之间测量 ΔE*ab。这是一次快速的色域内稳定性检查。</v>
       </c>
       <c r="C56" t="str">
-        <v>iccRoundTrip 往返 1：每個裝置色彩的 PCS 與其經過一次 Lab → 裝置 → Lab 往返後的 PCS 之間的 ΔE*ab。反映反演精度與色域對應。</v>
+        <v>iccviz 概覽：裝置值網格被轉換到 PCS、再回到裝置、再次到 PCS；在兩次 PCS 結果之間測量 ΔE*ab。這是一次快速的色域內穩定性檢查。</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip 往返 2：第一次与第二次往返之间的 ΔE*ab — 重复的 PCS 往返有多稳定（可重现性，与第一次往返的色域裁剪无关）。</v>
+        <v>iccRoundTrip 往返 1：每个设备颜色的 PCS 与其经过一次 Lab → 设备 → Lab 往返后的 PCS 之间的 ΔE*ab。反映反演精度和色域映射。</v>
       </c>
       <c r="C57" t="str">
-        <v>iccRoundTrip 往返 2：第一次與第二次往返之間的 ΔE*ab — 重複的 PCS 往返有多穩定（可重現性，與第一次往返的色域裁剪無關）。</v>
+        <v>iccRoundTrip 往返 1：每個裝置色彩的 PCS 與其經過一次 Lab → 裝置 → Lab 往返後的 PCS 之間的 ΔE*ab。反映反演精度與色域對應。</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 内的 PCS 颜色进行一次往返（Lab → 设备 → Lab）；ΔE*ab 分布可指示跨配置文件的互操作性。</v>
+        <v>iccRoundTrip 往返 2：第一次与第二次往返之间的 ΔE*ab — 重复的 PCS 往返有多稳定（可重现性，与第一次往返的色域裁剪无关）。</v>
       </c>
       <c r="C58" t="str">
-        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 內的 PCS 色彩進行一次往返（Lab → 裝置 → Lab）；ΔE*ab 分佈可指示跨設定檔的互操作性。</v>
+        <v>iccRoundTrip 往返 2：第一次與第二次往返之間的 ΔE*ab — 重複的 PCS 往返有多穩定（可重現性，與第一次往返的色域裁剪無關）。</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Settings</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B59" t="str">
-        <v>设置</v>
+        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 内的 PCS 颜色进行一次往返（Lab → 设备 → Lab）；ΔE*ab 分布可指示跨配置文件的互操作性。</v>
       </c>
       <c r="C59" t="str">
-        <v>設定</v>
+        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 內的 PCS 色彩進行一次往返（Lab → 裝置 → Lab）；ΔE*ab 分佈可指示跨設定檔的互操作性。</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Display</v>
+        <v>Settings</v>
       </c>
       <c r="B60" t="str">
-        <v>显示</v>
+        <v>设置</v>
       </c>
       <c r="C60" t="str">
-        <v>顯示</v>
+        <v>設定</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Background</v>
+        <v>Display</v>
       </c>
       <c r="B61" t="str">
-        <v>背景</v>
+        <v>显示</v>
       </c>
       <c r="C61" t="str">
-        <v>背景</v>
+        <v>顯示</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Language</v>
+        <v>Background</v>
       </c>
       <c r="B62" t="str">
-        <v>语言</v>
+        <v>背景</v>
       </c>
       <c r="C62" t="str">
-        <v>語言</v>
+        <v>背景</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>System</v>
+        <v>Language</v>
       </c>
       <c r="B63" t="str">
-        <v>系统</v>
+        <v>语言</v>
       </c>
       <c r="C63" t="str">
-        <v>系統</v>
+        <v>語言</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Light</v>
+        <v>System</v>
       </c>
       <c r="B64" t="str">
-        <v>浅色</v>
+        <v>系统</v>
       </c>
       <c r="C64" t="str">
-        <v>淺色</v>
+        <v>系統</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dark</v>
+        <v>Light</v>
       </c>
       <c r="B65" t="str">
-        <v>深色</v>
+        <v>浅色</v>
       </c>
       <c r="C65" t="str">
-        <v>深色</v>
+        <v>淺色</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>System default</v>
+        <v>Dark</v>
       </c>
       <c r="B66" t="str">
-        <v>系统默认</v>
+        <v>深色</v>
       </c>
       <c r="C66" t="str">
-        <v>系統預設</v>
+        <v>深色</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Number format</v>
+        <v>System default</v>
       </c>
       <c r="B67" t="str">
-        <v>数字格式</v>
+        <v>系统默认</v>
       </c>
       <c r="C67" t="str">
-        <v>數字格式</v>
+        <v>系統預設</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hexadecimal</v>
+        <v>Number format</v>
       </c>
       <c r="B68" t="str">
-        <v>十六进制</v>
+        <v>数字格式</v>
       </c>
       <c r="C68" t="str">
-        <v>十六進位</v>
+        <v>數字格式</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B69" t="str">
-        <v>十进制</v>
+        <v>十六进制</v>
       </c>
       <c r="C69" t="str">
-        <v>十進位</v>
+        <v>十六進位</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Help</v>
+        <v>Decimal</v>
       </c>
       <c r="B70" t="str">
-        <v>帮助</v>
+        <v>十进制</v>
       </c>
       <c r="C70" t="str">
-        <v>說明</v>
+        <v>十進位</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Contact</v>
+        <v>Help</v>
       </c>
       <c r="B71" t="str">
-        <v>联系</v>
+        <v>帮助</v>
       </c>
       <c r="C71" t="str">
-        <v>聯絡</v>
+        <v>說明</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>User guide</v>
+        <v>Contact</v>
       </c>
       <c r="B72" t="str">
-        <v>用户指南</v>
+        <v>联系</v>
       </c>
       <c r="C72" t="str">
-        <v>使用者指南</v>
+        <v>聯絡</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Search guide</v>
+        <v>User guide</v>
       </c>
       <c r="B73" t="str">
-        <v>搜索指南</v>
+        <v>用户指南</v>
       </c>
       <c r="C73" t="str">
-        <v>搜尋指南</v>
+        <v>使用者指南</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search the user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B74" t="str">
-        <v>搜索用户指南</v>
+        <v>搜索指南</v>
       </c>
       <c r="C74" t="str">
-        <v>搜尋使用者指南</v>
+        <v>搜尋指南</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Previous match</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B75" t="str">
-        <v>上一个匹配项</v>
+        <v>搜索用户指南</v>
       </c>
       <c r="C75" t="str">
-        <v>上一個相符項目</v>
+        <v>搜尋使用者指南</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Next match</v>
+        <v>Previous match</v>
       </c>
       <c r="B76" t="str">
-        <v>下一个匹配项</v>
+        <v>上一个匹配项</v>
       </c>
       <c r="C76" t="str">
-        <v>下一個相符項目</v>
+        <v>上一個相符項目</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Close user guide</v>
+        <v>Next match</v>
       </c>
       <c r="B77" t="str">
-        <v>关闭用户指南</v>
+        <v>下一个匹配项</v>
       </c>
       <c r="C77" t="str">
-        <v>關閉使用者指南</v>
+        <v>下一個相符項目</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading…</v>
+        <v>Close user guide</v>
       </c>
       <c r="B78" t="str">
-        <v>加载中…</v>
+        <v>关闭用户指南</v>
       </c>
       <c r="C78" t="str">
-        <v>載入中…</v>
+        <v>關閉使用者指南</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>无法加载用户指南。</v>
+        <v>加载中…</v>
       </c>
       <c r="C79" t="str">
-        <v>無法載入使用者指南。</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>None</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B80" t="str">
-        <v>无</v>
+        <v>无法加载用户指南。</v>
       </c>
       <c r="C80" t="str">
-        <v>無</v>
+        <v>無法載入使用者指南。</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B81" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>无</v>
       </c>
       <c r="C81" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>無</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Based on</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B82" t="str">
-        <v>基于</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C82" t="str">
-        <v>基於</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>demo implementation</v>
+        <v>Based on</v>
       </c>
       <c r="B83" t="str">
-        <v>演示实现</v>
+        <v>基于</v>
       </c>
       <c r="C83" t="str">
-        <v>示範實作</v>
+        <v>基於</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Validating…</v>
+        <v>demo implementation</v>
       </c>
       <c r="B84" t="str">
-        <v>正在验证…</v>
+        <v>演示实现</v>
       </c>
       <c r="C84" t="str">
-        <v>驗證中…</v>
+        <v>示範實作</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Save ICC profile</v>
+        <v>Validating…</v>
       </c>
       <c r="B85" t="str">
-        <v>保存 ICC 配置文件</v>
+        <v>正在验证…</v>
       </c>
       <c r="C85" t="str">
-        <v>儲存 ICC 設定檔</v>
+        <v>驗證中…</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B86" t="str">
-        <v>● 已修改 — 尚未保存</v>
+        <v>保存 ICC 配置文件</v>
       </c>
       <c r="C86" t="str">
-        <v>● 已修改 — 尚未儲存</v>
+        <v>儲存 ICC 設定檔</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B87" t="str">
-        <v>配置文件</v>
+        <v>● 已修改 — 尚未保存</v>
       </c>
       <c r="C87" t="str">
-        <v>設定檔</v>
+        <v>● 已修改 — 尚未儲存</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Show profile pool</v>
+        <v>Profiles</v>
       </c>
       <c r="B88" t="str">
-        <v>显示配置文件池</v>
+        <v>配置文件</v>
       </c>
       <c r="C88" t="str">
-        <v>顯示設定檔集區</v>
+        <v>設定檔</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Collapse</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B89" t="str">
-        <v>收起</v>
+        <v>显示配置文件池</v>
       </c>
       <c r="C89" t="str">
-        <v>收合</v>
+        <v>顯示設定檔集區</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Load Profiles</v>
+        <v>Collapse</v>
       </c>
       <c r="B90" t="str">
-        <v>加载配置文件</v>
+        <v>收起</v>
       </c>
       <c r="C90" t="str">
-        <v>載入設定檔</v>
+        <v>收合</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Remove</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B91" t="str">
-        <v>移除</v>
+        <v>加载配置文件</v>
       </c>
       <c r="C91" t="str">
-        <v>移除</v>
+        <v>載入設定檔</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Remove</v>
       </c>
       <c r="B92" t="str">
-        <v>将 ICC 配置文件拖放到此处</v>
+        <v>移除</v>
       </c>
       <c r="C92" t="str">
-        <v>將 ICC 設定檔拖放到此處</v>
+        <v>移除</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B93" t="str">
-        <v>或拖入图像 (TIFF/PNG/JPEG) 以提取其嵌入的配置文件 — 文件保留在您的设备上。</v>
+        <v>将 ICC 配置文件拖放到此处</v>
       </c>
       <c r="C93" t="str">
-        <v>或拖入影像 (TIFF/PNG/JPEG) 以擷取其內嵌設定檔 — 檔案會保留在您的裝置上。</v>
+        <v>將 ICC 設定檔拖放到此處</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>New from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B94" t="str">
-        <v>从 .cube 新建</v>
+        <v>或拖入图像 (TIFF/PNG/JPEG) 以提取其嵌入的配置文件 — 文件保留在您的设备上。</v>
       </c>
       <c r="C94" t="str">
-        <v>從 .cube 新建</v>
+        <v>或拖入影像 (TIFF/PNG/JPEG) 以擷取其內嵌設定檔 — 檔案會保留在您的裝置上。</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Sort by name</v>
+        <v>New from .cube</v>
       </c>
       <c r="B95" t="str">
-        <v>按名称排序</v>
+        <v>从 .cube 新建</v>
       </c>
       <c r="C95" t="str">
-        <v>依名稱排序</v>
+        <v>從 .cube 新建</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B96" t="str">
-        <v>A–Z</v>
+        <v>按名称排序</v>
       </c>
       <c r="C96" t="str">
-        <v>A–Z</v>
+        <v>依名稱排序</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B97" t="str">
-        <v>从 .cube 新建配置文件</v>
+        <v>A–Z</v>
       </c>
       <c r="C97" t="str">
-        <v>從 .cube 新建設定檔</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B98" t="str">
-        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并下载。</v>
+        <v>从 .cube 新建配置文件</v>
       </c>
       <c r="C98" t="str">
-        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並下載。</v>
+        <v>從 .cube 新建設定檔</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B99" t="str">
-        <v>选择 .cube 文件</v>
+        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并下载。</v>
       </c>
       <c r="C99" t="str">
-        <v>選擇 .cube 檔案</v>
+        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並下載。</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B100" t="str">
+        <v>选择 .cube 文件</v>
+      </c>
+      <c r="C100" t="str">
+        <v>選擇 .cube 檔案</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B101" t="str">
         <v>或拖放到此处，或在下方粘贴</v>
       </c>
-      <c r="C100" t="str">
+      <c r="C101" t="str">
         <v>或拖放到此處，或在下方貼上</v>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str" xml:space="preserve">
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B101" t="str" xml:space="preserve">
+      <c r="B102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="C101" t="str" xml:space="preserve">
+      <c r="C102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B102" t="str">
-        <v>取消</v>
-      </c>
-      <c r="C102" t="str">
-        <v>取消</v>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B103" t="str">
-        <v>创建 DeviceLink</v>
+        <v>取消</v>
       </c>
       <c r="C103" t="str">
-        <v>建立 DeviceLink</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B104" t="str">
-        <v>正在创建…</v>
+        <v>创建 DeviceLink</v>
       </c>
       <c r="C104" t="str">
-        <v>正在建立…</v>
+        <v>建立 DeviceLink</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B105" t="str">
-        <v>无法读取该文件。</v>
+        <v>正在创建…</v>
       </c>
       <c r="C105" t="str">
-        <v>無法讀取該檔案。</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B106" t="str">
-        <v>配置文件</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C106" t="str">
-        <v>設定檔</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B107" t="str">
-        <v>比较</v>
+        <v>配置文件</v>
       </c>
       <c r="C107" t="str">
-        <v>比較</v>
+        <v>設定檔</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B108" t="str">
-        <v>链接</v>
+        <v>比较</v>
       </c>
       <c r="C108" t="str">
-        <v>連結</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B109" t="str">
-        <v>光谱</v>
+        <v>链接</v>
       </c>
       <c r="C109" t="str">
-        <v>光譜</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B110" t="str">
-        <v>将配置文件从池中拖到此选项卡</v>
+        <v>光谱</v>
       </c>
       <c r="C110" t="str">
-        <v>將設定檔從集區拖到此分頁</v>
+        <v>光譜</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B111" t="str">
-        <v>移除</v>
+        <v>将配置文件从池中拖到此选项卡</v>
       </c>
       <c r="C111" t="str">
-        <v>移除</v>
+        <v>將設定檔從集區拖到此分頁</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B112" t="str">
-        <v>未选择配置文件</v>
+        <v>移除</v>
       </c>
       <c r="C112" t="str">
-        <v>未選擇設定檔</v>
+        <v>移除</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B113" t="str">
-        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
+        <v>未选择配置文件</v>
       </c>
       <c r="C113" t="str">
-        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
+        <v>未選擇設定檔</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B114" t="str">
-        <v>暂无可比较的内容</v>
+        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
       </c>
       <c r="C114" t="str">
-        <v>尚無可比較的內容</v>
+        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B115" t="str">
-        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
+        <v>暂无可比较的内容</v>
       </c>
       <c r="C115" t="str">
-        <v>將一個或多個設定檔拖到「比較」分頁。</v>
+        <v>尚無可比較的內容</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B116" t="str">
-        <v>色域比较</v>
+        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
       </c>
       <c r="C116" t="str">
-        <v>色域比較</v>
+        <v>將一個或多個設定檔拖到「比較」分頁。</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B117" t="str">
-        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
+        <v>色域比较</v>
       </c>
       <c r="C117" t="str">
-        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B118" t="str">
-        <v>渲染意图</v>
+        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
       </c>
       <c r="C118" t="str">
-        <v>轉換意圖</v>
+        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B119" t="str">
-        <v>外壳</v>
+        <v>渲染意图</v>
       </c>
       <c r="C119" t="str">
-        <v>外殼</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B120" t="str">
-        <v>线框</v>
+        <v>外壳</v>
       </c>
       <c r="C120" t="str">
-        <v>線框</v>
+        <v>外殼</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B121" t="str">
-        <v>轴编号</v>
+        <v>线框</v>
       </c>
       <c r="C121" t="str">
-        <v>軸編號</v>
+        <v>線框</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B122" t="str">
-        <v>不透明度</v>
+        <v>轴编号</v>
       </c>
       <c r="C122" t="str">
-        <v>不透明度</v>
+        <v>軸編號</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>颜色</v>
+        <v>不透明度</v>
       </c>
       <c r="C123" t="str">
-        <v>色彩</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>纯色</v>
+        <v>颜色</v>
       </c>
       <c r="C124" t="str">
-        <v>純色</v>
+        <v>色彩</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>按数值</v>
+        <v>纯色</v>
       </c>
       <c r="C125" t="str">
-        <v>依數值</v>
+        <v>純色</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>按色相</v>
+        <v>按数值</v>
       </c>
       <c r="C126" t="str">
-        <v>依色相</v>
+        <v>依數值</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>旋转</v>
+        <v>按色相</v>
       </c>
       <c r="C127" t="str">
-        <v>旋轉</v>
+        <v>依色相</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>转盘</v>
+        <v>旋转</v>
       </c>
       <c r="C128" t="str">
-        <v>轉盤</v>
+        <v>旋轉</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>轨道</v>
+        <v>转盘</v>
       </c>
       <c r="C129" t="str">
-        <v>軌道</v>
+        <v>轉盤</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>拖动速度</v>
+        <v>轨道</v>
       </c>
       <c r="C130" t="str">
-        <v>拖曳速度</v>
+        <v>軌道</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>翻滚</v>
+        <v>拖动速度</v>
       </c>
       <c r="C131" t="str">
-        <v>翻滾</v>
+        <v>拖曳速度</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>翻滚速度</v>
+        <v>翻滚</v>
       </c>
       <c r="C132" t="str">
-        <v>翻滾速度</v>
+        <v>翻滾</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>正在构建色域…</v>
+        <v>翻滚速度</v>
       </c>
       <c r="C133" t="str">
-        <v>正在建構色域…</v>
+        <v>翻滾速度</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>无色域</v>
+        <v>正在构建色域…</v>
       </c>
       <c r="C134" t="str">
-        <v>無色域</v>
+        <v>正在建構色域…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>显示/隐藏</v>
+        <v>无色域</v>
       </c>
       <c r="C135" t="str">
-        <v>顯示/隱藏</v>
+        <v>無色域</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>3D 色域外壳</v>
+        <v>显示/隐藏</v>
       </c>
       <c r="C136" t="str">
-        <v>3D 色域外殼</v>
+        <v>顯示/隱藏</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>2D 色域切片</v>
+        <v>3D 色域外壳</v>
       </c>
       <c r="C137" t="str">
-        <v>2D 色域切片</v>
+        <v>3D 色域外殼</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>平面</v>
+        <v>2D 色域切片</v>
       </c>
       <c r="C138" t="str">
-        <v>平面</v>
+        <v>2D 色域切片</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>L*</v>
+        <v>平面</v>
       </c>
       <c r="C139" t="str">
-        <v>L*</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="C140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="C141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
+        <v>b*</v>
       </c>
       <c r="C142" t="str">
-        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>链接</v>
+        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
       </c>
       <c r="C143" t="str">
-        <v>連結</v>
+        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
+        <v>链接</v>
       </c>
       <c r="C144" t="str">
-        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
+        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
       </c>
       <c r="C145" t="str">
-        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
+        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>V4 显示器生成器</v>
+        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
       </c>
       <c r="C146" t="str">
-        <v>V4 顯示器產生器</v>
+        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B147" t="str">
-        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
+        <v>V4 显示器生成器</v>
       </c>
       <c r="C147" t="str">
-        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
+        <v>V4 顯示器產生器</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>V5 RGB 显示器</v>
+        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
       </c>
       <c r="C148" t="str">
-        <v>V5 RGB 顯示器</v>
+        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>拖入显示器配置文件</v>
+        <v>V5 RGB 显示器</v>
       </c>
       <c r="C149" t="str">
-        <v>拖入顯示器設定檔</v>
+        <v>V5 RGB 顯示器</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>V5 观察者 (PCC)</v>
+        <v>拖入显示器配置文件</v>
       </c>
       <c r="C150" t="str">
-        <v>V5 觀察者 (PCC)</v>
+        <v>拖入顯示器設定檔</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>拖入观察者配置文件</v>
+        <v>V5 观察者 (PCC)</v>
       </c>
       <c r="C151" t="str">
-        <v>拖入觀察者設定檔</v>
+        <v>V5 觀察者 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
+        <v>拖入观察者配置文件</v>
       </c>
       <c r="C152" t="str">
-        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
+        <v>拖入觀察者設定檔</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>创建 V4 显示器配置文件</v>
+        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
       </c>
       <c r="C153" t="str">
-        <v>建立 V4 顯示器設定檔</v>
+        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>配置文件名称</v>
+        <v>创建 V4 显示器配置文件</v>
       </c>
       <c r="C154" t="str">
-        <v>設定檔名稱</v>
+        <v>建立 V4 顯示器設定檔</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>创建</v>
+        <v>配置文件名称</v>
       </c>
       <c r="C155" t="str">
-        <v>建立</v>
+        <v>設定檔名稱</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>正在创建…</v>
+        <v>创建</v>
       </c>
       <c r="C156" t="str">
-        <v>正在建立…</v>
+        <v>建立</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
+        <v>正在创建…</v>
       </c>
       <c r="C157" t="str">
-        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>链接流水线</v>
+        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
       </c>
       <c r="C158" t="str">
-        <v>連結管線</v>
+        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B159" t="str">
-        <v>构建一条配置文件链，然后生成 DeviceLink、转换图像，或通过它转换色彩数据集。</v>
+        <v>链接流水线</v>
       </c>
       <c r="C159" t="str">
-        <v>建立一條描述檔鏈，然後產生 DeviceLink、轉換影像，或透過它轉換色彩資料集。</v>
+        <v>連結管線</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B160" t="str">
-        <v>完成</v>
+        <v>构建一条配置文件链，然后生成 DeviceLink、转换图像，或通过它转换色彩数据集。</v>
       </c>
       <c r="C160" t="str">
-        <v>完成</v>
+        <v>建立一條描述檔鏈，然後產生 DeviceLink、轉換影像，或透過它轉換色彩資料集。</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B161" t="str">
-        <v>拖放图像以进行转换（TIFF/PNG/JPEG）</v>
+        <v>完成</v>
       </c>
       <c r="C161" t="str">
-        <v>拖放影像以進行轉換（TIFF/PNG/JPEG）</v>
+        <v>完成</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B162" t="str">
-        <v>正在检查图像…</v>
+        <v>拖放图像以进行转换（TIFF/PNG/JPEG）</v>
       </c>
       <c r="C162" t="str">
-        <v>正在檢查影像…</v>
+        <v>拖放影像以進行轉換（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B163" t="str">
-        <v>不受支持的图像格式（TIFF、PNG 或 JPEG）。</v>
+        <v>正在检查图像…</v>
       </c>
       <c r="C163" t="str">
-        <v>不受支援的影像格式（TIFF、PNG 或 JPEG）。</v>
+        <v>正在檢查影像…</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B164" t="str">
-        <v>图像过大（{mp} MP；上限 {max} MP）。</v>
+        <v>不受支持的图像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C164" t="str">
-        <v>影像過大（{mp} MP；上限 {max} MP）。</v>
+        <v>不受支援的影像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B165" t="str">
-        <v>转换图像</v>
+        <v>图像过大（{mp} MP；上限 {max} MP）。</v>
       </c>
       <c r="C165" t="str">
-        <v>轉換影像</v>
+        <v>影像過大（{mp} MP；上限 {max} MP）。</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B166" t="str">
-        <v>正在转换…</v>
+        <v>转换图像</v>
       </c>
       <c r="C166" t="str">
-        <v>正在轉換…</v>
+        <v>轉換影像</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B167" t="str">
-        <v>拖放配置文件以开始链条</v>
+        <v>正在转换…</v>
       </c>
       <c r="C167" t="str">
-        <v>拖放描述檔以開始鏈條</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B168" t="str">
-        <v>已移除</v>
+        <v>拖放配置文件以开始链条</v>
       </c>
       <c r="C168" t="str">
-        <v>已移除</v>
+        <v>拖放描述檔以開始鏈條</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B169" t="str">
-        <v>前移</v>
+        <v>已移除</v>
       </c>
       <c r="C169" t="str">
-        <v>前移</v>
+        <v>已移除</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B170" t="str">
-        <v>后移</v>
+        <v>前移</v>
       </c>
       <c r="C170" t="str">
-        <v>後移</v>
+        <v>前移</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B171" t="str">
-        <v>上移</v>
+        <v>后移</v>
       </c>
       <c r="C171" t="str">
-        <v>上移</v>
+        <v>後移</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B172" t="str">
-        <v>下移</v>
+        <v>上移</v>
       </c>
       <c r="C172" t="str">
-        <v>下移</v>
+        <v>上移</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B173" t="str">
-        <v>渲染意图（全部）</v>
+        <v>下移</v>
       </c>
       <c r="C173" t="str">
-        <v>演算意圖（全部）</v>
+        <v>下移</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B174" t="str">
-        <v>此转换的渲染意图</v>
+        <v>渲染意图（全部）</v>
       </c>
       <c r="C174" t="str">
-        <v>此轉換的演算意圖</v>
+        <v>演算意圖（全部）</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B175" t="str">
-        <v>各转换使用了不同的渲染意图</v>
+        <v>此转换的渲染意图</v>
       </c>
       <c r="C175" t="str">
-        <v>各轉換使用了不同的演算意圖</v>
+        <v>此轉換的演算意圖</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B176" t="str">
-        <v>翻转链条方向（反转首个转换，并影响整条链）</v>
+        <v>各转换使用了不同的渲染意图</v>
       </c>
       <c r="C176" t="str">
-        <v>翻轉鏈條方向（反轉首個轉換，並影響整條鏈）</v>
+        <v>各轉換使用了不同的演算意圖</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B177" t="str">
-        <v>链条中的某个配置文件已从池中移除——请将其移除以继续。</v>
+        <v>翻转链条方向（反转首个转换，并影响整条链）</v>
       </c>
       <c r="C177" t="str">
-        <v>鏈條中的某個描述檔已從集區中移除——請將其移除以繼續。</v>
+        <v>翻轉鏈條方向（反轉首個轉換，並影響整條鏈）</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B178" t="str">
-        <v>链条</v>
+        <v>链条中的某个配置文件已从池中移除——请将其移除以继续。</v>
       </c>
       <c r="C178" t="str">
-        <v>鏈條</v>
+        <v>鏈條中的某個描述檔已從集區中移除——請將其移除以繼續。</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B179" t="str">
-        <v>无法分析该链条。</v>
+        <v>链条</v>
       </c>
       <c r="C179" t="str">
-        <v>無法分析該鏈條。</v>
+        <v>鏈條</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B180" t="str">
-        <v>正在检查链条…</v>
+        <v>无法分析该链条。</v>
       </c>
       <c r="C180" t="str">
-        <v>正在檢查鏈條…</v>
+        <v>無法分析該鏈條。</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B181" t="str">
-        <v>链条未能衔接（{detail}）。</v>
+        <v>正在检查链条…</v>
       </c>
       <c r="C181" t="str">
-        <v>鏈條未能銜接（{detail}）。</v>
+        <v>正在檢查鏈條…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>配置文件 {n} 未能与上一阶段衔接（{detail}）。</v>
+        <v>链条未能衔接（{detail}）。</v>
       </c>
       <c r="C182" t="str">
-        <v>描述檔 {n} 未能與上一階段銜接（{detail}）。</v>
+        <v>鏈條未能銜接（{detail}）。</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B183" t="str">
-        <v>请先修复链条，再处理图像</v>
+        <v>配置文件 {n} 未能与上一阶段衔接（{detail}）。</v>
       </c>
       <c r="C183" t="str">
-        <v>請先修正鏈條，再處理影像</v>
+        <v>描述檔 {n} 未能與上一階段銜接（{detail}）。</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B184" t="str">
-        <v>清除</v>
+        <v>请先修复链条，再处理图像</v>
       </c>
       <c r="C184" t="str">
-        <v>清除</v>
+        <v>請先修正鏈條，再處理影像</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B185" t="str">
-        <v>生成 DeviceLink</v>
+        <v>清除</v>
       </c>
       <c r="C185" t="str">
-        <v>產生 DeviceLink</v>
+        <v>清除</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B186" t="str">
-        <v>DeviceLink 名称</v>
+        <v>生成 DeviceLink</v>
       </c>
       <c r="C186" t="str">
-        <v>DeviceLink 名稱</v>
+        <v>產生 DeviceLink</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B187" t="str">
-        <v>正在生成…</v>
+        <v>DeviceLink 名称</v>
       </c>
       <c r="C187" t="str">
-        <v>正在產生…</v>
+        <v>DeviceLink 名稱</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B188" t="str">
-        <v>已创建“{name}”——已添加到池和此标签页。</v>
+        <v>正在生成…</v>
       </c>
       <c r="C188" t="str">
-        <v>已建立「{name}」——已加入集區與此分頁。</v>
+        <v>正在產生…</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B189" t="str">
-        <v>拖放 {src} 图像以转换为 {dst}——结果将下载，不会被存储。</v>
+        <v>已创建“{name}”——已添加到池和此标签页。</v>
       </c>
       <c r="C189" t="str">
-        <v>拖放 {src} 影像以轉換為 {dst}——結果將下載，不會被儲存。</v>
+        <v>已建立「{name}」——已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B190" t="str">
-        <v>构建链条以处理图像</v>
+        <v>拖放 {src} 图像以转换为 {dst}——结果将下载，不会被存储。</v>
       </c>
       <c r="C190" t="str">
-        <v>建立鏈條以處理影像</v>
+        <v>拖放 {src} 影像以轉換為 {dst}——結果將下載，不會被儲存。</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B191" t="str">
-        <v>此链条的首尾并非图像色彩空间</v>
+        <v>构建链条以处理图像</v>
       </c>
       <c r="C191" t="str">
-        <v>此鏈條的首尾並非影像色彩空間</v>
+        <v>建立鏈條以處理影像</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B192" t="str">
-        <v>已保存转换后的图像。</v>
+        <v>此链条的首尾并非图像色彩空间</v>
       </c>
       <c r="C192" t="str">
-        <v>已儲存轉換後的影像。</v>
+        <v>此鏈條的首尾並非影像色彩空間</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B193" t="str">
-        <v>拖放色彩数据集（CGATS/CSV/CxF/JSON）</v>
+        <v>已保存转换后的图像。</v>
       </c>
       <c r="C193" t="str">
-        <v>拖放色彩資料集（CGATS/CSV/CxF/JSON）</v>
+        <v>已儲存轉換後的影像。</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B194" t="str">
-        <v>无法读取该文件。</v>
+        <v>拖放色彩数据集（CGATS/CSV/CxF/JSON）</v>
       </c>
       <c r="C194" t="str">
-        <v>無法讀取該檔案。</v>
+        <v>拖放色彩資料集（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B195" t="str">
-        <v>数据文件过大。</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C195" t="str">
-        <v>資料檔案過大。</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B196" t="str">
-        <v>转换数据</v>
+        <v>数据文件过大。</v>
       </c>
       <c r="C196" t="str">
-        <v>轉換資料</v>
+        <v>資料檔案過大。</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B197" t="str">
-        <v>正在转换…</v>
+        <v>转换数据</v>
       </c>
       <c r="C197" t="str">
-        <v>正在轉換…</v>
+        <v>轉換資料</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B198" t="str">
-        <v>偏好</v>
+        <v>正在转换…</v>
       </c>
       <c r="C198" t="str">
-        <v>偏好</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B199" t="str">
-        <v>观察者</v>
+        <v>偏好</v>
       </c>
       <c r="C199" t="str">
-        <v>觀察者</v>
+        <v>偏好</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B200" t="str">
-        <v>光源</v>
+        <v>观察者</v>
       </c>
       <c r="C200" t="str">
-        <v>光源</v>
+        <v>觀察者</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B201" t="str">
-        <v>条件</v>
+        <v>光源</v>
       </c>
       <c r="C201" t="str">
-        <v>條件</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B202" t="str">
-        <v>过滤 {n} 个重复项</v>
+        <v>条件</v>
       </c>
       <c r="C202" t="str">
-        <v>篩選 {n} 個重複項</v>
+        <v>條件</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B203" t="str">
-        <v>中位数</v>
+        <v>过滤 {n} 个重复项</v>
       </c>
       <c r="C203" t="str">
-        <v>中位數</v>
+        <v>篩選 {n} 個重複項</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B204" t="str">
-        <v>平均值</v>
+        <v>中位数</v>
       </c>
       <c r="C204" t="str">
-        <v>平均值</v>
+        <v>中位數</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B205" t="str">
-        <v>色块</v>
+        <v>平均值</v>
       </c>
       <c r="C205" t="str">
-        <v>色塊</v>
+        <v>平均值</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B206" t="str">
-        <v>{n} 个重复项</v>
+        <v>色块</v>
       </c>
       <c r="C206" t="str">
-        <v>{n} 個重複項</v>
+        <v>色塊</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B207" t="str">
-        <v>转换结果</v>
+        <v>{n} 个重复项</v>
       </c>
       <c r="C207" t="str">
-        <v>轉換結果</v>
+        <v>{n} 個重複項</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B208" t="str">
-        <v>{src} → {dst} · {n} 个色块</v>
+        <v>转换结果</v>
       </c>
       <c r="C208" t="str">
-        <v>{src} → {dst} · {n} 個色塊</v>
+        <v>轉換結果</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B209" t="str">
-        <v>显示前 {shown} 项，共 {total} 项——保存将写入全部数据。</v>
+        <v>{src} → {dst} · {n} 个色块</v>
       </c>
       <c r="C209" t="str">
-        <v>顯示前 {shown} 項，共 {total} 項——儲存將寫入全部資料。</v>
+        <v>{src} → {dst} · {n} 個色塊</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B210" t="str">
-        <v>另存为</v>
+        <v>显示前 {shown} 项，共 {total} 项——保存将写入全部数据。</v>
       </c>
       <c r="C210" t="str">
-        <v>另存新檔</v>
+        <v>顯示前 {shown} 項，共 {total} 項——儲存將寫入全部資料。</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B211" t="str">
-        <v>保存</v>
+        <v>另存为</v>
       </c>
       <c r="C211" t="str">
-        <v>儲存</v>
+        <v>另存新檔</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B212" t="str">
-        <v>反向转换</v>
+        <v>保存</v>
       </c>
       <c r="C212" t="str">
-        <v>反向轉換</v>
+        <v>儲存</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B213" t="str">
-        <v>正在反向计算…</v>
+        <v>反向转换</v>
       </c>
       <c r="C213" t="str">
-        <v>正在反向計算…</v>
+        <v>反向轉換</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B214" t="str">
-        <v>反转</v>
+        <v>正在反向计算…</v>
       </c>
       <c r="C214" t="str">
-        <v>反轉</v>
+        <v>正在反向計算…</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B215" t="str">
-        <v>最后阶段</v>
+        <v>反转</v>
       </c>
       <c r="C215" t="str">
-        <v>最後階段</v>
+        <v>反轉</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B216" t="str">
-        <v>第一阶段</v>
+        <v>最后阶段</v>
       </c>
       <c r="C216" t="str">
-        <v>第一階段</v>
+        <v>最後階段</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B217" t="str">
-        <v>输入数据为 {in} → 搜索 {out}</v>
+        <v>第一阶段</v>
       </c>
       <c r="C217" t="str">
-        <v>輸入資料為 {in} → 搜尋 {out}</v>
+        <v>第一階段</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B218" t="str">
-        <v>反转需要 2–3 个配置文件组成的链条</v>
+        <v>输入数据为 {in} → 搜索 {out}</v>
       </c>
       <c r="C218" t="str">
-        <v>反轉需要 2–3 個描述檔組成的鏈條</v>
+        <v>輸入資料為 {in} → 搜尋 {out}</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B219" t="str">
-        <v>数据集必须为 {in}；反向搜索将生成 {out}，并附带每个色块的可逆性代价。</v>
+        <v>反转需要 2–3 个配置文件组成的链条</v>
       </c>
       <c r="C219" t="str">
-        <v>資料集必須為 {in}；反向搜尋將產生 {out}，並附帶每個色塊的可逆性代價。</v>
+        <v>反轉需要 2–3 個描述檔組成的鏈條</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B220" t="str">
-        <v>ΔE 代价</v>
+        <v>数据集必须为 {in}；反向搜索将生成 {out}，并附带每个色块的可逆性代价。</v>
       </c>
       <c r="C220" t="str">
-        <v>ΔE 代價</v>
+        <v>資料集必須為 {in}；反向搜尋將產生 {out}，並附帶每個色塊的可逆性代價。</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B221" t="str">
-        <v>此图像嵌入了 ICC 配置文件。</v>
+        <v>ΔE 代价</v>
       </c>
       <c r="C221" t="str">
-        <v>此影像內嵌了 ICC 描述檔。</v>
+        <v>ΔE 代價</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>提取并添加到链条</v>
+        <v>此图像嵌入了 ICC 配置文件。</v>
       </c>
       <c r="C222" t="str">
-        <v>擷取並加入鏈條</v>
+        <v>此影像內嵌了 ICC 描述檔。</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B223" t="str">
-        <v>正在提取…</v>
+        <v>提取并添加到链条</v>
       </c>
       <c r="C223" t="str">
-        <v>正在擷取…</v>
+        <v>擷取並加入鏈條</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B224" t="str">
-        <v>忽略</v>
+        <v>正在提取…</v>
       </c>
       <c r="C224" t="str">
-        <v>忽略</v>
+        <v>正在擷取…</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B225" t="str">
-        <v>已提取嵌入的配置文件——已添加到池中并置于链条首位。</v>
+        <v>忽略</v>
       </c>
       <c r="C225" t="str">
-        <v>已擷取內嵌的描述檔——已加入集區並置於鏈條首位。</v>
+        <v>忽略</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B226" t="str">
-        <v>图像输出选项</v>
+        <v>已提取嵌入的配置文件——已添加到池中并置于链条首位。</v>
       </c>
       <c r="C226" t="str">
-        <v>影像輸出選項</v>
+        <v>已擷取內嵌的描述檔——已加入集區並置於鏈條首位。</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B227" t="str">
-        <v>编码</v>
+        <v>图像输出选项</v>
       </c>
       <c r="C227" t="str">
-        <v>編碼</v>
+        <v>影像輸出選項</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B228" t="str">
-        <v>与源相同</v>
+        <v>编码</v>
       </c>
       <c r="C228" t="str">
-        <v>與來源相同</v>
+        <v>編碼</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B229" t="str">
-        <v>8 位</v>
+        <v>与源相同</v>
       </c>
       <c r="C229" t="str">
-        <v>8 位元</v>
+        <v>與來源相同</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>16 位</v>
+        <v>8 位</v>
       </c>
       <c r="C230" t="str">
-        <v>16 位元</v>
+        <v>8 位元</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B231" t="str">
-        <v>浮点（32 位）</v>
+        <v>16 位</v>
       </c>
       <c r="C231" t="str">
-        <v>浮點（32 位元）</v>
+        <v>16 位元</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B232" t="str">
-        <v>压缩</v>
+        <v>浮点（32 位）</v>
       </c>
       <c r="C232" t="str">
-        <v>壓縮</v>
+        <v>浮點（32 位元）</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B233" t="str">
-        <v>无</v>
+        <v>压缩</v>
       </c>
       <c r="C233" t="str">
-        <v>無</v>
+        <v>壓縮</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B234" t="str">
-        <v>平面格式</v>
+        <v>无</v>
       </c>
       <c r="C234" t="str">
-        <v>平面格式</v>
+        <v>無</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B235" t="str">
-        <v>交错</v>
+        <v>平面格式</v>
       </c>
       <c r="C235" t="str">
-        <v>交錯</v>
+        <v>平面格式</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B236" t="str">
-        <v>分离</v>
+        <v>交错</v>
       </c>
       <c r="C236" t="str">
-        <v>分離</v>
+        <v>交錯</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B237" t="str">
-        <v>CMM 插值</v>
+        <v>分离</v>
       </c>
       <c r="C237" t="str">
-        <v>CMM 內插</v>
+        <v>分離</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B238" t="str">
-        <v>四面体</v>
+        <v>CMM 插值</v>
       </c>
       <c r="C238" t="str">
-        <v>四面體</v>
+        <v>CMM 內插</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B239" t="str">
-        <v>线性</v>
+        <v>四面体</v>
       </c>
       <c r="C239" t="str">
-        <v>線性</v>
+        <v>四面體</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B240" t="str">
-        <v>嵌入 ICC</v>
+        <v>线性</v>
       </c>
       <c r="C240" t="str">
-        <v>內嵌 ICC</v>
+        <v>線性</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B241" t="str">
-        <v>编码、压缩和平面格式会影响保存的 TIFF。除非设置了仅限 TIFF 的选项（浮点、LZW/ZIP、分离），否则 RGB/Gray 输出仍为 PNG。</v>
+        <v>嵌入 ICC</v>
       </c>
       <c r="C241" t="str">
-        <v>編碼、壓縮和平面格式會影響儲存的 TIFF。除非設定了僅限 TIFF 的選項（浮點、LZW/ZIP、分離），否則 RGB/Gray 輸出仍為 PNG。</v>
+        <v>內嵌 ICC</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B242" t="str">
-        <v>组装光谱 TIFF</v>
+        <v>编码、压缩和平面格式会影响保存的 TIFF。除非设置了仅限 TIFF 的选项（浮点、LZW/ZIP、分离），否则 RGB/Gray 输出仍为 PNG。</v>
       </c>
       <c r="C242" t="str">
-        <v>組裝光譜 TIFF</v>
+        <v>編碼、壓縮和平面格式會影響儲存的 TIFF。除非設定了僅限 TIFF 的選項（浮點、LZW/ZIP、分離），否則 RGB/Gray 輸出仍為 PNG。</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B243" t="str">
-        <v>按通道顺序拖放单通道光谱图像，然后将其组装为一个多通道 TIFF。</v>
+        <v>组装光谱 TIFF</v>
       </c>
       <c r="C243" t="str">
-        <v>依通道順序拖放單通道光譜影像，然後將其組裝為一個多通道 TIFF。</v>
+        <v>組裝光譜 TIFF</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B244" t="str">
-        <v>将光谱图像拖放到此处（或点击选择）</v>
+        <v>按通道顺序拖放单通道光谱图像，然后将其组装为一个多通道 TIFF。</v>
       </c>
       <c r="C244" t="str">
-        <v>將光譜影像拖放到此處（或點擊選擇）</v>
+        <v>依通道順序拖放單通道光譜影像，然後將其組裝為一個多通道 TIFF。</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B245" t="str">
-        <v>通道</v>
+        <v>将光谱图像拖放到此处（或点击选择）</v>
       </c>
       <c r="C245" t="str">
-        <v>通道</v>
+        <v>將光譜影像拖放到此處（或點擊選擇）</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B246" t="str">
-        <v>组装并保存</v>
+        <v>通道</v>
       </c>
       <c r="C246" t="str">
-        <v>組裝並儲存</v>
+        <v>通道</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B247" t="str">
-        <v>正在组装…</v>
+        <v>组装并保存</v>
       </c>
       <c r="C247" t="str">
-        <v>正在組裝…</v>
+        <v>組裝並儲存</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B248" t="str">
-        <v>已组装 {n} 个通道。</v>
+        <v>正在组装…</v>
       </c>
       <c r="C248" t="str">
-        <v>已組裝 {n} 個通道。</v>
+        <v>正在組裝…</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B249" t="str">
-        <v>这些文件似乎都不是图像（TIFF、PNG 或 JPEG）。</v>
+        <v>已组装 {n} 个通道。</v>
       </c>
       <c r="C249" t="str">
-        <v>這些檔案似乎都不是影像（TIFF、PNG 或 JPEG）。</v>
+        <v>已組裝 {n} 個通道。</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B250" t="str">
-        <v>取消</v>
+        <v>这些文件似乎都不是图像（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C250" t="str">
-        <v>取消</v>
+        <v>這些檔案似乎都不是影像（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B251" t="str">
-        <v>有 {n} 个文件未加载</v>
+        <v>取消</v>
       </c>
       <c r="C251" t="str">
-        <v>有 {n} 個檔案未載入</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B252" t="str">
-        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
+        <v>有 {n} 个文件未加载</v>
       </c>
       <c r="C252" t="str">
-        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
+        <v>有 {n} 個檔案未載入</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B253" t="str">
-        <v>确定</v>
+        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
       </c>
       <c r="C253" t="str">
-        <v>確定</v>
+        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B254" t="str">
-        <v>将 ICC 配置文件拖到此处</v>
+        <v>确定</v>
       </c>
       <c r="C254" t="str">
-        <v>將 ICC 設定檔拖到此處</v>
+        <v>確定</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B255" t="str">
-        <v>或</v>
+        <v>将 ICC 配置文件拖到此处</v>
       </c>
       <c r="C255" t="str">
-        <v>或</v>
+        <v>將 ICC 設定檔拖到此處</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B256" t="str">
-        <v>选择文件</v>
+        <v>或</v>
       </c>
       <c r="C256" t="str">
-        <v>選擇檔案</v>
+        <v>或</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B257" t="str">
-        <v>.icc 和 .icm 文件</v>
+        <v>选择文件</v>
       </c>
       <c r="C257" t="str">
-        <v>.icc 與 .icm 檔案</v>
+        <v>選擇檔案</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B258" t="str">
-        <v>标头</v>
+        <v>.icc 和 .icm 文件</v>
       </c>
       <c r="C258" t="str">
-        <v>標頭</v>
+        <v>.icc 與 .icm 檔案</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B259" t="str">
-        <v>标签</v>
+        <v>标头</v>
       </c>
       <c r="C259" t="str">
-        <v>標籤</v>
+        <v>標頭</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B260" t="str">
-        <v>验证</v>
+        <v>标签</v>
       </c>
       <c r="C260" t="str">
-        <v>驗證</v>
+        <v>標籤</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B261" t="str">
-        <v>分析</v>
+        <v>验证</v>
       </c>
       <c r="C261" t="str">
-        <v>分析</v>
+        <v>驗證</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B262" t="str">
-        <v>中性轴墨量</v>
+        <v>分析</v>
       </c>
       <c r="C262" t="str">
-        <v>中性軸墨量</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B263" t="str">
-        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
+        <v>中性轴墨量</v>
       </c>
       <c r="C263" t="str">
-        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
+        <v>中性軸墨量</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B264" t="str">
-        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
+        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
       </c>
       <c r="C264" t="str">
-        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
+        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B265" t="str">
-        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
+        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C265" t="str">
-        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
+        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B266" t="str">
-        <v>渲染意图</v>
+        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
       </c>
       <c r="C266" t="str">
-        <v>轉換意圖</v>
+        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B267" t="str">
-        <v>% 墨量</v>
+        <v>渲染意图</v>
       </c>
       <c r="C267" t="str">
-        <v>% 墨量</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Perceptual</v>
+        <v>% ink</v>
       </c>
       <c r="B268" t="str">
-        <v>感知</v>
+        <v>% 墨量</v>
       </c>
       <c r="C268" t="str">
-        <v>感知</v>
+        <v>% 墨量</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B269" t="str">
-        <v>相对比色</v>
+        <v>感知</v>
       </c>
       <c r="C269" t="str">
-        <v>相對比色</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B270" t="str">
-        <v>饱和度</v>
+        <v>相对比色</v>
       </c>
       <c r="C270" t="str">
-        <v>飽和度</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B271" t="str">
-        <v>绝对比色</v>
+        <v>饱和度</v>
       </c>
       <c r="C271" t="str">
-        <v>絕對比色</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>特性文件统计</v>
+        <v>绝对比色</v>
       </c>
       <c r="C272" t="str">
-        <v>特性檔統計</v>
+        <v>絕對比色</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B273" t="str">
-        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
+        <v>特性文件统计</v>
       </c>
       <c r="C273" t="str">
-        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
+        <v>特性檔統計</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B274" t="str">
-        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
+        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
       </c>
       <c r="C274" t="str">
-        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
+        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B275" t="str">
-        <v>渲染意图</v>
+        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
       </c>
       <c r="C275" t="str">
-        <v>轉換意圖</v>
+        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B276" t="str">
-        <v>色域体积 (ΔE³)</v>
+        <v>渲染意图</v>
       </c>
       <c r="C276" t="str">
-        <v>色域體積 (ΔE³)</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B277" t="str">
-        <v>往返 ΔE</v>
+        <v>色域体积 (ΔE³)</v>
       </c>
       <c r="C277" t="str">
-        <v>往返 ΔE</v>
+        <v>色域體積 (ΔE³)</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B278" t="str">
-        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C278" t="str">
-        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B279" t="str">
-        <v>均值</v>
+        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
       </c>
       <c r="C279" t="str">
-        <v>平均</v>
+        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B280" t="str">
-        <v>P90</v>
+        <v>均值</v>
       </c>
       <c r="C280" t="str">
-        <v>P90</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B281" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
       <c r="C281" t="str">
-        <v>最大</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B282" t="str">
-        <v>正在分析…</v>
+        <v>最大</v>
       </c>
       <c r="C282" t="str">
-        <v>正在分析…</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B283" t="str">
-        <v>分析</v>
+        <v>正在分析…</v>
       </c>
       <c r="C283" t="str">
-        <v>分析</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B284" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>分析</v>
       </c>
       <c r="C284" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B285" t="str">
-        <v>绘图</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C285" t="str">
-        <v>繪圖</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B286" t="str">
-        <v>原始输出</v>
+        <v>绘图</v>
       </c>
       <c r="C286" t="str">
-        <v>原始輸出</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B287" t="str">
-        <v>XML</v>
+        <v>原始输出</v>
       </c>
       <c r="C287" t="str">
-        <v>XML</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="C288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B289" t="str">
-        <v>曲线</v>
+        <v>JSON</v>
       </c>
       <c r="C289" t="str">
-        <v>曲線</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B290" t="str">
-        <v>输入曲线</v>
+        <v>曲线</v>
       </c>
       <c r="C290" t="str">
-        <v>輸入曲線</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B291" t="str">
-        <v>输出曲线</v>
+        <v>输入曲线</v>
       </c>
       <c r="C291" t="str">
-        <v>輸出曲線</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B292" t="str">
-        <v>CLUT 图像</v>
+        <v>输出曲线</v>
       </c>
       <c r="C292" t="str">
-        <v>CLUT 影像</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B293" t="str">
-        <v>色域图像</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C293" t="str">
-        <v>色域影像</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B294" t="str">
-        <v>色度</v>
+        <v>色域图像</v>
       </c>
       <c r="C294" t="str">
-        <v>色度</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B295" t="str">
-        <v>散点图</v>
+        <v>色度</v>
       </c>
       <c r="C295" t="str">
-        <v>散佈圖</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B296" t="str">
-        <v>色调响应曲线</v>
+        <v>散点图</v>
       </c>
       <c r="C296" t="str">
-        <v>色調響應曲線</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B297" t="str">
-        <v>曲线表</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C297" t="str">
-        <v>曲線表</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B298" t="str">
-        <v>表格</v>
+        <v>曲线表</v>
       </c>
       <c r="C298" t="str">
-        <v>表格</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B299" t="str">
-        <v>数据</v>
+        <v>表格</v>
       </c>
       <c r="C299" t="str">
-        <v>資料</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B300" t="str">
-        <v>求值</v>
+        <v>数据</v>
       </c>
       <c r="C300" t="str">
-        <v>求值</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B301" t="str">
-        <v>加载中…</v>
+        <v>求值</v>
       </c>
       <c r="C301" t="str">
-        <v>載入中…</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B302" t="str">
-        <v>输入</v>
+        <v>加载中…</v>
       </c>
       <c r="C302" t="str">
-        <v>輸入</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B303" t="str">
-        <v>输出</v>
+        <v>输入</v>
       </c>
       <c r="C303" t="str">
-        <v>輸出</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B304" t="str">
-        <v>浮点值</v>
+        <v>输出</v>
       </c>
       <c r="C304" t="str">
-        <v>浮點值</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B305" t="str">
-        <v>网格点</v>
+        <v>浮点值</v>
       </c>
       <c r="C305" t="str">
-        <v>網格點</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B306" t="str">
-        <v>归一化</v>
+        <v>网格点</v>
       </c>
       <c r="C306" t="str">
-        <v>正規化</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B307" t="str">
-        <v>可读值</v>
+        <v>归一化</v>
       </c>
       <c r="C307" t="str">
-        <v>可讀值</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B308" t="str">
-        <v>设备 → PCS</v>
+        <v>可读值</v>
       </c>
       <c r="C308" t="str">
-        <v>裝置 → PCS</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B309" t="str">
-        <v>PCS → 设备</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C309" t="str">
-        <v>PCS → 裝置</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B310" t="str">
-        <v>无 CLUT 网格</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C310" t="str">
-        <v>無 CLUT 網格</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B311" t="str">
-        <v>加载中…</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C311" t="str">
-        <v>載入中…</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B312" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>加载中…</v>
       </c>
       <c r="C312" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B313" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C313" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B314" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C314" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B315" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C315" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B316" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C316" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B317" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C317" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B318" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C318" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B319" t="str">
-        <v>安全性</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C319" t="str">
-        <v>安全性</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B320" t="str">
-        <v>符合性</v>
+        <v>安全性</v>
       </c>
       <c r="C320" t="str">
-        <v>符合性</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B321" t="str">
-        <v>质量</v>
+        <v>符合性</v>
       </c>
       <c r="C321" t="str">
-        <v>品質</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B322" t="str">
-        <v>报告</v>
+        <v>质量</v>
       </c>
       <c r="C322" t="str">
-        <v>報告</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B323" t="str">
-        <v>失败</v>
+        <v>报告</v>
       </c>
       <c r="C323" t="str">
-        <v>失敗</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B324" t="str">
-        <v>项检查</v>
+        <v>失败</v>
       </c>
       <c r="C324" t="str">
-        <v>項檢查</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B325" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>项检查</v>
       </c>
       <c r="C325" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B326" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C326" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B327" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C327" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B328" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C328" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B329" t="str">
-        <v>订阅</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C329" t="str">
-        <v>訂閱</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B330" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>订阅</v>
       </c>
       <c r="C330" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B331" t="str">
-        <v>订阅新版本通知</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C331" t="str">
-        <v>訂閱新版本通知</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B332" t="str">
-        <v>关闭</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C332" t="str">
-        <v>關閉</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B333" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>关闭</v>
       </c>
       <c r="C333" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B334" t="str">
-        <v>电子邮件地址</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C334" t="str">
-        <v>電子郵件地址</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B335" t="str">
-        <v>you@example.com</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C335" t="str">
-        <v>you@example.com</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B336" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
       <c r="C336" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B337" t="str">
-        <v>（选填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C337" t="str">
-        <v>（選填）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B338" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>（选填）</v>
       </c>
       <c r="C338" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B339" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C339" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B340" t="str">
-        <v>取消</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C340" t="str">
-        <v>取消</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B341" t="str">
-        <v>订阅</v>
+        <v>取消</v>
       </c>
       <c r="C341" t="str">
-        <v>訂閱</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B342" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>订阅</v>
       </c>
       <c r="C342" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B343" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C343" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B344" t="str">
-        <v>关闭</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C344" t="str">
-        <v>關閉</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B345" t="str">
-        <v>隐私声明</v>
+        <v>关闭</v>
       </c>
       <c r="C345" t="str">
-        <v>隱私聲明</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B346" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C346" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B347" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C347" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B348" t="str">
-        <v>请检查表单后重试。</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C348" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C349" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>网络错误，请重试。</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C350" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B351" t="str">
-        <v>错误：</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C351" t="str">
-        <v>錯誤：</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B352" t="str">
-        <v>转换为 XML</v>
+        <v>错误：</v>
       </c>
       <c r="C352" t="str">
-        <v>轉換為 XML</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B353" t="str">
-        <v>转换为 JSON</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C353" t="str">
-        <v>轉換為 JSON</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B354" t="str">
-        <v>转换为 ICC</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C354" t="str">
-        <v>轉換為 ICC</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B355" t="str">
-        <v>正在转换为 XML…</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C355" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B356" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C356" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B357" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C357" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B358" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C358" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B359" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C359" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B360" t="str">
-        <v>配置文件 ID</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C360" t="str">
-        <v>設定檔 ID</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B361" t="str">
-        <v>未找到标签。</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C361" t="str">
-        <v>找不到標籤。</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B362" t="str">
-        <v>标签名称</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C362" t="str">
-        <v>標籤名稱</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B363" t="str">
-        <v>ID</v>
+        <v>标签名称</v>
       </c>
       <c r="C363" t="str">
-        <v>ID</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B364" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
       <c r="C364" t="str">
-        <v>偏移</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B365" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
       <c r="C365" t="str">
-        <v>大小</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B366" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
       <c r="C366" t="str">
-        <v>填充</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B367" t="str">
-        <v>加载后字节已更改</v>
+        <v>填充</v>
       </c>
       <c r="C367" t="str">
-        <v>載入後位元組已變更</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B368" t="str">
-        <v>类型</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C368" t="str">
-        <v>類型</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B369" t="str">
-        <v>{type} 数组</v>
+        <v>类型</v>
       </c>
       <c r="C369" t="str">
-        <v>{type} 陣列</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B370" t="str">
-        <v>（无内容）</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C370" t="str">
-        <v>（無內容）</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B371" t="str">
-        <v>字节</v>
+        <v>（无内容）</v>
       </c>
       <c r="C371" t="str">
-        <v>位元組</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B372" t="str">
-        <v>正在加载完整描述…</v>
+        <v>字节</v>
       </c>
       <c r="C372" t="str">
-        <v>正在載入完整描述…</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B373" t="str">
-        <v>无法加载完整描述：</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C373" t="str">
-        <v>無法載入完整描述：</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B374" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C374" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B375" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C375" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B376" t="str">
-        <v>无验证输出</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C376" t="str">
-        <v>無驗證輸出</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B377" t="str">
-        <v>配置文件有效</v>
+        <v>无验证输出</v>
       </c>
       <c r="C377" t="str">
-        <v>設定檔有效</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B378" t="str">
-        <v>配置文件有警告</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C378" t="str">
-        <v>設定檔有警告</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B379" t="str">
-        <v>配置文件不合规</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C379" t="str">
-        <v>設定檔不符合規範</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B380" t="str">
-        <v>严重验证错误</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C380" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B381" t="str">
-        <v>未知验证状态</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C381" t="str">
-        <v>未知驗證狀態</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B382" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C382" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B383" t="str">
-        <v>未发现警告或错误。</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C383" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B384" t="str">
-        <v>有效</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C384" t="str">
-        <v>有效</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B385" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
       <c r="C385" t="str">
-        <v>警告</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B386" t="str">
-        <v>错误</v>
+        <v>警告</v>
       </c>
       <c r="C386" t="str">
-        <v>錯誤</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B387" t="str">
-        <v>未知</v>
+        <v>错误</v>
       </c>
       <c r="C387" t="str">
-        <v>未知</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B388" t="str">
-        <v>通过</v>
+        <v>未知</v>
       </c>
       <c r="C388" t="str">
-        <v>通過</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B389" t="str">
-        <v>失败</v>
+        <v>通过</v>
       </c>
       <c r="C389" t="str">
-        <v>失敗</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B390" t="str">
-        <v>在上下文中查看</v>
+        <v>失败</v>
       </c>
       <c r="C390" t="str">
-        <v>在上下文中檢視</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B391" t="str">
-        <v>验证详情</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C391" t="str">
-        <v>驗證詳情</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B392" t="str">
-        <v>触发字段</v>
+        <v>验证详情</v>
       </c>
       <c r="C392" t="str">
-        <v>觸發欄位</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B393" t="str">
-        <v>字段</v>
+        <v>触发字段</v>
       </c>
       <c r="C393" t="str">
-        <v>欄位</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B394" t="str">
-        <v>当前值</v>
+        <v>字段</v>
       </c>
       <c r="C394" t="str">
-        <v>目前值</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B395" t="str">
-        <v>要求：0</v>
+        <v>当前值</v>
       </c>
       <c r="C395" t="str">
-        <v>要求：0</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B396" t="str">
-        <v>预期：{value}</v>
+        <v>要求：0</v>
       </c>
       <c r="C396" t="str">
-        <v>預期：{value}</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B397" t="str">
-        <v>无效</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C397" t="str">
-        <v>無效</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B398" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>无效</v>
       </c>
       <c r="C398" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B399" t="str">
-        <v>关闭</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C399" t="str">
-        <v>關閉</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>关闭</v>
       </c>
       <c r="C400" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C401" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B402" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C402" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C403" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B404" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C404" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B405" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C405" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B406" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C406" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
       </c>
       <c r="C407" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B408" t="str">
-        <v>缩进</v>
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
       </c>
       <c r="C408" t="str">
-        <v>縮排</v>
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B409" t="str">
-        <v>排序键</v>
+        <v>缩进</v>
       </c>
       <c r="C409" t="str">
-        <v>排序鍵</v>
+        <v>縮排</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B410" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C410" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B410" t="str">
+      <c r="B411" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C410" t="str">
+      <c r="C411" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C410"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C411"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C411"/>
+  <dimension ref="A1:C445"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3363,1580 +3363,1954 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Perceptual</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B269" t="str">
-        <v>感知</v>
+        <v>L* 输出（色调）</v>
       </c>
       <c r="C269" t="str">
-        <v>感知</v>
+        <v>L* 輸出（色調）</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B270" t="str">
-        <v>相对比色</v>
+        <v>Δa*b*</v>
       </c>
       <c r="C270" t="str">
-        <v>相對比色</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Saturation</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B271" t="str">
-        <v>饱和度</v>
+        <v>极值比色</v>
       </c>
       <c r="C271" t="str">
-        <v>飽和度</v>
+        <v>極值比色</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B272" t="str">
-        <v>绝对比色</v>
+        <v>配置文件复现范围的两端：承印物白、它能打印的最深黑、该黑所耗的墨量，以及每个色相达到最饱和的位置。</v>
       </c>
       <c r="C272" t="str">
-        <v>絕對比色</v>
+        <v>設定檔重現範圍的兩端：承印物白、它能列印的最深黑、該黑所耗的墨量，以及每個色相達到最飽和的位置。</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Profile Statistics</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B273" t="str">
-        <v>特性文件统计</v>
+        <v>白点是零色料时的颜色——即空白承印物。黑点的求法是把 PCS 黑（L*=0，a*=b*=0）送入所选 B2A 表，得到配置文件为黑色选择的墨量，再把该墨量经 A2B1 读回。总墨量（TAC）即该墨量之和。绝对比色显示承印物自身的颜色；相对比色则将其重新参照到理想白。</v>
       </c>
       <c r="C273" t="str">
-        <v>特性檔統計</v>
+        <v>白點是零色料時的顏色——即空白承印物。黑點的求法是把 PCS 黑（L*=0，a*=b*=0）送入所選 B2A 表，得到設定檔為黑色選擇的墨量，再把該墨量經 A2B1 讀回。總墨量（TAC）即該墨量之和。絕對比色顯示承印物本身的顏色；相對比色則將其重新參照到理想白。</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative</v>
       </c>
       <c r="B274" t="str">
-        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
+        <v>相对</v>
       </c>
       <c r="C274" t="str">
-        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
+        <v>相對</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Absolute</v>
       </c>
       <c r="B275" t="str">
-        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
+        <v>绝对</v>
       </c>
       <c r="C275" t="str">
-        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
+        <v>絕對</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Rendering intent</v>
+        <v>White point</v>
       </c>
       <c r="B276" t="str">
-        <v>渲染意图</v>
+        <v>白点</v>
       </c>
       <c r="C276" t="str">
-        <v>轉換意圖</v>
+        <v>白點</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Black point</v>
       </c>
       <c r="B277" t="str">
-        <v>色域体积 (ΔE³)</v>
+        <v>黑点</v>
       </c>
       <c r="C277" t="str">
-        <v>色域體積 (ΔE³)</v>
+        <v>黑點</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B278" t="str">
-        <v>往返 ΔE</v>
+        <v>黑点处的墨量</v>
       </c>
       <c r="C278" t="str">
-        <v>往返 ΔE</v>
+        <v>黑點處的墨量</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>TAC</v>
       </c>
       <c r="B279" t="str">
-        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
+        <v>TAC</v>
       </c>
       <c r="C279" t="str">
-        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>mean</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B280" t="str">
-        <v>均值</v>
+        <v>此配置文件没有媒体白点标签，因此无法进行绝对比色。</v>
       </c>
       <c r="C280" t="str">
-        <v>平均</v>
+        <v>此設定檔沒有媒體白點標籤，因此無法進行絕對比色。</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>P90</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B281" t="str">
-        <v>P90</v>
+        <v>极值比色仅适用于输出（打印机）配置文件——它假定零色料即为空白承印物。</v>
       </c>
       <c r="C281" t="str">
-        <v>P90</v>
+        <v>極值比色僅適用於輸出（印表機）設定檔——它假定零色料即為空白承印物。</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>max</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B282" t="str">
-        <v>最大</v>
+        <v>实地与最大彩度</v>
       </c>
       <c r="C282" t="str">
-        <v>最大</v>
+        <v>實地與最大彩度</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysing…</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B283" t="str">
-        <v>正在分析…</v>
+        <v>每个油墨顶点的落点，以及沿途彩度最高的位置。经 A2B1 测得，因此这些行不随上方的渲染意图改变。在表现良好的配置文件中两行一致；若最大彩度在实地之前出现，超过该点的油墨只会使颜色变暗。</v>
       </c>
       <c r="C283" t="str">
-        <v>正在分析…</v>
+        <v>每個油墨頂點的落點，以及沿途彩度最高的位置。經 A2B1 量測，因此這些列不隨上方的轉換意圖改變。在表現良好的設定檔中兩列一致；若最大彩度在實地之前出現，超過該點的油墨只會使顏色變暗。</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Analysis</v>
+        <v>Hue</v>
       </c>
       <c r="B284" t="str">
-        <v>分析</v>
+        <v>色相</v>
       </c>
       <c r="C284" t="str">
-        <v>分析</v>
+        <v>色相</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Full tone</v>
       </c>
       <c r="B285" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>实地</v>
       </c>
       <c r="C285" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>實地</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Plot</v>
+        <v>Max C*</v>
       </c>
       <c r="B286" t="str">
-        <v>绘图</v>
+        <v>最大 C*</v>
       </c>
       <c r="C286" t="str">
-        <v>繪圖</v>
+        <v>最大 C*</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Raw Output</v>
+        <v>At ink</v>
       </c>
       <c r="B287" t="str">
-        <v>原始输出</v>
+        <v>对应墨量</v>
       </c>
       <c r="C287" t="str">
-        <v>原始輸出</v>
+        <v>對應墨量</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>XML</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B288" t="str">
-        <v>XML</v>
+        <v>最大彩度在实地之前达到——超过此点的油墨只会使颜色变暗。</v>
       </c>
       <c r="C288" t="str">
-        <v>XML</v>
+        <v>最大彩度在實地之前達到——超過此點的油墨只會使顏色變暗。</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>JSON</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B289" t="str">
-        <v>JSON</v>
+        <v>暗调中的用墨</v>
       </c>
       <c r="C289" t="str">
-        <v>JSON</v>
+        <v>暗部的用墨</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Curves</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B290" t="str">
-        <v>曲线</v>
+        <v>在一个恒定且刻意偏暗的明度上，沿 a*b* 平面取四条直线路径，送入所选 B2A 表。所有采样点的 L* 相同，因此某个色料出现的任何突变或反转都只能来自色相与彩度的处理——这正是暗调色域映射伪影的特征。</v>
       </c>
       <c r="C290" t="str">
-        <v>曲線</v>
+        <v>在一個固定且刻意偏暗的明度上，沿 a*b* 平面取四條直線路徑，送入所選 B2A 表。所有取樣點的 L* 相同，因此某個色料出現的任何突變或反轉都只能來自色相與彩度的處理——這正是暗部色域對應偽影的特徵。</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Input curves</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B291" t="str">
-        <v>输入曲线</v>
+        <v>暗调用墨仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C291" t="str">
-        <v>輸入曲線</v>
+        <v>暗部用墨僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Output curves</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B292" t="str">
-        <v>输出曲线</v>
+        <v>恒定 L* 平面</v>
       </c>
       <c r="C292" t="str">
-        <v>輸出曲線</v>
+        <v>固定 L* 平面</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>CLUT image</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B293" t="str">
-        <v>CLUT 图像</v>
+        <v>黑点补偿自</v>
       </c>
       <c r="C293" t="str">
-        <v>CLUT 影像</v>
+        <v>黑點補償自</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Gamut image</v>
+        <v>Position along path</v>
       </c>
       <c r="B294" t="str">
-        <v>色域图像</v>
+        <v>沿路径位置</v>
       </c>
       <c r="C294" t="str">
-        <v>色域影像</v>
+        <v>沿路徑位置</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Chromaticity</v>
+        <v>Path</v>
       </c>
       <c r="B295" t="str">
-        <v>色度</v>
+        <v>路径</v>
       </c>
       <c r="C295" t="str">
-        <v>色度</v>
+        <v>路徑</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Scatter plot</v>
+        <v>Cyan</v>
       </c>
       <c r="B296" t="str">
-        <v>散点图</v>
+        <v>青</v>
       </c>
       <c r="C296" t="str">
-        <v>散佈圖</v>
+        <v>青</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Tone response curve</v>
+        <v>Magenta</v>
       </c>
       <c r="B297" t="str">
-        <v>色调响应曲线</v>
+        <v>品红</v>
       </c>
       <c r="C297" t="str">
-        <v>色調響應曲線</v>
+        <v>洋紅</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Curve table</v>
+        <v>Yellow</v>
       </c>
       <c r="B298" t="str">
-        <v>曲线表</v>
+        <v>黄</v>
       </c>
       <c r="C298" t="str">
-        <v>曲線表</v>
+        <v>黃</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tables</v>
+        <v>Red</v>
       </c>
       <c r="B299" t="str">
-        <v>表格</v>
+        <v>红</v>
       </c>
       <c r="C299" t="str">
-        <v>表格</v>
+        <v>紅</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Data</v>
+        <v>Green</v>
       </c>
       <c r="B300" t="str">
-        <v>数据</v>
+        <v>绿</v>
       </c>
       <c r="C300" t="str">
-        <v>資料</v>
+        <v>綠</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Evaluate</v>
+        <v>Blue</v>
       </c>
       <c r="B301" t="str">
-        <v>求值</v>
+        <v>蓝</v>
       </c>
       <c r="C301" t="str">
-        <v>求值</v>
+        <v>藍</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Loading…</v>
+        <v>Black</v>
       </c>
       <c r="B302" t="str">
-        <v>加载中…</v>
+        <v>黑</v>
       </c>
       <c r="C302" t="str">
-        <v>載入中…</v>
+        <v>黑</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Input</v>
+        <v>Perceptual</v>
       </c>
       <c r="B303" t="str">
-        <v>输入</v>
+        <v>感知</v>
       </c>
       <c r="C303" t="str">
-        <v>輸入</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B304" t="str">
-        <v>输出</v>
+        <v>相对比色</v>
       </c>
       <c r="C304" t="str">
-        <v>輸出</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Floating point</v>
+        <v>Saturation</v>
       </c>
       <c r="B305" t="str">
-        <v>浮点值</v>
+        <v>饱和度</v>
       </c>
       <c r="C305" t="str">
-        <v>浮點值</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Grid point</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B306" t="str">
-        <v>网格点</v>
+        <v>绝对比色</v>
       </c>
       <c r="C306" t="str">
-        <v>網格點</v>
+        <v>絕對比色</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Normalized</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B307" t="str">
-        <v>归一化</v>
+        <v>特性文件统计</v>
       </c>
       <c r="C307" t="str">
-        <v>正規化</v>
+        <v>特性檔統計</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Human</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B308" t="str">
-        <v>可读值</v>
+        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
       </c>
       <c r="C308" t="str">
-        <v>可讀值</v>
+        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Device → PCS</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B309" t="str">
-        <v>设备 → PCS</v>
+        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
       </c>
       <c r="C309" t="str">
-        <v>裝置 → PCS</v>
+        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>PCS → Device</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B310" t="str">
-        <v>PCS → 设备</v>
+        <v>渲染意图</v>
       </c>
       <c r="C310" t="str">
-        <v>PCS → 裝置</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B311" t="str">
-        <v>无 CLUT 网格</v>
+        <v>色域体积 (ΔE³)</v>
       </c>
       <c r="C311" t="str">
-        <v>無 CLUT 網格</v>
+        <v>色域體積 (ΔE³)</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B312" t="str">
-        <v>加载中…</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C312" t="str">
-        <v>載入中…</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B313" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
       </c>
       <c r="C313" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Invalid profile URL:</v>
+        <v>mean</v>
       </c>
       <c r="B314" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>均值</v>
       </c>
       <c r="C314" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>P90</v>
       </c>
       <c r="B315" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>P90</v>
       </c>
       <c r="C315" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>max</v>
       </c>
       <c r="B316" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>最大</v>
       </c>
       <c r="C316" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Analysing…</v>
       </c>
       <c r="B317" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>正在分析…</v>
       </c>
       <c r="C317" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Analysis</v>
       </c>
       <c r="B318" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>分析</v>
       </c>
       <c r="C318" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B319" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C319" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Security</v>
+        <v>Plot</v>
       </c>
       <c r="B320" t="str">
-        <v>安全性</v>
+        <v>绘图</v>
       </c>
       <c r="C320" t="str">
-        <v>安全性</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Conformance</v>
+        <v>Raw Output</v>
       </c>
       <c r="B321" t="str">
-        <v>符合性</v>
+        <v>原始输出</v>
       </c>
       <c r="C321" t="str">
-        <v>符合性</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Quality</v>
+        <v>XML</v>
       </c>
       <c r="B322" t="str">
-        <v>质量</v>
+        <v>XML</v>
       </c>
       <c r="C322" t="str">
-        <v>品質</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>REPORT</v>
+        <v>JSON</v>
       </c>
       <c r="B323" t="str">
-        <v>报告</v>
+        <v>JSON</v>
       </c>
       <c r="C323" t="str">
-        <v>報告</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>FAIL</v>
+        <v>Curves</v>
       </c>
       <c r="B324" t="str">
-        <v>失败</v>
+        <v>曲线</v>
       </c>
       <c r="C324" t="str">
-        <v>失敗</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>checks</v>
+        <v>Input curves</v>
       </c>
       <c r="B325" t="str">
-        <v>项检查</v>
+        <v>输入曲线</v>
       </c>
       <c r="C325" t="str">
-        <v>項檢查</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Output curves</v>
       </c>
       <c r="B326" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>输出曲线</v>
       </c>
       <c r="C326" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>CLUT image</v>
       </c>
       <c r="B327" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C327" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Gamut image</v>
       </c>
       <c r="B328" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>色域图像</v>
       </c>
       <c r="C328" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Powered by {lib}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B329" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>色度</v>
       </c>
       <c r="C329" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Subscribe</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B330" t="str">
-        <v>订阅</v>
+        <v>散点图</v>
       </c>
       <c r="C330" t="str">
-        <v>訂閱</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B331" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C331" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Get notified about new releases</v>
+        <v>Curve table</v>
       </c>
       <c r="B332" t="str">
-        <v>订阅新版本通知</v>
+        <v>曲线表</v>
       </c>
       <c r="C332" t="str">
-        <v>訂閱新版本通知</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Close</v>
+        <v>Tables</v>
       </c>
       <c r="B333" t="str">
-        <v>关闭</v>
+        <v>表格</v>
       </c>
       <c r="C333" t="str">
-        <v>關閉</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Data</v>
       </c>
       <c r="B334" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>数据</v>
       </c>
       <c r="C334" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Email address</v>
+        <v>Evaluate</v>
       </c>
       <c r="B335" t="str">
-        <v>电子邮件地址</v>
+        <v>求值</v>
       </c>
       <c r="C335" t="str">
-        <v>電子郵件地址</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>you@example.com</v>
+        <v>Loading…</v>
       </c>
       <c r="B336" t="str">
-        <v>you@example.com</v>
+        <v>加载中…</v>
       </c>
       <c r="C336" t="str">
-        <v>you@example.com</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Input</v>
       </c>
       <c r="B337" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>输入</v>
       </c>
       <c r="C337" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>(optional)</v>
+        <v>Output</v>
       </c>
       <c r="B338" t="str">
-        <v>（选填）</v>
+        <v>输出</v>
       </c>
       <c r="C338" t="str">
-        <v>（選填）</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Floating point</v>
       </c>
       <c r="B339" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>浮点值</v>
       </c>
       <c r="C339" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Grid point</v>
       </c>
       <c r="B340" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>网格点</v>
       </c>
       <c r="C340" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Cancel</v>
+        <v>Normalized</v>
       </c>
       <c r="B341" t="str">
-        <v>取消</v>
+        <v>归一化</v>
       </c>
       <c r="C341" t="str">
-        <v>取消</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Subscribe</v>
+        <v>Human</v>
       </c>
       <c r="B342" t="str">
-        <v>订阅</v>
+        <v>可读值</v>
       </c>
       <c r="C342" t="str">
-        <v>訂閱</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B343" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C343" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B344" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C344" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Close</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B345" t="str">
-        <v>关闭</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C345" t="str">
-        <v>關閉</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Privacy notice</v>
+        <v>Loading…</v>
       </c>
       <c r="B346" t="str">
-        <v>隐私声明</v>
+        <v>加载中…</v>
       </c>
       <c r="C346" t="str">
-        <v>隱私聲明</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B347" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C347" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B348" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C348" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B349" t="str">
-        <v>请检查表单后重试。</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C349" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B350" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C350" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B351" t="str">
-        <v>网络错误，请重试。</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C351" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Error:</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B352" t="str">
-        <v>错误：</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C352" t="str">
-        <v>錯誤：</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to XML</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B353" t="str">
-        <v>转换为 XML</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C353" t="str">
-        <v>轉換為 XML</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to JSON</v>
+        <v>Security</v>
       </c>
       <c r="B354" t="str">
-        <v>转换为 JSON</v>
+        <v>安全性</v>
       </c>
       <c r="C354" t="str">
-        <v>轉換為 JSON</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to ICC</v>
+        <v>Conformance</v>
       </c>
       <c r="B355" t="str">
-        <v>转换为 ICC</v>
+        <v>符合性</v>
       </c>
       <c r="C355" t="str">
-        <v>轉換為 ICC</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to XML…</v>
+        <v>Quality</v>
       </c>
       <c r="B356" t="str">
-        <v>正在转换为 XML…</v>
+        <v>质量</v>
       </c>
       <c r="C356" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to JSON…</v>
+        <v>REPORT</v>
       </c>
       <c r="B357" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>报告</v>
       </c>
       <c r="C357" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to ICC…</v>
+        <v>FAIL</v>
       </c>
       <c r="B358" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>失败</v>
       </c>
       <c r="C358" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Load ICC profile</v>
+        <v>checks</v>
       </c>
       <c r="B359" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>项检查</v>
       </c>
       <c r="C359" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B360" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C360" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Profile ID</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B361" t="str">
-        <v>配置文件 ID</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C361" t="str">
-        <v>設定檔 ID</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B362" t="str">
-        <v>未找到标签。</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C362" t="str">
-        <v>找不到標籤。</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Tag Name</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B363" t="str">
-        <v>标签名称</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C363" t="str">
-        <v>標籤名稱</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>ID</v>
+        <v>Subscribe</v>
       </c>
       <c r="B364" t="str">
-        <v>ID</v>
+        <v>订阅</v>
       </c>
       <c r="C364" t="str">
-        <v>ID</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Offset</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B365" t="str">
-        <v>偏移</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C365" t="str">
-        <v>偏移</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Size</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B366" t="str">
-        <v>大小</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C366" t="str">
-        <v>大小</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Pad</v>
+        <v>Close</v>
       </c>
       <c r="B367" t="str">
-        <v>填充</v>
+        <v>关闭</v>
       </c>
       <c r="C367" t="str">
-        <v>填充</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Bytes changed since load</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B368" t="str">
-        <v>加载后字节已更改</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C368" t="str">
-        <v>載入後位元組已變更</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Type</v>
+        <v>Email address</v>
       </c>
       <c r="B369" t="str">
-        <v>类型</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C369" t="str">
-        <v>類型</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Array of {type}</v>
+        <v>you@example.com</v>
       </c>
       <c r="B370" t="str">
-        <v>{type} 数组</v>
+        <v>you@example.com</v>
       </c>
       <c r="C370" t="str">
-        <v>{type} 陣列</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>(No content)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B371" t="str">
-        <v>（无内容）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C371" t="str">
-        <v>（無內容）</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>bytes</v>
+        <v>(optional)</v>
       </c>
       <c r="B372" t="str">
-        <v>字节</v>
+        <v>（选填）</v>
       </c>
       <c r="C372" t="str">
-        <v>位元組</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Loading full description…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B373" t="str">
-        <v>正在加载完整描述…</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C373" t="str">
-        <v>正在載入完整描述…</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Could not load full description:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B374" t="str">
-        <v>无法加载完整描述：</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C374" t="str">
-        <v>無法載入完整描述：</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Cancel</v>
       </c>
       <c r="B375" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>取消</v>
       </c>
       <c r="C375" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B376" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>订阅</v>
       </c>
       <c r="C376" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>No validation output</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B377" t="str">
-        <v>无验证输出</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C377" t="str">
-        <v>無驗證輸出</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile is valid</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B378" t="str">
-        <v>配置文件有效</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C378" t="str">
-        <v>設定檔有效</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Close</v>
       </c>
       <c r="B379" t="str">
-        <v>配置文件有警告</v>
+        <v>关闭</v>
       </c>
       <c r="C379" t="str">
-        <v>設定檔有警告</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B380" t="str">
-        <v>配置文件不合规</v>
+        <v>隐私声明</v>
       </c>
       <c r="C380" t="str">
-        <v>設定檔不符合規範</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Critical validation error</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B381" t="str">
-        <v>严重验证错误</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C381" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Unknown validation status</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B382" t="str">
-        <v>未知验证状态</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C382" t="str">
-        <v>未知驗證狀態</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B383" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C383" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B384" t="str">
-        <v>未发现警告或错误。</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C384" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Valid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B385" t="str">
-        <v>有效</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C385" t="str">
-        <v>有效</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Warning</v>
+        <v>Error:</v>
       </c>
       <c r="B386" t="str">
-        <v>警告</v>
+        <v>错误：</v>
       </c>
       <c r="C386" t="str">
-        <v>警告</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Error</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B387" t="str">
-        <v>错误</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C387" t="str">
-        <v>錯誤</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Unknown</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B388" t="str">
-        <v>未知</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C388" t="str">
-        <v>未知</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Pass</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B389" t="str">
-        <v>通过</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C389" t="str">
-        <v>通過</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Fail</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B390" t="str">
-        <v>失败</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C390" t="str">
-        <v>失敗</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>View in context</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B391" t="str">
-        <v>在上下文中查看</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C391" t="str">
-        <v>在上下文中檢視</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Validation detail</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B392" t="str">
-        <v>验证详情</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C392" t="str">
-        <v>驗證詳情</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Triggered by</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B393" t="str">
-        <v>触发字段</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C393" t="str">
-        <v>觸發欄位</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Field</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B394" t="str">
-        <v>字段</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C394" t="str">
-        <v>欄位</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Current value</v>
+        <v>Profile ID</v>
       </c>
       <c r="B395" t="str">
-        <v>当前值</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C395" t="str">
-        <v>目前值</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Required: 0</v>
+        <v>No tags found.</v>
       </c>
       <c r="B396" t="str">
-        <v>要求：0</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C396" t="str">
-        <v>要求：0</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Expected: {value}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B397" t="str">
-        <v>预期：{value}</v>
+        <v>标签名称</v>
       </c>
       <c r="C397" t="str">
-        <v>預期：{value}</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Invalid</v>
+        <v>ID</v>
       </c>
       <c r="B398" t="str">
-        <v>无效</v>
+        <v>ID</v>
       </c>
       <c r="C398" t="str">
-        <v>無效</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Offset</v>
       </c>
       <c r="B399" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>偏移</v>
       </c>
       <c r="C399" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Size</v>
       </c>
       <c r="B400" t="str">
-        <v>关闭</v>
+        <v>大小</v>
       </c>
       <c r="C400" t="str">
-        <v>關閉</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pad</v>
       </c>
       <c r="B401" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>填充</v>
       </c>
       <c r="C401" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B402" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C402" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Type</v>
       </c>
       <c r="B403" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>类型</v>
       </c>
       <c r="C403" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B404" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C404" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved XML edits</v>
+        <v>(No content)</v>
       </c>
       <c r="B405" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>（无内容）</v>
       </c>
       <c r="C405" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>bytes</v>
       </c>
       <c r="B406" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>字节</v>
       </c>
       <c r="C406" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B407" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C407" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B408" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C408" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>indent</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B409" t="str">
-        <v>缩进</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C409" t="str">
-        <v>縮排</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>sort keys</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B410" t="str">
-        <v>排序键</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C410" t="str">
-        <v>排序鍵</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B411" t="str">
+        <v>无验证输出</v>
+      </c>
+      <c r="C411" t="str">
+        <v>無驗證輸出</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B412" t="str">
+        <v>配置文件有效</v>
+      </c>
+      <c r="C412" t="str">
+        <v>設定檔有效</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B413" t="str">
+        <v>配置文件有警告</v>
+      </c>
+      <c r="C413" t="str">
+        <v>設定檔有警告</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B414" t="str">
+        <v>配置文件不合规</v>
+      </c>
+      <c r="C414" t="str">
+        <v>設定檔不符合規範</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B415" t="str">
+        <v>严重验证错误</v>
+      </c>
+      <c r="C415" t="str">
+        <v>嚴重驗證錯誤</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B416" t="str">
+        <v>未知验证状态</v>
+      </c>
+      <c r="C416" t="str">
+        <v>未知驗證狀態</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B417" t="str">
+        <v>严重 — 仅供检查显示</v>
+      </c>
+      <c r="C417" t="str">
+        <v>嚴重 — 僅供檢視顯示</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B418" t="str">
+        <v>未发现警告或错误。</v>
+      </c>
+      <c r="C418" t="str">
+        <v>未發現警告或錯誤。</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B419" t="str">
+        <v>有效</v>
+      </c>
+      <c r="C419" t="str">
+        <v>有效</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B420" t="str">
+        <v>警告</v>
+      </c>
+      <c r="C420" t="str">
+        <v>警告</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B421" t="str">
+        <v>错误</v>
+      </c>
+      <c r="C421" t="str">
+        <v>錯誤</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B422" t="str">
+        <v>未知</v>
+      </c>
+      <c r="C422" t="str">
+        <v>未知</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B423" t="str">
+        <v>通过</v>
+      </c>
+      <c r="C423" t="str">
+        <v>通過</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B424" t="str">
+        <v>失败</v>
+      </c>
+      <c r="C424" t="str">
+        <v>失敗</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B425" t="str">
+        <v>在上下文中查看</v>
+      </c>
+      <c r="C425" t="str">
+        <v>在上下文中檢視</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B426" t="str">
+        <v>验证详情</v>
+      </c>
+      <c r="C426" t="str">
+        <v>驗證詳情</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B427" t="str">
+        <v>触发字段</v>
+      </c>
+      <c r="C427" t="str">
+        <v>觸發欄位</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B428" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C428" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B429" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C429" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B430" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C430" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B431" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C431" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B432" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C432" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B433" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C433" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B434" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C434" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B435" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C435" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B436" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C436" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B437" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C437" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B438" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C438" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B439" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C439" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B440" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C440" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B441" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C441" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B442" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C442" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B443" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C443" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B444" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C444" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B411" t="str">
+      <c r="B445" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C411" t="str">
+      <c r="C445" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C411"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C445"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C445"/>
+  <dimension ref="A1:C449"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -582,4735 +582,4779 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Specified gamut</v>
+        <v>Round-trip ΔE by lightness</v>
       </c>
       <c r="B17" t="str">
-        <v>指定色域</v>
+        <v>按明度的往返 ΔE</v>
       </c>
       <c r="C17" t="str">
-        <v>指定色域</v>
+        <v>依明度的往返 ΔE</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (lightness of the requested colour)</v>
       </c>
       <c r="B18" t="str">
-        <v>感知参考媒介色域</v>
+        <v>L*（所请求颜色的明度）</v>
       </c>
       <c r="C18" t="str">
-        <v>感知參考媒體色域</v>
+        <v>L*（所要求顏色的明度）</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not specified</v>
+        <v>ΔE*ab</v>
       </c>
       <c r="B19" t="str">
-        <v>未指定</v>
+        <v>ΔE*ab</v>
       </c>
       <c r="C19" t="str">
-        <v>未指定</v>
+        <v>ΔE*ab</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Not evaluated</v>
+        <v>points, gamut boundary → neutral</v>
       </c>
       <c r="B20" t="str">
-        <v>未评估</v>
+        <v>个点，色域边界 → 中性</v>
       </c>
       <c r="C20" t="str">
-        <v>未評估</v>
+        <v>個點，色域邊界 → 中性</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PRMG interoperability</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B21" t="str">
-        <v>PRMG 互操作性</v>
+        <v>指定色域</v>
       </c>
       <c r="C21" t="str">
-        <v>PRMG 互通性</v>
+        <v>指定色域</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B22" t="str">
-        <v>往返 ΔE</v>
+        <v>感知参考媒介色域</v>
       </c>
       <c r="C22" t="str">
-        <v>往返 ΔE</v>
+        <v>感知參考媒體色域</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Count</v>
+        <v>Not specified</v>
       </c>
       <c r="B23" t="str">
-        <v>数量</v>
+        <v>未指定</v>
       </c>
       <c r="C23" t="str">
-        <v>數量</v>
+        <v>未指定</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Share</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B24" t="str">
-        <v>占比</v>
+        <v>未评估</v>
       </c>
       <c r="C24" t="str">
-        <v>占比</v>
+        <v>未評估</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Total</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B25" t="str">
-        <v>总计</v>
+        <v>PRMG 互操作性</v>
       </c>
       <c r="C25" t="str">
-        <v>總計</v>
+        <v>PRMG 互通性</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B26" t="str">
-        <v>未评估 PRMG</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C26" t="str">
-        <v>未評估 PRMG</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>Count</v>
       </c>
       <c r="B27" t="str">
-        <v>针对某一渲染意图的整份配置文件指标：由设备→PCS 变换所包围的色域体积 (ΔE*ab³)，以及往返精度指标。选择渲染意图和往返类型 — 表格和直方图会相应更新。</v>
+        <v>数量</v>
       </c>
       <c r="C27" t="str">
-        <v>針對某一轉換意圖的整份設定檔指標：由裝置→PCS 轉換所包圍的色域體積 (ΔE*ab³)，以及往返精度指標。選擇轉換意圖與往返類型 — 表格與長條圖會隨之更新。</v>
+        <v>數量</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Round-trip type</v>
+        <v>Share</v>
       </c>
       <c r="B28" t="str">
-        <v>往返类型</v>
+        <v>占比</v>
       </c>
       <c r="C28" t="str">
-        <v>往返類型</v>
+        <v>占比</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Total</v>
       </c>
       <c r="B29" t="str">
-        <v>对此往返类型无影响</v>
+        <v>总计</v>
       </c>
       <c r="C29" t="str">
-        <v>對此往返類型無影響</v>
+        <v>總計</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B30" t="str">
-        <v>此往返类型不适用于该配置文件。</v>
+        <v>未评估 PRMG</v>
       </c>
       <c r="C30" t="str">
-        <v>此往返類型不適用於此設定檔。</v>
+        <v>未評估 PRMG</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B31" t="str">
-        <v>往返 ΔE 分布</v>
+        <v>针对某一渲染意图的整份配置文件指标：由设备→PCS 变换所包围的色域体积 (ΔE*ab³)，以及往返精度指标。选择渲染意图和往返类型 — 表格和直方图会相应更新。</v>
       </c>
       <c r="C31" t="str">
-        <v>往返 ΔE 分佈</v>
+        <v>針對某一轉換意圖的整份設定檔指標：由裝置→PCS 轉換所包圍的色域體積 (ΔE*ab³)，以及往返精度指標。選擇轉換意圖與往返類型 — 表格與長條圖會隨之更新。</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B32" t="str">
-        <v>没有往返样本落在评估区域内。</v>
+        <v>往返类型</v>
       </c>
       <c r="C32" t="str">
-        <v>沒有往返樣本落在評估區域內。</v>
+        <v>往返類型</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Std Dev</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B33" t="str">
-        <v>标准差</v>
+        <v>对此往返类型无影响</v>
       </c>
       <c r="C33" t="str">
-        <v>標準差</v>
+        <v>對此往返類型無影響</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Relative frequency</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B34" t="str">
-        <v>相对频率</v>
+        <v>此往返类型不适用于该配置文件。</v>
       </c>
       <c r="C34" t="str">
-        <v>相對頻率</v>
+        <v>此往返類型不適用於此設定檔。</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cumulative frequency</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B35" t="str">
-        <v>累积频率</v>
+        <v>往返 ΔE 分布</v>
       </c>
       <c r="C35" t="str">
-        <v>累積頻率</v>
+        <v>往返 ΔE 分佈</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Horizontal scale</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B36" t="str">
-        <v>水平刻度</v>
+        <v>没有往返样本落在评估区域内。</v>
       </c>
       <c r="C36" t="str">
-        <v>水平刻度</v>
+        <v>沒有往返樣本落在評估區域內。</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Integer ΔE</v>
+        <v>Std Dev</v>
       </c>
       <c r="B37" t="str">
-        <v>整数 ΔE</v>
+        <v>标准差</v>
       </c>
       <c r="C37" t="str">
-        <v>整數 ΔE</v>
+        <v>標準差</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Auto-scale</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B38" t="str">
-        <v>自动缩放</v>
+        <v>相对频率</v>
       </c>
       <c r="C38" t="str">
-        <v>自動縮放</v>
+        <v>相對頻率</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bins</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B39" t="str">
-        <v>分组</v>
+        <v>累积频率</v>
       </c>
       <c r="C39" t="str">
-        <v>分組</v>
+        <v>累積頻率</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CLUT Image</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B40" t="str">
-        <v>CLUT 图像</v>
+        <v>水平刻度</v>
       </c>
       <c r="C40" t="str">
-        <v>CLUT 影像</v>
+        <v>水平刻度</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B41" t="str">
-        <v>设备↔PCS 变换的颜色查找表 (CLUT)，平铺成一幅图像。选择要查看的渲染意图表。</v>
+        <v>整数 ΔE</v>
       </c>
       <c r="C41" t="str">
-        <v>裝置↔PCS 轉換的色彩查找表 (CLUT)，平鋪成一幅影像。選擇要檢視的轉換意圖表。</v>
+        <v>整數 ΔE</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B42" t="str">
-        <v>此配置文件没有可供可视化的基于 CLUT 的设备↔PCS 表。</v>
+        <v>自动缩放</v>
       </c>
       <c r="C42" t="str">
-        <v>此設定檔沒有可供視覺化的基於 CLUT 的裝置↔PCS 表。</v>
+        <v>自動縮放</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Gamut Image</v>
+        <v>Bins</v>
       </c>
       <c r="B43" t="str">
-        <v>色域图像</v>
+        <v>分组</v>
       </c>
       <c r="C43" t="str">
-        <v>色域影像</v>
+        <v>分組</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B44" t="str">
-        <v>色域标签的色域内/外映射：PCS 颜色可再现处为中性色，落在设备色域之外处为红色。</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C44" t="str">
-        <v>色域標籤的色域內/外對應：PCS 色彩可重現處為中性色，落在裝置色域之外處為紅色。</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B45" t="str">
-        <v>此配置文件没有可供可视化的色域标签。</v>
+        <v>设备↔PCS 变换的颜色查找表 (CLUT)，平铺成一幅图像。选择要查看的渲染意图表。</v>
       </c>
       <c r="C45" t="str">
-        <v>此設定檔沒有可供視覺化的色域標籤。</v>
+        <v>裝置↔PCS 轉換的色彩查找表 (CLUT)，平鋪成一幅影像。選擇要檢視的轉換意圖表。</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B46" t="str">
-        <v>垂直刻度</v>
+        <v>此配置文件没有可供可视化的基于 CLUT 的设备↔PCS 表。</v>
       </c>
       <c r="C46" t="str">
-        <v>垂直刻度</v>
+        <v>此設定檔沒有可供視覺化的基於 CLUT 的裝置↔PCS 表。</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>X–Y</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B47" t="str">
-        <v>X–Y</v>
+        <v>色域图像</v>
       </c>
       <c r="C47" t="str">
-        <v>X–Y</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B48" t="str">
-        <v>色调增益</v>
+        <v>色域标签的色域内/外映射：PCS 颜色可再现处为中性色，落在设备色域之外处为红色。</v>
       </c>
       <c r="C48" t="str">
-        <v>色調增益</v>
+        <v>色域標籤的色域內/外對應：PCS 色彩可重現處為中性色，落在裝置色域之外處為紅色。</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B49" t="str">
-        <v>色调增益（输出 − 输入）</v>
+        <v>此配置文件没有可供可视化的色域标签。</v>
       </c>
       <c r="C49" t="str">
-        <v>色調增益（輸出 − 輸入）</v>
+        <v>此設定檔沒有可供視覺化的色域標籤。</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Show full dump</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B50" t="str">
-        <v>显示完整转储</v>
+        <v>垂直刻度</v>
       </c>
       <c r="C50" t="str">
-        <v>顯示完整傾印</v>
+        <v>垂直刻度</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Output truncated for performance.</v>
+        <v>X–Y</v>
       </c>
       <c r="B51" t="str">
-        <v>为提升性能，输出已截断。</v>
+        <v>X–Y</v>
       </c>
       <c r="C51" t="str">
-        <v>為提升效能，輸出已截斷。</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B52" t="str">
-        <v>色域内概览 (RT0)</v>
+        <v>色调增益</v>
       </c>
       <c r="C52" t="str">
-        <v>色域內概覽 (RT0)</v>
+        <v>色調增益</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B53" t="str">
-        <v>反演 + 色域 (RT1)</v>
+        <v>色调增益（输出 − 输入）</v>
       </c>
       <c r="C53" t="str">
-        <v>反演 + 色域 (RT1)</v>
+        <v>色調增益（輸出 − 輸入）</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Show full dump</v>
       </c>
       <c r="B54" t="str">
-        <v>可重现性 (RT2)</v>
+        <v>显示完整转储</v>
       </c>
       <c r="C54" t="str">
-        <v>可重現性 (RT2)</v>
+        <v>顯示完整傾印</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PRMG interoperability</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B55" t="str">
-        <v>PRMG 互操作性</v>
+        <v>为提升性能，输出已截断。</v>
       </c>
       <c r="C55" t="str">
-        <v>PRMG 互操作性</v>
+        <v>為提升效能，輸出已截斷。</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B56" t="str">
-        <v>iccviz 概览：设备值网格被转换到 PCS、再回到设备、再次到 PCS；在两次 PCS 结果之间测量 ΔE*ab。这是一次快速的色域内稳定性检查。</v>
+        <v>色域内概览 (RT0)</v>
       </c>
       <c r="C56" t="str">
-        <v>iccviz 概覽：裝置值網格被轉換到 PCS、再回到裝置、再次到 PCS；在兩次 PCS 結果之間測量 ΔE*ab。這是一次快速的色域內穩定性檢查。</v>
+        <v>色域內概覽 (RT0)</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip 往返 1：每个设备颜色的 PCS 与其经过一次 Lab → 设备 → Lab 往返后的 PCS 之间的 ΔE*ab。反映反演精度和色域映射。</v>
+        <v>反演 + 色域 (RT1)</v>
       </c>
       <c r="C57" t="str">
-        <v>iccRoundTrip 往返 1：每個裝置色彩的 PCS 與其經過一次 Lab → 裝置 → Lab 往返後的 PCS 之間的 ΔE*ab。反映反演精度與色域對應。</v>
+        <v>反演 + 色域 (RT1)</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip 往返 2：第一次与第二次往返之间的 ΔE*ab — 重复的 PCS 往返有多稳定（可重现性，与第一次往返的色域裁剪无关）。</v>
+        <v>可重现性 (RT2)</v>
       </c>
       <c r="C58" t="str">
-        <v>iccRoundTrip 往返 2：第一次與第二次往返之間的 ΔE*ab — 重複的 PCS 往返有多穩定（可重現性，與第一次往返的色域裁剪無關）。</v>
+        <v>可重現性 (RT2)</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B59" t="str">
-        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 内的 PCS 颜色进行一次往返（Lab → 设备 → Lab）；ΔE*ab 分布可指示跨配置文件的互操作性。</v>
+        <v>PRMG 互操作性</v>
       </c>
       <c r="C59" t="str">
-        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 內的 PCS 色彩進行一次往返（Lab → 裝置 → Lab）；ΔE*ab 分佈可指示跨設定檔的互操作性。</v>
+        <v>PRMG 互操作性</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Settings</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B60" t="str">
-        <v>设置</v>
+        <v>iccviz 概览：设备值网格被转换到 PCS、再回到设备、再次到 PCS；在两次 PCS 结果之间测量 ΔE*ab。这是一次快速的色域内稳定性检查。</v>
       </c>
       <c r="C60" t="str">
-        <v>設定</v>
+        <v>iccviz 概覽：裝置值網格被轉換到 PCS、再回到裝置、再次到 PCS；在兩次 PCS 結果之間測量 ΔE*ab。這是一次快速的色域內穩定性檢查。</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Display</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B61" t="str">
-        <v>显示</v>
+        <v>iccRoundTrip 往返 1：每个设备颜色的 PCS 与其经过一次 Lab → 设备 → Lab 往返后的 PCS 之间的 ΔE*ab。反映反演精度和色域映射。</v>
       </c>
       <c r="C61" t="str">
-        <v>顯示</v>
+        <v>iccRoundTrip 往返 1：每個裝置色彩的 PCS 與其經過一次 Lab → 裝置 → Lab 往返後的 PCS 之間的 ΔE*ab。反映反演精度與色域對應。</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Background</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B62" t="str">
-        <v>背景</v>
+        <v>iccRoundTrip 往返 2：第一次与第二次往返之间的 ΔE*ab — 重复的 PCS 往返有多稳定（可重现性，与第一次往返的色域裁剪无关）。</v>
       </c>
       <c r="C62" t="str">
-        <v>背景</v>
+        <v>iccRoundTrip 往返 2：第一次與第二次往返之間的 ΔE*ab — 重複的 PCS 往返有多穩定（可重現性，與第一次往返的色域裁剪無關）。</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Language</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B63" t="str">
-        <v>语言</v>
+        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 内的 PCS 颜色进行一次往返（Lab → 设备 → Lab）；ΔE*ab 分布可指示跨配置文件的互操作性。</v>
       </c>
       <c r="C63" t="str">
-        <v>語言</v>
+        <v>iccRoundTrip PRMG：Perceptual Reference Medium Gamut 內的 PCS 色彩進行一次往返（Lab → 裝置 → Lab）；ΔE*ab 分佈可指示跨設定檔的互操作性。</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>System</v>
+        <v>Settings</v>
       </c>
       <c r="B64" t="str">
-        <v>系统</v>
+        <v>设置</v>
       </c>
       <c r="C64" t="str">
-        <v>系統</v>
+        <v>設定</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Light</v>
+        <v>Display</v>
       </c>
       <c r="B65" t="str">
-        <v>浅色</v>
+        <v>显示</v>
       </c>
       <c r="C65" t="str">
-        <v>淺色</v>
+        <v>顯示</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Dark</v>
+        <v>Background</v>
       </c>
       <c r="B66" t="str">
-        <v>深色</v>
+        <v>背景</v>
       </c>
       <c r="C66" t="str">
-        <v>深色</v>
+        <v>背景</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>System default</v>
+        <v>Language</v>
       </c>
       <c r="B67" t="str">
-        <v>系统默认</v>
+        <v>语言</v>
       </c>
       <c r="C67" t="str">
-        <v>系統預設</v>
+        <v>語言</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Number format</v>
+        <v>System</v>
       </c>
       <c r="B68" t="str">
-        <v>数字格式</v>
+        <v>系统</v>
       </c>
       <c r="C68" t="str">
-        <v>數字格式</v>
+        <v>系統</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hexadecimal</v>
+        <v>Light</v>
       </c>
       <c r="B69" t="str">
-        <v>十六进制</v>
+        <v>浅色</v>
       </c>
       <c r="C69" t="str">
-        <v>十六進位</v>
+        <v>淺色</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Decimal</v>
+        <v>Dark</v>
       </c>
       <c r="B70" t="str">
-        <v>十进制</v>
+        <v>深色</v>
       </c>
       <c r="C70" t="str">
-        <v>十進位</v>
+        <v>深色</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Help</v>
+        <v>System default</v>
       </c>
       <c r="B71" t="str">
-        <v>帮助</v>
+        <v>系统默认</v>
       </c>
       <c r="C71" t="str">
-        <v>說明</v>
+        <v>系統預設</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Contact</v>
+        <v>Number format</v>
       </c>
       <c r="B72" t="str">
-        <v>联系</v>
+        <v>数字格式</v>
       </c>
       <c r="C72" t="str">
-        <v>聯絡</v>
+        <v>數字格式</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>User guide</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B73" t="str">
-        <v>用户指南</v>
+        <v>十六进制</v>
       </c>
       <c r="C73" t="str">
-        <v>使用者指南</v>
+        <v>十六進位</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search guide</v>
+        <v>Decimal</v>
       </c>
       <c r="B74" t="str">
-        <v>搜索指南</v>
+        <v>十进制</v>
       </c>
       <c r="C74" t="str">
-        <v>搜尋指南</v>
+        <v>十進位</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Search the user guide</v>
+        <v>Help</v>
       </c>
       <c r="B75" t="str">
-        <v>搜索用户指南</v>
+        <v>帮助</v>
       </c>
       <c r="C75" t="str">
-        <v>搜尋使用者指南</v>
+        <v>說明</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Previous match</v>
+        <v>Contact</v>
       </c>
       <c r="B76" t="str">
-        <v>上一个匹配项</v>
+        <v>联系</v>
       </c>
       <c r="C76" t="str">
-        <v>上一個相符項目</v>
+        <v>聯絡</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Next match</v>
+        <v>User guide</v>
       </c>
       <c r="B77" t="str">
-        <v>下一个匹配项</v>
+        <v>用户指南</v>
       </c>
       <c r="C77" t="str">
-        <v>下一個相符項目</v>
+        <v>使用者指南</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Close user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B78" t="str">
-        <v>关闭用户指南</v>
+        <v>搜索指南</v>
       </c>
       <c r="C78" t="str">
-        <v>關閉使用者指南</v>
+        <v>搜尋指南</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B79" t="str">
-        <v>加载中…</v>
+        <v>搜索用户指南</v>
       </c>
       <c r="C79" t="str">
-        <v>載入中…</v>
+        <v>搜尋使用者指南</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Previous match</v>
       </c>
       <c r="B80" t="str">
-        <v>无法加载用户指南。</v>
+        <v>上一个匹配项</v>
       </c>
       <c r="C80" t="str">
-        <v>無法載入使用者指南。</v>
+        <v>上一個相符項目</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>None</v>
+        <v>Next match</v>
       </c>
       <c r="B81" t="str">
-        <v>无</v>
+        <v>下一个匹配项</v>
       </c>
       <c r="C81" t="str">
-        <v>無</v>
+        <v>下一個相符項目</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Close user guide</v>
       </c>
       <c r="B82" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>关闭用户指南</v>
       </c>
       <c r="C82" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>關閉使用者指南</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Based on</v>
+        <v>Loading…</v>
       </c>
       <c r="B83" t="str">
-        <v>基于</v>
+        <v>加载中…</v>
       </c>
       <c r="C83" t="str">
-        <v>基於</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B84" t="str">
-        <v>演示实现</v>
+        <v>无法加载用户指南。</v>
       </c>
       <c r="C84" t="str">
-        <v>示範實作</v>
+        <v>無法載入使用者指南。</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Validating…</v>
+        <v>None</v>
       </c>
       <c r="B85" t="str">
-        <v>正在验证…</v>
+        <v>无</v>
       </c>
       <c r="C85" t="str">
-        <v>驗證中…</v>
+        <v>無</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Save ICC profile</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B86" t="str">
-        <v>保存 ICC 配置文件</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C86" t="str">
-        <v>儲存 ICC 設定檔</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Based on</v>
       </c>
       <c r="B87" t="str">
-        <v>● 已修改 — 尚未保存</v>
+        <v>基于</v>
       </c>
       <c r="C87" t="str">
-        <v>● 已修改 — 尚未儲存</v>
+        <v>基於</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Profiles</v>
+        <v>demo implementation</v>
       </c>
       <c r="B88" t="str">
-        <v>配置文件</v>
+        <v>演示实现</v>
       </c>
       <c r="C88" t="str">
-        <v>設定檔</v>
+        <v>示範實作</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Show profile pool</v>
+        <v>Validating…</v>
       </c>
       <c r="B89" t="str">
-        <v>显示配置文件池</v>
+        <v>正在验证…</v>
       </c>
       <c r="C89" t="str">
-        <v>顯示設定檔集區</v>
+        <v>驗證中…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Collapse</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B90" t="str">
-        <v>收起</v>
+        <v>保存 ICC 配置文件</v>
       </c>
       <c r="C90" t="str">
-        <v>收合</v>
+        <v>儲存 ICC 設定檔</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Load Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B91" t="str">
-        <v>加载配置文件</v>
+        <v>● 已修改 — 尚未保存</v>
       </c>
       <c r="C91" t="str">
-        <v>載入設定檔</v>
+        <v>● 已修改 — 尚未儲存</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Remove</v>
+        <v>Profiles</v>
       </c>
       <c r="B92" t="str">
-        <v>移除</v>
+        <v>配置文件</v>
       </c>
       <c r="C92" t="str">
-        <v>移除</v>
+        <v>設定檔</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B93" t="str">
-        <v>将 ICC 配置文件拖放到此处</v>
+        <v>显示配置文件池</v>
       </c>
       <c r="C93" t="str">
-        <v>將 ICC 設定檔拖放到此處</v>
+        <v>顯示設定檔集區</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Collapse</v>
       </c>
       <c r="B94" t="str">
-        <v>或拖入图像 (TIFF/PNG/JPEG) 以提取其嵌入的配置文件 — 文件保留在您的设备上。</v>
+        <v>收起</v>
       </c>
       <c r="C94" t="str">
-        <v>或拖入影像 (TIFF/PNG/JPEG) 以擷取其內嵌設定檔 — 檔案會保留在您的裝置上。</v>
+        <v>收合</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>New from .cube</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B95" t="str">
-        <v>从 .cube 新建</v>
+        <v>加载配置文件</v>
       </c>
       <c r="C95" t="str">
-        <v>從 .cube 新建</v>
+        <v>載入設定檔</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sort by name</v>
+        <v>Remove</v>
       </c>
       <c r="B96" t="str">
-        <v>按名称排序</v>
+        <v>移除</v>
       </c>
       <c r="C96" t="str">
-        <v>依名稱排序</v>
+        <v>移除</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A–Z</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B97" t="str">
-        <v>A–Z</v>
+        <v>将 ICC 配置文件拖放到此处</v>
       </c>
       <c r="C97" t="str">
-        <v>A–Z</v>
+        <v>將 ICC 設定檔拖放到此處</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>New profile from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B98" t="str">
-        <v>从 .cube 新建配置文件</v>
+        <v>或拖入图像 (TIFF/PNG/JPEG) 以提取其嵌入的配置文件 — 文件保留在您的设备上。</v>
       </c>
       <c r="C98" t="str">
-        <v>從 .cube 新建設定檔</v>
+        <v>或拖入影像 (TIFF/PNG/JPEG) 以擷取其內嵌設定檔 — 檔案會保留在您的裝置上。</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New from .cube</v>
       </c>
       <c r="B99" t="str">
-        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并下载。</v>
+        <v>从 .cube 新建</v>
       </c>
       <c r="C99" t="str">
-        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並下載。</v>
+        <v>從 .cube 新建</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Choose .cube file</v>
+        <v>Sort by name</v>
       </c>
       <c r="B100" t="str">
-        <v>选择 .cube 文件</v>
+        <v>按名称排序</v>
       </c>
       <c r="C100" t="str">
-        <v>選擇 .cube 檔案</v>
+        <v>依名稱排序</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>A–Z</v>
+      </c>
+      <c r="B101" t="str">
+        <v>A–Z</v>
+      </c>
+      <c r="C101" t="str">
+        <v>A–Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>New profile from .cube</v>
+      </c>
+      <c r="B102" t="str">
+        <v>从 .cube 新建配置文件</v>
+      </c>
+      <c r="C102" t="str">
+        <v>從 .cube 新建設定檔</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+      </c>
+      <c r="B103" t="str">
+        <v>从 Adobe/Resolve 的 .cube 3D LUT 创建 ICC DeviceLink。结果会添加到您的池中并下载。</v>
+      </c>
+      <c r="C103" t="str">
+        <v>從 Adobe/Resolve 的 .cube 3D LUT 建立 ICC DeviceLink。結果會加入您的集區並下載。</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B104" t="str">
+        <v>选择 .cube 文件</v>
+      </c>
+      <c r="C104" t="str">
+        <v>選擇 .cube 檔案</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B105" t="str">
         <v>或拖放到此处，或在下方粘贴</v>
       </c>
-      <c r="C101" t="str">
+      <c r="C105" t="str">
         <v>或拖放到此處，或在下方貼上</v>
       </c>
     </row>
-    <row r="102" xml:space="preserve">
-      <c r="A102" t="str" xml:space="preserve">
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B102" t="str" xml:space="preserve">
+      <c r="B106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="C102" t="str" xml:space="preserve">
+      <c r="C106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B103" t="str">
-        <v>取消</v>
-      </c>
-      <c r="C103" t="str">
-        <v>取消</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Create DeviceLink</v>
-      </c>
-      <c r="B104" t="str">
-        <v>创建 DeviceLink</v>
-      </c>
-      <c r="C104" t="str">
-        <v>建立 DeviceLink</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Creating…</v>
-      </c>
-      <c r="B105" t="str">
-        <v>正在创建…</v>
-      </c>
-      <c r="C105" t="str">
-        <v>正在建立…</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Could not read that file.</v>
-      </c>
-      <c r="B106" t="str">
-        <v>无法读取该文件。</v>
-      </c>
-      <c r="C106" t="str">
-        <v>無法讀取該檔案。</v>
-      </c>
-    </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Profile</v>
+        <v>Cancel</v>
       </c>
       <c r="B107" t="str">
-        <v>配置文件</v>
+        <v>取消</v>
       </c>
       <c r="C107" t="str">
-        <v>設定檔</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Compare</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B108" t="str">
-        <v>比较</v>
+        <v>创建 DeviceLink</v>
       </c>
       <c r="C108" t="str">
-        <v>比較</v>
+        <v>建立 DeviceLink</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Combine</v>
+        <v>Creating…</v>
       </c>
       <c r="B109" t="str">
-        <v>链接</v>
+        <v>正在创建…</v>
       </c>
       <c r="C109" t="str">
-        <v>連結</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Spectral</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B110" t="str">
-        <v>光谱</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C110" t="str">
-        <v>光譜</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Profile</v>
       </c>
       <c r="B111" t="str">
-        <v>将配置文件从池中拖到此选项卡</v>
+        <v>配置文件</v>
       </c>
       <c r="C111" t="str">
-        <v>將設定檔從集區拖到此分頁</v>
+        <v>設定檔</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Remove</v>
+        <v>Compare</v>
       </c>
       <c r="B112" t="str">
-        <v>移除</v>
+        <v>比较</v>
       </c>
       <c r="C112" t="str">
-        <v>移除</v>
+        <v>比較</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No profile selected</v>
+        <v>Combine</v>
       </c>
       <c r="B113" t="str">
-        <v>未选择配置文件</v>
+        <v>链接</v>
       </c>
       <c r="C113" t="str">
-        <v>未選擇設定檔</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Spectral</v>
       </c>
       <c r="B114" t="str">
-        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
+        <v>光谱</v>
       </c>
       <c r="C114" t="str">
-        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
+        <v>光譜</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B115" t="str">
-        <v>暂无可比较的内容</v>
+        <v>将配置文件从池中拖到此选项卡</v>
       </c>
       <c r="C115" t="str">
-        <v>尚無可比較的內容</v>
+        <v>將設定檔從集區拖到此分頁</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Remove</v>
       </c>
       <c r="B116" t="str">
-        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
+        <v>移除</v>
       </c>
       <c r="C116" t="str">
-        <v>將一個或多個設定檔拖到「比較」分頁。</v>
+        <v>移除</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Gamut comparison</v>
+        <v>No profile selected</v>
       </c>
       <c r="B117" t="str">
-        <v>色域比较</v>
+        <v>未选择配置文件</v>
       </c>
       <c r="C117" t="str">
-        <v>色域比較</v>
+        <v>未選擇設定檔</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B118" t="str">
-        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
+        <v>将配置文件从池中拖到“配置文件”选项卡以检查它。</v>
       </c>
       <c r="C118" t="str">
-        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
+        <v>將設定檔從集區拖到「設定檔」分頁以檢查它。</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rendering intent</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B119" t="str">
-        <v>渲染意图</v>
+        <v>暂无可比较的内容</v>
       </c>
       <c r="C119" t="str">
-        <v>轉換意圖</v>
+        <v>尚無可比較的內容</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Shell</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B120" t="str">
-        <v>外壳</v>
+        <v>将一个或多个配置文件拖到“比较”选项卡。</v>
       </c>
       <c r="C120" t="str">
-        <v>外殼</v>
+        <v>將一個或多個設定檔拖到「比較」分頁。</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Wireframe</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B121" t="str">
-        <v>线框</v>
+        <v>色域比较</v>
       </c>
       <c r="C121" t="str">
-        <v>線框</v>
+        <v>色域比較</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Axis numbers</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B122" t="str">
-        <v>轴编号</v>
+        <v>3D 色域和 2D 切片视图即将在此呈现。已累积：</v>
       </c>
       <c r="C122" t="str">
-        <v>軸編號</v>
+        <v>3D 色域與 2D 切片檢視即將在此呈現。已累積：</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B123" t="str">
-        <v>不透明度</v>
+        <v>渲染意图</v>
       </c>
       <c r="C123" t="str">
-        <v>不透明度</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Shell</v>
       </c>
       <c r="B124" t="str">
-        <v>颜色</v>
+        <v>外壳</v>
       </c>
       <c r="C124" t="str">
-        <v>色彩</v>
+        <v>外殼</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Wireframe</v>
       </c>
       <c r="B125" t="str">
-        <v>纯色</v>
+        <v>线框</v>
       </c>
       <c r="C125" t="str">
-        <v>純色</v>
+        <v>線框</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B126" t="str">
-        <v>按数值</v>
+        <v>轴编号</v>
       </c>
       <c r="C126" t="str">
-        <v>依數值</v>
+        <v>軸編號</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Opacity</v>
       </c>
       <c r="B127" t="str">
-        <v>按色相</v>
+        <v>不透明度</v>
       </c>
       <c r="C127" t="str">
-        <v>依色相</v>
+        <v>不透明度</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>Colour</v>
       </c>
       <c r="B128" t="str">
-        <v>旋转</v>
+        <v>颜色</v>
       </c>
       <c r="C128" t="str">
-        <v>旋轉</v>
+        <v>色彩</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>Solid</v>
       </c>
       <c r="B129" t="str">
-        <v>转盘</v>
+        <v>纯色</v>
       </c>
       <c r="C129" t="str">
-        <v>轉盤</v>
+        <v>純色</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>By value</v>
       </c>
       <c r="B130" t="str">
-        <v>轨道</v>
+        <v>按数值</v>
       </c>
       <c r="C130" t="str">
-        <v>軌道</v>
+        <v>依數值</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>By hue</v>
       </c>
       <c r="B131" t="str">
-        <v>拖动速度</v>
+        <v>按色相</v>
       </c>
       <c r="C131" t="str">
-        <v>拖曳速度</v>
+        <v>依色相</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Rotation</v>
       </c>
       <c r="B132" t="str">
-        <v>翻滚</v>
+        <v>旋转</v>
       </c>
       <c r="C132" t="str">
-        <v>翻滾</v>
+        <v>旋轉</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B133" t="str">
-        <v>翻滚速度</v>
+        <v>转盘</v>
       </c>
       <c r="C133" t="str">
-        <v>翻滾速度</v>
+        <v>轉盤</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Orbit</v>
       </c>
       <c r="B134" t="str">
-        <v>正在构建色域…</v>
+        <v>轨道</v>
       </c>
       <c r="C134" t="str">
-        <v>正在建構色域…</v>
+        <v>軌道</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Drag speed</v>
       </c>
       <c r="B135" t="str">
-        <v>无色域</v>
+        <v>拖动速度</v>
       </c>
       <c r="C135" t="str">
-        <v>無色域</v>
+        <v>拖曳速度</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Roll</v>
       </c>
       <c r="B136" t="str">
-        <v>显示/隐藏</v>
+        <v>翻滚</v>
       </c>
       <c r="C136" t="str">
-        <v>顯示/隱藏</v>
+        <v>翻滾</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>Roll speed</v>
       </c>
       <c r="B137" t="str">
-        <v>3D 色域外壳</v>
+        <v>翻滚速度</v>
       </c>
       <c r="C137" t="str">
-        <v>3D 色域外殼</v>
+        <v>翻滾速度</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B138" t="str">
-        <v>2D 色域切片</v>
+        <v>正在构建色域…</v>
       </c>
       <c r="C138" t="str">
-        <v>2D 色域切片</v>
+        <v>正在建構色域…</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>no gamut</v>
       </c>
       <c r="B139" t="str">
-        <v>平面</v>
+        <v>无色域</v>
       </c>
       <c r="C139" t="str">
-        <v>平面</v>
+        <v>無色域</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>Show / hide</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>显示/隐藏</v>
       </c>
       <c r="C140" t="str">
-        <v>L*</v>
+        <v>顯示/隱藏</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>3D 色域外壳</v>
       </c>
       <c r="C141" t="str">
-        <v>a*</v>
+        <v>3D 色域外殼</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>2D 色域切片</v>
       </c>
       <c r="C142" t="str">
-        <v>b*</v>
+        <v>2D 色域切片</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>Plane</v>
       </c>
       <c r="B143" t="str">
-        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
+        <v>平面</v>
       </c>
       <c r="C143" t="str">
-        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
+        <v>平面</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>L*</v>
       </c>
       <c r="B144" t="str">
-        <v>链接</v>
+        <v>L*</v>
       </c>
       <c r="C144" t="str">
-        <v>連結</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>a*</v>
       </c>
       <c r="B145" t="str">
-        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
+        <v>a*</v>
       </c>
       <c r="C145" t="str">
-        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>b*</v>
       </c>
       <c r="B146" t="str">
-        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
+        <v>b*</v>
       </c>
       <c r="C146" t="str">
-        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Observer Change</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B147" t="str">
-        <v>V4 显示器生成器</v>
+        <v>所选配置文件中没有可用于导出色域的设备→PCS 变换。</v>
       </c>
       <c r="C147" t="str">
-        <v>V4 顯示器產生器</v>
+        <v>所選設定檔中沒有可用於推導色域的裝置→PCS 轉換。</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Linking</v>
       </c>
       <c r="B148" t="str">
-        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
+        <v>链接</v>
       </c>
       <c r="C148" t="str">
-        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
+        <v>連結</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B149" t="str">
-        <v>V5 RGB 显示器</v>
+        <v>DeviceLink 生成和多配置文件变换将在后续阶段推出。</v>
       </c>
       <c r="C149" t="str">
-        <v>V5 RGB 顯示器</v>
+        <v>DeviceLink 產生與多設定檔轉換將在後續階段推出。</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B150" t="str">
-        <v>拖入显示器配置文件</v>
+        <v>更多链接生成器 (DeviceLink, …) 将在此推出。</v>
       </c>
       <c r="C150" t="str">
-        <v>拖入顯示器設定檔</v>
+        <v>更多連結產生器 (DeviceLink, …) 將在此推出。</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Observer Change</v>
       </c>
       <c r="B151" t="str">
-        <v>V5 观察者 (PCC)</v>
+        <v>V4 显示器生成器</v>
       </c>
       <c r="C151" t="str">
-        <v>V5 觀察者 (PCC)</v>
+        <v>V4 顯示器產生器</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B152" t="str">
-        <v>拖入观察者配置文件</v>
+        <v>将 V5 RGB 显示器配置文件和 V5 观察者配置文件拖到此处，以构建 V4 显示器配置文件。</v>
       </c>
       <c r="C152" t="str">
-        <v>拖入觀察者設定檔</v>
+        <v>將 V5 RGB 顯示器設定檔與 V5 觀察者設定檔拖到此處，以建立 V4 顯示器設定檔。</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B153" t="str">
-        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
+        <v>V5 RGB 显示器</v>
       </c>
       <c r="C153" t="str">
-        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
+        <v>V5 RGB 顯示器</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B154" t="str">
-        <v>创建 V4 显示器配置文件</v>
+        <v>拖入显示器配置文件</v>
       </c>
       <c r="C154" t="str">
-        <v>建立 V4 顯示器設定檔</v>
+        <v>拖入顯示器設定檔</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B155" t="str">
-        <v>配置文件名称</v>
+        <v>V5 观察者 (PCC)</v>
       </c>
       <c r="C155" t="str">
-        <v>設定檔名稱</v>
+        <v>V5 觀察者 (PCC)</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B156" t="str">
-        <v>创建</v>
+        <v>拖入观察者配置文件</v>
       </c>
       <c r="C156" t="str">
-        <v>建立</v>
+        <v>拖入觀察者設定檔</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B157" t="str">
-        <v>正在创建…</v>
+        <v>已忽略一个既不是 V5 RGB 显示器也不是观察者的配置文件。</v>
       </c>
       <c r="C157" t="str">
-        <v>正在建立…</v>
+        <v>已忽略一個既非 V5 RGB 顯示器也非觀察者的設定檔。</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B158" t="str">
-        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
+        <v>创建 V4 显示器配置文件</v>
       </c>
       <c r="C158" t="str">
-        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
+        <v>建立 V4 顯示器設定檔</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Link Pipeline</v>
+        <v>Profile name</v>
       </c>
       <c r="B159" t="str">
-        <v>链接流水线</v>
+        <v>配置文件名称</v>
       </c>
       <c r="C159" t="str">
-        <v>連結管線</v>
+        <v>設定檔名稱</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Create</v>
       </c>
       <c r="B160" t="str">
-        <v>构建一条配置文件链，然后生成 DeviceLink、转换图像，或通过它转换色彩数据集。</v>
+        <v>创建</v>
       </c>
       <c r="C160" t="str">
-        <v>建立一條描述檔鏈，然後產生 DeviceLink、轉換影像，或透過它轉換色彩資料集。</v>
+        <v>建立</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Done</v>
+        <v>Making…</v>
       </c>
       <c r="B161" t="str">
-        <v>完成</v>
+        <v>正在创建…</v>
       </c>
       <c r="C161" t="str">
-        <v>完成</v>
+        <v>正在建立…</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B162" t="str">
-        <v>拖放图像以进行转换（TIFF/PNG/JPEG）</v>
+        <v>已创建“{name}” — 已添加到池和此选项卡。</v>
       </c>
       <c r="C162" t="str">
-        <v>拖放影像以進行轉換（TIFF/PNG/JPEG）</v>
+        <v>已建立「{name}」 — 已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Checking image…</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B163" t="str">
-        <v>正在检查图像…</v>
+        <v>链接流水线</v>
       </c>
       <c r="C163" t="str">
-        <v>正在檢查影像…</v>
+        <v>連結管線</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B164" t="str">
-        <v>不受支持的图像格式（TIFF、PNG 或 JPEG）。</v>
+        <v>构建一条配置文件链，然后生成 DeviceLink、转换图像，或通过它转换色彩数据集。</v>
       </c>
       <c r="C164" t="str">
-        <v>不受支援的影像格式（TIFF、PNG 或 JPEG）。</v>
+        <v>建立一條描述檔鏈，然後產生 DeviceLink、轉換影像，或透過它轉換色彩資料集。</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Done</v>
       </c>
       <c r="B165" t="str">
-        <v>图像过大（{mp} MP；上限 {max} MP）。</v>
+        <v>完成</v>
       </c>
       <c r="C165" t="str">
-        <v>影像過大（{mp} MP；上限 {max} MP）。</v>
+        <v>完成</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transform Image</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B166" t="str">
-        <v>转换图像</v>
+        <v>拖放图像以进行转换（TIFF/PNG/JPEG）</v>
       </c>
       <c r="C166" t="str">
-        <v>轉換影像</v>
+        <v>拖放影像以進行轉換（TIFF/PNG/JPEG）</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Transforming…</v>
+        <v>Checking image…</v>
       </c>
       <c r="B167" t="str">
-        <v>正在转换…</v>
+        <v>正在检查图像…</v>
       </c>
       <c r="C167" t="str">
-        <v>正在轉換…</v>
+        <v>正在檢查影像…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B168" t="str">
-        <v>拖放配置文件以开始链条</v>
+        <v>不受支持的图像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C168" t="str">
-        <v>拖放描述檔以開始鏈條</v>
+        <v>不受支援的影像格式（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>removed</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B169" t="str">
-        <v>已移除</v>
+        <v>图像过大（{mp} MP；上限 {max} MP）。</v>
       </c>
       <c r="C169" t="str">
-        <v>已移除</v>
+        <v>影像過大（{mp} MP；上限 {max} MP）。</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move earlier</v>
+        <v>Transform Image</v>
       </c>
       <c r="B170" t="str">
-        <v>前移</v>
+        <v>转换图像</v>
       </c>
       <c r="C170" t="str">
-        <v>前移</v>
+        <v>轉換影像</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move later</v>
+        <v>Transforming…</v>
       </c>
       <c r="B171" t="str">
-        <v>后移</v>
+        <v>正在转换…</v>
       </c>
       <c r="C171" t="str">
-        <v>後移</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move up</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B172" t="str">
-        <v>上移</v>
+        <v>拖放配置文件以开始链条</v>
       </c>
       <c r="C172" t="str">
-        <v>上移</v>
+        <v>拖放描述檔以開始鏈條</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move down</v>
+        <v>removed</v>
       </c>
       <c r="B173" t="str">
-        <v>下移</v>
+        <v>已移除</v>
       </c>
       <c r="C173" t="str">
-        <v>下移</v>
+        <v>已移除</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move earlier</v>
       </c>
       <c r="B174" t="str">
-        <v>渲染意图（全部）</v>
+        <v>前移</v>
       </c>
       <c r="C174" t="str">
-        <v>演算意圖（全部）</v>
+        <v>前移</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Move later</v>
       </c>
       <c r="B175" t="str">
-        <v>此转换的渲染意图</v>
+        <v>后移</v>
       </c>
       <c r="C175" t="str">
-        <v>此轉換的演算意圖</v>
+        <v>後移</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Move up</v>
       </c>
       <c r="B176" t="str">
-        <v>各转换使用了不同的渲染意图</v>
+        <v>上移</v>
       </c>
       <c r="C176" t="str">
-        <v>各轉換使用了不同的演算意圖</v>
+        <v>上移</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Move down</v>
       </c>
       <c r="B177" t="str">
-        <v>翻转链条方向（反转首个转换，并影响整条链）</v>
+        <v>下移</v>
       </c>
       <c r="C177" t="str">
-        <v>翻轉鏈條方向（反轉首個轉換，並影響整條鏈）</v>
+        <v>下移</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B178" t="str">
-        <v>链条中的某个配置文件已从池中移除——请将其移除以继续。</v>
+        <v>渲染意图（全部）</v>
       </c>
       <c r="C178" t="str">
-        <v>鏈條中的某個描述檔已從集區中移除——請將其移除以繼續。</v>
+        <v>演算意圖（全部）</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Chain</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B179" t="str">
-        <v>链条</v>
+        <v>此转换的渲染意图</v>
       </c>
       <c r="C179" t="str">
-        <v>鏈條</v>
+        <v>此轉換的演算意圖</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B180" t="str">
-        <v>无法分析该链条。</v>
+        <v>各转换使用了不同的渲染意图</v>
       </c>
       <c r="C180" t="str">
-        <v>無法分析該鏈條。</v>
+        <v>各轉換使用了不同的演算意圖</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Checking chain…</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B181" t="str">
-        <v>正在检查链条…</v>
+        <v>翻转链条方向（反转首个转换，并影响整条链）</v>
       </c>
       <c r="C181" t="str">
-        <v>正在檢查鏈條…</v>
+        <v>翻轉鏈條方向（反轉首個轉換，並影響整條鏈）</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B182" t="str">
-        <v>链条未能衔接（{detail}）。</v>
+        <v>链条中的某个配置文件已从池中移除——请将其移除以继续。</v>
       </c>
       <c r="C182" t="str">
-        <v>鏈條未能銜接（{detail}）。</v>
+        <v>鏈條中的某個描述檔已從集區中移除——請將其移除以繼續。</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Chain</v>
       </c>
       <c r="B183" t="str">
-        <v>配置文件 {n} 未能与上一阶段衔接（{detail}）。</v>
+        <v>链条</v>
       </c>
       <c r="C183" t="str">
-        <v>描述檔 {n} 未能與上一階段銜接（{detail}）。</v>
+        <v>鏈條</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B184" t="str">
-        <v>请先修复链条，再处理图像</v>
+        <v>无法分析该链条。</v>
       </c>
       <c r="C184" t="str">
-        <v>請先修正鏈條，再處理影像</v>
+        <v>無法分析該鏈條。</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Clear</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B185" t="str">
-        <v>清除</v>
+        <v>正在检查链条…</v>
       </c>
       <c r="C185" t="str">
-        <v>清除</v>
+        <v>正在檢查鏈條…</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Make DeviceLink</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B186" t="str">
-        <v>生成 DeviceLink</v>
+        <v>链条未能衔接（{detail}）。</v>
       </c>
       <c r="C186" t="str">
-        <v>產生 DeviceLink</v>
+        <v>鏈條未能銜接（{detail}）。</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>DeviceLink name</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>DeviceLink 名称</v>
+        <v>配置文件 {n} 未能与上一阶段衔接（{detail}）。</v>
       </c>
       <c r="C187" t="str">
-        <v>DeviceLink 名稱</v>
+        <v>描述檔 {n} 未能與上一階段銜接（{detail}）。</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Making…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B188" t="str">
-        <v>正在生成…</v>
+        <v>请先修复链条，再处理图像</v>
       </c>
       <c r="C188" t="str">
-        <v>正在產生…</v>
+        <v>請先修正鏈條，再處理影像</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Clear</v>
       </c>
       <c r="B189" t="str">
-        <v>已创建“{name}”——已添加到池和此标签页。</v>
+        <v>清除</v>
       </c>
       <c r="C189" t="str">
-        <v>已建立「{name}」——已加入集區與此分頁。</v>
+        <v>清除</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B190" t="str">
-        <v>拖放 {src} 图像以转换为 {dst}——结果将下载，不会被存储。</v>
+        <v>生成 DeviceLink</v>
       </c>
       <c r="C190" t="str">
-        <v>拖放 {src} 影像以轉換為 {dst}——結果將下載，不會被儲存。</v>
+        <v>產生 DeviceLink</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Build a chain to process images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B191" t="str">
-        <v>构建链条以处理图像</v>
+        <v>DeviceLink 名称</v>
       </c>
       <c r="C191" t="str">
-        <v>建立鏈條以處理影像</v>
+        <v>DeviceLink 名稱</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Making…</v>
       </c>
       <c r="B192" t="str">
-        <v>此链条的首尾并非图像色彩空间</v>
+        <v>正在生成…</v>
       </c>
       <c r="C192" t="str">
-        <v>此鏈條的首尾並非影像色彩空間</v>
+        <v>正在產生…</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B193" t="str">
-        <v>已保存转换后的图像。</v>
+        <v>已创建“{name}”——已添加到池和此标签页。</v>
       </c>
       <c r="C193" t="str">
-        <v>已儲存轉換後的影像。</v>
+        <v>已建立「{name}」——已加入集區與此分頁。</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B194" t="str">
-        <v>拖放色彩数据集（CGATS/CSV/CxF/JSON）</v>
+        <v>拖放 {src} 图像以转换为 {dst}——结果将下载，不会被存储。</v>
       </c>
       <c r="C194" t="str">
-        <v>拖放色彩資料集（CGATS/CSV/CxF/JSON）</v>
+        <v>拖放 {src} 影像以轉換為 {dst}——結果將下載，不會被儲存。</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Could not read that file.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B195" t="str">
-        <v>无法读取该文件。</v>
+        <v>构建链条以处理图像</v>
       </c>
       <c r="C195" t="str">
-        <v>無法讀取該檔案。</v>
+        <v>建立鏈條以處理影像</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Data file too large.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B196" t="str">
-        <v>数据文件过大。</v>
+        <v>此链条的首尾并非图像色彩空间</v>
       </c>
       <c r="C196" t="str">
-        <v>資料檔案過大。</v>
+        <v>此鏈條的首尾並非影像色彩空間</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transform Data</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B197" t="str">
-        <v>转换数据</v>
+        <v>已保存转换后的图像。</v>
       </c>
       <c r="C197" t="str">
-        <v>轉換資料</v>
+        <v>已儲存轉換後的影像。</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Transforming…</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B198" t="str">
-        <v>正在转换…</v>
+        <v>拖放色彩数据集（CGATS/CSV/CxF/JSON）</v>
       </c>
       <c r="C198" t="str">
-        <v>正在轉換…</v>
+        <v>拖放色彩資料集（CGATS/CSV/CxF/JSON）</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Prefer</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B199" t="str">
-        <v>偏好</v>
+        <v>无法读取该文件。</v>
       </c>
       <c r="C199" t="str">
-        <v>偏好</v>
+        <v>無法讀取該檔案。</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Observer</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B200" t="str">
-        <v>观察者</v>
+        <v>数据文件过大。</v>
       </c>
       <c r="C200" t="str">
-        <v>觀察者</v>
+        <v>資料檔案過大。</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Illuminant</v>
+        <v>Transform Data</v>
       </c>
       <c r="B201" t="str">
-        <v>光源</v>
+        <v>转换数据</v>
       </c>
       <c r="C201" t="str">
-        <v>光源</v>
+        <v>轉換資料</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Condition</v>
+        <v>Transforming…</v>
       </c>
       <c r="B202" t="str">
-        <v>条件</v>
+        <v>正在转换…</v>
       </c>
       <c r="C202" t="str">
-        <v>條件</v>
+        <v>正在轉換…</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Prefer</v>
       </c>
       <c r="B203" t="str">
-        <v>过滤 {n} 个重复项</v>
+        <v>偏好</v>
       </c>
       <c r="C203" t="str">
-        <v>篩選 {n} 個重複項</v>
+        <v>偏好</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>median</v>
+        <v>Observer</v>
       </c>
       <c r="B204" t="str">
-        <v>中位数</v>
+        <v>观察者</v>
       </c>
       <c r="C204" t="str">
-        <v>中位數</v>
+        <v>觀察者</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>mean</v>
+        <v>Illuminant</v>
       </c>
       <c r="B205" t="str">
-        <v>平均值</v>
+        <v>光源</v>
       </c>
       <c r="C205" t="str">
-        <v>平均值</v>
+        <v>光源</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>patches</v>
+        <v>Condition</v>
       </c>
       <c r="B206" t="str">
-        <v>色块</v>
+        <v>条件</v>
       </c>
       <c r="C206" t="str">
-        <v>色塊</v>
+        <v>條件</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>{n} duplicates</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B207" t="str">
-        <v>{n} 个重复项</v>
+        <v>过滤 {n} 个重复项</v>
       </c>
       <c r="C207" t="str">
-        <v>{n} 個重複項</v>
+        <v>篩選 {n} 個重複項</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Transform result</v>
+        <v>median</v>
       </c>
       <c r="B208" t="str">
-        <v>转换结果</v>
+        <v>中位数</v>
       </c>
       <c r="C208" t="str">
-        <v>轉換結果</v>
+        <v>中位數</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>mean</v>
       </c>
       <c r="B209" t="str">
-        <v>{src} → {dst} · {n} 个色块</v>
+        <v>平均值</v>
       </c>
       <c r="C209" t="str">
-        <v>{src} → {dst} · {n} 個色塊</v>
+        <v>平均值</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>patches</v>
       </c>
       <c r="B210" t="str">
-        <v>显示前 {shown} 项，共 {total} 项——保存将写入全部数据。</v>
+        <v>色块</v>
       </c>
       <c r="C210" t="str">
-        <v>顯示前 {shown} 項，共 {total} 項——儲存將寫入全部資料。</v>
+        <v>色塊</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save as</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B211" t="str">
-        <v>另存为</v>
+        <v>{n} 个重复项</v>
       </c>
       <c r="C211" t="str">
-        <v>另存新檔</v>
+        <v>{n} 個重複項</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Save</v>
+        <v>Transform result</v>
       </c>
       <c r="B212" t="str">
-        <v>保存</v>
+        <v>转换结果</v>
       </c>
       <c r="C212" t="str">
-        <v>儲存</v>
+        <v>轉換結果</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Invert Transform</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B213" t="str">
-        <v>反向转换</v>
+        <v>{src} → {dst} · {n} 个色块</v>
       </c>
       <c r="C213" t="str">
-        <v>反向轉換</v>
+        <v>{src} → {dst} · {n} 個色塊</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Inverting…</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B214" t="str">
-        <v>正在反向计算…</v>
+        <v>显示前 {shown} 项，共 {total} 项——保存将写入全部数据。</v>
       </c>
       <c r="C214" t="str">
-        <v>正在反向計算…</v>
+        <v>顯示前 {shown} 項，共 {total} 項——儲存將寫入全部資料。</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert</v>
+        <v>Save as</v>
       </c>
       <c r="B215" t="str">
-        <v>反转</v>
+        <v>另存为</v>
       </c>
       <c r="C215" t="str">
-        <v>反轉</v>
+        <v>另存新檔</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>last stage</v>
+        <v>Save</v>
       </c>
       <c r="B216" t="str">
-        <v>最后阶段</v>
+        <v>保存</v>
       </c>
       <c r="C216" t="str">
-        <v>最後階段</v>
+        <v>儲存</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>first stage</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B217" t="str">
-        <v>第一阶段</v>
+        <v>反向转换</v>
       </c>
       <c r="C217" t="str">
-        <v>第一階段</v>
+        <v>反向轉換</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>Inverting…</v>
       </c>
       <c r="B218" t="str">
-        <v>输入数据为 {in} → 搜索 {out}</v>
+        <v>正在反向计算…</v>
       </c>
       <c r="C218" t="str">
-        <v>輸入資料為 {in} → 搜尋 {out}</v>
+        <v>正在反向計算…</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Invert</v>
       </c>
       <c r="B219" t="str">
-        <v>反转需要 2–3 个配置文件组成的链条</v>
+        <v>反转</v>
       </c>
       <c r="C219" t="str">
-        <v>反轉需要 2–3 個描述檔組成的鏈條</v>
+        <v>反轉</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>last stage</v>
       </c>
       <c r="B220" t="str">
-        <v>数据集必须为 {in}；反向搜索将生成 {out}，并附带每个色块的可逆性代价。</v>
+        <v>最后阶段</v>
       </c>
       <c r="C220" t="str">
-        <v>資料集必須為 {in}；反向搜尋將產生 {out}，並附帶每個色塊的可逆性代價。</v>
+        <v>最後階段</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>ΔE cost</v>
+        <v>first stage</v>
       </c>
       <c r="B221" t="str">
-        <v>ΔE 代价</v>
+        <v>第一阶段</v>
       </c>
       <c r="C221" t="str">
-        <v>ΔE 代價</v>
+        <v>第一階段</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B222" t="str">
-        <v>此图像嵌入了 ICC 配置文件。</v>
+        <v>输入数据为 {in} → 搜索 {out}</v>
       </c>
       <c r="C222" t="str">
-        <v>此影像內嵌了 ICC 描述檔。</v>
+        <v>輸入資料為 {in} → 搜尋 {out}</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B223" t="str">
-        <v>提取并添加到链条</v>
+        <v>反转需要 2–3 个配置文件组成的链条</v>
       </c>
       <c r="C223" t="str">
-        <v>擷取並加入鏈條</v>
+        <v>反轉需要 2–3 個描述檔組成的鏈條</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Extracting…</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B224" t="str">
-        <v>正在提取…</v>
+        <v>数据集必须为 {in}；反向搜索将生成 {out}，并附带每个色块的可逆性代价。</v>
       </c>
       <c r="C224" t="str">
-        <v>正在擷取…</v>
+        <v>資料集必須為 {in}；反向搜尋將產生 {out}，並附帶每個色塊的可逆性代價。</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Dismiss</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B225" t="str">
-        <v>忽略</v>
+        <v>ΔE 代价</v>
       </c>
       <c r="C225" t="str">
-        <v>忽略</v>
+        <v>ΔE 代價</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B226" t="str">
-        <v>已提取嵌入的配置文件——已添加到池中并置于链条首位。</v>
+        <v>此图像嵌入了 ICC 配置文件。</v>
       </c>
       <c r="C226" t="str">
-        <v>已擷取內嵌的描述檔——已加入集區並置於鏈條首位。</v>
+        <v>此影像內嵌了 ICC 描述檔。</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Image output options</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B227" t="str">
-        <v>图像输出选项</v>
+        <v>提取并添加到链条</v>
       </c>
       <c r="C227" t="str">
-        <v>影像輸出選項</v>
+        <v>擷取並加入鏈條</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Encoding</v>
+        <v>Extracting…</v>
       </c>
       <c r="B228" t="str">
-        <v>编码</v>
+        <v>正在提取…</v>
       </c>
       <c r="C228" t="str">
-        <v>編碼</v>
+        <v>正在擷取…</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Same as source</v>
+        <v>Dismiss</v>
       </c>
       <c r="B229" t="str">
-        <v>与源相同</v>
+        <v>忽略</v>
       </c>
       <c r="C229" t="str">
-        <v>與來源相同</v>
+        <v>忽略</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>8-bit</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B230" t="str">
-        <v>8 位</v>
+        <v>已提取嵌入的配置文件——已添加到池中并置于链条首位。</v>
       </c>
       <c r="C230" t="str">
-        <v>8 位元</v>
+        <v>已擷取內嵌的描述檔——已加入集區並置於鏈條首位。</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>16-bit</v>
+        <v>Image output options</v>
       </c>
       <c r="B231" t="str">
-        <v>16 位</v>
+        <v>图像输出选项</v>
       </c>
       <c r="C231" t="str">
-        <v>16 位元</v>
+        <v>影像輸出選項</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Float (32-bit)</v>
+        <v>Encoding</v>
       </c>
       <c r="B232" t="str">
-        <v>浮点（32 位）</v>
+        <v>编码</v>
       </c>
       <c r="C232" t="str">
-        <v>浮點（32 位元）</v>
+        <v>編碼</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Compression</v>
+        <v>Same as source</v>
       </c>
       <c r="B233" t="str">
-        <v>压缩</v>
+        <v>与源相同</v>
       </c>
       <c r="C233" t="str">
-        <v>壓縮</v>
+        <v>與來源相同</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>None</v>
+        <v>8-bit</v>
       </c>
       <c r="B234" t="str">
-        <v>无</v>
+        <v>8 位</v>
       </c>
       <c r="C234" t="str">
-        <v>無</v>
+        <v>8 位元</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Planar</v>
+        <v>16-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>平面格式</v>
+        <v>16 位</v>
       </c>
       <c r="C235" t="str">
-        <v>平面格式</v>
+        <v>16 位元</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Composite</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B236" t="str">
-        <v>交错</v>
+        <v>浮点（32 位）</v>
       </c>
       <c r="C236" t="str">
-        <v>交錯</v>
+        <v>浮點（32 位元）</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Separated</v>
+        <v>Compression</v>
       </c>
       <c r="B237" t="str">
-        <v>分离</v>
+        <v>压缩</v>
       </c>
       <c r="C237" t="str">
-        <v>分離</v>
+        <v>壓縮</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>CMM interpolation</v>
+        <v>None</v>
       </c>
       <c r="B238" t="str">
-        <v>CMM 插值</v>
+        <v>无</v>
       </c>
       <c r="C238" t="str">
-        <v>CMM 內插</v>
+        <v>無</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Tetrahedral</v>
+        <v>Planar</v>
       </c>
       <c r="B239" t="str">
-        <v>四面体</v>
+        <v>平面格式</v>
       </c>
       <c r="C239" t="str">
-        <v>四面體</v>
+        <v>平面格式</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Linear</v>
+        <v>Composite</v>
       </c>
       <c r="B240" t="str">
-        <v>线性</v>
+        <v>交错</v>
       </c>
       <c r="C240" t="str">
-        <v>線性</v>
+        <v>交錯</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Embed ICC</v>
+        <v>Separated</v>
       </c>
       <c r="B241" t="str">
-        <v>嵌入 ICC</v>
+        <v>分离</v>
       </c>
       <c r="C241" t="str">
-        <v>內嵌 ICC</v>
+        <v>分離</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B242" t="str">
-        <v>编码、压缩和平面格式会影响保存的 TIFF。除非设置了仅限 TIFF 的选项（浮点、LZW/ZIP、分离），否则 RGB/Gray 输出仍为 PNG。</v>
+        <v>CMM 插值</v>
       </c>
       <c r="C242" t="str">
-        <v>編碼、壓縮和平面格式會影響儲存的 TIFF。除非設定了僅限 TIFF 的選項（浮點、LZW/ZIP、分離），否則 RGB/Gray 輸出仍為 PNG。</v>
+        <v>CMM 內插</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B243" t="str">
-        <v>组装光谱 TIFF</v>
+        <v>四面体</v>
       </c>
       <c r="C243" t="str">
-        <v>組裝光譜 TIFF</v>
+        <v>四面體</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Linear</v>
       </c>
       <c r="B244" t="str">
-        <v>按通道顺序拖放单通道光谱图像，然后将其组装为一个多通道 TIFF。</v>
+        <v>线性</v>
       </c>
       <c r="C244" t="str">
-        <v>依通道順序拖放單通道光譜影像，然後將其組裝為一個多通道 TIFF。</v>
+        <v>線性</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B245" t="str">
-        <v>将光谱图像拖放到此处（或点击选择）</v>
+        <v>嵌入 ICC</v>
       </c>
       <c r="C245" t="str">
-        <v>將光譜影像拖放到此處（或點擊選擇）</v>
+        <v>內嵌 ICC</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>ch</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B246" t="str">
-        <v>通道</v>
+        <v>编码、压缩和平面格式会影响保存的 TIFF。除非设置了仅限 TIFF 的选项（浮点、LZW/ZIP、分离），否则 RGB/Gray 输出仍为 PNG。</v>
       </c>
       <c r="C246" t="str">
-        <v>通道</v>
+        <v>編碼、壓縮和平面格式會影響儲存的 TIFF。除非設定了僅限 TIFF 的選項（浮點、LZW/ZIP、分離），否則 RGB/Gray 輸出仍為 PNG。</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B247" t="str">
-        <v>组装并保存</v>
+        <v>组装光谱 TIFF</v>
       </c>
       <c r="C247" t="str">
-        <v>組裝並儲存</v>
+        <v>組裝光譜 TIFF</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembling…</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B248" t="str">
-        <v>正在组装…</v>
+        <v>按通道顺序拖放单通道光谱图像，然后将其组装为一个多通道 TIFF。</v>
       </c>
       <c r="C248" t="str">
-        <v>正在組裝…</v>
+        <v>依通道順序拖放單通道光譜影像，然後將其組裝為一個多通道 TIFF。</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B249" t="str">
-        <v>已组装 {n} 个通道。</v>
+        <v>将光谱图像拖放到此处（或点击选择）</v>
       </c>
       <c r="C249" t="str">
-        <v>已組裝 {n} 個通道。</v>
+        <v>將光譜影像拖放到此處（或點擊選擇）</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>ch</v>
       </c>
       <c r="B250" t="str">
-        <v>这些文件似乎都不是图像（TIFF、PNG 或 JPEG）。</v>
+        <v>通道</v>
       </c>
       <c r="C250" t="str">
-        <v>這些檔案似乎都不是影像（TIFF、PNG 或 JPEG）。</v>
+        <v>通道</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B251" t="str">
-        <v>取消</v>
+        <v>组装并保存</v>
       </c>
       <c r="C251" t="str">
-        <v>取消</v>
+        <v>組裝並儲存</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Assembling…</v>
       </c>
       <c r="B252" t="str">
-        <v>有 {n} 个文件未加载</v>
+        <v>正在组装…</v>
       </c>
       <c r="C252" t="str">
-        <v>有 {n} 個檔案未載入</v>
+        <v>正在組裝…</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B253" t="str">
-        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
+        <v>已组装 {n} 个通道。</v>
       </c>
       <c r="C253" t="str">
-        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
+        <v>已組裝 {n} 個通道。</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>OK</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B254" t="str">
-        <v>确定</v>
+        <v>这些文件似乎都不是图像（TIFF、PNG 或 JPEG）。</v>
       </c>
       <c r="C254" t="str">
-        <v>確定</v>
+        <v>這些檔案似乎都不是影像（TIFF、PNG 或 JPEG）。</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Cancel</v>
       </c>
       <c r="B255" t="str">
-        <v>将 ICC 配置文件拖到此处</v>
+        <v>取消</v>
       </c>
       <c r="C255" t="str">
-        <v>將 ICC 設定檔拖到此處</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>or</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B256" t="str">
-        <v>或</v>
+        <v>有 {n} 个文件未加载</v>
       </c>
       <c r="C256" t="str">
-        <v>或</v>
+        <v>有 {n} 個檔案未載入</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Choose file</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B257" t="str">
-        <v>选择文件</v>
+        <v>这些文件不是 ICC 配置文件，因此未添加到池中：</v>
       </c>
       <c r="C257" t="str">
-        <v>選擇檔案</v>
+        <v>這些檔案不是 ICC 設定檔，因此未加入集區：</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>.icc and .icm files</v>
+        <v>OK</v>
       </c>
       <c r="B258" t="str">
-        <v>.icc 和 .icm 文件</v>
+        <v>确定</v>
       </c>
       <c r="C258" t="str">
-        <v>.icc 與 .icm 檔案</v>
+        <v>確定</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Header</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B259" t="str">
-        <v>标头</v>
+        <v>将 ICC 配置文件拖到此处</v>
       </c>
       <c r="C259" t="str">
-        <v>標頭</v>
+        <v>將 ICC 設定檔拖到此處</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Tags</v>
+        <v>or</v>
       </c>
       <c r="B260" t="str">
-        <v>标签</v>
+        <v>或</v>
       </c>
       <c r="C260" t="str">
-        <v>標籤</v>
+        <v>或</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Validation</v>
+        <v>Choose file</v>
       </c>
       <c r="B261" t="str">
-        <v>验证</v>
+        <v>选择文件</v>
       </c>
       <c r="C261" t="str">
-        <v>驗證</v>
+        <v>選擇檔案</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Analysis</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B262" t="str">
-        <v>分析</v>
+        <v>.icc 和 .icm 文件</v>
       </c>
       <c r="C262" t="str">
-        <v>分析</v>
+        <v>.icc 與 .icm 檔案</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Header</v>
       </c>
       <c r="B263" t="str">
-        <v>中性轴墨量</v>
+        <v>标头</v>
       </c>
       <c r="C263" t="str">
-        <v>中性軸墨量</v>
+        <v>標頭</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Tags</v>
       </c>
       <c r="B264" t="str">
-        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
+        <v>标签</v>
       </c>
       <c r="C264" t="str">
-        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
+        <v>標籤</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Validation</v>
       </c>
       <c r="B265" t="str">
-        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
+        <v>验证</v>
       </c>
       <c r="C265" t="str">
-        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
+        <v>驗證</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Analysis</v>
       </c>
       <c r="B266" t="str">
-        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
+        <v>分析</v>
       </c>
       <c r="C266" t="str">
-        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Rendering intent</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B267" t="str">
-        <v>渲染意图</v>
+        <v>中性轴墨量</v>
       </c>
       <c r="C267" t="str">
-        <v>轉換意圖</v>
+        <v>中性軸墨量</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>% ink</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B268" t="str">
-        <v>% 墨量</v>
+        <v>随着明度从白色（L*=100）到黑色（L*=0），沿中性轴（a*=b*=0）施加的设备色料。</v>
       </c>
       <c r="C268" t="str">
-        <v>% 墨量</v>
+        <v>隨著明度從白色（L*=100）到黑色（L*=0），沿中性軸（a*=b*=0）施加的裝置色料。</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>L* out (tone)</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B269" t="str">
-        <v>L* 输出（色调）</v>
+        <v>中性轴墨量仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C269" t="str">
-        <v>L* 輸出（色調）</v>
+        <v>中性軸墨量僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Δa*b*</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B270" t="str">
-        <v>Δa*b*</v>
+        <v>此配置文件没有可采样的 B2A（PCS→设备）表。</v>
       </c>
       <c r="C270" t="str">
-        <v>Δa*b*</v>
+        <v>此設定檔沒有可取樣的 B2A（PCS→裝置）表。</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B271" t="str">
-        <v>极值比色</v>
+        <v>渲染意图</v>
       </c>
       <c r="C271" t="str">
-        <v>極值比色</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>% ink</v>
       </c>
       <c r="B272" t="str">
-        <v>配置文件复现范围的两端：承印物白、它能打印的最深黑、该黑所耗的墨量，以及每个色相达到最饱和的位置。</v>
+        <v>% 墨量</v>
       </c>
       <c r="C272" t="str">
-        <v>設定檔重現範圍的兩端：承印物白、它能列印的最深黑、該黑所耗的墨量，以及每個色相達到最飽和的位置。</v>
+        <v>% 墨量</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B273" t="str">
-        <v>白点是零色料时的颜色——即空白承印物。黑点的求法是把 PCS 黑（L*=0，a*=b*=0）送入所选 B2A 表，得到配置文件为黑色选择的墨量，再把该墨量经 A2B1 读回。总墨量（TAC）即该墨量之和。绝对比色显示承印物自身的颜色；相对比色则将其重新参照到理想白。</v>
+        <v>L* 输出（色调）</v>
       </c>
       <c r="C273" t="str">
-        <v>白點是零色料時的顏色——即空白承印物。黑點的求法是把 PCS 黑（L*=0，a*=b*=0）送入所選 B2A 表，得到設定檔為黑色選擇的墨量，再把該墨量經 A2B1 讀回。總墨量（TAC）即該墨量之和。絕對比色顯示承印物本身的顏色；相對比色則將其重新參照到理想白。</v>
+        <v>L* 輸出（色調）</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Relative</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B274" t="str">
-        <v>相对</v>
+        <v>Δa*b*</v>
       </c>
       <c r="C274" t="str">
-        <v>相對</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Absolute</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B275" t="str">
-        <v>绝对</v>
+        <v>极值比色</v>
       </c>
       <c r="C275" t="str">
-        <v>絕對</v>
+        <v>極值比色</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>White point</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B276" t="str">
-        <v>白点</v>
+        <v>配置文件复现范围的两端：承印物白、它能打印的最深黑、该黑所耗的墨量，以及每个色相达到最饱和的位置。</v>
       </c>
       <c r="C276" t="str">
-        <v>白點</v>
+        <v>設定檔重現範圍的兩端：承印物白、它能列印的最深黑、該黑所耗的墨量，以及每個色相達到最飽和的位置。</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Black point</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B277" t="str">
-        <v>黑点</v>
+        <v>白点是零色料时的颜色——即空白承印物。黑点的求法是把 PCS 黑（L*=0，a*=b*=0）送入所选 B2A 表，得到配置文件为黑色选择的墨量，再把该墨量经 A2B1 读回。总墨量（TAC）即该墨量之和。绝对比色显示承印物自身的颜色；相对比色则将其重新参照到理想白。</v>
       </c>
       <c r="C277" t="str">
-        <v>黑點</v>
+        <v>白點是零色料時的顏色——即空白承印物。黑點的求法是把 PCS 黑（L*=0，a*=b*=0）送入所選 B2A 表，得到設定檔為黑色選擇的墨量，再把該墨量經 A2B1 讀回。總墨量（TAC）即該墨量之和。絕對比色顯示承印物本身的顏色；相對比色則將其重新參照到理想白。</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Inking at black point</v>
+        <v>Relative</v>
       </c>
       <c r="B278" t="str">
-        <v>黑点处的墨量</v>
+        <v>相对</v>
       </c>
       <c r="C278" t="str">
-        <v>黑點處的墨量</v>
+        <v>相對</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TAC</v>
+        <v>Absolute</v>
       </c>
       <c r="B279" t="str">
-        <v>TAC</v>
+        <v>绝对</v>
       </c>
       <c r="C279" t="str">
-        <v>TAC</v>
+        <v>絕對</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>White point</v>
       </c>
       <c r="B280" t="str">
-        <v>此配置文件没有媒体白点标签，因此无法进行绝对比色。</v>
+        <v>白点</v>
       </c>
       <c r="C280" t="str">
-        <v>此設定檔沒有媒體白點標籤，因此無法進行絕對比色。</v>
+        <v>白點</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>Black point</v>
       </c>
       <c r="B281" t="str">
-        <v>极值比色仅适用于输出（打印机）配置文件——它假定零色料即为空白承印物。</v>
+        <v>黑点</v>
       </c>
       <c r="C281" t="str">
-        <v>極值比色僅適用於輸出（印表機）設定檔——它假定零色料即為空白承印物。</v>
+        <v>黑點</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B282" t="str">
-        <v>实地与最大彩度</v>
+        <v>黑点处的墨量</v>
       </c>
       <c r="C282" t="str">
-        <v>實地與最大彩度</v>
+        <v>黑點處的墨量</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>TAC</v>
       </c>
       <c r="B283" t="str">
-        <v>每个油墨顶点的落点，以及沿途彩度最高的位置。经 A2B1 测得，因此这些行不随上方的渲染意图改变。在表现良好的配置文件中两行一致；若最大彩度在实地之前出现，超过该点的油墨只会使颜色变暗。</v>
+        <v>TAC</v>
       </c>
       <c r="C283" t="str">
-        <v>每個油墨頂點的落點，以及沿途彩度最高的位置。經 A2B1 量測，因此這些列不隨上方的轉換意圖改變。在表現良好的設定檔中兩列一致；若最大彩度在實地之前出現，超過該點的油墨只會使顏色變暗。</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Hue</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B284" t="str">
-        <v>色相</v>
+        <v>此配置文件没有媒体白点标签，因此无法进行绝对比色。</v>
       </c>
       <c r="C284" t="str">
-        <v>色相</v>
+        <v>此設定檔沒有媒體白點標籤，因此無法進行絕對比色。</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Full tone</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B285" t="str">
-        <v>实地</v>
+        <v>极值比色仅适用于输出（打印机）配置文件——它假定零色料即为空白承印物。</v>
       </c>
       <c r="C285" t="str">
-        <v>實地</v>
+        <v>極值比色僅適用於輸出（印表機）設定檔——它假定零色料即為空白承印物。</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Max C*</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B286" t="str">
-        <v>最大 C*</v>
+        <v>实地与最大彩度</v>
       </c>
       <c r="C286" t="str">
-        <v>最大 C*</v>
+        <v>實地與最大彩度</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>At ink</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B287" t="str">
-        <v>对应墨量</v>
+        <v>每个油墨顶点的落点，以及沿途彩度最高的位置。经 A2B1 测得，因此这些行不随上方的渲染意图改变。在表现良好的配置文件中两行一致；若最大彩度在实地之前出现，超过该点的油墨只会使颜色变暗。</v>
       </c>
       <c r="C287" t="str">
-        <v>對應墨量</v>
+        <v>每個油墨頂點的落點，以及沿途彩度最高的位置。經 A2B1 量測，因此這些列不隨上方的轉換意圖改變。在表現良好的設定檔中兩列一致；若最大彩度在實地之前出現，超過該點的油墨只會使顏色變暗。</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>Hue</v>
       </c>
       <c r="B288" t="str">
-        <v>最大彩度在实地之前达到——超过此点的油墨只会使颜色变暗。</v>
+        <v>色相</v>
       </c>
       <c r="C288" t="str">
-        <v>最大彩度在實地之前達到——超過此點的油墨只會使顏色變暗。</v>
+        <v>色相</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Full tone</v>
       </c>
       <c r="B289" t="str">
-        <v>暗调中的用墨</v>
+        <v>实地</v>
       </c>
       <c r="C289" t="str">
-        <v>暗部的用墨</v>
+        <v>實地</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Max C*</v>
       </c>
       <c r="B290" t="str">
-        <v>在一个恒定且刻意偏暗的明度上，沿 a*b* 平面取四条直线路径，送入所选 B2A 表。所有采样点的 L* 相同，因此某个色料出现的任何突变或反转都只能来自色相与彩度的处理——这正是暗调色域映射伪影的特征。</v>
+        <v>最大 C*</v>
       </c>
       <c r="C290" t="str">
-        <v>在一個固定且刻意偏暗的明度上，沿 a*b* 平面取四條直線路徑，送入所選 B2A 表。所有取樣點的 L* 相同，因此某個色料出現的任何突變或反轉都只能來自色相與彩度的處理——這正是暗部色域對應偽影的特徵。</v>
+        <v>最大 C*</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>At ink</v>
       </c>
       <c r="B291" t="str">
-        <v>暗调用墨仅适用于输出（打印机）配置文件。</v>
+        <v>对应墨量</v>
       </c>
       <c r="C291" t="str">
-        <v>暗部用墨僅適用於輸出（印表機）設定檔。</v>
+        <v>對應墨量</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Constant L* plane</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B292" t="str">
-        <v>恒定 L* 平面</v>
+        <v>最大彩度在实地之前达到——超过此点的油墨只会使颜色变暗。</v>
       </c>
       <c r="C292" t="str">
-        <v>固定 L* 平面</v>
+        <v>最大彩度在實地之前達到——超過此點的油墨只會使顏色變暗。</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>black-point compensated from</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B293" t="str">
-        <v>黑点补偿自</v>
+        <v>暗调中的用墨</v>
       </c>
       <c r="C293" t="str">
-        <v>黑點補償自</v>
+        <v>暗部的用墨</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Position along path</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B294" t="str">
-        <v>沿路径位置</v>
+        <v>在一个恒定且刻意偏暗的明度上，沿 a*b* 平面取四条直线路径，送入所选 B2A 表。所有采样点的 L* 相同，因此某个色料出现的任何突变或反转都只能来自色相与彩度的处理——这正是暗调色域映射伪影的特征。</v>
       </c>
       <c r="C294" t="str">
-        <v>沿路徑位置</v>
+        <v>在一個固定且刻意偏暗的明度上，沿 a*b* 平面取四條直線路徑，送入所選 B2A 表。所有取樣點的 L* 相同，因此某個色料出現的任何突變或反轉都只能來自色相與彩度的處理——這正是暗部色域對應偽影的特徵。</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Path</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B295" t="str">
-        <v>路径</v>
+        <v>暗调用墨仅适用于输出（打印机）配置文件。</v>
       </c>
       <c r="C295" t="str">
-        <v>路徑</v>
+        <v>暗部用墨僅適用於輸出（印表機）設定檔。</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Cyan</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B296" t="str">
-        <v>青</v>
+        <v>恒定 L* 平面</v>
       </c>
       <c r="C296" t="str">
-        <v>青</v>
+        <v>固定 L* 平面</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Magenta</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B297" t="str">
-        <v>品红</v>
+        <v>黑点补偿自</v>
       </c>
       <c r="C297" t="str">
-        <v>洋紅</v>
+        <v>黑點補償自</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Yellow</v>
+        <v>Position along path</v>
       </c>
       <c r="B298" t="str">
-        <v>黄</v>
+        <v>沿路径位置</v>
       </c>
       <c r="C298" t="str">
-        <v>黃</v>
+        <v>沿路徑位置</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Red</v>
+        <v>Path</v>
       </c>
       <c r="B299" t="str">
-        <v>红</v>
+        <v>路径</v>
       </c>
       <c r="C299" t="str">
-        <v>紅</v>
+        <v>路徑</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Green</v>
+        <v>Cyan</v>
       </c>
       <c r="B300" t="str">
-        <v>绿</v>
+        <v>青</v>
       </c>
       <c r="C300" t="str">
-        <v>綠</v>
+        <v>青</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Blue</v>
+        <v>Magenta</v>
       </c>
       <c r="B301" t="str">
-        <v>蓝</v>
+        <v>品红</v>
       </c>
       <c r="C301" t="str">
-        <v>藍</v>
+        <v>洋紅</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Black</v>
+        <v>Yellow</v>
       </c>
       <c r="B302" t="str">
-        <v>黑</v>
+        <v>黄</v>
       </c>
       <c r="C302" t="str">
-        <v>黑</v>
+        <v>黃</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Perceptual</v>
+        <v>Red</v>
       </c>
       <c r="B303" t="str">
-        <v>感知</v>
+        <v>红</v>
       </c>
       <c r="C303" t="str">
-        <v>感知</v>
+        <v>紅</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Green</v>
       </c>
       <c r="B304" t="str">
-        <v>相对比色</v>
+        <v>绿</v>
       </c>
       <c r="C304" t="str">
-        <v>相對比色</v>
+        <v>綠</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Saturation</v>
+        <v>Blue</v>
       </c>
       <c r="B305" t="str">
-        <v>饱和度</v>
+        <v>蓝</v>
       </c>
       <c r="C305" t="str">
-        <v>飽和度</v>
+        <v>藍</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Black</v>
       </c>
       <c r="B306" t="str">
-        <v>绝对比色</v>
+        <v>黑</v>
       </c>
       <c r="C306" t="str">
-        <v>絕對比色</v>
+        <v>黑</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Profile Statistics</v>
+        <v>Perceptual</v>
       </c>
       <c r="B307" t="str">
-        <v>特性文件统计</v>
+        <v>感知</v>
       </c>
       <c r="C307" t="str">
-        <v>特性檔統計</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B308" t="str">
-        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
+        <v>相对比色</v>
       </c>
       <c r="C308" t="str">
-        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B309" t="str">
-        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
+        <v>饱和度</v>
       </c>
       <c r="C309" t="str">
-        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Rendering intent</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B310" t="str">
-        <v>渲染意图</v>
+        <v>绝对比色</v>
       </c>
       <c r="C310" t="str">
-        <v>轉換意圖</v>
+        <v>絕對比色</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B311" t="str">
-        <v>色域体积 (ΔE³)</v>
+        <v>特性文件统计</v>
       </c>
       <c r="C311" t="str">
-        <v>色域體積 (ΔE³)</v>
+        <v>特性檔統計</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B312" t="str">
-        <v>往返 ΔE</v>
+        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
       </c>
       <c r="C312" t="str">
-        <v>往返 ΔE</v>
+        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B313" t="str">
-        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
+        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
       </c>
       <c r="C313" t="str">
-        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
+        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>mean</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B314" t="str">
-        <v>均值</v>
+        <v>渲染意图</v>
       </c>
       <c r="C314" t="str">
-        <v>平均</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>P90</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B315" t="str">
-        <v>P90</v>
+        <v>色域体积 (ΔE³)</v>
       </c>
       <c r="C315" t="str">
-        <v>P90</v>
+        <v>色域體積 (ΔE³)</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>max</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B316" t="str">
-        <v>最大</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C316" t="str">
-        <v>最大</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Analysing…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B317" t="str">
-        <v>正在分析…</v>
+        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
       </c>
       <c r="C317" t="str">
-        <v>正在分析…</v>
+        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Analysis</v>
+        <v>mean</v>
       </c>
       <c r="B318" t="str">
-        <v>分析</v>
+        <v>均值</v>
       </c>
       <c r="C318" t="str">
-        <v>分析</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>P90</v>
       </c>
       <c r="B319" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>P90</v>
       </c>
       <c r="C319" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Plot</v>
+        <v>max</v>
       </c>
       <c r="B320" t="str">
-        <v>绘图</v>
+        <v>最大</v>
       </c>
       <c r="C320" t="str">
-        <v>繪圖</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Raw Output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B321" t="str">
-        <v>原始输出</v>
+        <v>正在分析…</v>
       </c>
       <c r="C321" t="str">
-        <v>原始輸出</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>XML</v>
+        <v>Analysis</v>
       </c>
       <c r="B322" t="str">
-        <v>XML</v>
+        <v>分析</v>
       </c>
       <c r="C322" t="str">
-        <v>XML</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>JSON</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B323" t="str">
-        <v>JSON</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C323" t="str">
-        <v>JSON</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Curves</v>
+        <v>Plot</v>
       </c>
       <c r="B324" t="str">
-        <v>曲线</v>
+        <v>绘图</v>
       </c>
       <c r="C324" t="str">
-        <v>曲線</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Input curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B325" t="str">
-        <v>输入曲线</v>
+        <v>原始输出</v>
       </c>
       <c r="C325" t="str">
-        <v>輸入曲線</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Output curves</v>
+        <v>XML</v>
       </c>
       <c r="B326" t="str">
-        <v>输出曲线</v>
+        <v>XML</v>
       </c>
       <c r="C326" t="str">
-        <v>輸出曲線</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>CLUT image</v>
+        <v>JSON</v>
       </c>
       <c r="B327" t="str">
-        <v>CLUT 图像</v>
+        <v>JSON</v>
       </c>
       <c r="C327" t="str">
-        <v>CLUT 影像</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Gamut image</v>
+        <v>Curves</v>
       </c>
       <c r="B328" t="str">
-        <v>色域图像</v>
+        <v>曲线</v>
       </c>
       <c r="C328" t="str">
-        <v>色域影像</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Chromaticity</v>
+        <v>Input curves</v>
       </c>
       <c r="B329" t="str">
-        <v>色度</v>
+        <v>输入曲线</v>
       </c>
       <c r="C329" t="str">
-        <v>色度</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Scatter plot</v>
+        <v>Output curves</v>
       </c>
       <c r="B330" t="str">
-        <v>散点图</v>
+        <v>输出曲线</v>
       </c>
       <c r="C330" t="str">
-        <v>散佈圖</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Tone response curve</v>
+        <v>CLUT image</v>
       </c>
       <c r="B331" t="str">
-        <v>色调响应曲线</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C331" t="str">
-        <v>色調響應曲線</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Curve table</v>
+        <v>Gamut image</v>
       </c>
       <c r="B332" t="str">
-        <v>曲线表</v>
+        <v>色域图像</v>
       </c>
       <c r="C332" t="str">
-        <v>曲線表</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Tables</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B333" t="str">
-        <v>表格</v>
+        <v>色度</v>
       </c>
       <c r="C333" t="str">
-        <v>表格</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Data</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B334" t="str">
-        <v>数据</v>
+        <v>散点图</v>
       </c>
       <c r="C334" t="str">
-        <v>資料</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Evaluate</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B335" t="str">
-        <v>求值</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C335" t="str">
-        <v>求值</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Loading…</v>
+        <v>Curve table</v>
       </c>
       <c r="B336" t="str">
-        <v>加载中…</v>
+        <v>曲线表</v>
       </c>
       <c r="C336" t="str">
-        <v>載入中…</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Input</v>
+        <v>Tables</v>
       </c>
       <c r="B337" t="str">
-        <v>输入</v>
+        <v>表格</v>
       </c>
       <c r="C337" t="str">
-        <v>輸入</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Output</v>
+        <v>Data</v>
       </c>
       <c r="B338" t="str">
-        <v>输出</v>
+        <v>数据</v>
       </c>
       <c r="C338" t="str">
-        <v>輸出</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Floating point</v>
+        <v>Evaluate</v>
       </c>
       <c r="B339" t="str">
-        <v>浮点值</v>
+        <v>求值</v>
       </c>
       <c r="C339" t="str">
-        <v>浮點值</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Grid point</v>
+        <v>Loading…</v>
       </c>
       <c r="B340" t="str">
-        <v>网格点</v>
+        <v>加载中…</v>
       </c>
       <c r="C340" t="str">
-        <v>網格點</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Normalized</v>
+        <v>Input</v>
       </c>
       <c r="B341" t="str">
-        <v>归一化</v>
+        <v>输入</v>
       </c>
       <c r="C341" t="str">
-        <v>正規化</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Human</v>
+        <v>Output</v>
       </c>
       <c r="B342" t="str">
-        <v>可读值</v>
+        <v>输出</v>
       </c>
       <c r="C342" t="str">
-        <v>可讀值</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Device → PCS</v>
+        <v>Floating point</v>
       </c>
       <c r="B343" t="str">
-        <v>设备 → PCS</v>
+        <v>浮点值</v>
       </c>
       <c r="C343" t="str">
-        <v>裝置 → PCS</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>PCS → Device</v>
+        <v>Grid point</v>
       </c>
       <c r="B344" t="str">
-        <v>PCS → 设备</v>
+        <v>网格点</v>
       </c>
       <c r="C344" t="str">
-        <v>PCS → 裝置</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>No CLUT grid</v>
+        <v>Normalized</v>
       </c>
       <c r="B345" t="str">
-        <v>无 CLUT 网格</v>
+        <v>归一化</v>
       </c>
       <c r="C345" t="str">
-        <v>無 CLUT 網格</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Loading…</v>
+        <v>Human</v>
       </c>
       <c r="B346" t="str">
-        <v>加载中…</v>
+        <v>可读值</v>
       </c>
       <c r="C346" t="str">
-        <v>載入中…</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B347" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C347" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Invalid profile URL:</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B348" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C348" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B349" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C349" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Loading…</v>
       </c>
       <c r="B350" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>加载中…</v>
       </c>
       <c r="C350" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B351" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C351" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B352" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C352" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B353" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C353" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Security</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B354" t="str">
-        <v>安全性</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C354" t="str">
-        <v>安全性</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Conformance</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B355" t="str">
-        <v>符合性</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C355" t="str">
-        <v>符合性</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Quality</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B356" t="str">
-        <v>质量</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C356" t="str">
-        <v>品質</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>REPORT</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B357" t="str">
-        <v>报告</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C357" t="str">
-        <v>報告</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>FAIL</v>
+        <v>Security</v>
       </c>
       <c r="B358" t="str">
-        <v>失败</v>
+        <v>安全性</v>
       </c>
       <c r="C358" t="str">
-        <v>失敗</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>checks</v>
+        <v>Conformance</v>
       </c>
       <c r="B359" t="str">
-        <v>项检查</v>
+        <v>符合性</v>
       </c>
       <c r="C359" t="str">
-        <v>項檢查</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Quality</v>
       </c>
       <c r="B360" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>质量</v>
       </c>
       <c r="C360" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B361" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>报告</v>
       </c>
       <c r="C361" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B362" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>失败</v>
       </c>
       <c r="C362" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B363" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>项检查</v>
       </c>
       <c r="C363" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B364" t="str">
-        <v>订阅</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C364" t="str">
-        <v>訂閱</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B365" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C365" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B366" t="str">
-        <v>订阅新版本通知</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C366" t="str">
-        <v>訂閱新版本通知</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B367" t="str">
-        <v>关闭</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C367" t="str">
-        <v>關閉</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B368" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>订阅</v>
       </c>
       <c r="C368" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B369" t="str">
-        <v>电子邮件地址</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C369" t="str">
-        <v>電子郵件地址</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B370" t="str">
-        <v>you@example.com</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C370" t="str">
-        <v>you@example.com</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B371" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>关闭</v>
       </c>
       <c r="C371" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B372" t="str">
-        <v>（选填）</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C372" t="str">
-        <v>（選填）</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B373" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C373" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B374" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>you@example.com</v>
       </c>
       <c r="C374" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B375" t="str">
-        <v>取消</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C375" t="str">
-        <v>取消</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B376" t="str">
-        <v>订阅</v>
+        <v>（选填）</v>
       </c>
       <c r="C376" t="str">
-        <v>訂閱</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B377" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C377" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B378" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C378" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B379" t="str">
-        <v>关闭</v>
+        <v>取消</v>
       </c>
       <c r="C379" t="str">
-        <v>關閉</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B380" t="str">
-        <v>隐私声明</v>
+        <v>订阅</v>
       </c>
       <c r="C380" t="str">
-        <v>隱私聲明</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B381" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C381" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B382" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C382" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B383" t="str">
-        <v>请检查表单后重试。</v>
+        <v>关闭</v>
       </c>
       <c r="C383" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B384" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>隐私声明</v>
       </c>
       <c r="C384" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B385" t="str">
-        <v>网络错误，请重试。</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C385" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B386" t="str">
-        <v>错误：</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C386" t="str">
-        <v>錯誤：</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B387" t="str">
-        <v>转换为 XML</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C387" t="str">
-        <v>轉換為 XML</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B388" t="str">
-        <v>转换为 JSON</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C388" t="str">
-        <v>轉換為 JSON</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B389" t="str">
-        <v>转换为 ICC</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C389" t="str">
-        <v>轉換為 ICC</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B390" t="str">
-        <v>正在转换为 XML…</v>
+        <v>错误：</v>
       </c>
       <c r="C390" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B391" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C391" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B392" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C392" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B393" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C393" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B394" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C394" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B395" t="str">
-        <v>配置文件 ID</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C395" t="str">
-        <v>設定檔 ID</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B396" t="str">
-        <v>未找到标签。</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C396" t="str">
-        <v>找不到標籤。</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B397" t="str">
-        <v>标签名称</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C397" t="str">
-        <v>標籤名稱</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B398" t="str">
-        <v>ID</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C398" t="str">
-        <v>ID</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B399" t="str">
-        <v>偏移</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C399" t="str">
-        <v>偏移</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B400" t="str">
-        <v>大小</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C400" t="str">
-        <v>大小</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B401" t="str">
-        <v>填充</v>
+        <v>标签名称</v>
       </c>
       <c r="C401" t="str">
-        <v>填充</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B402" t="str">
-        <v>加载后字节已更改</v>
+        <v>ID</v>
       </c>
       <c r="C402" t="str">
-        <v>載入後位元組已變更</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B403" t="str">
-        <v>类型</v>
+        <v>偏移</v>
       </c>
       <c r="C403" t="str">
-        <v>類型</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B404" t="str">
-        <v>{type} 数组</v>
+        <v>大小</v>
       </c>
       <c r="C404" t="str">
-        <v>{type} 陣列</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B405" t="str">
-        <v>（无内容）</v>
+        <v>填充</v>
       </c>
       <c r="C405" t="str">
-        <v>（無內容）</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B406" t="str">
-        <v>字节</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C406" t="str">
-        <v>位元組</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B407" t="str">
-        <v>正在加载完整描述…</v>
+        <v>类型</v>
       </c>
       <c r="C407" t="str">
-        <v>正在載入完整描述…</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B408" t="str">
-        <v>无法加载完整描述：</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C408" t="str">
-        <v>無法載入完整描述：</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B409" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>（无内容）</v>
       </c>
       <c r="C409" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B410" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>字节</v>
       </c>
       <c r="C410" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B411" t="str">
-        <v>无验证输出</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C411" t="str">
-        <v>無驗證輸出</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B412" t="str">
-        <v>配置文件有效</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C412" t="str">
-        <v>設定檔有效</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B413" t="str">
-        <v>配置文件有警告</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C413" t="str">
-        <v>設定檔有警告</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B414" t="str">
-        <v>配置文件不合规</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C414" t="str">
-        <v>設定檔不符合規範</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B415" t="str">
-        <v>严重验证错误</v>
+        <v>无验证输出</v>
       </c>
       <c r="C415" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B416" t="str">
-        <v>未知验证状态</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C416" t="str">
-        <v>未知驗證狀態</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B417" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C417" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B418" t="str">
-        <v>未发现警告或错误。</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C418" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B419" t="str">
-        <v>有效</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C419" t="str">
-        <v>有效</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B420" t="str">
-        <v>警告</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C420" t="str">
-        <v>警告</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B421" t="str">
-        <v>错误</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C421" t="str">
-        <v>錯誤</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B422" t="str">
-        <v>未知</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C422" t="str">
-        <v>未知</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B423" t="str">
-        <v>通过</v>
+        <v>有效</v>
       </c>
       <c r="C423" t="str">
-        <v>通過</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B424" t="str">
-        <v>失败</v>
+        <v>警告</v>
       </c>
       <c r="C424" t="str">
-        <v>失敗</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B425" t="str">
-        <v>在上下文中查看</v>
+        <v>错误</v>
       </c>
       <c r="C425" t="str">
-        <v>在上下文中檢視</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B426" t="str">
-        <v>验证详情</v>
+        <v>未知</v>
       </c>
       <c r="C426" t="str">
-        <v>驗證詳情</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B427" t="str">
-        <v>触发字段</v>
+        <v>通过</v>
       </c>
       <c r="C427" t="str">
-        <v>觸發欄位</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B428" t="str">
-        <v>字段</v>
+        <v>失败</v>
       </c>
       <c r="C428" t="str">
-        <v>欄位</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B429" t="str">
-        <v>当前值</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C429" t="str">
-        <v>目前值</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B430" t="str">
-        <v>要求：0</v>
+        <v>验证详情</v>
       </c>
       <c r="C430" t="str">
-        <v>要求：0</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B431" t="str">
-        <v>预期：{value}</v>
+        <v>触发字段</v>
       </c>
       <c r="C431" t="str">
-        <v>預期：{value}</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B432" t="str">
-        <v>无效</v>
+        <v>字段</v>
       </c>
       <c r="C432" t="str">
-        <v>無效</v>
+        <v>欄位</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B433" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>当前值</v>
       </c>
       <c r="C433" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>目前值</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B434" t="str">
-        <v>关闭</v>
+        <v>要求：0</v>
       </c>
       <c r="C434" t="str">
-        <v>關閉</v>
+        <v>要求：0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B435" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>预期：{value}</v>
       </c>
       <c r="C435" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>預期：{value}</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B436" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>无效</v>
       </c>
       <c r="C436" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>無效</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B437" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>无法将此结果关联到具体字段。</v>
       </c>
       <c r="C437" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>無法將此結果關聯到特定欄位。</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B438" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>关闭</v>
       </c>
       <c r="C438" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B439" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>正在加载 XML 编辑器…</v>
       </c>
       <c r="C439" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>正在載入 XML 編輯器…</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B440" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>正在加载 JSON 编辑器…</v>
       </c>
       <c r="C440" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>正在載入 JSON 編輯器…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B441" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C441" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B442" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
       </c>
       <c r="C442" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B443" t="str">
-        <v>缩进</v>
+        <v>● 未保存的 XML 修改</v>
       </c>
       <c r="C443" t="str">
-        <v>縮排</v>
+        <v>● 未儲存的 XML 修改</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B444" t="str">
-        <v>排序键</v>
+        <v>● 未保存的 JSON 修改</v>
       </c>
       <c r="C444" t="str">
-        <v>排序鍵</v>
+        <v>● 未儲存的 JSON 修改</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B445" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C445" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B446" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C446" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B447" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C447" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B448" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C448" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B445" t="str">
+      <c r="B449" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C445" t="str">
+      <c r="C449" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C445"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C449"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Zh.xlsx
+++ b/translations/Eng-Zh.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C449"/>
+  <dimension ref="A1:C466"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3704,1657 +3704,1844 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Cyan</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B300" t="str">
-        <v>青</v>
+        <v>经中性轴的原色墨路</v>
       </c>
       <c r="C300" t="str">
-        <v>青</v>
+        <v>經中性軸的原色墨路</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Magenta</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B301" t="str">
-        <v>品红</v>
+        <v>色域内的三条路径——青→红、品红→绿、黄→蓝——每条都在其两端明度的中点经过中性轴，通过所选的 B2A 表。每个采样点都在色域内，因此与暗调路径不同，某个着色剂的任何突变或反转都是 CLUT 平滑性缺陷，而非色域映射伪影。</v>
       </c>
       <c r="C301" t="str">
-        <v>洋紅</v>
+        <v>色域內的三條路徑——青→紅、洋紅→綠、黃→藍——每條都在其兩端明度的中點經過中性軸，通過所選的 B2A 表。每個取樣點都在色域內，因此與暗調路徑不同，某個著色劑的任何突變或反轉都是 CLUT 平滑性缺陷，而非色域映射假影。</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Yellow</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B302" t="str">
-        <v>黄</v>
+        <v>原色墨路仅适用于输出（打印机）特性文件。</v>
       </c>
       <c r="C302" t="str">
-        <v>黃</v>
+        <v>原色墨路僅適用於輸出（印表機）特性檔。</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Red</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B303" t="str">
-        <v>红</v>
+        <v>沿路径的位置（中点为中性）</v>
       </c>
       <c r="C303" t="str">
-        <v>紅</v>
+        <v>沿路徑的位置（中點為中性）</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Green</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B304" t="str">
-        <v>绿</v>
+        <v>已为此意图应用黑场补偿。</v>
       </c>
       <c r="C304" t="str">
-        <v>綠</v>
+        <v>已為此意圖套用黑場補償。</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Blue</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B305" t="str">
-        <v>蓝</v>
+        <v>墨量统计</v>
       </c>
       <c r="C305" t="str">
-        <v>藍</v>
+        <v>墨量統計</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Black</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B306" t="str">
-        <v>黑</v>
+        <v>特性文件施加的每种着色剂的用量，以总量和占总量的比例表示——即分色的用墨特征。</v>
       </c>
       <c r="C306" t="str">
-        <v>黑</v>
+        <v>特性檔施加的每種著色劑的用量，以總量和佔總量的比例表示——即分色的用墨特徵。</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Perceptual</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B307" t="str">
-        <v>感知</v>
+        <v>墨量统计仅适用于输出（打印机）特性文件。</v>
       </c>
       <c r="C307" t="str">
-        <v>感知</v>
+        <v>墨量統計僅適用於輸出（印表機）特性檔。</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B308" t="str">
-        <v>相对比色</v>
+        <v>中性轴</v>
       </c>
       <c r="C308" t="str">
-        <v>相對比色</v>
+        <v>中性軸</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Saturation</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B309" t="str">
-        <v>饱和度</v>
+        <v>平均覆盖率</v>
       </c>
       <c r="C309" t="str">
-        <v>飽和度</v>
+        <v>平均覆蓋率</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Share of ink</v>
       </c>
       <c r="B310" t="str">
-        <v>绝对比色</v>
+        <v>墨量占比</v>
       </c>
       <c r="C310" t="str">
-        <v>絕對比色</v>
+        <v>墨量佔比</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Profile Statistics</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B311" t="str">
-        <v>特性文件统计</v>
+        <v>墨量占比是中性构建的指纹——每种着色剂在施加总墨量中所占的比例，与采样数量无关。</v>
       </c>
       <c r="C311" t="str">
-        <v>特性檔統計</v>
+        <v>墨量佔比是中性建構的指紋——每種著色劑在施加總墨量中所佔的比例，與取樣數量無關。</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B312" t="str">
-        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
+        <v>色域内的点</v>
       </c>
       <c r="C312" t="str">
-        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
+        <v>色域內的點</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B313" t="str">
-        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
+        <v>对色域内所有颜色的墨量统计需要 B2A 方向的色域边界，目前尚未构建——待完成。</v>
       </c>
       <c r="C313" t="str">
-        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
+        <v>對色域內所有顏色的墨量統計需要 B2A 方向的色域邊界，目前尚未建構——待完成。</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Rendering intent</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B314" t="str">
-        <v>渲染意图</v>
+        <v>没有可汇总的着色剂数据。</v>
       </c>
       <c r="C314" t="str">
-        <v>轉換意圖</v>
+        <v>沒有可彙總的著色劑資料。</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B315" t="str">
-        <v>色域体积 (ΔE³)</v>
+        <v>在下方选择 B2A（PCS→设备）表，即可查看每种着色剂的灰度墨量覆盖图。</v>
       </c>
       <c r="C315" t="str">
-        <v>色域體積 (ΔE³)</v>
+        <v>在下方選擇 B2A（PCS→裝置）表，即可檢視每種著色劑的灰階墨量覆蓋圖。</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B316" t="str">
-        <v>往返 ΔE</v>
+        <v>每种着色剂在同一网格上的墨量覆盖（越暗表示墨量越多）。</v>
       </c>
       <c r="C316" t="str">
-        <v>往返 ΔE</v>
+        <v>每種著色劑在同一網格上的墨量覆蓋（越暗表示墨量越多）。</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Cyan</v>
       </c>
       <c r="B317" t="str">
-        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
+        <v>青</v>
       </c>
       <c r="C317" t="str">
-        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
+        <v>青</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>mean</v>
+        <v>Magenta</v>
       </c>
       <c r="B318" t="str">
-        <v>均值</v>
+        <v>品红</v>
       </c>
       <c r="C318" t="str">
-        <v>平均</v>
+        <v>洋紅</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>P90</v>
+        <v>Yellow</v>
       </c>
       <c r="B319" t="str">
-        <v>P90</v>
+        <v>黄</v>
       </c>
       <c r="C319" t="str">
-        <v>P90</v>
+        <v>黃</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>max</v>
+        <v>Red</v>
       </c>
       <c r="B320" t="str">
-        <v>最大</v>
+        <v>红</v>
       </c>
       <c r="C320" t="str">
-        <v>最大</v>
+        <v>紅</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Analysing…</v>
+        <v>Green</v>
       </c>
       <c r="B321" t="str">
-        <v>正在分析…</v>
+        <v>绿</v>
       </c>
       <c r="C321" t="str">
-        <v>正在分析…</v>
+        <v>綠</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Analysis</v>
+        <v>Blue</v>
       </c>
       <c r="B322" t="str">
-        <v>分析</v>
+        <v>蓝</v>
       </c>
       <c r="C322" t="str">
-        <v>分析</v>
+        <v>藍</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Black</v>
       </c>
       <c r="B323" t="str">
-        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
+        <v>黑</v>
       </c>
       <c r="C323" t="str">
-        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
+        <v>黑</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Plot</v>
+        <v>Perceptual</v>
       </c>
       <c r="B324" t="str">
-        <v>绘图</v>
+        <v>感知</v>
       </c>
       <c r="C324" t="str">
-        <v>繪圖</v>
+        <v>感知</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Raw Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B325" t="str">
-        <v>原始输出</v>
+        <v>相对比色</v>
       </c>
       <c r="C325" t="str">
-        <v>原始輸出</v>
+        <v>相對比色</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>XML</v>
+        <v>Saturation</v>
       </c>
       <c r="B326" t="str">
-        <v>XML</v>
+        <v>饱和度</v>
       </c>
       <c r="C326" t="str">
-        <v>XML</v>
+        <v>飽和度</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>JSON</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B327" t="str">
-        <v>JSON</v>
+        <v>绝对比色</v>
       </c>
       <c r="C327" t="str">
-        <v>JSON</v>
+        <v>絕對比色</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Curves</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B328" t="str">
-        <v>曲线</v>
+        <v>特性文件统计</v>
       </c>
       <c r="C328" t="str">
-        <v>曲線</v>
+        <v>特性檔統計</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Input curves</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B329" t="str">
-        <v>输入曲线</v>
+        <v>按渲染意图给出的整档指标：设备→PCS 变换所包围的色域体积（ΔE*ab³），以及 B2A 往返精度——通过特性文件进行 Lab → 设备 → Lab 往返的 ΔE*ab。</v>
       </c>
       <c r="C329" t="str">
-        <v>輸入曲線</v>
+        <v>依轉換意圖給出的整檔指標：裝置→PCS 轉換所包圍的色域體積（ΔE*ab³），以及 B2A 往返精度——透過特性檔進行 Lab → 裝置 → Lab 往返的 ΔE*ab。</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Output curves</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B330" t="str">
-        <v>输出曲线</v>
+        <v>此特性文件没有设备↔PCS CLUT——特性文件统计不适用（例如矩阵/TRC 显示器特性文件）。</v>
       </c>
       <c r="C330" t="str">
-        <v>輸出曲線</v>
+        <v>此特性檔沒有裝置↔PCS CLUT——特性檔統計不適用（例如矩陣/TRC 顯示器特性檔）。</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>CLUT image</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B331" t="str">
-        <v>CLUT 图像</v>
+        <v>渲染意图</v>
       </c>
       <c r="C331" t="str">
-        <v>CLUT 影像</v>
+        <v>轉換意圖</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut image</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B332" t="str">
-        <v>色域图像</v>
+        <v>色域体积 (ΔE³)</v>
       </c>
       <c r="C332" t="str">
-        <v>色域影像</v>
+        <v>色域體積 (ΔE³)</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Chromaticity</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B333" t="str">
-        <v>色度</v>
+        <v>往返 ΔE</v>
       </c>
       <c r="C333" t="str">
-        <v>色度</v>
+        <v>往返 ΔE</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Scatter plot</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B334" t="str">
-        <v>散点图</v>
+        <v>色域边界塌陷或大部分未定义，因此此色域体积不可靠。</v>
       </c>
       <c r="C334" t="str">
-        <v>散佈圖</v>
+        <v>色域邊界塌陷或大部分未定義，因此此色域體積不可靠。</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Tone response curve</v>
+        <v>mean</v>
       </c>
       <c r="B335" t="str">
-        <v>色调响应曲线</v>
+        <v>均值</v>
       </c>
       <c r="C335" t="str">
-        <v>色調響應曲線</v>
+        <v>平均</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Curve table</v>
+        <v>P90</v>
       </c>
       <c r="B336" t="str">
-        <v>曲线表</v>
+        <v>P90</v>
       </c>
       <c r="C336" t="str">
-        <v>曲線表</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Tables</v>
+        <v>max</v>
       </c>
       <c r="B337" t="str">
-        <v>表格</v>
+        <v>最大</v>
       </c>
       <c r="C337" t="str">
-        <v>表格</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Data</v>
+        <v>Analysing…</v>
       </c>
       <c r="B338" t="str">
-        <v>数据</v>
+        <v>正在分析…</v>
       </c>
       <c r="C338" t="str">
-        <v>資料</v>
+        <v>正在分析…</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Evaluate</v>
+        <v>Analysis</v>
       </c>
       <c r="B339" t="str">
-        <v>求值</v>
+        <v>分析</v>
       </c>
       <c r="C339" t="str">
-        <v>求值</v>
+        <v>分析</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Loading…</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B340" t="str">
-        <v>加载中…</v>
+        <v>基于设备→PCS 转换的整个配置文件质量分析。</v>
       </c>
       <c r="C340" t="str">
-        <v>載入中…</v>
+        <v>基於裝置→PCS 轉換的整個設定檔品質分析。</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Input</v>
+        <v>Plot</v>
       </c>
       <c r="B341" t="str">
-        <v>输入</v>
+        <v>绘图</v>
       </c>
       <c r="C341" t="str">
-        <v>輸入</v>
+        <v>繪圖</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Output</v>
+        <v>Raw Output</v>
       </c>
       <c r="B342" t="str">
-        <v>输出</v>
+        <v>原始输出</v>
       </c>
       <c r="C342" t="str">
-        <v>輸出</v>
+        <v>原始輸出</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Floating point</v>
+        <v>XML</v>
       </c>
       <c r="B343" t="str">
-        <v>浮点值</v>
+        <v>XML</v>
       </c>
       <c r="C343" t="str">
-        <v>浮點值</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Grid point</v>
+        <v>JSON</v>
       </c>
       <c r="B344" t="str">
-        <v>网格点</v>
+        <v>JSON</v>
       </c>
       <c r="C344" t="str">
-        <v>網格點</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Normalized</v>
+        <v>Curves</v>
       </c>
       <c r="B345" t="str">
-        <v>归一化</v>
+        <v>曲线</v>
       </c>
       <c r="C345" t="str">
-        <v>正規化</v>
+        <v>曲線</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Human</v>
+        <v>Input curves</v>
       </c>
       <c r="B346" t="str">
-        <v>可读值</v>
+        <v>输入曲线</v>
       </c>
       <c r="C346" t="str">
-        <v>可讀值</v>
+        <v>輸入曲線</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Device → PCS</v>
+        <v>Output curves</v>
       </c>
       <c r="B347" t="str">
-        <v>设备 → PCS</v>
+        <v>输出曲线</v>
       </c>
       <c r="C347" t="str">
-        <v>裝置 → PCS</v>
+        <v>輸出曲線</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>PCS → Device</v>
+        <v>CLUT image</v>
       </c>
       <c r="B348" t="str">
-        <v>PCS → 设备</v>
+        <v>CLUT 图像</v>
       </c>
       <c r="C348" t="str">
-        <v>PCS → 裝置</v>
+        <v>CLUT 影像</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut image</v>
       </c>
       <c r="B349" t="str">
-        <v>无 CLUT 网格</v>
+        <v>色域图像</v>
       </c>
       <c r="C349" t="str">
-        <v>無 CLUT 網格</v>
+        <v>色域影像</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Loading…</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B350" t="str">
-        <v>加载中…</v>
+        <v>色度</v>
       </c>
       <c r="C350" t="str">
-        <v>載入中…</v>
+        <v>色度</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B351" t="str">
-        <v>中性 = 色域内 · 红色 = 色域外</v>
+        <v>散点图</v>
       </c>
       <c r="C351" t="str">
-        <v>中性 = 色域內 · 紅色 = 色域外</v>
+        <v>散佈圖</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B352" t="str">
-        <v>无效的配置文件 URL：</v>
+        <v>色调响应曲线</v>
       </c>
       <c r="C352" t="str">
-        <v>無效的設定檔 URL：</v>
+        <v>色調響應曲線</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curve table</v>
       </c>
       <c r="B353" t="str">
-        <v>无法从以下位置获取配置文件：</v>
+        <v>曲线表</v>
       </c>
       <c r="C353" t="str">
-        <v>無法從以下位置擷取設定檔：</v>
+        <v>曲線表</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Tables</v>
       </c>
       <c r="B354" t="str">
-        <v>从此外部网站加载 ICC 配置文件？</v>
+        <v>表格</v>
       </c>
       <c r="C354" t="str">
-        <v>從此外部網站載入 ICC 設定檔？</v>
+        <v>表格</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Data</v>
       </c>
       <c r="B355" t="str">
-        <v>正在加载 Profile Assessment WG 报告…</v>
+        <v>数据</v>
       </c>
       <c r="C355" t="str">
-        <v>正在載入 Profile Assessment WG 報告…</v>
+        <v>資料</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B356" t="str">
-        <v>正在运行 Profile Assessment WG 检查…</v>
+        <v>求值</v>
       </c>
       <c r="C356" t="str">
-        <v>正在執行 Profile Assessment WG 檢查…</v>
+        <v>求值</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading…</v>
       </c>
       <c r="B357" t="str">
-        <v>Profile Assessment WG 报告</v>
+        <v>加载中…</v>
       </c>
       <c r="C357" t="str">
-        <v>Profile Assessment WG 報告</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Security</v>
+        <v>Input</v>
       </c>
       <c r="B358" t="str">
-        <v>安全性</v>
+        <v>输入</v>
       </c>
       <c r="C358" t="str">
-        <v>安全性</v>
+        <v>輸入</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Conformance</v>
+        <v>Output</v>
       </c>
       <c r="B359" t="str">
-        <v>符合性</v>
+        <v>输出</v>
       </c>
       <c r="C359" t="str">
-        <v>符合性</v>
+        <v>輸出</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Quality</v>
+        <v>Floating point</v>
       </c>
       <c r="B360" t="str">
-        <v>质量</v>
+        <v>浮点值</v>
       </c>
       <c r="C360" t="str">
-        <v>品質</v>
+        <v>浮點值</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>REPORT</v>
+        <v>Grid point</v>
       </c>
       <c r="B361" t="str">
-        <v>报告</v>
+        <v>网格点</v>
       </c>
       <c r="C361" t="str">
-        <v>報告</v>
+        <v>網格點</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>FAIL</v>
+        <v>Normalized</v>
       </c>
       <c r="B362" t="str">
-        <v>失败</v>
+        <v>归一化</v>
       </c>
       <c r="C362" t="str">
-        <v>失敗</v>
+        <v>正規化</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>checks</v>
+        <v>Human</v>
       </c>
       <c r="B363" t="str">
-        <v>项检查</v>
+        <v>可读值</v>
       </c>
       <c r="C363" t="str">
-        <v>項檢查</v>
+        <v>可讀值</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B364" t="str">
-        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
+        <v>设备 → PCS</v>
       </c>
       <c r="C364" t="str">
-        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
+        <v>裝置 → PCS</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B365" t="str">
-        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
+        <v>PCS → 设备</v>
       </c>
       <c r="C365" t="str">
-        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
+        <v>PCS → 裝置</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ICC Profile Tool</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B366" t="str">
-        <v>ICC 配置文件工具</v>
+        <v>无 CLUT 网格</v>
       </c>
       <c r="C366" t="str">
-        <v>ICC 設定檔工具</v>
+        <v>無 CLUT 網格</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Powered by {lib}</v>
+        <v>Loading…</v>
       </c>
       <c r="B367" t="str">
-        <v>由 {lib} 提供支持</v>
+        <v>加载中…</v>
       </c>
       <c r="C367" t="str">
-        <v>由 {lib} 提供支援</v>
+        <v>載入中…</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Subscribe</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B368" t="str">
-        <v>订阅</v>
+        <v>中性 = 色域内 · 红色 = 色域外</v>
       </c>
       <c r="C368" t="str">
-        <v>訂閱</v>
+        <v>中性 = 色域內 · 紅色 = 色域外</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B369" t="str">
-        <v>在 profiletool 新版本发布时收到通知</v>
+        <v>无效的配置文件 URL：</v>
       </c>
       <c r="C369" t="str">
-        <v>在 profiletool 新版本發佈時收到通知</v>
+        <v>無效的設定檔 URL：</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Get notified about new releases</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B370" t="str">
-        <v>订阅新版本通知</v>
+        <v>无法从以下位置获取配置文件：</v>
       </c>
       <c r="C370" t="str">
-        <v>訂閱新版本通知</v>
+        <v>無法從以下位置擷取設定檔：</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Close</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B371" t="str">
-        <v>关闭</v>
+        <v>从此外部网站加载 ICC 配置文件？</v>
       </c>
       <c r="C371" t="str">
-        <v>關閉</v>
+        <v>從此外部網站載入 ICC 設定檔？</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B372" t="str">
-        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
+        <v>正在加载 Profile Assessment WG 报告…</v>
       </c>
       <c r="C372" t="str">
-        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
+        <v>正在載入 Profile Assessment WG 報告…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Email address</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B373" t="str">
-        <v>电子邮件地址</v>
+        <v>正在运行 Profile Assessment WG 检查…</v>
       </c>
       <c r="C373" t="str">
-        <v>電子郵件地址</v>
+        <v>正在執行 Profile Assessment WG 檢查…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG 报告</v>
       </c>
       <c r="C374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG 報告</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Security</v>
       </c>
       <c r="B375" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>安全性</v>
       </c>
       <c r="C375" t="str">
-        <v>您打算如何使用 profiletool？</v>
+        <v>安全性</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>(optional)</v>
+        <v>Conformance</v>
       </c>
       <c r="B376" t="str">
-        <v>（选填）</v>
+        <v>符合性</v>
       </c>
       <c r="C376" t="str">
-        <v>（選填）</v>
+        <v>符合性</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Quality</v>
       </c>
       <c r="B377" t="str">
-        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
+        <v>质量</v>
       </c>
       <c r="C377" t="str">
-        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
+        <v>品質</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B378" t="str">
-        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
+        <v>报告</v>
       </c>
       <c r="C378" t="str">
-        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
+        <v>報告</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B379" t="str">
-        <v>取消</v>
+        <v>失败</v>
       </c>
       <c r="C379" t="str">
-        <v>取消</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B380" t="str">
-        <v>订阅</v>
+        <v>项检查</v>
       </c>
       <c r="C380" t="str">
-        <v>訂閱</v>
+        <v>項檢查</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B381" t="str">
-        <v>谢谢 — 我们会再联系您。</v>
+        <v>由 iccPawgReport (iccDEV) 生成 · ICC Profile Assessment Working Group 检查清单。</v>
       </c>
       <c r="C381" t="str">
-        <v>感謝 — 我們會再聯絡您。</v>
+        <v>由 iccPawgReport (iccDEV) 產生 · ICC Profile Assessment Working Group 檢查清單。</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B382" t="str">
-        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
+        <v>ICC 配置文件工具 · 由 IccProfLib 提供支持</v>
       </c>
       <c r="C382" t="str">
-        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
+        <v>ICC 設定檔工具 · 由 IccProfLib 提供支援</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B383" t="str">
-        <v>关闭</v>
+        <v>ICC 配置文件工具</v>
       </c>
       <c r="C383" t="str">
-        <v>關閉</v>
+        <v>ICC 設定檔工具</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B384" t="str">
-        <v>隐私声明</v>
+        <v>由 {lib} 提供支持</v>
       </c>
       <c r="C384" t="str">
-        <v>隱私聲明</v>
+        <v>由 {lib} 提供支援</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B385" t="str">
-        <v>请输入有效的电子邮件地址。</v>
+        <v>订阅</v>
       </c>
       <c r="C385" t="str">
-        <v>請輸入有效的電子郵件地址。</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B386" t="str">
-        <v>请求过多，请稍后再试。</v>
+        <v>在 profiletool 新版本发布时收到通知</v>
       </c>
       <c r="C386" t="str">
-        <v>請求過多，請稍後再試。</v>
+        <v>在 profiletool 新版本發佈時收到通知</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B387" t="str">
-        <v>请检查表单后重试。</v>
+        <v>订阅新版本通知</v>
       </c>
       <c r="C387" t="str">
-        <v>請檢查表單後重試。</v>
+        <v>訂閱新版本通知</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B388" t="str">
-        <v>无法发送您的请求，请重试。</v>
+        <v>关闭</v>
       </c>
       <c r="C388" t="str">
-        <v>無法傳送您的請求，請重試。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B389" t="str">
-        <v>网络错误，请重试。</v>
+        <v>当 profiletool 发布新的主版本或次版本时，我们会通过邮件通知您。补丁版本不在此列。您的邮箱地址会经过人工审核后才会被加入。</v>
       </c>
       <c r="C389" t="str">
-        <v>網路錯誤，請重試。</v>
+        <v>當 profiletool 發佈新的主版本或次版本時，我們會以郵件通知您。修補版本不在此列。您的郵件地址會經過人工審核後才會加入。</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B390" t="str">
-        <v>错误：</v>
+        <v>电子邮件地址</v>
       </c>
       <c r="C390" t="str">
-        <v>錯誤：</v>
+        <v>電子郵件地址</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B391" t="str">
-        <v>转换为 XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="C391" t="str">
-        <v>轉換為 XML</v>
+        <v>you@example.com</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B392" t="str">
-        <v>转换为 JSON</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
       <c r="C392" t="str">
-        <v>轉換為 JSON</v>
+        <v>您打算如何使用 profiletool？</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B393" t="str">
-        <v>转换为 ICC</v>
+        <v>（选填）</v>
       </c>
       <c r="C393" t="str">
-        <v>轉換為 ICC</v>
+        <v>（選填）</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B394" t="str">
-        <v>正在转换为 XML…</v>
+        <v>例如：用于印刷校准的 ICC 配置文件评估</v>
       </c>
       <c r="C394" t="str">
-        <v>正在轉換為 XML…</v>
+        <v>例如：用於印刷校準的 ICC 設定檔評估</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B395" t="str">
-        <v>正在转换为 JSON…</v>
+        <v>我同意接收关于 profiletool 版本发布的邮件。我可以随时退订。</v>
       </c>
       <c r="C395" t="str">
-        <v>正在轉換為 JSON…</v>
+        <v>我同意接收關於 profiletool 版本發佈的郵件。我可以隨時取消訂閱。</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B396" t="str">
-        <v>正在转换为 ICC…</v>
+        <v>取消</v>
       </c>
       <c r="C396" t="str">
-        <v>正在轉換為 ICC…</v>
+        <v>取消</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B397" t="str">
-        <v>加载 ICC 配置文件</v>
+        <v>订阅</v>
       </c>
       <c r="C397" t="str">
-        <v>載入 ICC 設定檔</v>
+        <v>訂閱</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B398" t="str">
-        <v>ICC 配置文件拖放区</v>
+        <v>谢谢 — 我们会再联系您。</v>
       </c>
       <c r="C398" t="str">
-        <v>ICC 設定檔拖放區</v>
+        <v>感謝 — 我們會再聯絡您。</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B399" t="str">
-        <v>配置文件 ID</v>
+        <v>审核通过后，您将收到一封欢迎邮件。之后只有在 profiletool 发布新版本时才会收到我们的邮件。</v>
       </c>
       <c r="C399" t="str">
-        <v>設定檔 ID</v>
+        <v>審核通過後，您將收到歡迎郵件。之後只有在 profiletool 發佈新版本時才會收到我們的訊息。</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>未找到标签。</v>
+        <v>关闭</v>
       </c>
       <c r="C400" t="str">
-        <v>找不到標籤。</v>
+        <v>關閉</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B401" t="str">
-        <v>标签名称</v>
+        <v>隐私声明</v>
       </c>
       <c r="C401" t="str">
-        <v>標籤名稱</v>
+        <v>隱私聲明</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B402" t="str">
-        <v>ID</v>
+        <v>请输入有效的电子邮件地址。</v>
       </c>
       <c r="C402" t="str">
-        <v>ID</v>
+        <v>請輸入有效的電子郵件地址。</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B403" t="str">
-        <v>偏移</v>
+        <v>请求过多，请稍后再试。</v>
       </c>
       <c r="C403" t="str">
-        <v>偏移</v>
+        <v>請求過多，請稍後再試。</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B404" t="str">
-        <v>大小</v>
+        <v>请检查表单后重试。</v>
       </c>
       <c r="C404" t="str">
-        <v>大小</v>
+        <v>請檢查表單後重試。</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>填充</v>
+        <v>无法发送您的请求，请重试。</v>
       </c>
       <c r="C405" t="str">
-        <v>填充</v>
+        <v>無法傳送您的請求，請重試。</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>加载后字节已更改</v>
+        <v>网络错误，请重试。</v>
       </c>
       <c r="C406" t="str">
-        <v>載入後位元組已變更</v>
+        <v>網路錯誤，請重試。</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B407" t="str">
-        <v>类型</v>
+        <v>错误：</v>
       </c>
       <c r="C407" t="str">
-        <v>類型</v>
+        <v>錯誤：</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B408" t="str">
-        <v>{type} 数组</v>
+        <v>转换为 XML</v>
       </c>
       <c r="C408" t="str">
-        <v>{type} 陣列</v>
+        <v>轉換為 XML</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B409" t="str">
-        <v>（无内容）</v>
+        <v>转换为 JSON</v>
       </c>
       <c r="C409" t="str">
-        <v>（無內容）</v>
+        <v>轉換為 JSON</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B410" t="str">
-        <v>字节</v>
+        <v>转换为 ICC</v>
       </c>
       <c r="C410" t="str">
-        <v>位元組</v>
+        <v>轉換為 ICC</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B411" t="str">
-        <v>正在加载完整描述…</v>
+        <v>正在转换为 XML…</v>
       </c>
       <c r="C411" t="str">
-        <v>正在載入完整描述…</v>
+        <v>正在轉換為 XML…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B412" t="str">
-        <v>无法加载完整描述：</v>
+        <v>正在转换为 JSON…</v>
       </c>
       <c r="C412" t="str">
-        <v>無法載入完整描述：</v>
+        <v>正在轉換為 JSON…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B413" t="str">
-        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
+        <v>正在转换为 ICC…</v>
       </c>
       <c r="C413" t="str">
-        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
+        <v>正在轉換為 ICC…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B414" t="str">
-        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
+        <v>加载 ICC 配置文件</v>
       </c>
       <c r="C414" t="str">
-        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
+        <v>載入 ICC 設定檔</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B415" t="str">
-        <v>无验证输出</v>
+        <v>ICC 配置文件拖放区</v>
       </c>
       <c r="C415" t="str">
-        <v>無驗證輸出</v>
+        <v>ICC 設定檔拖放區</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B416" t="str">
-        <v>配置文件有效</v>
+        <v>配置文件 ID</v>
       </c>
       <c r="C416" t="str">
-        <v>設定檔有效</v>
+        <v>設定檔 ID</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B417" t="str">
-        <v>配置文件有警告</v>
+        <v>未找到标签。</v>
       </c>
       <c r="C417" t="str">
-        <v>設定檔有警告</v>
+        <v>找不到標籤。</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B418" t="str">
-        <v>配置文件不合规</v>
+        <v>标签名称</v>
       </c>
       <c r="C418" t="str">
-        <v>設定檔不符合規範</v>
+        <v>標籤名稱</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B419" t="str">
-        <v>严重验证错误</v>
+        <v>ID</v>
       </c>
       <c r="C419" t="str">
-        <v>嚴重驗證錯誤</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B420" t="str">
-        <v>未知验证状态</v>
+        <v>偏移</v>
       </c>
       <c r="C420" t="str">
-        <v>未知驗證狀態</v>
+        <v>偏移</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B421" t="str">
-        <v>严重 — 仅供检查显示</v>
+        <v>大小</v>
       </c>
       <c r="C421" t="str">
-        <v>嚴重 — 僅供檢視顯示</v>
+        <v>大小</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B422" t="str">
-        <v>未发现警告或错误。</v>
+        <v>填充</v>
       </c>
       <c r="C422" t="str">
-        <v>未發現警告或錯誤。</v>
+        <v>填充</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B423" t="str">
-        <v>有效</v>
+        <v>加载后字节已更改</v>
       </c>
       <c r="C423" t="str">
-        <v>有效</v>
+        <v>載入後位元組已變更</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B424" t="str">
-        <v>警告</v>
+        <v>类型</v>
       </c>
       <c r="C424" t="str">
-        <v>警告</v>
+        <v>類型</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B425" t="str">
-        <v>错误</v>
+        <v>{type} 数组</v>
       </c>
       <c r="C425" t="str">
-        <v>錯誤</v>
+        <v>{type} 陣列</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B426" t="str">
-        <v>未知</v>
+        <v>（无内容）</v>
       </c>
       <c r="C426" t="str">
-        <v>未知</v>
+        <v>（無內容）</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B427" t="str">
-        <v>通过</v>
+        <v>字节</v>
       </c>
       <c r="C427" t="str">
-        <v>通過</v>
+        <v>位元組</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B428" t="str">
-        <v>失败</v>
+        <v>正在加载完整描述…</v>
       </c>
       <c r="C428" t="str">
-        <v>失敗</v>
+        <v>正在載入完整描述…</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B429" t="str">
-        <v>在上下文中查看</v>
+        <v>无法加载完整描述：</v>
       </c>
       <c r="C429" t="str">
-        <v>在上下文中檢視</v>
+        <v>無法載入完整描述：</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B430" t="str">
-        <v>验证详情</v>
+        <v>无法完整解析此配置文件，不得应用。下方的标头和标签目录仅供检查。</v>
       </c>
       <c r="C430" t="str">
-        <v>驗證詳情</v>
+        <v>無法完整解析此設定檔，不得套用。下方的標頭和標籤目錄僅供檢視。</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B431" t="str">
-        <v>触发字段</v>
+        <v>标签内容不可用 — 无法完整解析该配置文件。</v>
       </c>
       <c r="C431" t="str">
-        <v>觸發欄位</v>
+        <v>標籤內容不可用 — 無法完整解析該設定檔。</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B432" t="str">
-        <v>字段</v>
+        <v>无验证输出</v>
       </c>
       <c r="C432" t="str">
-        <v>欄位</v>
+        <v>無驗證輸出</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B433" t="str">
-        <v>当前值</v>
+        <v>配置文件有效</v>
       </c>
       <c r="C433" t="str">
-        <v>目前值</v>
+        <v>設定檔有效</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B434" t="str">
-        <v>要求：0</v>
+        <v>配置文件有警告</v>
       </c>
       <c r="C434" t="str">
-        <v>要求：0</v>
+        <v>設定檔有警告</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B435" t="str">
-        <v>预期：{value}</v>
+        <v>配置文件不合规</v>
       </c>
       <c r="C435" t="str">
-        <v>預期：{value}</v>
+        <v>設定檔不符合規範</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B436" t="str">
-        <v>无效</v>
+        <v>严重验证错误</v>
       </c>
       <c r="C436" t="str">
-        <v>無效</v>
+        <v>嚴重驗證錯誤</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B437" t="str">
-        <v>无法将此结果关联到具体字段。</v>
+        <v>未知验证状态</v>
       </c>
       <c r="C437" t="str">
-        <v>無法將此結果關聯到特定欄位。</v>
+        <v>未知驗證狀態</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B438" t="str">
-        <v>关闭</v>
+        <v>严重 — 仅供检查显示</v>
       </c>
       <c r="C438" t="str">
-        <v>關閉</v>
+        <v>嚴重 — 僅供檢視顯示</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B439" t="str">
-        <v>正在加载 XML 编辑器…</v>
+        <v>未发现警告或错误。</v>
       </c>
       <c r="C439" t="str">
-        <v>正在載入 XML 編輯器…</v>
+        <v>未發現警告或錯誤。</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B440" t="str">
-        <v>正在加载 JSON 编辑器…</v>
+        <v>有效</v>
       </c>
       <c r="C440" t="str">
-        <v>正在載入 JSON 編輯器…</v>
+        <v>有效</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B441" t="str">
-        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>警告</v>
       </c>
       <c r="C441" t="str">
-        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>警告</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B442" t="str">
-        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+        <v>错误</v>
       </c>
       <c r="C442" t="str">
-        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+        <v>錯誤</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B443" t="str">
-        <v>● 未保存的 XML 修改</v>
+        <v>未知</v>
       </c>
       <c r="C443" t="str">
-        <v>● 未儲存的 XML 修改</v>
+        <v>未知</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B444" t="str">
-        <v>● 未保存的 JSON 修改</v>
+        <v>通过</v>
       </c>
       <c r="C444" t="str">
-        <v>● 未儲存的 JSON 修改</v>
+        <v>通過</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B445" t="str">
-        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+        <v>失败</v>
       </c>
       <c r="C445" t="str">
-        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+        <v>失敗</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B446" t="str">
-        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+        <v>在上下文中查看</v>
       </c>
       <c r="C446" t="str">
-        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+        <v>在上下文中檢視</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B447" t="str">
-        <v>缩进</v>
+        <v>验证详情</v>
       </c>
       <c r="C447" t="str">
-        <v>縮排</v>
+        <v>驗證詳情</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B448" t="str">
-        <v>排序键</v>
+        <v>触发字段</v>
       </c>
       <c r="C448" t="str">
-        <v>排序鍵</v>
+        <v>觸發欄位</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B449" t="str">
+        <v>字段</v>
+      </c>
+      <c r="C449" t="str">
+        <v>欄位</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B450" t="str">
+        <v>当前值</v>
+      </c>
+      <c r="C450" t="str">
+        <v>目前值</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B451" t="str">
+        <v>要求：0</v>
+      </c>
+      <c r="C451" t="str">
+        <v>要求：0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B452" t="str">
+        <v>预期：{value}</v>
+      </c>
+      <c r="C452" t="str">
+        <v>預期：{value}</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B453" t="str">
+        <v>无效</v>
+      </c>
+      <c r="C453" t="str">
+        <v>無效</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B454" t="str">
+        <v>无法将此结果关联到具体字段。</v>
+      </c>
+      <c r="C454" t="str">
+        <v>無法將此結果關聯到特定欄位。</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B455" t="str">
+        <v>关闭</v>
+      </c>
+      <c r="C455" t="str">
+        <v>關閉</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B456" t="str">
+        <v>正在加载 XML 编辑器…</v>
+      </c>
+      <c r="C456" t="str">
+        <v>正在載入 XML 編輯器…</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B457" t="str">
+        <v>正在加载 JSON 编辑器…</v>
+      </c>
+      <c r="C457" t="str">
+        <v>正在載入 JSON 編輯器…</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B458" t="str">
+        <v>您有未保存的 XML 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C458" t="str">
+        <v>您有未儲存的 XML 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B459" t="str">
+        <v>您有未保存的 JSON 修改。要用 ICC 配置文件的新转换覆盖它们吗？</v>
+      </c>
+      <c r="C459" t="str">
+        <v>您有未儲存的 JSON 修改。要用 ICC 設定檔的新轉換覆寫它們嗎？</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B460" t="str">
+        <v>● 未保存的 XML 修改</v>
+      </c>
+      <c r="C460" t="str">
+        <v>● 未儲存的 XML 修改</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B461" t="str">
+        <v>● 未保存的 JSON 修改</v>
+      </c>
+      <c r="C461" t="str">
+        <v>● 未儲存的 JSON 修改</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B462" t="str">
+        <v>点击&lt;em&gt;转换为 XML&lt;/em&gt;以生成该配置文件的可编辑 XML 表示。该 XML 由与上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 代码路径生成。</v>
+      </c>
+      <c r="C462" t="str">
+        <v>點擊&lt;em&gt;轉換為 XML&lt;/em&gt;以產生此設定檔的可編輯 XML 表示。該 XML 由與上游 &lt;code&gt;IccToXml&lt;/code&gt; 工具相同的 IccLibXML 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B463" t="str">
+        <v>点击&lt;em&gt;转换为 JSON&lt;/em&gt;以生成该配置文件的可编辑 JSON 表示。该 JSON 由与上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 代码路径生成。</v>
+      </c>
+      <c r="C463" t="str">
+        <v>點擊&lt;em&gt;轉換為 JSON&lt;/em&gt;以產生此設定檔的可編輯 JSON 表示。該 JSON 由與上游 &lt;code&gt;IccToJson&lt;/code&gt; 工具相同的 IccLibJSON 程式碼路徑產生。</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B464" t="str">
+        <v>缩进</v>
+      </c>
+      <c r="C464" t="str">
+        <v>縮排</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B465" t="str">
+        <v>排序键</v>
+      </c>
+      <c r="C465" t="str">
+        <v>排序鍵</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B449" t="str">
+      <c r="B466" t="str">
         <v>已从编辑写入配置文件，但重新验证失败：</v>
       </c>
-      <c r="C449" t="str">
+      <c r="C466" t="str">
         <v>已從編輯寫入設定檔，但重新驗證失敗：</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C449"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C466"/>
   </ignoredErrors>
 </worksheet>
 </file>